--- a/data/BC.MI.xlsx
+++ b/data/BC.MI.xlsx
@@ -62886,6 +62886,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2719">
+      <c r="A2719" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2719" t="n">
+        <v>196605</v>
+      </c>
+      <c r="C2719" t="n">
+        <v>77.8000030517578</v>
+      </c>
+      <c r="D2719" t="n">
+        <v>75.6999969482422</v>
+      </c>
+      <c r="E2719" t="n">
+        <v>76.5</v>
+      </c>
+      <c r="F2719" t="n">
+        <v>76.1600036621094</v>
+      </c>
+      <c r="G2719" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/BC.MI.xlsx
+++ b/data/BC.MI.xlsx
@@ -62909,6 +62909,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2720">
+      <c r="A2720" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2720" t="n">
+        <v>193755</v>
+      </c>
+      <c r="C2720" t="n">
+        <v>76.4800033569336</v>
+      </c>
+      <c r="D2720" t="n">
+        <v>75</v>
+      </c>
+      <c r="E2720" t="n">
+        <v>75.6800003051758</v>
+      </c>
+      <c r="F2720" t="n">
+        <v>75.5999984741211</v>
+      </c>
+      <c r="G2720" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/BC.MI.xlsx
+++ b/data/BC.MI.xlsx
@@ -62932,6 +62932,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2721">
+      <c r="A2721" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2721" t="n">
+        <v>176123</v>
+      </c>
+      <c r="C2721" t="n">
+        <v>77.5999984741211</v>
+      </c>
+      <c r="D2721" t="n">
+        <v>75.3399963378906</v>
+      </c>
+      <c r="E2721" t="n">
+        <v>75.6399993896484</v>
+      </c>
+      <c r="F2721" t="n">
+        <v>77.2799987792969</v>
+      </c>
+      <c r="G2721" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/BC.MI.xlsx
+++ b/data/BC.MI.xlsx
@@ -62955,6 +62955,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2722">
+      <c r="A2722" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2722" t="n">
+        <v>341559</v>
+      </c>
+      <c r="C2722" t="n">
+        <v>79.8399963378906</v>
+      </c>
+      <c r="D2722" t="n">
+        <v>77.8600006103516</v>
+      </c>
+      <c r="E2722" t="n">
+        <v>77.9800033569336</v>
+      </c>
+      <c r="F2722" t="n">
+        <v>78.5400009155273</v>
+      </c>
+      <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/BC.MI.xlsx
+++ b/data/BC.MI.xlsx
@@ -62796,22 +62796,22 @@
     </row>
     <row r="2715">
       <c r="A2715" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2715" t="n">
-        <v>196461</v>
+        <v>233706</v>
       </c>
       <c r="C2715" t="n">
-        <v>81.4199981689453</v>
+        <v>81.1999969482422</v>
       </c>
       <c r="D2715" t="n">
-        <v>79.6999969482422</v>
+        <v>79.8399963378906</v>
       </c>
       <c r="E2715" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F2715" t="n">
-        <v>80.3000030517578</v>
+        <v>80.5400009155273</v>
       </c>
       <c r="G2715" t="s">
         <v>7</v>
@@ -62819,22 +62819,22 @@
     </row>
     <row r="2716">
       <c r="A2716" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2716" t="n">
-        <v>212148</v>
+        <v>196461</v>
       </c>
       <c r="C2716" t="n">
-        <v>80.2799987792969</v>
+        <v>81.4199981689453</v>
       </c>
       <c r="D2716" t="n">
-        <v>78.3399963378906</v>
+        <v>79.6999969482422</v>
       </c>
       <c r="E2716" t="n">
-        <v>79.5</v>
+        <v>80</v>
       </c>
       <c r="F2716" t="n">
-        <v>78.620002746582</v>
+        <v>80.3000030517578</v>
       </c>
       <c r="G2716" t="s">
         <v>7</v>
@@ -62842,22 +62842,22 @@
     </row>
     <row r="2717">
       <c r="A2717" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2717" t="n">
-        <v>269924</v>
+        <v>212148</v>
       </c>
       <c r="C2717" t="n">
-        <v>78.6999969482422</v>
+        <v>80.2799987792969</v>
       </c>
       <c r="D2717" t="n">
-        <v>76.5800018310547</v>
+        <v>78.3399963378906</v>
       </c>
       <c r="E2717" t="n">
-        <v>78.4199981689453</v>
+        <v>79.5</v>
       </c>
       <c r="F2717" t="n">
-        <v>76.5800018310547</v>
+        <v>78.620002746582</v>
       </c>
       <c r="G2717" t="s">
         <v>7</v>
@@ -62865,22 +62865,22 @@
     </row>
     <row r="2718">
       <c r="A2718" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2718" t="n">
-        <v>228461</v>
+        <v>269924</v>
       </c>
       <c r="C2718" t="n">
-        <v>78.1999969482422</v>
+        <v>78.6999969482422</v>
       </c>
       <c r="D2718" t="n">
-        <v>76.4400024414062</v>
+        <v>76.5800018310547</v>
       </c>
       <c r="E2718" t="n">
-        <v>77</v>
+        <v>78.4199981689453</v>
       </c>
       <c r="F2718" t="n">
-        <v>76.7200012207031</v>
+        <v>76.5800018310547</v>
       </c>
       <c r="G2718" t="s">
         <v>7</v>
@@ -62888,22 +62888,22 @@
     </row>
     <row r="2719">
       <c r="A2719" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2719" t="n">
-        <v>196605</v>
+        <v>228461</v>
       </c>
       <c r="C2719" t="n">
-        <v>77.8000030517578</v>
+        <v>78.1999969482422</v>
       </c>
       <c r="D2719" t="n">
-        <v>75.6999969482422</v>
+        <v>76.4400024414062</v>
       </c>
       <c r="E2719" t="n">
-        <v>76.5</v>
+        <v>77</v>
       </c>
       <c r="F2719" t="n">
-        <v>76.1600036621094</v>
+        <v>76.7200012207031</v>
       </c>
       <c r="G2719" t="s">
         <v>7</v>
@@ -62911,22 +62911,22 @@
     </row>
     <row r="2720">
       <c r="A2720" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2720" t="n">
-        <v>193755</v>
+        <v>196605</v>
       </c>
       <c r="C2720" t="n">
-        <v>76.4800033569336</v>
+        <v>77.8000030517578</v>
       </c>
       <c r="D2720" t="n">
-        <v>75</v>
+        <v>75.6999969482422</v>
       </c>
       <c r="E2720" t="n">
-        <v>75.6800003051758</v>
+        <v>76.5</v>
       </c>
       <c r="F2720" t="n">
-        <v>75.5999984741211</v>
+        <v>76.1600036621094</v>
       </c>
       <c r="G2720" t="s">
         <v>7</v>
@@ -62934,22 +62934,22 @@
     </row>
     <row r="2721">
       <c r="A2721" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2721" t="n">
-        <v>176123</v>
+        <v>193755</v>
       </c>
       <c r="C2721" t="n">
-        <v>77.5999984741211</v>
+        <v>76.4800033569336</v>
       </c>
       <c r="D2721" t="n">
-        <v>75.3399963378906</v>
+        <v>75</v>
       </c>
       <c r="E2721" t="n">
-        <v>75.6399993896484</v>
+        <v>75.6800003051758</v>
       </c>
       <c r="F2721" t="n">
-        <v>77.2799987792969</v>
+        <v>75.5999984741211</v>
       </c>
       <c r="G2721" t="s">
         <v>7</v>
@@ -62957,24 +62957,47 @@
     </row>
     <row r="2722">
       <c r="A2722" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2722" t="n">
-        <v>341559</v>
+        <v>176123</v>
       </c>
       <c r="C2722" t="n">
-        <v>79.8399963378906</v>
+        <v>77.5999984741211</v>
       </c>
       <c r="D2722" t="n">
-        <v>77.8600006103516</v>
+        <v>75.3399963378906</v>
       </c>
       <c r="E2722" t="n">
-        <v>77.9800033569336</v>
+        <v>75.6399993896484</v>
       </c>
       <c r="F2722" t="n">
-        <v>78.5400009155273</v>
+        <v>77.2799987792969</v>
       </c>
       <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2723">
+      <c r="A2723" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2723" t="n">
+        <v>697308</v>
+      </c>
+      <c r="C2723" t="n">
+        <v>80.3600006103516</v>
+      </c>
+      <c r="D2723" t="n">
+        <v>78</v>
+      </c>
+      <c r="E2723" t="n">
+        <v>78.2600021362305</v>
+      </c>
+      <c r="F2723" t="n">
+        <v>79</v>
+      </c>
+      <c r="G2723" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/BC.MI.xlsx
+++ b/data/BC.MI.xlsx
@@ -447,7 +447,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G3" t="n">
-        <v>14.6633529663086</v>
+        <v>14.6633539199829</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>15.5</v>
       </c>
       <c r="G4" t="n">
-        <v>14.2944650650024</v>
+        <v>14.2944641113281</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>15.1700000762939</v>
       </c>
       <c r="G5" t="n">
-        <v>13.9901304244995</v>
+        <v>13.9901294708252</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>14.9300003051758</v>
       </c>
       <c r="G6" t="n">
-        <v>13.7687959671021</v>
+        <v>13.7687978744507</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>14.9099998474121</v>
       </c>
       <c r="G7" t="n">
-        <v>13.7503519058228</v>
+        <v>13.7503528594971</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G9" t="n">
-        <v>14.8477983474731</v>
+        <v>14.8477973937988</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G10" t="n">
-        <v>15.1244649887085</v>
+        <v>15.1244640350342</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>16.3799991607666</v>
       </c>
       <c r="G11" t="n">
-        <v>15.1060190200806</v>
+        <v>15.1060218811035</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>15.460000038147</v>
       </c>
       <c r="G12" t="n">
-        <v>14.2575750350952</v>
+        <v>14.2575759887695</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>15.6700000762939</v>
       </c>
       <c r="G13" t="n">
-        <v>14.4512414932251</v>
+        <v>14.4512424468994</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>15.0799999237061</v>
       </c>
       <c r="G14" t="n">
-        <v>13.9071283340454</v>
+        <v>13.907130241394</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>15.0299997329712</v>
       </c>
       <c r="G15" t="n">
-        <v>13.8610162734985</v>
+        <v>13.8610181808472</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G17" t="n">
-        <v>14.1561307907104</v>
+        <v>14.1561317443848</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>15.8100004196167</v>
       </c>
       <c r="G18" t="n">
-        <v>14.5803537368774</v>
+        <v>14.5803527832031</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G19" t="n">
-        <v>14.2022409439087</v>
+        <v>14.202241897583</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>14.9799995422363</v>
       </c>
       <c r="G20" t="n">
-        <v>13.8149080276489</v>
+        <v>13.8149070739746</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G21" t="n">
-        <v>14.2391309738159</v>
+        <v>14.2391300201416</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>15.460000038147</v>
       </c>
       <c r="G23" t="n">
-        <v>14.2575750350952</v>
+        <v>14.2575759887695</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>15.1700000762939</v>
       </c>
       <c r="G25" t="n">
-        <v>13.9901304244995</v>
+        <v>13.9901294708252</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>14.9899997711182</v>
       </c>
       <c r="G26" t="n">
-        <v>13.8241300582886</v>
+        <v>13.8241310119629</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>14.3800001144409</v>
       </c>
       <c r="G27" t="n">
-        <v>13.2615728378296</v>
+        <v>13.2615747451782</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G28" t="n">
-        <v>12.5422391891479</v>
+        <v>12.5422401428223</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>13.2799997329712</v>
       </c>
       <c r="G30" t="n">
-        <v>12.2471265792847</v>
+        <v>12.247127532959</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>14.5</v>
       </c>
       <c r="G32" t="n">
-        <v>13.3722410202026</v>
+        <v>13.3722400665283</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G33" t="n">
-        <v>13.0033502578735</v>
+        <v>13.0033512115479</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G35" t="n">
-        <v>13.2339067459106</v>
+        <v>13.233907699585</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>15.0200004577637</v>
       </c>
       <c r="G39" t="n">
-        <v>13.8517971038818</v>
+        <v>13.8517951965332</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>15.0799999237061</v>
       </c>
       <c r="G40" t="n">
-        <v>13.9071283340454</v>
+        <v>13.907130241394</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>14.7299995422363</v>
       </c>
       <c r="G41" t="n">
-        <v>13.5843515396118</v>
+        <v>13.5843524932861</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>14.8100004196167</v>
       </c>
       <c r="G42" t="n">
-        <v>13.6581315994263</v>
+        <v>13.6581296920776</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G43" t="n">
-        <v>13.9255752563477</v>
+        <v>13.9255743026733</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G44" t="n">
-        <v>14.0546855926514</v>
+        <v>14.0546865463257</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G45" t="n">
-        <v>14.2391309738159</v>
+        <v>14.2391300201416</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>15.4700002670288</v>
       </c>
       <c r="G46" t="n">
-        <v>14.2667970657349</v>
+        <v>14.2667980194092</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G47" t="n">
-        <v>14.0731315612793</v>
+        <v>14.073130607605</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G48" t="n">
-        <v>14.2022409439087</v>
+        <v>14.202241897583</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>15.5</v>
       </c>
       <c r="G49" t="n">
-        <v>14.2944650650024</v>
+        <v>14.2944641113281</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>16.5</v>
       </c>
       <c r="G51" t="n">
-        <v>15.2166872024536</v>
+        <v>15.2166862487793</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G52" t="n">
-        <v>15.4011344909668</v>
+        <v>15.4011325836182</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>16.3199996948242</v>
       </c>
       <c r="G53" t="n">
-        <v>15.050687789917</v>
+        <v>15.0506896972656</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>15.6700000762939</v>
       </c>
       <c r="G55" t="n">
-        <v>14.4512414932251</v>
+        <v>14.4512424468994</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>16.4599990844727</v>
       </c>
       <c r="G56" t="n">
-        <v>15.1797962188721</v>
+        <v>15.1797971725464</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>16.5699996948242</v>
       </c>
       <c r="G57" t="n">
-        <v>15.2812442779541</v>
+        <v>15.2812404632568</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G58" t="n">
-        <v>15.4011344909668</v>
+        <v>15.4011325836182</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>16.7399997711182</v>
       </c>
       <c r="G59" t="n">
-        <v>15.4380207061768</v>
+        <v>15.4380197525024</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>16.6399993896484</v>
       </c>
       <c r="G60" t="n">
-        <v>15.345796585083</v>
+        <v>15.345799446106</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G61" t="n">
-        <v>15.1244649887085</v>
+        <v>15.1244640350342</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G62" t="n">
-        <v>15.4933528900146</v>
+        <v>15.493353843689</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>16.6399993896484</v>
       </c>
       <c r="G63" t="n">
-        <v>15.345796585083</v>
+        <v>15.345799446106</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>16.5900001525879</v>
       </c>
       <c r="G65" t="n">
-        <v>15.2996854782104</v>
+        <v>15.2996883392334</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G66" t="n">
-        <v>14.8939085006714</v>
+        <v>14.89391040802</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G67" t="n">
-        <v>14.8016872406006</v>
+        <v>14.8016862869263</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G68" t="n">
-        <v>14.4327955245972</v>
+        <v>14.4327974319458</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>16.4099998474121</v>
       </c>
       <c r="G70" t="n">
-        <v>15.1336870193481</v>
+        <v>15.1336851119995</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>16.8299999237061</v>
       </c>
       <c r="G72" t="n">
-        <v>15.5210218429565</v>
+        <v>15.5210208892822</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G73" t="n">
-        <v>15.5394668579102</v>
+        <v>15.5394659042358</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>16.9400005340576</v>
       </c>
       <c r="G74" t="n">
-        <v>15.6224660873413</v>
+        <v>15.6224699020386</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G75" t="n">
-        <v>16.0928039550781</v>
+        <v>16.0928020477295</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G76" t="n">
-        <v>16.185022354126</v>
+        <v>16.1850204467773</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>17.5400009155273</v>
       </c>
       <c r="G77" t="n">
-        <v>16.1758003234863</v>
+        <v>16.1757984161377</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G79" t="n">
-        <v>16.046688079834</v>
+        <v>16.0466899871826</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>17.5699996948242</v>
       </c>
       <c r="G80" t="n">
-        <v>16.2034683227539</v>
+        <v>16.2034664154053</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G81" t="n">
-        <v>16.0835781097412</v>
+        <v>16.0835800170898</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>17.5200004577637</v>
       </c>
       <c r="G82" t="n">
-        <v>16.1573581695557</v>
+        <v>16.1573543548584</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>17.5200004577637</v>
       </c>
       <c r="G83" t="n">
-        <v>16.1573581695557</v>
+        <v>16.1573543548584</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G84" t="n">
-        <v>15.8161315917969</v>
+        <v>15.8161325454712</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>17.3600006103516</v>
       </c>
       <c r="G85" t="n">
-        <v>16.009801864624</v>
+        <v>16.0097980499268</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>17.5300006866455</v>
       </c>
       <c r="G86" t="n">
-        <v>16.1665802001953</v>
+        <v>16.166576385498</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G89" t="n">
-        <v>16.185022354126</v>
+        <v>16.1850204467773</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G91" t="n">
-        <v>16.185022354126</v>
+        <v>16.1850204467773</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G92" t="n">
-        <v>16.185022354126</v>
+        <v>16.1850204467773</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G93" t="n">
-        <v>16.0651302337646</v>
+        <v>16.0651321411133</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>17.5900001525879</v>
       </c>
       <c r="G94" t="n">
-        <v>16.2219142913818</v>
+        <v>16.2219123840332</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G95" t="n">
-        <v>16.0651302337646</v>
+        <v>16.0651321411133</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>17.7800006866455</v>
       </c>
       <c r="G96" t="n">
-        <v>16.3971366882324</v>
+        <v>16.3971328735352</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>17.8199996948242</v>
       </c>
       <c r="G97" t="n">
-        <v>16.434024810791</v>
+        <v>16.4340229034424</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G99" t="n">
-        <v>16.2311344146729</v>
+        <v>16.2311363220215</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>17.5200004577637</v>
       </c>
       <c r="G100" t="n">
-        <v>16.2775897979736</v>
+        <v>16.277587890625</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>17.5900001525879</v>
       </c>
       <c r="G102" t="n">
-        <v>16.3426265716553</v>
+        <v>16.342622756958</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>17.6599998474121</v>
       </c>
       <c r="G103" t="n">
-        <v>16.4076595306396</v>
+        <v>16.407657623291</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>17.7299995422363</v>
       </c>
       <c r="G106" t="n">
-        <v>16.472692489624</v>
+        <v>16.4726963043213</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>17.75</v>
       </c>
       <c r="G107" t="n">
-        <v>16.4912757873535</v>
+        <v>16.4912796020508</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>17.5799999237061</v>
       </c>
       <c r="G109" t="n">
-        <v>16.3333320617676</v>
+        <v>16.3333339691162</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G111" t="n">
-        <v>16.4448223114014</v>
+        <v>16.4448261260986</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>17.8799991607666</v>
       </c>
       <c r="G112" t="n">
-        <v>16.6120586395264</v>
+        <v>16.6120567321777</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>17.8700008392334</v>
       </c>
       <c r="G113" t="n">
-        <v>16.6027679443359</v>
+        <v>16.6027698516846</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>17.2399997711182</v>
       </c>
       <c r="G114" t="n">
-        <v>16.0174446105957</v>
+        <v>16.0174427032471</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>16.6700000762939</v>
       </c>
       <c r="G115" t="n">
-        <v>15.4878625869751</v>
+        <v>15.4878644943237</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>16.4400005340576</v>
       </c>
       <c r="G116" t="n">
-        <v>15.2741756439209</v>
+        <v>15.2741737365723</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G118" t="n">
-        <v>15.1441020965576</v>
+        <v>15.144100189209</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>17.6200008392334</v>
       </c>
       <c r="G119" t="n">
-        <v>16.3704986572266</v>
+        <v>16.3704967498779</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G120" t="n">
-        <v>16.3983707427979</v>
+        <v>16.3983688354492</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>17.2700004577637</v>
       </c>
       <c r="G122" t="n">
-        <v>16.045316696167</v>
+        <v>16.0453205108643</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G123" t="n">
-        <v>16.3519172668457</v>
+        <v>16.3519153594971</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>16.0100002288818</v>
       </c>
       <c r="G126" t="n">
-        <v>14.8746690750122</v>
+        <v>14.8746681213379</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>16.1599998474121</v>
       </c>
       <c r="G128" t="n">
-        <v>15.0140314102173</v>
+        <v>15.014030456543</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>16.4799995422363</v>
       </c>
       <c r="G129" t="n">
-        <v>15.3113374710083</v>
+        <v>15.3113393783569</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>16.1599998474121</v>
       </c>
       <c r="G130" t="n">
-        <v>15.0140314102173</v>
+        <v>15.014030456543</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>15.710000038147</v>
       </c>
       <c r="G131" t="n">
-        <v>14.5959424972534</v>
+        <v>14.5959415435791</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>15.210000038147</v>
       </c>
       <c r="G132" t="n">
-        <v>14.1313982009888</v>
+        <v>14.1313991546631</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G135" t="n">
-        <v>14.7260141372681</v>
+        <v>14.7260150909424</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>16.5100002288818</v>
       </c>
       <c r="G136" t="n">
-        <v>15.3392095565796</v>
+        <v>15.3392105102539</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>16.6299991607666</v>
       </c>
       <c r="G137" t="n">
-        <v>15.4506998062134</v>
+        <v>15.4507007598877</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>16.4899997711182</v>
       </c>
       <c r="G138" t="n">
-        <v>15.3206272125244</v>
+        <v>15.320629119873</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G139" t="n">
-        <v>15.2370119094849</v>
+        <v>15.2370100021362</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>16.5599994659424</v>
       </c>
       <c r="G141" t="n">
-        <v>15.3856639862061</v>
+        <v>15.3856649398804</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>16.8199996948242</v>
       </c>
       <c r="G143" t="n">
-        <v>15.6272258758545</v>
+        <v>15.6272277832031</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>16.9899997711182</v>
       </c>
       <c r="G144" t="n">
-        <v>15.7851734161377</v>
+        <v>15.7851724624634</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>16.7800006866455</v>
       </c>
       <c r="G145" t="n">
-        <v>15.59006690979</v>
+        <v>15.5900650024414</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>16.9300003051758</v>
       </c>
       <c r="G147" t="n">
-        <v>15.7294282913208</v>
+        <v>15.7294263839722</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G150" t="n">
-        <v>15.4692821502686</v>
+        <v>15.4692831039429</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G151" t="n">
-        <v>15.181266784668</v>
+        <v>15.1812658309937</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>16.4699993133545</v>
       </c>
       <c r="G152" t="n">
-        <v>15.3020477294922</v>
+        <v>15.3020467758179</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>16.4899997711182</v>
       </c>
       <c r="G153" t="n">
-        <v>15.3206272125244</v>
+        <v>15.320629119873</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G154" t="n">
-        <v>15.4414129257202</v>
+        <v>15.4414119720459</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>16.9099998474121</v>
       </c>
       <c r="G155" t="n">
-        <v>15.7108469009399</v>
+        <v>15.7108449935913</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>17.0300006866455</v>
       </c>
       <c r="G156" t="n">
-        <v>15.8223371505737</v>
+        <v>15.8223361968994</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>17.2900009155273</v>
       </c>
       <c r="G157" t="n">
-        <v>16.0639019012451</v>
+        <v>16.0638980865479</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G158" t="n">
-        <v>16.1103515625</v>
+        <v>16.1103553771973</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>17.1700000762939</v>
       </c>
       <c r="G160" t="n">
-        <v>15.9524068832397</v>
+        <v>15.9524097442627</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G161" t="n">
-        <v>16.1660976409912</v>
+        <v>16.1660957336426</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>17.5300006866455</v>
       </c>
       <c r="G162" t="n">
-        <v>16.2868785858154</v>
+        <v>16.2868766784668</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>17.4899997711182</v>
       </c>
       <c r="G163" t="n">
-        <v>16.2497158050537</v>
+        <v>16.2497138977051</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>17.5400009155273</v>
       </c>
       <c r="G164" t="n">
-        <v>16.2961692810059</v>
+        <v>16.2961711883545</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>17.5200004577637</v>
       </c>
       <c r="G165" t="n">
-        <v>16.2775897979736</v>
+        <v>16.277587890625</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>17.75</v>
       </c>
       <c r="G167" t="n">
-        <v>16.4912757873535</v>
+        <v>16.4912796020508</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>17.75</v>
       </c>
       <c r="G168" t="n">
-        <v>16.4912757873535</v>
+        <v>16.4912796020508</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>17.5</v>
       </c>
       <c r="G169" t="n">
-        <v>16.2590065002441</v>
+        <v>16.2590084075928</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>17.8299999237061</v>
       </c>
       <c r="G170" t="n">
-        <v>16.5656051635742</v>
+        <v>16.5656070709229</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>17.8799991607666</v>
       </c>
       <c r="G171" t="n">
-        <v>16.6120586395264</v>
+        <v>16.6120567321777</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>18.0799999237061</v>
       </c>
       <c r="G174" t="n">
-        <v>16.7978763580322</v>
+        <v>16.7978744506836</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>18</v>
       </c>
       <c r="G175" t="n">
-        <v>16.7235507965088</v>
+        <v>16.7235488891602</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>17.8899993896484</v>
       </c>
       <c r="G176" t="n">
-        <v>16.6213455200195</v>
+        <v>16.6213493347168</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>18</v>
       </c>
       <c r="G177" t="n">
-        <v>16.7235507965088</v>
+        <v>16.7235488891602</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>17.9899997711182</v>
       </c>
       <c r="G178" t="n">
-        <v>16.7142562866211</v>
+        <v>16.7142581939697</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>18.0400009155273</v>
       </c>
       <c r="G179" t="n">
-        <v>16.7607135772705</v>
+        <v>16.7607116699219</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>18</v>
       </c>
       <c r="G180" t="n">
-        <v>16.7235507965088</v>
+        <v>16.7235488891602</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G181" t="n">
-        <v>16.6306419372559</v>
+        <v>16.6306400299072</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G182" t="n">
-        <v>16.6306419372559</v>
+        <v>16.6306400299072</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>18</v>
       </c>
       <c r="G183" t="n">
-        <v>16.7235507965088</v>
+        <v>16.7235488891602</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G184" t="n">
-        <v>16.677095413208</v>
+        <v>16.6770973205566</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G185" t="n">
-        <v>16.4819850921631</v>
+        <v>16.481990814209</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>17.9699993133545</v>
       </c>
       <c r="G186" t="n">
-        <v>16.6956787109375</v>
+        <v>16.6956748962402</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>17.8199996948242</v>
       </c>
       <c r="G187" t="n">
-        <v>16.5563144683838</v>
+        <v>16.5563125610352</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G188" t="n">
-        <v>16.6306419372559</v>
+        <v>16.6306400299072</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G192" t="n">
-        <v>16.2125568389893</v>
+        <v>16.212553024292</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G195" t="n">
-        <v>16.6306419372559</v>
+        <v>16.6306400299072</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>18</v>
       </c>
       <c r="G196" t="n">
-        <v>16.7235507965088</v>
+        <v>16.7235488891602</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>17.9400005340576</v>
       </c>
       <c r="G197" t="n">
-        <v>16.6678066253662</v>
+        <v>16.6678047180176</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>18</v>
       </c>
       <c r="G198" t="n">
-        <v>16.7235507965088</v>
+        <v>16.7235488891602</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G200" t="n">
-        <v>16.5377292633057</v>
+        <v>16.5377311706543</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>17.9400005340576</v>
       </c>
       <c r="G201" t="n">
-        <v>16.6678066253662</v>
+        <v>16.6678047180176</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G202" t="n">
-        <v>16.5377292633057</v>
+        <v>16.5377311706543</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>17.9699993133545</v>
       </c>
       <c r="G203" t="n">
-        <v>16.6956787109375</v>
+        <v>16.6956748962402</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>17.9599990844727</v>
       </c>
       <c r="G204" t="n">
-        <v>16.6863842010498</v>
+        <v>16.6863861083984</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G206" t="n">
-        <v>16.6306419372559</v>
+        <v>16.6306400299072</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G207" t="n">
-        <v>16.6306419372559</v>
+        <v>16.6306400299072</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>17.9899997711182</v>
       </c>
       <c r="G208" t="n">
-        <v>16.7142562866211</v>
+        <v>16.7142581939697</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>17.9899997711182</v>
       </c>
       <c r="G209" t="n">
-        <v>16.7142562866211</v>
+        <v>16.7142581939697</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>17.9899997711182</v>
       </c>
       <c r="G210" t="n">
-        <v>16.7142562866211</v>
+        <v>16.7142581939697</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>18</v>
       </c>
       <c r="G211" t="n">
-        <v>16.7235507965088</v>
+        <v>16.7235488891602</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>18.0400009155273</v>
       </c>
       <c r="G214" t="n">
-        <v>16.7607135772705</v>
+        <v>16.7607116699219</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>18</v>
       </c>
       <c r="G215" t="n">
-        <v>16.7235507965088</v>
+        <v>16.7235488891602</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>18</v>
       </c>
       <c r="G217" t="n">
-        <v>16.7235507965088</v>
+        <v>16.7235488891602</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>18</v>
       </c>
       <c r="G218" t="n">
-        <v>16.7235507965088</v>
+        <v>16.7235488891602</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>17.9599990844727</v>
       </c>
       <c r="G219" t="n">
-        <v>16.6863842010498</v>
+        <v>16.6863861083984</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>18.0799999237061</v>
       </c>
       <c r="G220" t="n">
-        <v>16.7978763580322</v>
+        <v>16.7978744506836</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>18.0799999237061</v>
       </c>
       <c r="G221" t="n">
-        <v>16.7978763580322</v>
+        <v>16.7978744506836</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>17.9300003051758</v>
       </c>
       <c r="G223" t="n">
-        <v>16.6585121154785</v>
+        <v>16.6585140228271</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>18</v>
       </c>
       <c r="G224" t="n">
-        <v>16.7235507965088</v>
+        <v>16.7235488891602</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>18</v>
       </c>
       <c r="G225" t="n">
-        <v>16.7235507965088</v>
+        <v>16.7235488891602</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>17.9899997711182</v>
       </c>
       <c r="G226" t="n">
-        <v>16.7142562866211</v>
+        <v>16.7142581939697</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>17.9400005340576</v>
       </c>
       <c r="G229" t="n">
-        <v>16.6678066253662</v>
+        <v>16.6678047180176</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>18</v>
       </c>
       <c r="G231" t="n">
-        <v>16.7235507965088</v>
+        <v>16.7235488891602</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>17.8299999237061</v>
       </c>
       <c r="G232" t="n">
-        <v>16.5656051635742</v>
+        <v>16.5656070709229</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G234" t="n">
-        <v>16.5377292633057</v>
+        <v>16.5377311706543</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>18</v>
       </c>
       <c r="G235" t="n">
-        <v>16.7235507965088</v>
+        <v>16.7235488891602</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G236" t="n">
-        <v>16.677095413208</v>
+        <v>16.6770973205566</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>17.8099994659424</v>
       </c>
       <c r="G237" t="n">
-        <v>16.5470218658447</v>
+        <v>16.5470237731934</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>18.1399993896484</v>
       </c>
       <c r="G239" t="n">
-        <v>16.8536224365234</v>
+        <v>16.8536205291748</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>18.3400001525879</v>
       </c>
       <c r="G243" t="n">
-        <v>17.0394401550293</v>
+        <v>17.039436340332</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>18.4400005340576</v>
       </c>
       <c r="G245" t="n">
-        <v>17.1323490142822</v>
+        <v>17.1323471069336</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G249" t="n">
-        <v>17.4668140411377</v>
+        <v>17.466817855835</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>18.9899997711182</v>
       </c>
       <c r="G250" t="n">
-        <v>17.6433429718018</v>
+        <v>17.6433448791504</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>19.9099998474121</v>
       </c>
       <c r="G251" t="n">
-        <v>18.4981021881104</v>
+        <v>18.498104095459</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>20</v>
       </c>
       <c r="G252" t="n">
-        <v>18.5817241668701</v>
+        <v>18.5817222595215</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>20</v>
       </c>
       <c r="G253" t="n">
-        <v>18.5817241668701</v>
+        <v>18.5817222595215</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>19.9799995422363</v>
       </c>
       <c r="G255" t="n">
-        <v>18.5631408691406</v>
+        <v>18.563138961792</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>20</v>
       </c>
       <c r="G256" t="n">
-        <v>18.5817241668701</v>
+        <v>18.5817222595215</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>20.3400001525879</v>
       </c>
       <c r="G257" t="n">
-        <v>18.897611618042</v>
+        <v>18.8976097106934</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>20.5499992370605</v>
       </c>
       <c r="G258" t="n">
-        <v>19.0927200317383</v>
+        <v>19.092716217041</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>20.5900001525879</v>
       </c>
       <c r="G259" t="n">
-        <v>19.1298828125</v>
+        <v>19.1298809051514</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>21.5400009155273</v>
       </c>
       <c r="G264" t="n">
-        <v>20.0125141143799</v>
+        <v>20.0125160217285</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>21.5</v>
       </c>
       <c r="G266" t="n">
-        <v>19.9753532409668</v>
+        <v>19.9753513336182</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>21.5200004577637</v>
       </c>
       <c r="G267" t="n">
-        <v>19.993932723999</v>
+        <v>19.9939346313477</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>21.7800006866455</v>
       </c>
       <c r="G268" t="n">
-        <v>20.2354927062988</v>
+        <v>20.2354984283447</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G271" t="n">
-        <v>20.62571144104</v>
+        <v>20.6257095336914</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>21.9599990844727</v>
       </c>
       <c r="G272" t="n">
-        <v>20.4027290344238</v>
+        <v>20.4027309417725</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>21.9899997711182</v>
       </c>
       <c r="G273" t="n">
-        <v>20.4306030273438</v>
+        <v>20.4306049346924</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>21.6399993896484</v>
       </c>
       <c r="G274" t="n">
-        <v>20.1054248809814</v>
+        <v>20.1054191589355</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>21.3600006103516</v>
       </c>
       <c r="G275" t="n">
-        <v>19.8452777862549</v>
+        <v>19.8452758789062</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>21.0599994659424</v>
       </c>
       <c r="G276" t="n">
-        <v>19.5665512084961</v>
+        <v>19.5665531158447</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>20.9799995422363</v>
       </c>
       <c r="G277" t="n">
-        <v>19.492223739624</v>
+        <v>19.4922256469727</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>20.7399997711182</v>
       </c>
       <c r="G278" t="n">
-        <v>19.2692451477051</v>
+        <v>19.2692470550537</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>21.0599994659424</v>
       </c>
       <c r="G280" t="n">
-        <v>19.5665512084961</v>
+        <v>19.5665531158447</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G281" t="n">
-        <v>19.46435546875</v>
+        <v>19.4643516540527</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G288" t="n">
-        <v>19.1391754150391</v>
+        <v>19.1391735076904</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>20.6100006103516</v>
       </c>
       <c r="G290" t="n">
-        <v>19.1484642028809</v>
+        <v>19.1484661102295</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>20.1900005340576</v>
       </c>
       <c r="G292" t="n">
-        <v>18.7582492828369</v>
+        <v>18.7582473754883</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G293" t="n">
-        <v>18.860445022583</v>
+        <v>18.8604488372803</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G296" t="n">
-        <v>18.6281776428223</v>
+        <v>18.6281757354736</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>19.6499996185303</v>
       </c>
       <c r="G297" t="n">
-        <v>18.2565383911133</v>
+        <v>18.2565422058105</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>19.5</v>
       </c>
       <c r="G298" t="n">
-        <v>18.1171798706055</v>
+        <v>18.1171760559082</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>19.4300003051758</v>
       </c>
       <c r="G299" t="n">
-        <v>18.0521450042725</v>
+        <v>18.0521430969238</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>19.7900009155273</v>
       </c>
       <c r="G300" t="n">
-        <v>18.3866157531738</v>
+        <v>18.3866138458252</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>20.4599990844727</v>
       </c>
       <c r="G301" t="n">
-        <v>19.0090961456299</v>
+        <v>19.0091018676758</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>20.7299995422363</v>
       </c>
       <c r="G302" t="n">
-        <v>19.2599544525146</v>
+        <v>19.2599563598633</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>20.4400005340576</v>
       </c>
       <c r="G303" t="n">
-        <v>18.9905185699463</v>
+        <v>18.9905204772949</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>20.5900001525879</v>
       </c>
       <c r="G304" t="n">
-        <v>19.1298828125</v>
+        <v>19.1298809051514</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>20.9899997711182</v>
       </c>
       <c r="G307" t="n">
-        <v>19.5015144348145</v>
+        <v>19.5015182495117</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>21.0300006866455</v>
       </c>
       <c r="G308" t="n">
-        <v>19.5386810302734</v>
+        <v>19.5386791229248</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>20.8199996948242</v>
       </c>
       <c r="G309" t="n">
-        <v>19.3435707092285</v>
+        <v>19.3435726165771</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>21.3600006103516</v>
       </c>
       <c r="G310" t="n">
-        <v>19.8452777862549</v>
+        <v>19.8452758789062</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>21.8899993896484</v>
       </c>
       <c r="G311" t="n">
-        <v>20.3376903533936</v>
+        <v>20.3376941680908</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>22.0300006866455</v>
       </c>
       <c r="G312" t="n">
-        <v>20.4677696228027</v>
+        <v>20.4677677154541</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G313" t="n">
-        <v>20.5328006744385</v>
+        <v>20.5328025817871</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>22.0900001525879</v>
       </c>
       <c r="G314" t="n">
-        <v>20.5235157012939</v>
+        <v>20.523509979248</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>22.2299995422363</v>
       </c>
       <c r="G315" t="n">
-        <v>20.6535816192627</v>
+        <v>20.6535835266113</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G316" t="n">
-        <v>21.0902519226074</v>
+        <v>21.0902557373047</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>22.6299991607666</v>
       </c>
       <c r="G317" t="n">
-        <v>21.0252170562744</v>
+        <v>21.0252151489258</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>22.3299999237061</v>
       </c>
       <c r="G319" t="n">
-        <v>20.7464923858643</v>
+        <v>20.7464904785156</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>22.2099990844727</v>
       </c>
       <c r="G320" t="n">
-        <v>20.6350021362305</v>
+        <v>20.6350002288818</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G321" t="n">
-        <v>20.62571144104</v>
+        <v>20.6257095336914</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>22.3400001525879</v>
       </c>
       <c r="G322" t="n">
-        <v>20.7557830810547</v>
+        <v>20.7557849884033</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>22.6100006103516</v>
       </c>
       <c r="G325" t="n">
-        <v>21.0066356658936</v>
+        <v>21.0066375732422</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>22.9599990844727</v>
       </c>
       <c r="G328" t="n">
-        <v>21.3318138122559</v>
+        <v>21.3318157196045</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>22.7199993133545</v>
       </c>
       <c r="G330" t="n">
-        <v>21.1088371276855</v>
+        <v>21.1088352203369</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>22.6299991607666</v>
       </c>
       <c r="G331" t="n">
-        <v>21.0252170562744</v>
+        <v>21.0252151489258</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>22.8899993896484</v>
       </c>
       <c r="G332" t="n">
-        <v>21.2667770385742</v>
+        <v>21.2667789459229</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G334" t="n">
-        <v>21.7406139373779</v>
+        <v>21.7406158447266</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>23.4200000762939</v>
       </c>
       <c r="G336" t="n">
-        <v>21.7591934204102</v>
+        <v>21.7591972351074</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>23.6499996185303</v>
       </c>
       <c r="G337" t="n">
-        <v>21.9728851318359</v>
+        <v>21.9728870391846</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>24.1700000762939</v>
       </c>
       <c r="G339" t="n">
-        <v>22.4560108184814</v>
+        <v>22.4560089111328</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>24.5</v>
       </c>
       <c r="G343" t="n">
-        <v>22.7626075744629</v>
+        <v>22.7626094818115</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>24.5</v>
       </c>
       <c r="G344" t="n">
-        <v>22.7626075744629</v>
+        <v>22.7626094818115</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>23.6499996185303</v>
       </c>
       <c r="G345" t="n">
-        <v>21.9728851318359</v>
+        <v>21.9728870391846</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>24</v>
       </c>
       <c r="G346" t="n">
-        <v>22.2980651855469</v>
+        <v>22.2980690002441</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>23.3899993896484</v>
       </c>
       <c r="G348" t="n">
-        <v>21.7313232421875</v>
+        <v>21.7313213348389</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>23.5</v>
       </c>
       <c r="G354" t="n">
-        <v>21.8335227966309</v>
+        <v>21.8335208892822</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>23.3199996948242</v>
       </c>
       <c r="G355" t="n">
-        <v>21.8148155212402</v>
+        <v>21.8148136138916</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>23.3700008392334</v>
       </c>
       <c r="G356" t="n">
-        <v>21.8615875244141</v>
+        <v>21.8615894317627</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>23.3799991607666</v>
       </c>
       <c r="G357" t="n">
-        <v>21.8709373474121</v>
+        <v>21.8709392547607</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>23.3099994659424</v>
       </c>
       <c r="G361" t="n">
-        <v>21.8054580688477</v>
+        <v>21.8054599761963</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>23.0400009155273</v>
       </c>
       <c r="G363" t="n">
-        <v>21.5528869628906</v>
+        <v>21.5528888702393</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>22.8799991607666</v>
       </c>
       <c r="G364" t="n">
-        <v>21.4032135009766</v>
+        <v>21.4032154083252</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>22.9400005340576</v>
       </c>
       <c r="G367" t="n">
-        <v>21.459342956543</v>
+        <v>21.4593410491943</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>22.75</v>
       </c>
       <c r="G368" t="n">
-        <v>21.2816028594971</v>
+        <v>21.2816047668457</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>22.7099990844727</v>
       </c>
       <c r="G369" t="n">
-        <v>21.2441864013672</v>
+        <v>21.2441883087158</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G371" t="n">
-        <v>21.141284942627</v>
+        <v>21.1412868499756</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G373" t="n">
-        <v>21.1880569458008</v>
+        <v>21.1880588531494</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>22.8600006103516</v>
       </c>
       <c r="G374" t="n">
-        <v>21.3845043182373</v>
+        <v>21.3845062255859</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>22.7600002288818</v>
       </c>
       <c r="G375" t="n">
-        <v>21.290958404541</v>
+        <v>21.2909603118896</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>23.6399993896484</v>
       </c>
       <c r="G377" t="n">
-        <v>22.1141605377197</v>
+        <v>22.1141586303711</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G378" t="n">
-        <v>22.2638301849365</v>
+        <v>22.2638320922852</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>23</v>
       </c>
       <c r="G383" t="n">
-        <v>21.5154705047607</v>
+        <v>21.5154666900635</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>23.0499992370605</v>
       </c>
       <c r="G385" t="n">
-        <v>21.5622386932373</v>
+        <v>21.5622406005859</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>22.8700008392334</v>
       </c>
       <c r="G386" t="n">
-        <v>21.3938598632812</v>
+        <v>21.3938617706299</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>22.7900009155273</v>
       </c>
       <c r="G387" t="n">
-        <v>21.3190250396729</v>
+        <v>21.3190231323242</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G388" t="n">
-        <v>21.141284942627</v>
+        <v>21.1412868499756</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>23</v>
       </c>
       <c r="G389" t="n">
-        <v>21.5154705047607</v>
+        <v>21.5154666900635</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>23</v>
       </c>
       <c r="G390" t="n">
-        <v>21.5154705047607</v>
+        <v>21.5154666900635</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>23.3199996948242</v>
       </c>
       <c r="G392" t="n">
-        <v>21.8148155212402</v>
+        <v>21.8148136138916</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>23.7099990844727</v>
       </c>
       <c r="G393" t="n">
-        <v>22.1796436309814</v>
+        <v>22.1796398162842</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>23.75</v>
       </c>
       <c r="G395" t="n">
-        <v>22.2170600891113</v>
+        <v>22.2170581817627</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G396" t="n">
-        <v>22.2638301849365</v>
+        <v>22.2638320922852</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>23.9500007629395</v>
       </c>
       <c r="G397" t="n">
-        <v>22.4041538238525</v>
+        <v>22.4041519165039</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>24.0900001525879</v>
       </c>
       <c r="G398" t="n">
-        <v>22.5351161956787</v>
+        <v>22.5351142883301</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>24.3099994659424</v>
       </c>
       <c r="G399" t="n">
-        <v>22.7409133911133</v>
+        <v>22.7409114837646</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>24.5</v>
       </c>
       <c r="G401" t="n">
-        <v>22.9186496734619</v>
+        <v>22.9186477661133</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>24.4099998474121</v>
       </c>
       <c r="G404" t="n">
-        <v>22.8344593048096</v>
+        <v>22.8344573974609</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G405" t="n">
-        <v>23.1992874145508</v>
+        <v>23.1992893218994</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>25</v>
       </c>
       <c r="G406" t="n">
-        <v>23.3863773345947</v>
+        <v>23.3863792419434</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>24.5599994659424</v>
       </c>
       <c r="G407" t="n">
-        <v>22.9747791290283</v>
+        <v>22.9747753143311</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G408" t="n">
-        <v>23.1992874145508</v>
+        <v>23.1992893218994</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>24.4200000762939</v>
       </c>
       <c r="G409" t="n">
-        <v>22.8438129425049</v>
+        <v>22.8438167572021</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G410" t="n">
-        <v>23.1057434082031</v>
+        <v>23.1057415008545</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>24.75</v>
       </c>
       <c r="G411" t="n">
-        <v>23.152515411377</v>
+        <v>23.1525115966797</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>24.0300006866455</v>
       </c>
       <c r="G413" t="n">
-        <v>22.4789886474609</v>
+        <v>22.4789867401123</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>24.0900001525879</v>
       </c>
       <c r="G414" t="n">
-        <v>22.5351161956787</v>
+        <v>22.5351142883301</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>24.3400001525879</v>
       </c>
       <c r="G416" t="n">
-        <v>22.7689762115479</v>
+        <v>22.7689781188965</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>24.0100002288818</v>
       </c>
       <c r="G417" t="n">
-        <v>22.4602813720703</v>
+        <v>22.4602794647217</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>23.9799995422363</v>
       </c>
       <c r="G418" t="n">
-        <v>22.4322128295898</v>
+        <v>22.4322147369385</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>24.0900001525879</v>
       </c>
       <c r="G420" t="n">
-        <v>22.5351161956787</v>
+        <v>22.5351142883301</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G421" t="n">
-        <v>22.3573780059814</v>
+        <v>22.3573760986328</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G422" t="n">
-        <v>22.3573780059814</v>
+        <v>22.3573760986328</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>23.7199993133545</v>
       </c>
       <c r="G423" t="n">
-        <v>22.1889953613281</v>
+        <v>22.1889972686768</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>23.4099998474121</v>
       </c>
       <c r="G424" t="n">
-        <v>21.8990039825439</v>
+        <v>21.8990058898926</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>23.3799991607666</v>
       </c>
       <c r="G425" t="n">
-        <v>21.8709373474121</v>
+        <v>21.8709392547607</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G426" t="n">
-        <v>23.1992874145508</v>
+        <v>23.1992893218994</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G427" t="n">
-        <v>23.5734672546387</v>
+        <v>23.5734691619873</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>25.4500007629395</v>
       </c>
       <c r="G428" t="n">
-        <v>23.807336807251</v>
+        <v>23.8073348999023</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>24.9699993133545</v>
       </c>
       <c r="G429" t="n">
-        <v>23.3583145141602</v>
+        <v>23.3583164215088</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>24.6800003051758</v>
       </c>
       <c r="G430" t="n">
-        <v>23.0870304107666</v>
+        <v>23.0870342254639</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>24.4599990844727</v>
       </c>
       <c r="G431" t="n">
-        <v>22.881233215332</v>
+        <v>22.8812313079834</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>25</v>
       </c>
       <c r="G433" t="n">
-        <v>23.3863773345947</v>
+        <v>23.3863792419434</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>25.8700008392334</v>
       </c>
       <c r="G436" t="n">
-        <v>24.2002239227295</v>
+        <v>24.2002258300781</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>26</v>
       </c>
       <c r="G437" t="n">
-        <v>24.3218326568604</v>
+        <v>24.321834564209</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>26.0699996948242</v>
       </c>
       <c r="G440" t="n">
-        <v>24.3873157501221</v>
+        <v>24.3873138427734</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>26.1800003051758</v>
       </c>
       <c r="G442" t="n">
-        <v>24.4902153015137</v>
+        <v>24.4902172088623</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>26.0900001525879</v>
       </c>
       <c r="G444" t="n">
-        <v>24.40602684021</v>
+        <v>24.4060249328613</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G445" t="n">
-        <v>24.2282886505127</v>
+        <v>24.2282867431641</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>26</v>
       </c>
       <c r="G447" t="n">
-        <v>24.3218326568604</v>
+        <v>24.321834564209</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>26.2399997711182</v>
       </c>
       <c r="G448" t="n">
-        <v>24.5463447570801</v>
+        <v>24.5463428497314</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>27.1800003051758</v>
       </c>
       <c r="G449" t="n">
-        <v>25.4256687164307</v>
+        <v>25.4256725311279</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>27.1800003051758</v>
       </c>
       <c r="G450" t="n">
-        <v>25.4256687164307</v>
+        <v>25.4256725311279</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>27.1900005340576</v>
       </c>
       <c r="G451" t="n">
-        <v>25.4350280761719</v>
+        <v>25.435022354126</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>26.9599990844727</v>
       </c>
       <c r="G452" t="n">
-        <v>25.2198696136475</v>
+        <v>25.2198715209961</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G456" t="n">
-        <v>25.1637439727783</v>
+        <v>25.1637420654297</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>27.1800003051758</v>
       </c>
       <c r="G457" t="n">
-        <v>25.4256687164307</v>
+        <v>25.4256725311279</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>27.1900005340576</v>
       </c>
       <c r="G458" t="n">
-        <v>25.4350280761719</v>
+        <v>25.435022354126</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G464" t="n">
-        <v>25.1637439727783</v>
+        <v>25.1637420654297</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>27.1499996185303</v>
       </c>
       <c r="G465" t="n">
-        <v>25.3976097106934</v>
+        <v>25.3976058959961</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>27.0799999237061</v>
       </c>
       <c r="G466" t="n">
-        <v>25.3321228027344</v>
+        <v>25.332124710083</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>28.8199996948242</v>
       </c>
       <c r="G470" t="n">
-        <v>26.9598159790039</v>
+        <v>26.9598178863525</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G471" t="n">
-        <v>26.5669231414795</v>
+        <v>26.5669269561768</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>28.5599994659424</v>
       </c>
       <c r="G472" t="n">
-        <v>26.7165946960449</v>
+        <v>26.7165985107422</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>28.1499996185303</v>
       </c>
       <c r="G473" t="n">
-        <v>26.3330612182617</v>
+        <v>26.3330593109131</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>28.4899997711182</v>
       </c>
       <c r="G474" t="n">
-        <v>26.6511173248291</v>
+        <v>26.6511154174805</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>27.9300003051758</v>
       </c>
       <c r="G476" t="n">
-        <v>26.1272640228271</v>
+        <v>26.1272621154785</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>27.5</v>
       </c>
       <c r="G477" t="n">
-        <v>25.7250156402588</v>
+        <v>25.7250175476074</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>26.5699996948242</v>
       </c>
       <c r="G479" t="n">
-        <v>24.8550434112549</v>
+        <v>24.8550415039062</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>26.5699996948242</v>
       </c>
       <c r="G481" t="n">
-        <v>24.8550434112549</v>
+        <v>24.8550415039062</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>26.9300003051758</v>
       </c>
       <c r="G482" t="n">
-        <v>25.1918087005615</v>
+        <v>25.1918067932129</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>26.5</v>
       </c>
       <c r="G483" t="n">
-        <v>24.7895622253418</v>
+        <v>24.7895603179932</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>26.9500007629395</v>
       </c>
       <c r="G484" t="n">
-        <v>25.2105178833008</v>
+        <v>25.2105159759521</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>26.5499992370605</v>
       </c>
       <c r="G487" t="n">
-        <v>24.836332321167</v>
+        <v>24.8363342285156</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>26.6599998474121</v>
       </c>
       <c r="G489" t="n">
-        <v>24.93922996521</v>
+        <v>24.9392337799072</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>26.5599994659424</v>
       </c>
       <c r="G490" t="n">
-        <v>24.8456859588623</v>
+        <v>24.8456878662109</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G492" t="n">
-        <v>24.8831081390381</v>
+        <v>24.8831062316895</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>26.4899997711182</v>
       </c>
       <c r="G493" t="n">
-        <v>24.7802047729492</v>
+        <v>24.7802066802979</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>27.1800003051758</v>
       </c>
       <c r="G495" t="n">
-        <v>25.4256687164307</v>
+        <v>25.4256725311279</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>27.0200004577637</v>
       </c>
       <c r="G496" t="n">
-        <v>25.2759990692139</v>
+        <v>25.2759971618652</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>27.2900009155273</v>
       </c>
       <c r="G497" t="n">
-        <v>25.5285720825195</v>
+        <v>25.5285682678223</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>27.7900009155273</v>
       </c>
       <c r="G498" t="n">
-        <v>25.9962978363037</v>
+        <v>25.9962997436523</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G499" t="n">
-        <v>25.912109375</v>
+        <v>25.9121074676514</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G500" t="n">
-        <v>26.0992012023926</v>
+        <v>26.0991973876953</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>26.1700000762939</v>
       </c>
       <c r="G501" t="n">
-        <v>24.4808597564697</v>
+        <v>24.4808616638184</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>26.7700004577637</v>
       </c>
       <c r="G503" t="n">
-        <v>25.0421371459961</v>
+        <v>25.0421352386475</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>27.1499996185303</v>
       </c>
       <c r="G506" t="n">
-        <v>25.3976097106934</v>
+        <v>25.3976058959961</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>27.5</v>
       </c>
       <c r="G513" t="n">
-        <v>25.7250156402588</v>
+        <v>25.7250175476074</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>27.5499992370605</v>
       </c>
       <c r="G514" t="n">
-        <v>25.7717876434326</v>
+        <v>25.7717895507812</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>28.5499992370605</v>
       </c>
       <c r="G516" t="n">
-        <v>26.7072448730469</v>
+        <v>26.7072429656982</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>27.25</v>
       </c>
       <c r="G524" t="n">
-        <v>25.491153717041</v>
+        <v>25.4911518096924</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>27.1499996185303</v>
       </c>
       <c r="G531" t="n">
-        <v>25.3976097106934</v>
+        <v>25.3976058959961</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G534" t="n">
-        <v>24.8831081390381</v>
+        <v>24.8831062316895</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>26.1000003814697</v>
       </c>
       <c r="G535" t="n">
-        <v>24.4153785705566</v>
+        <v>24.4153804779053</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G536" t="n">
-        <v>24.2282886505127</v>
+        <v>24.2282867431641</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G537" t="n">
-        <v>23.6670150756836</v>
+        <v>23.6670169830322</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>26</v>
       </c>
       <c r="G538" t="n">
-        <v>24.3218326568604</v>
+        <v>24.321834564209</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G539" t="n">
-        <v>23.5734672546387</v>
+        <v>23.5734691619873</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>25.75</v>
       </c>
       <c r="G541" t="n">
-        <v>24.0879669189453</v>
+        <v>24.0879707336426</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G544" t="n">
-        <v>24.5089244842529</v>
+        <v>24.5089282989502</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G548" t="n">
-        <v>24.2282886505127</v>
+        <v>24.2282867431641</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>25.4500007629395</v>
       </c>
       <c r="G550" t="n">
-        <v>23.807336807251</v>
+        <v>23.8073348999023</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>25.4500007629395</v>
       </c>
       <c r="G552" t="n">
-        <v>23.807336807251</v>
+        <v>23.8073348999023</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>25.75</v>
       </c>
       <c r="G554" t="n">
-        <v>24.0879669189453</v>
+        <v>24.0879707336426</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>25.1000003814697</v>
       </c>
       <c r="G555" t="n">
-        <v>23.4799213409424</v>
+        <v>23.479923248291</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G556" t="n">
-        <v>23.6670150756836</v>
+        <v>23.6670169830322</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>26.1000003814697</v>
       </c>
       <c r="G560" t="n">
-        <v>24.4153785705566</v>
+        <v>24.4153804779053</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G562" t="n">
-        <v>24.6960182189941</v>
+        <v>24.6960144042969</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>26.1000003814697</v>
       </c>
       <c r="G563" t="n">
-        <v>24.4153785705566</v>
+        <v>24.4153804779053</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>26</v>
       </c>
       <c r="G565" t="n">
-        <v>24.3218326568604</v>
+        <v>24.321834564209</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>26.3500003814697</v>
       </c>
       <c r="G567" t="n">
-        <v>24.649242401123</v>
+        <v>24.6492443084717</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>26.3500003814697</v>
       </c>
       <c r="G568" t="n">
-        <v>24.649242401123</v>
+        <v>24.6492443084717</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>25.25</v>
       </c>
       <c r="G571" t="n">
-        <v>23.6202411651611</v>
+        <v>23.6202449798584</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>25.25</v>
       </c>
       <c r="G572" t="n">
-        <v>23.6202411651611</v>
+        <v>23.6202449798584</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>25.1000003814697</v>
       </c>
       <c r="G573" t="n">
-        <v>23.4799213409424</v>
+        <v>23.479923248291</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>27.5499992370605</v>
       </c>
       <c r="G580" t="n">
-        <v>25.7717876434326</v>
+        <v>25.7717895507812</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>27.5</v>
       </c>
       <c r="G582" t="n">
-        <v>25.7250156402588</v>
+        <v>25.7250175476074</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>27.5</v>
       </c>
       <c r="G585" t="n">
-        <v>25.7250156402588</v>
+        <v>25.7250175476074</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G586" t="n">
-        <v>26.0056533813477</v>
+        <v>26.0056495666504</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>27.6499996185303</v>
       </c>
       <c r="G587" t="n">
-        <v>25.8653316497803</v>
+        <v>25.8653354644775</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G589" t="n">
-        <v>25.912109375</v>
+        <v>25.9121074676514</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G590" t="n">
-        <v>26.0056533813477</v>
+        <v>26.0056495666504</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G591" t="n">
-        <v>26.0992012023926</v>
+        <v>26.0991973876953</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G592" t="n">
-        <v>25.8185615539551</v>
+        <v>25.8185634613037</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G594" t="n">
-        <v>25.8185615539551</v>
+        <v>25.8185634613037</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G595" t="n">
-        <v>25.8185615539551</v>
+        <v>25.8185634613037</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G596" t="n">
-        <v>26.0992012023926</v>
+        <v>26.0991973876953</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>28.5499992370605</v>
       </c>
       <c r="G598" t="n">
-        <v>26.7072448730469</v>
+        <v>26.7072429656982</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>28</v>
       </c>
       <c r="G599" t="n">
-        <v>26.1927452087402</v>
+        <v>26.1927433013916</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>30.5499992370605</v>
       </c>
       <c r="G602" t="n">
-        <v>28.5781536102295</v>
+        <v>28.5781555175781</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G603" t="n">
-        <v>28.2507476806641</v>
+        <v>28.2507457733154</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G604" t="n">
-        <v>28.4378356933594</v>
+        <v>28.437837600708</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>30.25</v>
       </c>
       <c r="G605" t="n">
-        <v>28.2975177764893</v>
+        <v>28.2975158691406</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>30.9500007629395</v>
       </c>
       <c r="G606" t="n">
-        <v>28.9523372650146</v>
+        <v>28.952335357666</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>30.8500003814697</v>
       </c>
       <c r="G607" t="n">
-        <v>28.8587894439697</v>
+        <v>28.8587913513184</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G608" t="n">
-        <v>29.1607780456543</v>
+        <v>29.1607818603516</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>31.4500007629395</v>
       </c>
       <c r="G610" t="n">
-        <v>29.6798229217529</v>
+        <v>29.6798248291016</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>31.7000007629395</v>
       </c>
       <c r="G611" t="n">
-        <v>29.9157543182373</v>
+        <v>29.9157524108887</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>31.3500003814697</v>
       </c>
       <c r="G612" t="n">
-        <v>29.5854511260986</v>
+        <v>29.5854530334473</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>31.7000007629395</v>
       </c>
       <c r="G613" t="n">
-        <v>29.9157543182373</v>
+        <v>29.9157524108887</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>32.7000007629395</v>
       </c>
       <c r="G615" t="n">
-        <v>30.8594646453857</v>
+        <v>30.8594665527344</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>34.25</v>
       </c>
       <c r="G616" t="n">
-        <v>32.3222274780273</v>
+        <v>32.3222236633301</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>35.6500015258789</v>
       </c>
       <c r="G618" t="n">
-        <v>33.643424987793</v>
+        <v>33.6434288024902</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>36.7999992370605</v>
       </c>
       <c r="G619" t="n">
-        <v>34.7286949157715</v>
+        <v>34.7286987304688</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>37.7999992370605</v>
       </c>
       <c r="G620" t="n">
-        <v>35.6724128723145</v>
+        <v>35.6724090576172</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>35.75</v>
       </c>
       <c r="G623" t="n">
-        <v>33.7378005981445</v>
+        <v>33.73779296875</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>36.5999984741211</v>
       </c>
       <c r="G625" t="n">
-        <v>34.5399513244629</v>
+        <v>34.5399475097656</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>37.6500015258789</v>
       </c>
       <c r="G627" t="n">
-        <v>35.5308570861816</v>
+        <v>35.5308532714844</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>37.2999992370605</v>
       </c>
       <c r="G630" t="n">
-        <v>35.2005500793457</v>
+        <v>35.200553894043</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>36.9000015258789</v>
       </c>
       <c r="G631" t="n">
-        <v>34.8230743408203</v>
+        <v>34.823070526123</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>38.0999984741211</v>
       </c>
       <c r="G632" t="n">
-        <v>35.9555282592773</v>
+        <v>35.9555244445801</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>38.0499992370605</v>
       </c>
       <c r="G633" t="n">
-        <v>35.908332824707</v>
+        <v>35.9083404541016</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>37.6500015258789</v>
       </c>
       <c r="G635" t="n">
-        <v>35.5308570861816</v>
+        <v>35.5308532714844</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>38.5499992370605</v>
       </c>
       <c r="G638" t="n">
-        <v>36.3801918029785</v>
+        <v>36.3801956176758</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>32.8499984741211</v>
       </c>
       <c r="G642" t="n">
-        <v>31.0010204315186</v>
+        <v>31.0010223388672</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>33.0499992370605</v>
       </c>
       <c r="G643" t="n">
-        <v>31.1897659301758</v>
+        <v>31.1897678375244</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G644" t="n">
-        <v>30.9538402557373</v>
+        <v>30.9538383483887</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>32.6500015258789</v>
       </c>
       <c r="G646" t="n">
-        <v>30.8122825622559</v>
+        <v>30.8122787475586</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>34.5499992370605</v>
       </c>
       <c r="G647" t="n">
-        <v>32.6053352355957</v>
+        <v>32.6053314208984</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>35.3499984741211</v>
       </c>
       <c r="G648" t="n">
-        <v>33.3603096008301</v>
+        <v>33.3603134155273</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>36.4000015258789</v>
       </c>
       <c r="G650" t="n">
-        <v>34.3512115478516</v>
+        <v>34.3512077331543</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>35.9500007629395</v>
       </c>
       <c r="G652" t="n">
-        <v>33.9265365600586</v>
+        <v>33.9265403747559</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>36.7999992370605</v>
       </c>
       <c r="G666" t="n">
-        <v>34.7286949157715</v>
+        <v>34.7286987304688</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G669" t="n">
-        <v>35.1061859130859</v>
+        <v>35.1061820983887</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>37.7000007629395</v>
       </c>
       <c r="G670" t="n">
-        <v>35.5780410766602</v>
+        <v>35.5780448913574</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>37.7000007629395</v>
       </c>
       <c r="G671" t="n">
-        <v>35.5780410766602</v>
+        <v>35.5780448913574</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>40.7999992370605</v>
       </c>
       <c r="G674" t="n">
-        <v>38.5035591125488</v>
+        <v>38.5035552978516</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>39.5999984741211</v>
       </c>
       <c r="G678" t="n">
-        <v>37.37109375</v>
+        <v>37.3710899353027</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>38.9500007629395</v>
       </c>
       <c r="G682" t="n">
-        <v>36.757682800293</v>
+        <v>36.7576789855957</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>37.7000007629395</v>
       </c>
       <c r="G683" t="n">
-        <v>35.5780410766602</v>
+        <v>35.5780448913574</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>36.1500015258789</v>
       </c>
       <c r="G685" t="n">
-        <v>34.1152839660645</v>
+        <v>34.1152801513672</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>35.25</v>
       </c>
       <c r="G687" t="n">
-        <v>33.265941619873</v>
+        <v>33.2659378051758</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>35.0499992370605</v>
       </c>
       <c r="G688" t="n">
-        <v>33.0771903991699</v>
+        <v>33.0771980285645</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>34.7999992370605</v>
       </c>
       <c r="G689" t="n">
-        <v>32.8412704467773</v>
+        <v>32.8412666320801</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>34.5</v>
       </c>
       <c r="G691" t="n">
-        <v>32.5581550598145</v>
+        <v>32.5581474304199</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>34.9000015258789</v>
       </c>
       <c r="G692" t="n">
-        <v>32.9356422424316</v>
+        <v>32.9356384277344</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>34.2999992370605</v>
       </c>
       <c r="G693" t="n">
-        <v>32.3694076538086</v>
+        <v>32.3694114685059</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>34.0999984741211</v>
       </c>
       <c r="G695" t="n">
-        <v>32.1806640625</v>
+        <v>32.1806678771973</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>34</v>
       </c>
       <c r="G696" t="n">
-        <v>32.086296081543</v>
+        <v>32.0862998962402</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>34.75</v>
       </c>
       <c r="G697" t="n">
-        <v>32.7940788269043</v>
+        <v>32.7940826416016</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>34.1500015258789</v>
       </c>
       <c r="G698" t="n">
-        <v>32.2278518676758</v>
+        <v>32.227855682373</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>33.8499984741211</v>
       </c>
       <c r="G699" t="n">
-        <v>31.9447345733643</v>
+        <v>31.9447326660156</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>34.25</v>
       </c>
       <c r="G700" t="n">
-        <v>32.3222274780273</v>
+        <v>32.3222236633301</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>33.25</v>
       </c>
       <c r="G703" t="n">
-        <v>31.3785133361816</v>
+        <v>31.378511428833</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G704" t="n">
-        <v>31.4256973266602</v>
+        <v>31.4256954193115</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>32.5</v>
       </c>
       <c r="G705" t="n">
-        <v>30.6707229614258</v>
+        <v>30.6707210540771</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>29.8500003814697</v>
       </c>
       <c r="G710" t="n">
-        <v>28.1698780059814</v>
+        <v>28.1698799133301</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>29.5</v>
       </c>
       <c r="G711" t="n">
-        <v>27.8395824432373</v>
+        <v>27.8395805358887</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>29.0499992370605</v>
       </c>
       <c r="G712" t="n">
-        <v>27.414909362793</v>
+        <v>27.4149074554443</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>29.75</v>
       </c>
       <c r="G713" t="n">
-        <v>28.0755100250244</v>
+        <v>28.0755081176758</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>29.5499992370605</v>
       </c>
       <c r="G714" t="n">
-        <v>27.8867645263672</v>
+        <v>27.8867664337158</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>29.5</v>
       </c>
       <c r="G715" t="n">
-        <v>27.8395824432373</v>
+        <v>27.8395805358887</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>29.0499992370605</v>
       </c>
       <c r="G719" t="n">
-        <v>27.414909362793</v>
+        <v>27.4149074554443</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>29.0499992370605</v>
       </c>
       <c r="G721" t="n">
-        <v>27.414909362793</v>
+        <v>27.4149074554443</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>29.6499996185303</v>
       </c>
       <c r="G722" t="n">
-        <v>27.9811363220215</v>
+        <v>27.9811382293701</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>30.9500007629395</v>
       </c>
       <c r="G727" t="n">
-        <v>29.2079677581787</v>
+        <v>29.2079658508301</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G730" t="n">
-        <v>29.6326389312744</v>
+        <v>29.6326370239258</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G731" t="n">
-        <v>29.0664081573486</v>
+        <v>29.0664043426514</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>31.0499992370605</v>
       </c>
       <c r="G733" t="n">
-        <v>29.3023357391357</v>
+        <v>29.302339553833</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>30.9500007629395</v>
       </c>
       <c r="G734" t="n">
-        <v>29.2079677581787</v>
+        <v>29.2079658508301</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>30.9500007629395</v>
       </c>
       <c r="G736" t="n">
-        <v>29.2079677581787</v>
+        <v>29.2079658508301</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>29</v>
       </c>
       <c r="G743" t="n">
-        <v>27.3677234649658</v>
+        <v>27.3677215576172</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>29.8500003814697</v>
       </c>
       <c r="G746" t="n">
-        <v>28.1698780059814</v>
+        <v>28.1698799133301</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G749" t="n">
-        <v>29.6326389312744</v>
+        <v>29.6326370239258</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G753" t="n">
-        <v>26.5183811187744</v>
+        <v>26.5183792114258</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>28.25</v>
       </c>
       <c r="G755" t="n">
-        <v>26.6599388122559</v>
+        <v>26.6599349975586</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G758" t="n">
-        <v>25.8577785491943</v>
+        <v>25.857780456543</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>27.8500003814697</v>
       </c>
       <c r="G759" t="n">
-        <v>26.2824516296387</v>
+        <v>26.2824535369873</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>28</v>
       </c>
       <c r="G762" t="n">
-        <v>26.4240074157715</v>
+        <v>26.4240093231201</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>30.0499992370605</v>
       </c>
       <c r="G763" t="n">
-        <v>28.3586235046387</v>
+        <v>28.35862159729</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>30</v>
       </c>
       <c r="G765" t="n">
-        <v>28.3114376068115</v>
+        <v>28.3114395141602</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G768" t="n">
-        <v>26.3296356201172</v>
+        <v>26.3296337127686</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>28.0499992370605</v>
       </c>
       <c r="G770" t="n">
-        <v>26.4711933135986</v>
+        <v>26.47119140625</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G771" t="n">
-        <v>26.1408939361572</v>
+        <v>26.1408958435059</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G772" t="n">
-        <v>25.8577785491943</v>
+        <v>25.857780456543</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G773" t="n">
-        <v>26.3296356201172</v>
+        <v>26.3296337127686</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>29</v>
       </c>
       <c r="G778" t="n">
-        <v>27.3677234649658</v>
+        <v>27.3677215576172</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G780" t="n">
-        <v>29.0664081573486</v>
+        <v>29.0664043426514</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>30.1499996185303</v>
       </c>
       <c r="G783" t="n">
-        <v>28.4529933929443</v>
+        <v>28.452995300293</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>31.25</v>
       </c>
       <c r="G784" t="n">
-        <v>29.4910831451416</v>
+        <v>29.4910793304443</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>31.5499992370605</v>
       </c>
       <c r="G785" t="n">
-        <v>29.7741966247559</v>
+        <v>29.7741928100586</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>31.5499992370605</v>
       </c>
       <c r="G787" t="n">
-        <v>29.7741966247559</v>
+        <v>29.7741928100586</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>33.25</v>
       </c>
       <c r="G789" t="n">
-        <v>31.3785133361816</v>
+        <v>31.378511428833</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>33.25</v>
       </c>
       <c r="G791" t="n">
-        <v>31.3785133361816</v>
+        <v>31.378511428833</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>33.25</v>
       </c>
       <c r="G792" t="n">
-        <v>31.3785133361816</v>
+        <v>31.378511428833</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>34</v>
       </c>
       <c r="G793" t="n">
-        <v>32.086296081543</v>
+        <v>32.0862998962402</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>34.0999984741211</v>
       </c>
       <c r="G795" t="n">
-        <v>32.1806640625</v>
+        <v>32.1806678771973</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G798" t="n">
-        <v>31.8975505828857</v>
+        <v>31.8975524902344</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G799" t="n">
-        <v>31.8975505828857</v>
+        <v>31.8975524902344</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G800" t="n">
-        <v>31.8975505828857</v>
+        <v>31.8975524902344</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>35.1500015258789</v>
       </c>
       <c r="G802" t="n">
-        <v>33.1715698242188</v>
+        <v>33.1715660095215</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>33.8499984741211</v>
       </c>
       <c r="G803" t="n">
-        <v>31.9447345733643</v>
+        <v>31.9447326660156</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>33.8499984741211</v>
       </c>
       <c r="G804" t="n">
-        <v>31.9447345733643</v>
+        <v>31.9447326660156</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>34.25</v>
       </c>
       <c r="G805" t="n">
-        <v>32.3222274780273</v>
+        <v>32.3222236633301</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>35.0499992370605</v>
       </c>
       <c r="G806" t="n">
-        <v>33.0771903991699</v>
+        <v>33.0771980285645</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>35.1500015258789</v>
       </c>
       <c r="G807" t="n">
-        <v>33.1715698242188</v>
+        <v>33.1715660095215</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>34.9000015258789</v>
       </c>
       <c r="G809" t="n">
-        <v>32.9356422424316</v>
+        <v>32.9356384277344</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>34.7999992370605</v>
       </c>
       <c r="G810" t="n">
-        <v>32.8412704467773</v>
+        <v>32.8412666320801</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>34.2999992370605</v>
       </c>
       <c r="G811" t="n">
-        <v>32.3694076538086</v>
+        <v>32.3694114685059</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>34.7999992370605</v>
       </c>
       <c r="G812" t="n">
-        <v>32.8412704467773</v>
+        <v>32.8412666320801</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>34.7000007629395</v>
       </c>
       <c r="G813" t="n">
-        <v>32.7468948364258</v>
+        <v>32.746898651123</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>35.1500015258789</v>
       </c>
       <c r="G815" t="n">
-        <v>33.1715698242188</v>
+        <v>33.1715660095215</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>31.4500007629395</v>
       </c>
       <c r="G817" t="n">
-        <v>29.6798229217529</v>
+        <v>29.6798248291016</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G821" t="n">
-        <v>29.6326389312744</v>
+        <v>29.6326370239258</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>31.25</v>
       </c>
       <c r="G822" t="n">
-        <v>29.4910831451416</v>
+        <v>29.4910793304443</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>30.9500007629395</v>
       </c>
       <c r="G823" t="n">
-        <v>29.2079677581787</v>
+        <v>29.2079658508301</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>31.3199996948242</v>
       </c>
       <c r="G827" t="n">
-        <v>29.5571403503418</v>
+        <v>29.5571384429932</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>31.7000007629395</v>
       </c>
       <c r="G828" t="n">
-        <v>29.9157543182373</v>
+        <v>29.9157524108887</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>32.060001373291</v>
       </c>
       <c r="G829" t="n">
-        <v>30.2554874420166</v>
+        <v>30.2554893493652</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>32.2400016784668</v>
       </c>
       <c r="G830" t="n">
-        <v>30.4253597259521</v>
+        <v>30.4253616333008</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G831" t="n">
-        <v>30.5763530731201</v>
+        <v>30.5763549804688</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>31.6200008392334</v>
       </c>
       <c r="G838" t="n">
-        <v>29.8402576446533</v>
+        <v>29.8402557373047</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G840" t="n">
-        <v>29.4438934326172</v>
+        <v>29.4438972473145</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>32.060001373291</v>
       </c>
       <c r="G842" t="n">
-        <v>30.2554874420166</v>
+        <v>30.2554893493652</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>31.1200008392334</v>
       </c>
       <c r="G847" t="n">
-        <v>29.3683986663818</v>
+        <v>29.3684005737305</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>31.7000007629395</v>
       </c>
       <c r="G850" t="n">
-        <v>29.9157543182373</v>
+        <v>29.9157524108887</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>31.0799999237061</v>
       </c>
       <c r="G851" t="n">
-        <v>29.3306503295898</v>
+        <v>29.3306484222412</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>30.1399993896484</v>
       </c>
       <c r="G852" t="n">
-        <v>28.4435577392578</v>
+        <v>28.4435558319092</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G854" t="n">
-        <v>28.1226940155029</v>
+        <v>28.1226921081543</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>30.0400009155273</v>
       </c>
       <c r="G855" t="n">
-        <v>28.3491859436035</v>
+        <v>28.3491878509521</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>29.6800003051758</v>
       </c>
       <c r="G861" t="n">
-        <v>28.2860412597656</v>
+        <v>28.286039352417</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>29.3799991607666</v>
       </c>
       <c r="G863" t="n">
-        <v>28.000129699707</v>
+        <v>28.0001316070557</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>29.5400009155273</v>
       </c>
       <c r="G864" t="n">
-        <v>28.1526184082031</v>
+        <v>28.1526165008545</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G871" t="n">
-        <v>26.9708518981934</v>
+        <v>26.970853805542</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>29</v>
       </c>
       <c r="G881" t="n">
-        <v>27.6379776000977</v>
+        <v>27.637975692749</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>29.5200004577637</v>
       </c>
       <c r="G882" t="n">
-        <v>28.1335544586182</v>
+        <v>28.1335563659668</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>29.3400001525879</v>
       </c>
       <c r="G884" t="n">
-        <v>27.962007522583</v>
+        <v>27.9620094299316</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G887" t="n">
-        <v>27.7332801818848</v>
+        <v>27.7332820892334</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>29.6599998474121</v>
       </c>
       <c r="G888" t="n">
-        <v>28.2669792175293</v>
+        <v>28.2669773101807</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G892" t="n">
-        <v>29.4487419128418</v>
+        <v>29.4487400054932</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>30.9200000762939</v>
       </c>
       <c r="G894" t="n">
-        <v>29.4678001403809</v>
+        <v>29.4678020477295</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>31.7800006866455</v>
       </c>
       <c r="G898" t="n">
-        <v>30.2874126434326</v>
+        <v>30.287410736084</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>30.4200000762939</v>
       </c>
       <c r="G899" t="n">
-        <v>28.991283416748</v>
+        <v>28.9912853240967</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>30.5400009155273</v>
       </c>
       <c r="G900" t="n">
-        <v>29.1056499481201</v>
+        <v>29.1056518554688</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>30.4799995422363</v>
       </c>
       <c r="G902" t="n">
-        <v>29.0484676361084</v>
+        <v>29.0484657287598</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G903" t="n">
-        <v>28.8769207000732</v>
+        <v>28.8769226074219</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>30.0599994659424</v>
       </c>
       <c r="G905" t="n">
-        <v>28.648193359375</v>
+        <v>28.6481914520264</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>29.7199993133545</v>
       </c>
       <c r="G908" t="n">
-        <v>28.324161529541</v>
+        <v>28.3241634368896</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>29.5</v>
       </c>
       <c r="G909" t="n">
-        <v>28.1144943237305</v>
+        <v>28.1144962310791</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>28.2399997711182</v>
       </c>
       <c r="G932" t="n">
-        <v>26.9136714935303</v>
+        <v>26.9136695861816</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>28</v>
       </c>
       <c r="G933" t="n">
-        <v>26.684944152832</v>
+        <v>26.6849422454834</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>27.5799999237061</v>
       </c>
       <c r="G934" t="n">
-        <v>26.2846698760986</v>
+        <v>26.28466796875</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>29.0400009155273</v>
       </c>
       <c r="G939" t="n">
-        <v>27.6760997772217</v>
+        <v>27.676097869873</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>29</v>
       </c>
       <c r="G941" t="n">
-        <v>27.6379776000977</v>
+        <v>27.637975692749</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G942" t="n">
-        <v>27.7332801818848</v>
+        <v>27.7332820892334</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>28.0599994659424</v>
       </c>
       <c r="G944" t="n">
-        <v>26.7421245574951</v>
+        <v>26.7421264648438</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>27.9599990844727</v>
       </c>
       <c r="G947" t="n">
-        <v>26.646821975708</v>
+        <v>26.6468200683594</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>27.9599990844727</v>
       </c>
       <c r="G948" t="n">
-        <v>26.646821975708</v>
+        <v>26.6468200683594</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>28.4599990844727</v>
       </c>
       <c r="G950" t="n">
-        <v>27.1233386993408</v>
+        <v>27.1233367919922</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>28.6800003051758</v>
       </c>
       <c r="G956" t="n">
-        <v>27.3330059051514</v>
+        <v>27.3330078125</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>28</v>
       </c>
       <c r="G957" t="n">
-        <v>26.684944152832</v>
+        <v>26.6849422454834</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>26.8600006103516</v>
       </c>
       <c r="G960" t="n">
-        <v>25.5984840393066</v>
+        <v>25.5984859466553</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>26.7800006866455</v>
       </c>
       <c r="G961" t="n">
-        <v>25.5222454071045</v>
+        <v>25.5222434997559</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G962" t="n">
-        <v>25.5413017272949</v>
+        <v>25.5412998199463</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>26.7800006866455</v>
       </c>
       <c r="G963" t="n">
-        <v>25.5222454071045</v>
+        <v>25.5222434997559</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>27.8199996948242</v>
       </c>
       <c r="G968" t="n">
-        <v>26.5133972167969</v>
+        <v>26.5133953094482</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>26.7199993133545</v>
       </c>
       <c r="G970" t="n">
-        <v>25.4650592803955</v>
+        <v>25.4650611877441</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>27.6599998474121</v>
       </c>
       <c r="G972" t="n">
-        <v>26.3609085083008</v>
+        <v>26.3609104156494</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>28.7399997711182</v>
       </c>
       <c r="G973" t="n">
-        <v>27.3901901245117</v>
+        <v>27.3901882171631</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>27.9599990844727</v>
       </c>
       <c r="G975" t="n">
-        <v>26.646821975708</v>
+        <v>26.6468200683594</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>28.7399997711182</v>
       </c>
       <c r="G979" t="n">
-        <v>27.3901901245117</v>
+        <v>27.3901882171631</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G982" t="n">
-        <v>28.0191917419434</v>
+        <v>28.0191898345947</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>30.0400009155273</v>
       </c>
       <c r="G990" t="n">
-        <v>28.6291313171387</v>
+        <v>28.6291332244873</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>33.6199989318848</v>
       </c>
       <c r="G997" t="n">
-        <v>32.0409927368164</v>
+        <v>32.0409889221191</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>32.3400001525879</v>
       </c>
       <c r="G999" t="n">
-        <v>30.8211078643799</v>
+        <v>30.8211097717285</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G1000" t="n">
-        <v>30.7829875946045</v>
+        <v>30.7829856872559</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G1001" t="n">
-        <v>31.2595043182373</v>
+        <v>31.2595062255859</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>32.3800010681152</v>
       </c>
       <c r="G1003" t="n">
-        <v>30.8592319488525</v>
+        <v>30.8592338562012</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>32.7200012207031</v>
       </c>
       <c r="G1004" t="n">
-        <v>31.1832656860352</v>
+        <v>31.1832637786865</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>32.3800010681152</v>
       </c>
       <c r="G1006" t="n">
-        <v>30.8592319488525</v>
+        <v>30.8592338562012</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>31.9599990844727</v>
       </c>
       <c r="G1010" t="n">
-        <v>30.4589538574219</v>
+        <v>30.4589557647705</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>32</v>
       </c>
       <c r="G1011" t="n">
-        <v>30.4970779418945</v>
+        <v>30.4970798492432</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>32.3400001525879</v>
       </c>
       <c r="G1016" t="n">
-        <v>30.8211078643799</v>
+        <v>30.8211097717285</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>34.560001373291</v>
       </c>
       <c r="G1020" t="n">
-        <v>32.9368476867676</v>
+        <v>32.9368515014648</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>36.1399993896484</v>
       </c>
       <c r="G1023" t="n">
-        <v>34.4426383972168</v>
+        <v>34.4426422119141</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>37.2599983215332</v>
       </c>
       <c r="G1025" t="n">
-        <v>35.5100364685059</v>
+        <v>35.5100326538086</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>38.5400009155273</v>
       </c>
       <c r="G1028" t="n">
-        <v>36.729923248291</v>
+        <v>36.7299194335938</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>34.4799995422363</v>
       </c>
       <c r="G1033" t="n">
-        <v>32.8606033325195</v>
+        <v>32.8605995178223</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>34.2200012207031</v>
       </c>
       <c r="G1034" t="n">
-        <v>32.6128120422363</v>
+        <v>32.6128158569336</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>33.1399993896484</v>
       </c>
       <c r="G1036" t="n">
-        <v>31.5835380554199</v>
+        <v>31.5835361480713</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>32.8199996948242</v>
       </c>
       <c r="G1037" t="n">
-        <v>31.2785682678223</v>
+        <v>31.2785663604736</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>33.5200004577637</v>
       </c>
       <c r="G1039" t="n">
-        <v>31.9456920623779</v>
+        <v>31.9456939697266</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>34.5800018310547</v>
       </c>
       <c r="G1040" t="n">
-        <v>32.9559059143066</v>
+        <v>32.9559097290039</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G1042" t="n">
-        <v>31.2595043182373</v>
+        <v>31.2595062255859</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>33.1399993896484</v>
       </c>
       <c r="G1044" t="n">
-        <v>31.5835380554199</v>
+        <v>31.5835361480713</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>33.6399993896484</v>
       </c>
       <c r="G1049" t="n">
-        <v>32.0600547790527</v>
+        <v>32.0600509643555</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>29.5400009155273</v>
       </c>
       <c r="G1056" t="n">
-        <v>28.1526184082031</v>
+        <v>28.1526165008545</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>30</v>
       </c>
       <c r="G1057" t="n">
-        <v>28.5910110473633</v>
+        <v>28.5910129547119</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>29.6800003051758</v>
       </c>
       <c r="G1061" t="n">
-        <v>28.2860412597656</v>
+        <v>28.286039352417</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>26.7800006866455</v>
       </c>
       <c r="G1065" t="n">
-        <v>25.5222454071045</v>
+        <v>25.5222434997559</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28397,7 +28397,7 @@
         <v>26</v>
       </c>
       <c r="G1078" t="n">
-        <v>24.7788772583008</v>
+        <v>24.7788753509521</v>
       </c>
       <c r="H1078" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>27.6800003051758</v>
       </c>
       <c r="G1079" t="n">
-        <v>26.3799724578857</v>
+        <v>26.3799743652344</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28449,7 +28449,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1080" t="n">
-        <v>26.4943351745605</v>
+        <v>26.4943370819092</v>
       </c>
       <c r="H1080" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>25.6800003051758</v>
       </c>
       <c r="G1082" t="n">
-        <v>24.4739036560059</v>
+        <v>24.4739055633545</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>24.6800003051758</v>
       </c>
       <c r="G1083" t="n">
-        <v>23.5208721160889</v>
+        <v>23.5208702087402</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G1087" t="n">
-        <v>24.5882682800293</v>
+        <v>24.5882663726807</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28709,7 +28709,7 @@
         <v>27.3400001525879</v>
       </c>
       <c r="G1090" t="n">
-        <v>26.0559425354004</v>
+        <v>26.0559406280518</v>
       </c>
       <c r="H1090" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>28.6200008392334</v>
       </c>
       <c r="G1093" t="n">
-        <v>27.2758274078369</v>
+        <v>27.2758255004883</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>28.7399997711182</v>
       </c>
       <c r="G1094" t="n">
-        <v>27.3901901245117</v>
+        <v>27.3901882171631</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G1096" t="n">
-        <v>27.7332801818848</v>
+        <v>27.7332820892334</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>29.3799991607666</v>
       </c>
       <c r="G1099" t="n">
-        <v>28.000129699707</v>
+        <v>28.0001316070557</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -28969,7 +28969,7 @@
         <v>27.6200008392334</v>
       </c>
       <c r="G1100" t="n">
-        <v>26.3227939605713</v>
+        <v>26.3227920532227</v>
       </c>
       <c r="H1100" t="s">
         <v>8</v>
@@ -29021,7 +29021,7 @@
         <v>27.6200008392334</v>
       </c>
       <c r="G1102" t="n">
-        <v>26.3227939605713</v>
+        <v>26.3227920532227</v>
       </c>
       <c r="H1102" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1106" t="n">
-        <v>25.5413017272949</v>
+        <v>25.5412998199463</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>26.5</v>
       </c>
       <c r="G1108" t="n">
-        <v>25.2553939819336</v>
+        <v>25.255392074585</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29203,7 +29203,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1109" t="n">
-        <v>25.5413017272949</v>
+        <v>25.5412998199463</v>
       </c>
       <c r="H1109" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>27.6200008392334</v>
       </c>
       <c r="G1110" t="n">
-        <v>26.3227939605713</v>
+        <v>26.3227920532227</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>27.9400005340576</v>
       </c>
       <c r="G1116" t="n">
-        <v>26.6277599334717</v>
+        <v>26.6277618408203</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>30.0599994659424</v>
       </c>
       <c r="G1122" t="n">
-        <v>28.648193359375</v>
+        <v>28.6481914520264</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29567,7 +29567,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1123" t="n">
-        <v>29.6393489837646</v>
+        <v>29.639347076416</v>
       </c>
       <c r="H1123" t="s">
         <v>8</v>
@@ -29619,7 +29619,7 @@
         <v>31.5</v>
       </c>
       <c r="G1125" t="n">
-        <v>30.0205631256104</v>
+        <v>30.0205612182617</v>
       </c>
       <c r="H1125" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>30.6599998474121</v>
       </c>
       <c r="G1127" t="n">
-        <v>29.2200126647949</v>
+        <v>29.2200107574463</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G1130" t="n">
-        <v>26.9708518981934</v>
+        <v>26.970853805542</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29801,7 +29801,7 @@
         <v>28.6200008392334</v>
       </c>
       <c r="G1132" t="n">
-        <v>27.2758274078369</v>
+        <v>27.2758255004883</v>
       </c>
       <c r="H1132" t="s">
         <v>8</v>
@@ -29931,7 +29931,7 @@
         <v>27.5200004577637</v>
       </c>
       <c r="G1137" t="n">
-        <v>26.2274875640869</v>
+        <v>26.2274894714355</v>
       </c>
       <c r="H1137" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>26.4200000762939</v>
       </c>
       <c r="G1138" t="n">
-        <v>25.1791496276855</v>
+        <v>25.1791477203369</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -29983,7 +29983,7 @@
         <v>26.4200000762939</v>
       </c>
       <c r="G1139" t="n">
-        <v>25.1791496276855</v>
+        <v>25.1791477203369</v>
       </c>
       <c r="H1139" t="s">
         <v>8</v>
@@ -30035,7 +30035,7 @@
         <v>26.4400005340576</v>
       </c>
       <c r="G1141" t="n">
-        <v>25.1982097625732</v>
+        <v>25.1982116699219</v>
       </c>
       <c r="H1141" t="s">
         <v>8</v>
@@ -30269,7 +30269,7 @@
         <v>25.7199993133545</v>
       </c>
       <c r="G1150" t="n">
-        <v>24.5120277404785</v>
+        <v>24.5120258331299</v>
       </c>
       <c r="H1150" t="s">
         <v>8</v>
@@ -30425,7 +30425,7 @@
         <v>25.0200004577637</v>
       </c>
       <c r="G1156" t="n">
-        <v>23.8449039459229</v>
+        <v>23.8449058532715</v>
       </c>
       <c r="H1156" t="s">
         <v>8</v>
@@ -30451,7 +30451,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G1157" t="n">
-        <v>23.7305393218994</v>
+        <v>23.730541229248</v>
       </c>
       <c r="H1157" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>23.9799995422363</v>
       </c>
       <c r="G1159" t="n">
-        <v>22.8537483215332</v>
+        <v>22.8537502288818</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30581,7 +30581,7 @@
         <v>24.6200008392334</v>
       </c>
       <c r="G1162" t="n">
-        <v>23.4636898040771</v>
+        <v>23.4636917114258</v>
       </c>
       <c r="H1162" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>25.1399993896484</v>
       </c>
       <c r="G1165" t="n">
-        <v>23.9592685699463</v>
+        <v>23.9592666625977</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30737,7 +30737,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G1168" t="n">
-        <v>24.5882682800293</v>
+        <v>24.5882663726807</v>
       </c>
       <c r="H1168" t="s">
         <v>8</v>
@@ -30971,7 +30971,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G1177" t="n">
-        <v>24.5882682800293</v>
+        <v>24.5882663726807</v>
       </c>
       <c r="H1177" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>26</v>
       </c>
       <c r="G1182" t="n">
-        <v>24.7788772583008</v>
+        <v>24.7788753509521</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31127,7 +31127,7 @@
         <v>26.0200004577637</v>
       </c>
       <c r="G1183" t="n">
-        <v>24.7979373931885</v>
+        <v>24.7979393005371</v>
       </c>
       <c r="H1183" t="s">
         <v>8</v>
@@ -31179,7 +31179,7 @@
         <v>26.4400005340576</v>
       </c>
       <c r="G1185" t="n">
-        <v>25.1982097625732</v>
+        <v>25.1982116699219</v>
       </c>
       <c r="H1185" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>25.7199993133545</v>
       </c>
       <c r="G1189" t="n">
-        <v>24.5120277404785</v>
+        <v>24.5120258331299</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>25.8199996948242</v>
       </c>
       <c r="G1195" t="n">
-        <v>24.6073303222656</v>
+        <v>24.6073322296143</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>27.1599998474121</v>
       </c>
       <c r="G1199" t="n">
-        <v>25.8843955993652</v>
+        <v>25.8843936920166</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31569,7 +31569,7 @@
         <v>26.0200004577637</v>
       </c>
       <c r="G1200" t="n">
-        <v>24.7979373931885</v>
+        <v>24.7979393005371</v>
       </c>
       <c r="H1200" t="s">
         <v>8</v>
@@ -31673,7 +31673,7 @@
         <v>25.3400001525879</v>
       </c>
       <c r="G1204" t="n">
-        <v>24.1498737335205</v>
+        <v>24.1498718261719</v>
       </c>
       <c r="H1204" t="s">
         <v>8</v>
@@ -31803,7 +31803,7 @@
         <v>26.2199993133545</v>
       </c>
       <c r="G1209" t="n">
-        <v>24.9885425567627</v>
+        <v>24.9885444641113</v>
       </c>
       <c r="H1209" t="s">
         <v>8</v>
@@ -31829,7 +31829,7 @@
         <v>27.2399997711182</v>
       </c>
       <c r="G1210" t="n">
-        <v>25.960636138916</v>
+        <v>25.9606380462646</v>
       </c>
       <c r="H1210" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>27.6800003051758</v>
       </c>
       <c r="G1214" t="n">
-        <v>26.3799724578857</v>
+        <v>26.3799743652344</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -32011,7 +32011,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1217" t="n">
-        <v>26.4943351745605</v>
+        <v>26.4943370819092</v>
       </c>
       <c r="H1217" t="s">
         <v>8</v>
@@ -32089,7 +32089,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1220" t="n">
-        <v>25.9225177764893</v>
+        <v>25.9225158691406</v>
       </c>
       <c r="H1220" t="s">
         <v>8</v>
@@ -32115,7 +32115,7 @@
         <v>27.3400001525879</v>
       </c>
       <c r="G1221" t="n">
-        <v>26.0559425354004</v>
+        <v>26.0559406280518</v>
       </c>
       <c r="H1221" t="s">
         <v>8</v>
@@ -32141,7 +32141,7 @@
         <v>27.1399993896484</v>
       </c>
       <c r="G1222" t="n">
-        <v>25.8653335571289</v>
+        <v>25.8653354644775</v>
       </c>
       <c r="H1222" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1223" t="n">
-        <v>25.9225177764893</v>
+        <v>25.9225158691406</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32219,7 +32219,7 @@
         <v>26.7600002288818</v>
       </c>
       <c r="G1225" t="n">
-        <v>25.5031814575195</v>
+        <v>25.5031833648682</v>
       </c>
       <c r="H1225" t="s">
         <v>8</v>
@@ -32245,7 +32245,7 @@
         <v>26.6800003051758</v>
       </c>
       <c r="G1226" t="n">
-        <v>25.4269371032715</v>
+        <v>25.4269390106201</v>
       </c>
       <c r="H1226" t="s">
         <v>8</v>
@@ -32271,7 +32271,7 @@
         <v>26.3799991607666</v>
       </c>
       <c r="G1227" t="n">
-        <v>25.1410293579102</v>
+        <v>25.1410274505615</v>
       </c>
       <c r="H1227" t="s">
         <v>8</v>
@@ -32297,7 +32297,7 @@
         <v>25.4400005340576</v>
       </c>
       <c r="G1228" t="n">
-        <v>24.2451763153076</v>
+        <v>24.2451782226562</v>
       </c>
       <c r="H1228" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>25.7600002288818</v>
       </c>
       <c r="G1229" t="n">
-        <v>24.5501499176025</v>
+        <v>24.5501480102539</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32375,7 +32375,7 @@
         <v>26.4400005340576</v>
       </c>
       <c r="G1231" t="n">
-        <v>25.1982097625732</v>
+        <v>25.1982116699219</v>
       </c>
       <c r="H1231" t="s">
         <v>8</v>
@@ -32401,7 +32401,7 @@
         <v>26.7600002288818</v>
       </c>
       <c r="G1232" t="n">
-        <v>25.5031814575195</v>
+        <v>25.5031833648682</v>
       </c>
       <c r="H1232" t="s">
         <v>8</v>
@@ -32427,7 +32427,7 @@
         <v>27.2399997711182</v>
       </c>
       <c r="G1233" t="n">
-        <v>25.960636138916</v>
+        <v>25.9606380462646</v>
       </c>
       <c r="H1233" t="s">
         <v>8</v>
@@ -32453,7 +32453,7 @@
         <v>27.1399993896484</v>
       </c>
       <c r="G1234" t="n">
-        <v>25.8653335571289</v>
+        <v>25.8653354644775</v>
       </c>
       <c r="H1234" t="s">
         <v>8</v>
@@ -32479,7 +32479,7 @@
         <v>27.6800003051758</v>
       </c>
       <c r="G1235" t="n">
-        <v>26.3799724578857</v>
+        <v>26.3799743652344</v>
       </c>
       <c r="H1235" t="s">
         <v>8</v>
@@ -32505,7 +32505,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G1236" t="n">
-        <v>26.9708518981934</v>
+        <v>26.970853805542</v>
       </c>
       <c r="H1236" t="s">
         <v>8</v>
@@ -32557,7 +32557,7 @@
         <v>27.9599990844727</v>
       </c>
       <c r="G1238" t="n">
-        <v>26.646821975708</v>
+        <v>26.6468200683594</v>
       </c>
       <c r="H1238" t="s">
         <v>8</v>
@@ -32635,7 +32635,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G1241" t="n">
-        <v>29.4487419128418</v>
+        <v>29.4487400054932</v>
       </c>
       <c r="H1241" t="s">
         <v>8</v>
@@ -32739,7 +32739,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1245" t="n">
-        <v>31.7360229492188</v>
+        <v>31.7360248565674</v>
       </c>
       <c r="H1245" t="s">
         <v>8</v>
@@ -32765,7 +32765,7 @@
         <v>33.3600006103516</v>
       </c>
       <c r="G1246" t="n">
-        <v>31.7932052612305</v>
+        <v>31.7932033538818</v>
       </c>
       <c r="H1246" t="s">
         <v>8</v>
@@ -32843,7 +32843,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G1249" t="n">
-        <v>31.5454158782959</v>
+        <v>31.5454139709473</v>
       </c>
       <c r="H1249" t="s">
         <v>8</v>
@@ -32895,7 +32895,7 @@
         <v>33.5400009155273</v>
       </c>
       <c r="G1251" t="n">
-        <v>31.964750289917</v>
+        <v>31.9647483825684</v>
       </c>
       <c r="H1251" t="s">
         <v>8</v>
@@ -32921,7 +32921,7 @@
         <v>34.4599990844727</v>
       </c>
       <c r="G1252" t="n">
-        <v>32.8415451049805</v>
+        <v>32.8415412902832</v>
       </c>
       <c r="H1252" t="s">
         <v>8</v>
@@ -33051,7 +33051,7 @@
         <v>36.439998626709</v>
       </c>
       <c r="G1257" t="n">
-        <v>34.7285499572754</v>
+        <v>34.7285461425781</v>
       </c>
       <c r="H1257" t="s">
         <v>8</v>
@@ -33129,7 +33129,7 @@
         <v>35.8199996948242</v>
       </c>
       <c r="G1260" t="n">
-        <v>34.1376609802246</v>
+        <v>34.1376647949219</v>
       </c>
       <c r="H1260" t="s">
         <v>8</v>
@@ -33155,7 +33155,7 @@
         <v>36.5400009155273</v>
       </c>
       <c r="G1261" t="n">
-        <v>34.8238525390625</v>
+        <v>34.8238563537598</v>
       </c>
       <c r="H1261" t="s">
         <v>8</v>
@@ -33181,7 +33181,7 @@
         <v>36.3800010681152</v>
       </c>
       <c r="G1262" t="n">
-        <v>34.6713638305664</v>
+        <v>34.6713676452637</v>
       </c>
       <c r="H1262" t="s">
         <v>8</v>
@@ -33233,7 +33233,7 @@
         <v>36.1199989318848</v>
       </c>
       <c r="G1264" t="n">
-        <v>34.4235725402832</v>
+        <v>34.4235763549805</v>
       </c>
       <c r="H1264" t="s">
         <v>8</v>
@@ -33337,7 +33337,7 @@
         <v>36.4799995422363</v>
       </c>
       <c r="G1268" t="n">
-        <v>34.7666702270508</v>
+        <v>34.7666664123535</v>
       </c>
       <c r="H1268" t="s">
         <v>8</v>
@@ -33389,7 +33389,7 @@
         <v>35.7000007629395</v>
       </c>
       <c r="G1270" t="n">
-        <v>34.0233039855957</v>
+        <v>34.0233001708984</v>
       </c>
       <c r="H1270" t="s">
         <v>8</v>
@@ -33415,7 +33415,7 @@
         <v>35.8400001525879</v>
       </c>
       <c r="G1271" t="n">
-        <v>34.1567268371582</v>
+        <v>34.1567306518555</v>
       </c>
       <c r="H1271" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>34.5800018310547</v>
       </c>
       <c r="G1272" t="n">
-        <v>32.9559059143066</v>
+        <v>32.9559097290039</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33623,7 +33623,7 @@
         <v>34.8600006103516</v>
       </c>
       <c r="G1279" t="n">
-        <v>33.2227554321289</v>
+        <v>33.2227516174316</v>
       </c>
       <c r="H1279" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>34.5</v>
       </c>
       <c r="G1282" t="n">
-        <v>32.8796577453613</v>
+        <v>32.8796615600586</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33753,7 +33753,7 @@
         <v>34.8400001525879</v>
       </c>
       <c r="G1284" t="n">
-        <v>33.2036895751953</v>
+        <v>33.2036933898926</v>
       </c>
       <c r="H1284" t="s">
         <v>8</v>
@@ -33805,7 +33805,7 @@
         <v>33.5400009155273</v>
       </c>
       <c r="G1286" t="n">
-        <v>31.964750289917</v>
+        <v>31.9647483825684</v>
       </c>
       <c r="H1286" t="s">
         <v>8</v>
@@ -33831,7 +33831,7 @@
         <v>34.1399993896484</v>
       </c>
       <c r="G1287" t="n">
-        <v>32.5365715026855</v>
+        <v>32.5365753173828</v>
       </c>
       <c r="H1287" t="s">
         <v>8</v>
@@ -33909,7 +33909,7 @@
         <v>33.0400009155273</v>
       </c>
       <c r="G1290" t="n">
-        <v>31.4882335662842</v>
+        <v>31.4882354736328</v>
       </c>
       <c r="H1290" t="s">
         <v>8</v>
@@ -33961,7 +33961,7 @@
         <v>33.6199989318848</v>
       </c>
       <c r="G1292" t="n">
-        <v>32.0409927368164</v>
+        <v>32.0409889221191</v>
       </c>
       <c r="H1292" t="s">
         <v>8</v>
@@ -33987,7 +33987,7 @@
         <v>33.5200004577637</v>
       </c>
       <c r="G1293" t="n">
-        <v>31.9456920623779</v>
+        <v>31.9456939697266</v>
       </c>
       <c r="H1293" t="s">
         <v>8</v>
@@ -34065,7 +34065,7 @@
         <v>34.4000015258789</v>
       </c>
       <c r="G1296" t="n">
-        <v>32.7843627929688</v>
+        <v>32.7843589782715</v>
       </c>
       <c r="H1296" t="s">
         <v>8</v>
@@ -34169,7 +34169,7 @@
         <v>35.1800003051758</v>
       </c>
       <c r="G1300" t="n">
-        <v>33.5277290344238</v>
+        <v>33.5277252197266</v>
       </c>
       <c r="H1300" t="s">
         <v>8</v>
@@ -34273,7 +34273,7 @@
         <v>34.1399993896484</v>
       </c>
       <c r="G1304" t="n">
-        <v>32.5365715026855</v>
+        <v>32.5365753173828</v>
       </c>
       <c r="H1304" t="s">
         <v>8</v>
@@ -34377,7 +34377,7 @@
         <v>34.4000015258789</v>
       </c>
       <c r="G1308" t="n">
-        <v>32.7843627929688</v>
+        <v>32.7843589782715</v>
       </c>
       <c r="H1308" t="s">
         <v>8</v>
@@ -34403,7 +34403,7 @@
         <v>34.4000015258789</v>
       </c>
       <c r="G1309" t="n">
-        <v>32.7843627929688</v>
+        <v>32.7843589782715</v>
       </c>
       <c r="H1309" t="s">
         <v>8</v>
@@ -34481,7 +34481,7 @@
         <v>34.8600006103516</v>
       </c>
       <c r="G1312" t="n">
-        <v>33.2227554321289</v>
+        <v>33.2227516174316</v>
       </c>
       <c r="H1312" t="s">
         <v>8</v>
@@ -34533,7 +34533,7 @@
         <v>34.060001373291</v>
       </c>
       <c r="G1314" t="n">
-        <v>32.4603309631348</v>
+        <v>32.4603271484375</v>
       </c>
       <c r="H1314" t="s">
         <v>8</v>
@@ -34559,7 +34559,7 @@
         <v>33.3600006103516</v>
       </c>
       <c r="G1315" t="n">
-        <v>31.7932052612305</v>
+        <v>31.7932033538818</v>
       </c>
       <c r="H1315" t="s">
         <v>8</v>
@@ -34637,7 +34637,7 @@
         <v>34.8400001525879</v>
       </c>
       <c r="G1318" t="n">
-        <v>33.2036895751953</v>
+        <v>33.2036933898926</v>
       </c>
       <c r="H1318" t="s">
         <v>8</v>
@@ -34689,7 +34689,7 @@
         <v>38.8800010681152</v>
       </c>
       <c r="G1320" t="n">
-        <v>37.053955078125</v>
+        <v>37.0539512634277</v>
       </c>
       <c r="H1320" t="s">
         <v>8</v>
@@ -35027,7 +35027,7 @@
         <v>36.6599998474121</v>
       </c>
       <c r="G1333" t="n">
-        <v>34.9382133483887</v>
+        <v>34.9382171630859</v>
       </c>
       <c r="H1333" t="s">
         <v>8</v>
@@ -35079,7 +35079,7 @@
         <v>39</v>
       </c>
       <c r="G1335" t="n">
-        <v>37.1683158874512</v>
+        <v>37.1683197021484</v>
       </c>
       <c r="H1335" t="s">
         <v>8</v>
@@ -35157,7 +35157,7 @@
         <v>38.8600006103516</v>
       </c>
       <c r="G1338" t="n">
-        <v>37.0348930358887</v>
+        <v>37.0348892211914</v>
       </c>
       <c r="H1338" t="s">
         <v>8</v>
@@ -35209,7 +35209,7 @@
         <v>40.2400016784668</v>
       </c>
       <c r="G1340" t="n">
-        <v>38.3500747680664</v>
+        <v>38.3500785827637</v>
       </c>
       <c r="H1340" t="s">
         <v>8</v>
@@ -35235,7 +35235,7 @@
         <v>40.9799995422363</v>
       </c>
       <c r="G1341" t="n">
-        <v>39.0553207397461</v>
+        <v>39.0553169250488</v>
       </c>
       <c r="H1341" t="s">
         <v>8</v>
@@ -35339,7 +35339,7 @@
         <v>40.6199989318848</v>
       </c>
       <c r="G1345" t="n">
-        <v>38.712230682373</v>
+        <v>38.7122344970703</v>
       </c>
       <c r="H1345" t="s">
         <v>8</v>
@@ -35469,7 +35469,7 @@
         <v>43.4599990844727</v>
       </c>
       <c r="G1350" t="n">
-        <v>41.4188385009766</v>
+        <v>41.4188423156738</v>
       </c>
       <c r="H1350" t="s">
         <v>8</v>
@@ -35703,7 +35703,7 @@
         <v>44</v>
       </c>
       <c r="G1359" t="n">
-        <v>41.9334831237793</v>
+        <v>41.9334869384766</v>
       </c>
       <c r="H1359" t="s">
         <v>8</v>
@@ -35807,7 +35807,7 @@
         <v>43.8400001525879</v>
       </c>
       <c r="G1363" t="n">
-        <v>41.7809982299805</v>
+        <v>41.7809944152832</v>
       </c>
       <c r="H1363" t="s">
         <v>8</v>
@@ -35859,7 +35859,7 @@
         <v>44.2000007629395</v>
       </c>
       <c r="G1365" t="n">
-        <v>42.1240921020508</v>
+        <v>42.1240882873535</v>
       </c>
       <c r="H1365" t="s">
         <v>8</v>
@@ -35911,7 +35911,7 @@
         <v>45.4599990844727</v>
       </c>
       <c r="G1367" t="n">
-        <v>43.3249092102051</v>
+        <v>43.3249053955078</v>
       </c>
       <c r="H1367" t="s">
         <v>8</v>
@@ -35963,7 +35963,7 @@
         <v>45.560001373291</v>
       </c>
       <c r="G1369" t="n">
-        <v>43.4202156066895</v>
+        <v>43.4202194213867</v>
       </c>
       <c r="H1369" t="s">
         <v>8</v>
@@ -36015,7 +36015,7 @@
         <v>45.4199981689453</v>
       </c>
       <c r="G1371" t="n">
-        <v>43.286792755127</v>
+        <v>43.2867889404297</v>
       </c>
       <c r="H1371" t="s">
         <v>8</v>
@@ -36197,7 +36197,7 @@
         <v>48.9599990844727</v>
       </c>
       <c r="G1378" t="n">
-        <v>46.660530090332</v>
+        <v>46.6605339050293</v>
       </c>
       <c r="H1378" t="s">
         <v>8</v>
@@ -36353,7 +36353,7 @@
         <v>47.7200012207031</v>
       </c>
       <c r="G1384" t="n">
-        <v>45.4787673950195</v>
+        <v>45.4787712097168</v>
       </c>
       <c r="H1384" t="s">
         <v>8</v>
@@ -36899,7 +36899,7 @@
         <v>51.4500007629395</v>
       </c>
       <c r="G1405" t="n">
-        <v>49.0335884094238</v>
+        <v>49.0335845947266</v>
       </c>
       <c r="H1405" t="s">
         <v>8</v>
@@ -36977,7 +36977,7 @@
         <v>49.6599998474121</v>
       </c>
       <c r="G1408" t="n">
-        <v>47.3276557922363</v>
+        <v>47.3276596069336</v>
       </c>
       <c r="H1408" t="s">
         <v>8</v>
@@ -37159,7 +37159,7 @@
         <v>51.4500007629395</v>
       </c>
       <c r="G1415" t="n">
-        <v>49.0335884094238</v>
+        <v>49.0335845947266</v>
       </c>
       <c r="H1415" t="s">
         <v>8</v>
@@ -37211,7 +37211,7 @@
         <v>52.0999984741211</v>
       </c>
       <c r="G1417" t="n">
-        <v>49.6530532836914</v>
+        <v>49.6530570983887</v>
       </c>
       <c r="H1417" t="s">
         <v>8</v>
@@ -37237,7 +37237,7 @@
         <v>52.2999992370605</v>
       </c>
       <c r="G1418" t="n">
-        <v>49.8436622619629</v>
+        <v>49.8436584472656</v>
       </c>
       <c r="H1418" t="s">
         <v>8</v>
@@ -37315,7 +37315,7 @@
         <v>54.2000007629395</v>
       </c>
       <c r="G1421" t="n">
-        <v>51.654426574707</v>
+        <v>51.6544303894043</v>
       </c>
       <c r="H1421" t="s">
         <v>8</v>
@@ -37341,7 +37341,7 @@
         <v>54.8499984741211</v>
       </c>
       <c r="G1422" t="n">
-        <v>52.2738952636719</v>
+        <v>52.2738914489746</v>
       </c>
       <c r="H1422" t="s">
         <v>8</v>
@@ -37367,7 +37367,7 @@
         <v>54.8499984741211</v>
       </c>
       <c r="G1423" t="n">
-        <v>52.2738952636719</v>
+        <v>52.2738914489746</v>
       </c>
       <c r="H1423" t="s">
         <v>8</v>
@@ -37419,7 +37419,7 @@
         <v>55.5999984741211</v>
       </c>
       <c r="G1425" t="n">
-        <v>52.9886703491211</v>
+        <v>52.9886741638184</v>
       </c>
       <c r="H1425" t="s">
         <v>8</v>
@@ -37471,7 +37471,7 @@
         <v>54.9000015258789</v>
       </c>
       <c r="G1427" t="n">
-        <v>52.3215522766113</v>
+        <v>52.3215560913086</v>
       </c>
       <c r="H1427" t="s">
         <v>8</v>
@@ -37783,7 +37783,7 @@
         <v>49.7999992370605</v>
       </c>
       <c r="G1439" t="n">
-        <v>47.4610786437988</v>
+        <v>47.4610824584961</v>
       </c>
       <c r="H1439" t="s">
         <v>8</v>
@@ -37809,7 +37809,7 @@
         <v>49.9000015258789</v>
       </c>
       <c r="G1440" t="n">
-        <v>47.5563888549805</v>
+        <v>47.5563850402832</v>
       </c>
       <c r="H1440" t="s">
         <v>8</v>
@@ -37965,7 +37965,7 @@
         <v>49.1399993896484</v>
       </c>
       <c r="G1446" t="n">
-        <v>46.8320770263672</v>
+        <v>46.8320732116699</v>
       </c>
       <c r="H1446" t="s">
         <v>8</v>
@@ -38121,7 +38121,7 @@
         <v>47.1599998474121</v>
       </c>
       <c r="G1452" t="n">
-        <v>44.945068359375</v>
+        <v>44.9450721740723</v>
       </c>
       <c r="H1452" t="s">
         <v>8</v>
@@ -38147,7 +38147,7 @@
         <v>47.9599990844727</v>
       </c>
       <c r="G1453" t="n">
-        <v>45.7074966430664</v>
+        <v>45.7075004577637</v>
       </c>
       <c r="H1453" t="s">
         <v>8</v>
@@ -38199,7 +38199,7 @@
         <v>48.4799995422363</v>
       </c>
       <c r="G1455" t="n">
-        <v>46.2030715942383</v>
+        <v>46.2030754089355</v>
       </c>
       <c r="H1455" t="s">
         <v>8</v>
@@ -38251,7 +38251,7 @@
         <v>49.7999992370605</v>
       </c>
       <c r="G1457" t="n">
-        <v>47.4610786437988</v>
+        <v>47.4610824584961</v>
       </c>
       <c r="H1457" t="s">
         <v>8</v>
@@ -38355,7 +38355,7 @@
         <v>47.5400009155273</v>
       </c>
       <c r="G1461" t="n">
-        <v>45.3072242736816</v>
+        <v>45.3072204589844</v>
       </c>
       <c r="H1461" t="s">
         <v>8</v>
@@ -38381,7 +38381,7 @@
         <v>47.5400009155273</v>
       </c>
       <c r="G1462" t="n">
-        <v>45.3072242736816</v>
+        <v>45.3072204589844</v>
       </c>
       <c r="H1462" t="s">
         <v>8</v>
@@ -38407,7 +38407,7 @@
         <v>47.8199996948242</v>
       </c>
       <c r="G1463" t="n">
-        <v>45.5740737915039</v>
+        <v>45.5740699768066</v>
       </c>
       <c r="H1463" t="s">
         <v>8</v>
@@ -38459,7 +38459,7 @@
         <v>47.560001373291</v>
       </c>
       <c r="G1465" t="n">
-        <v>45.3262825012207</v>
+        <v>45.326286315918</v>
       </c>
       <c r="H1465" t="s">
         <v>8</v>
@@ -38485,7 +38485,7 @@
         <v>46.939998626709</v>
       </c>
       <c r="G1466" t="n">
-        <v>44.7353973388672</v>
+        <v>44.7354011535645</v>
       </c>
       <c r="H1466" t="s">
         <v>8</v>
@@ -38511,7 +38511,7 @@
         <v>47.7200012207031</v>
       </c>
       <c r="G1467" t="n">
-        <v>45.4787673950195</v>
+        <v>45.4787712097168</v>
       </c>
       <c r="H1467" t="s">
         <v>8</v>
@@ -38537,7 +38537,7 @@
         <v>47.0400009155273</v>
       </c>
       <c r="G1468" t="n">
-        <v>44.8307075500488</v>
+        <v>44.8307037353516</v>
       </c>
       <c r="H1468" t="s">
         <v>8</v>
@@ -38563,7 +38563,7 @@
         <v>47.060001373291</v>
       </c>
       <c r="G1469" t="n">
-        <v>44.8497695922852</v>
+        <v>44.8497657775879</v>
       </c>
       <c r="H1469" t="s">
         <v>8</v>
@@ -38589,7 +38589,7 @@
         <v>47.7400016784668</v>
       </c>
       <c r="G1470" t="n">
-        <v>45.4978332519531</v>
+        <v>45.4978294372559</v>
       </c>
       <c r="H1470" t="s">
         <v>8</v>
@@ -38771,7 +38771,7 @@
         <v>50.75</v>
       </c>
       <c r="G1477" t="n">
-        <v>48.3664627075195</v>
+        <v>48.3664588928223</v>
       </c>
       <c r="H1477" t="s">
         <v>8</v>
@@ -38979,7 +38979,7 @@
         <v>53.5499992370605</v>
       </c>
       <c r="G1485" t="n">
-        <v>51.0349578857422</v>
+        <v>51.0349540710449</v>
       </c>
       <c r="H1485" t="s">
         <v>8</v>
@@ -39005,7 +39005,7 @@
         <v>54.9000015258789</v>
       </c>
       <c r="G1486" t="n">
-        <v>52.3215522766113</v>
+        <v>52.3215560913086</v>
       </c>
       <c r="H1486" t="s">
         <v>8</v>
@@ -39031,7 +39031,7 @@
         <v>58.2000007629395</v>
       </c>
       <c r="G1487" t="n">
-        <v>55.4665603637695</v>
+        <v>55.4665641784668</v>
       </c>
       <c r="H1487" t="s">
         <v>8</v>
@@ -39135,7 +39135,7 @@
         <v>61.8499984741211</v>
       </c>
       <c r="G1491" t="n">
-        <v>58.9451293945312</v>
+        <v>58.9451332092285</v>
       </c>
       <c r="H1491" t="s">
         <v>8</v>
@@ -39213,7 +39213,7 @@
         <v>62.7000007629395</v>
       </c>
       <c r="G1494" t="n">
-        <v>59.7552108764648</v>
+        <v>59.7552146911621</v>
       </c>
       <c r="H1494" t="s">
         <v>8</v>
@@ -39239,7 +39239,7 @@
         <v>62.4500007629395</v>
       </c>
       <c r="G1495" t="n">
-        <v>59.5169563293457</v>
+        <v>59.516960144043</v>
       </c>
       <c r="H1495" t="s">
         <v>8</v>
@@ -39265,7 +39265,7 @@
         <v>61.9000015258789</v>
       </c>
       <c r="G1496" t="n">
-        <v>58.9927864074707</v>
+        <v>58.992790222168</v>
       </c>
       <c r="H1496" t="s">
         <v>8</v>
@@ -39291,7 +39291,7 @@
         <v>61.8499984741211</v>
       </c>
       <c r="G1497" t="n">
-        <v>58.9451293945312</v>
+        <v>58.9451332092285</v>
       </c>
       <c r="H1497" t="s">
         <v>8</v>
@@ -39317,7 +39317,7 @@
         <v>60.0999984741211</v>
       </c>
       <c r="G1498" t="n">
-        <v>57.2773246765137</v>
+        <v>57.2773208618164</v>
       </c>
       <c r="H1498" t="s">
         <v>8</v>
@@ -39447,7 +39447,7 @@
         <v>55.3499984741211</v>
       </c>
       <c r="G1503" t="n">
-        <v>52.750415802002</v>
+        <v>52.7504196166992</v>
       </c>
       <c r="H1503" t="s">
         <v>8</v>
@@ -39837,7 +39837,7 @@
         <v>55.5999984741211</v>
       </c>
       <c r="G1518" t="n">
-        <v>52.9886703491211</v>
+        <v>52.9886741638184</v>
       </c>
       <c r="H1518" t="s">
         <v>8</v>
@@ -39863,7 +39863,7 @@
         <v>55.7000007629395</v>
       </c>
       <c r="G1519" t="n">
-        <v>53.0839805603027</v>
+        <v>53.0839767456055</v>
       </c>
       <c r="H1519" t="s">
         <v>8</v>
@@ -39967,7 +39967,7 @@
         <v>58.25</v>
       </c>
       <c r="G1523" t="n">
-        <v>55.5142059326172</v>
+        <v>55.5142097473145</v>
       </c>
       <c r="H1523" t="s">
         <v>8</v>
@@ -40019,7 +40019,7 @@
         <v>60.5999984741211</v>
       </c>
       <c r="G1525" t="n">
-        <v>57.7538414001465</v>
+        <v>57.7538452148438</v>
       </c>
       <c r="H1525" t="s">
         <v>8</v>
@@ -40071,7 +40071,7 @@
         <v>63.1500015258789</v>
       </c>
       <c r="G1527" t="n">
-        <v>60.1840782165527</v>
+        <v>60.18408203125</v>
       </c>
       <c r="H1527" t="s">
         <v>8</v>
@@ -40123,7 +40123,7 @@
         <v>63.5</v>
       </c>
       <c r="G1529" t="n">
-        <v>60.5176391601562</v>
+        <v>60.5176429748535</v>
       </c>
       <c r="H1529" t="s">
         <v>8</v>
@@ -40279,7 +40279,7 @@
         <v>56</v>
       </c>
       <c r="G1535" t="n">
-        <v>53.3698883056641</v>
+        <v>53.3698844909668</v>
       </c>
       <c r="H1535" t="s">
         <v>8</v>
@@ -40331,7 +40331,7 @@
         <v>55.5999984741211</v>
       </c>
       <c r="G1537" t="n">
-        <v>52.9886703491211</v>
+        <v>52.9886741638184</v>
       </c>
       <c r="H1537" t="s">
         <v>8</v>
@@ -40383,7 +40383,7 @@
         <v>55.0499992370605</v>
       </c>
       <c r="G1539" t="n">
-        <v>52.4645004272461</v>
+        <v>52.4645042419434</v>
       </c>
       <c r="H1539" t="s">
         <v>8</v>
@@ -40513,7 +40513,7 @@
         <v>53.75</v>
       </c>
       <c r="G1544" t="n">
-        <v>51.2255630493164</v>
+        <v>51.2255668640137</v>
       </c>
       <c r="H1544" t="s">
         <v>8</v>
@@ -40669,7 +40669,7 @@
         <v>52.2999992370605</v>
       </c>
       <c r="G1550" t="n">
-        <v>49.8436622619629</v>
+        <v>49.8436584472656</v>
       </c>
       <c r="H1550" t="s">
         <v>8</v>
@@ -40747,7 +40747,7 @@
         <v>52.9500007629395</v>
       </c>
       <c r="G1553" t="n">
-        <v>50.4631309509277</v>
+        <v>50.463134765625</v>
       </c>
       <c r="H1553" t="s">
         <v>8</v>
@@ -40799,7 +40799,7 @@
         <v>54.0499992370605</v>
       </c>
       <c r="G1555" t="n">
-        <v>51.5114707946777</v>
+        <v>51.5114669799805</v>
       </c>
       <c r="H1555" t="s">
         <v>8</v>
@@ -40929,7 +40929,7 @@
         <v>52.75</v>
       </c>
       <c r="G1560" t="n">
-        <v>50.2725296020508</v>
+        <v>50.2725257873535</v>
       </c>
       <c r="H1560" t="s">
         <v>8</v>
@@ -41007,7 +41007,7 @@
         <v>51.4500007629395</v>
       </c>
       <c r="G1563" t="n">
-        <v>49.0335884094238</v>
+        <v>49.0335845947266</v>
       </c>
       <c r="H1563" t="s">
         <v>8</v>
@@ -41059,7 +41059,7 @@
         <v>48.4799995422363</v>
       </c>
       <c r="G1565" t="n">
-        <v>46.2030715942383</v>
+        <v>46.2030754089355</v>
       </c>
       <c r="H1565" t="s">
         <v>8</v>
@@ -41189,7 +41189,7 @@
         <v>47.5200004577637</v>
       </c>
       <c r="G1570" t="n">
-        <v>45.2881622314453</v>
+        <v>45.288158416748</v>
       </c>
       <c r="H1570" t="s">
         <v>8</v>
@@ -41267,7 +41267,7 @@
         <v>41.939998626709</v>
       </c>
       <c r="G1573" t="n">
-        <v>39.9702339172363</v>
+        <v>39.9702377319336</v>
       </c>
       <c r="H1573" t="s">
         <v>8</v>
@@ -41345,7 +41345,7 @@
         <v>46.939998626709</v>
       </c>
       <c r="G1576" t="n">
-        <v>44.7353973388672</v>
+        <v>44.7354011535645</v>
       </c>
       <c r="H1576" t="s">
         <v>8</v>
@@ -41371,7 +41371,7 @@
         <v>47.1800003051758</v>
       </c>
       <c r="G1577" t="n">
-        <v>44.9641304016113</v>
+        <v>44.9641342163086</v>
       </c>
       <c r="H1577" t="s">
         <v>8</v>
@@ -41397,7 +41397,7 @@
         <v>48.5</v>
       </c>
       <c r="G1578" t="n">
-        <v>46.2221336364746</v>
+        <v>46.2221374511719</v>
       </c>
       <c r="H1578" t="s">
         <v>8</v>
@@ -41657,7 +41657,7 @@
         <v>54.0499992370605</v>
       </c>
       <c r="G1588" t="n">
-        <v>51.5114707946777</v>
+        <v>51.5114669799805</v>
       </c>
       <c r="H1588" t="s">
         <v>8</v>
@@ -41813,7 +41813,7 @@
         <v>51.3499984741211</v>
       </c>
       <c r="G1594" t="n">
-        <v>48.9382781982422</v>
+        <v>48.9382820129395</v>
       </c>
       <c r="H1594" t="s">
         <v>8</v>
@@ -41995,7 +41995,7 @@
         <v>50.75</v>
       </c>
       <c r="G1601" t="n">
-        <v>48.3664627075195</v>
+        <v>48.3664588928223</v>
       </c>
       <c r="H1601" t="s">
         <v>8</v>
@@ -42021,7 +42021,7 @@
         <v>52.0999984741211</v>
       </c>
       <c r="G1602" t="n">
-        <v>49.6530532836914</v>
+        <v>49.6530570983887</v>
       </c>
       <c r="H1602" t="s">
         <v>8</v>
@@ -42099,7 +42099,7 @@
         <v>48.3199996948242</v>
       </c>
       <c r="G1605" t="n">
-        <v>46.0505905151367</v>
+        <v>46.0505867004395</v>
       </c>
       <c r="H1605" t="s">
         <v>8</v>
@@ -42151,7 +42151,7 @@
         <v>47.1599998474121</v>
       </c>
       <c r="G1607" t="n">
-        <v>44.945068359375</v>
+        <v>44.9450721740723</v>
       </c>
       <c r="H1607" t="s">
         <v>8</v>
@@ -42177,7 +42177,7 @@
         <v>48.4799995422363</v>
       </c>
       <c r="G1608" t="n">
-        <v>46.2030715942383</v>
+        <v>46.2030754089355</v>
       </c>
       <c r="H1608" t="s">
         <v>8</v>
@@ -42203,7 +42203,7 @@
         <v>49.2599983215332</v>
       </c>
       <c r="G1609" t="n">
-        <v>46.9464340209961</v>
+        <v>46.9464378356934</v>
       </c>
       <c r="H1609" t="s">
         <v>8</v>
@@ -42385,7 +42385,7 @@
         <v>44.3400001525879</v>
       </c>
       <c r="G1616" t="n">
-        <v>42.2575187683105</v>
+        <v>42.2575149536133</v>
       </c>
       <c r="H1616" t="s">
         <v>8</v>
@@ -42489,7 +42489,7 @@
         <v>47.5400009155273</v>
       </c>
       <c r="G1620" t="n">
-        <v>45.3072242736816</v>
+        <v>45.3072204589844</v>
       </c>
       <c r="H1620" t="s">
         <v>8</v>
@@ -42541,7 +42541,7 @@
         <v>47.4799995422363</v>
       </c>
       <c r="G1622" t="n">
-        <v>45.2500457763672</v>
+        <v>45.2500419616699</v>
       </c>
       <c r="H1622" t="s">
         <v>8</v>
@@ -42775,7 +42775,7 @@
         <v>46.6199989318848</v>
       </c>
       <c r="G1631" t="n">
-        <v>44.8488349914551</v>
+        <v>44.8488311767578</v>
       </c>
       <c r="H1631" t="s">
         <v>8</v>
@@ -42801,7 +42801,7 @@
         <v>46.7200012207031</v>
       </c>
       <c r="G1632" t="n">
-        <v>44.9450340270996</v>
+        <v>44.9450378417969</v>
       </c>
       <c r="H1632" t="s">
         <v>8</v>
@@ -42879,7 +42879,7 @@
         <v>46.6199989318848</v>
       </c>
       <c r="G1635" t="n">
-        <v>44.8488349914551</v>
+        <v>44.8488311767578</v>
       </c>
       <c r="H1635" t="s">
         <v>8</v>
@@ -42983,7 +42983,7 @@
         <v>44.0800018310547</v>
       </c>
       <c r="G1639" t="n">
-        <v>42.4053344726562</v>
+        <v>42.405330657959</v>
       </c>
       <c r="H1639" t="s">
         <v>8</v>
@@ -43061,7 +43061,7 @@
         <v>41.3600006103516</v>
       </c>
       <c r="G1642" t="n">
-        <v>39.7886734008789</v>
+        <v>39.7886695861816</v>
       </c>
       <c r="H1642" t="s">
         <v>8</v>
@@ -43087,7 +43087,7 @@
         <v>40.1599998474121</v>
       </c>
       <c r="G1643" t="n">
-        <v>38.6342620849609</v>
+        <v>38.6342582702637</v>
       </c>
       <c r="H1643" t="s">
         <v>8</v>
@@ -43295,7 +43295,7 @@
         <v>43.9000015258789</v>
       </c>
       <c r="G1651" t="n">
-        <v>42.232177734375</v>
+        <v>42.2321739196777</v>
       </c>
       <c r="H1651" t="s">
         <v>8</v>
@@ -43399,7 +43399,7 @@
         <v>43.060001373291</v>
       </c>
       <c r="G1655" t="n">
-        <v>41.4240837097168</v>
+        <v>41.4240875244141</v>
       </c>
       <c r="H1655" t="s">
         <v>8</v>
@@ -43555,7 +43555,7 @@
         <v>46.7200012207031</v>
       </c>
       <c r="G1661" t="n">
-        <v>44.9450340270996</v>
+        <v>44.9450378417969</v>
       </c>
       <c r="H1661" t="s">
         <v>8</v>
@@ -43581,7 +43581,7 @@
         <v>47.439998626709</v>
       </c>
       <c r="G1662" t="n">
-        <v>45.6376838684082</v>
+        <v>45.6376800537109</v>
       </c>
       <c r="H1662" t="s">
         <v>8</v>
@@ -43711,7 +43711,7 @@
         <v>51.4500007629395</v>
       </c>
       <c r="G1667" t="n">
-        <v>49.4953346252441</v>
+        <v>49.4953384399414</v>
       </c>
       <c r="H1667" t="s">
         <v>8</v>
@@ -43737,7 +43737,7 @@
         <v>52.1500015258789</v>
       </c>
       <c r="G1668" t="n">
-        <v>50.1687393188477</v>
+        <v>50.1687431335449</v>
       </c>
       <c r="H1668" t="s">
         <v>8</v>
@@ -43789,7 +43789,7 @@
         <v>53.0999984741211</v>
       </c>
       <c r="G1670" t="n">
-        <v>51.082649230957</v>
+        <v>51.0826454162598</v>
       </c>
       <c r="H1670" t="s">
         <v>8</v>
@@ -43815,7 +43815,7 @@
         <v>52.25</v>
       </c>
       <c r="G1671" t="n">
-        <v>50.2649421691895</v>
+        <v>50.2649459838867</v>
       </c>
       <c r="H1671" t="s">
         <v>8</v>
@@ -43867,7 +43867,7 @@
         <v>54.9500007629395</v>
       </c>
       <c r="G1673" t="n">
-        <v>52.8623657226562</v>
+        <v>52.862361907959</v>
       </c>
       <c r="H1673" t="s">
         <v>8</v>
@@ -44153,7 +44153,7 @@
         <v>56.6500015258789</v>
       </c>
       <c r="G1684" t="n">
-        <v>54.4977798461914</v>
+        <v>54.4977836608887</v>
       </c>
       <c r="H1684" t="s">
         <v>8</v>
@@ -44257,7 +44257,7 @@
         <v>57</v>
       </c>
       <c r="G1688" t="n">
-        <v>54.8344802856445</v>
+        <v>54.8344841003418</v>
       </c>
       <c r="H1688" t="s">
         <v>8</v>
@@ -44439,7 +44439,7 @@
         <v>53.9000015258789</v>
       </c>
       <c r="G1695" t="n">
-        <v>51.8522605895996</v>
+        <v>51.8522567749023</v>
       </c>
       <c r="H1695" t="s">
         <v>8</v>
@@ -44465,7 +44465,7 @@
         <v>51.7999992370605</v>
       </c>
       <c r="G1696" t="n">
-        <v>49.8320388793945</v>
+        <v>49.8320426940918</v>
       </c>
       <c r="H1696" t="s">
         <v>8</v>
@@ -44517,7 +44517,7 @@
         <v>52.7000007629395</v>
       </c>
       <c r="G1698" t="n">
-        <v>50.6978492736816</v>
+        <v>50.6978454589844</v>
       </c>
       <c r="H1698" t="s">
         <v>8</v>
@@ -44595,7 +44595,7 @@
         <v>51.7999992370605</v>
       </c>
       <c r="G1701" t="n">
-        <v>49.8320388793945</v>
+        <v>49.8320426940918</v>
       </c>
       <c r="H1701" t="s">
         <v>8</v>
@@ -44621,7 +44621,7 @@
         <v>52.3499984741211</v>
       </c>
       <c r="G1702" t="n">
-        <v>50.3611450195312</v>
+        <v>50.361141204834</v>
       </c>
       <c r="H1702" t="s">
         <v>8</v>
@@ -44647,7 +44647,7 @@
         <v>52.8499984741211</v>
       </c>
       <c r="G1703" t="n">
-        <v>50.8421440124512</v>
+        <v>50.8421478271484</v>
       </c>
       <c r="H1703" t="s">
         <v>8</v>
@@ -44803,7 +44803,7 @@
         <v>51.4500007629395</v>
       </c>
       <c r="G1709" t="n">
-        <v>49.4953346252441</v>
+        <v>49.4953384399414</v>
       </c>
       <c r="H1709" t="s">
         <v>8</v>
@@ -44829,7 +44829,7 @@
         <v>51.7000007629395</v>
       </c>
       <c r="G1710" t="n">
-        <v>49.73583984375</v>
+        <v>49.7358360290527</v>
       </c>
       <c r="H1710" t="s">
         <v>8</v>
@@ -44855,7 +44855,7 @@
         <v>52.1500015258789</v>
       </c>
       <c r="G1711" t="n">
-        <v>50.1687393188477</v>
+        <v>50.1687431335449</v>
       </c>
       <c r="H1711" t="s">
         <v>8</v>
@@ -44881,7 +44881,7 @@
         <v>49.0999984741211</v>
       </c>
       <c r="G1712" t="n">
-        <v>47.2346153259277</v>
+        <v>47.2346115112305</v>
       </c>
       <c r="H1712" t="s">
         <v>8</v>
@@ -44985,7 +44985,7 @@
         <v>49.0999984741211</v>
       </c>
       <c r="G1716" t="n">
-        <v>47.2346153259277</v>
+        <v>47.2346115112305</v>
       </c>
       <c r="H1716" t="s">
         <v>8</v>
@@ -45037,7 +45037,7 @@
         <v>50.0499992370605</v>
       </c>
       <c r="G1718" t="n">
-        <v>48.1485176086426</v>
+        <v>48.1485214233398</v>
       </c>
       <c r="H1718" t="s">
         <v>8</v>
@@ -45063,7 +45063,7 @@
         <v>48.9799995422363</v>
       </c>
       <c r="G1719" t="n">
-        <v>47.1191711425781</v>
+        <v>47.1191749572754</v>
       </c>
       <c r="H1719" t="s">
         <v>8</v>
@@ -45089,7 +45089,7 @@
         <v>51.2999992370605</v>
       </c>
       <c r="G1720" t="n">
-        <v>49.3510360717773</v>
+        <v>49.3510322570801</v>
       </c>
       <c r="H1720" t="s">
         <v>8</v>
@@ -45141,7 +45141,7 @@
         <v>51.0499992370605</v>
       </c>
       <c r="G1722" t="n">
-        <v>49.1105270385742</v>
+        <v>49.1105308532715</v>
       </c>
       <c r="H1722" t="s">
         <v>8</v>
@@ -45245,7 +45245,7 @@
         <v>50.0499992370605</v>
       </c>
       <c r="G1726" t="n">
-        <v>48.1485176086426</v>
+        <v>48.1485214233398</v>
       </c>
       <c r="H1726" t="s">
         <v>8</v>
@@ -45271,7 +45271,7 @@
         <v>50.5999984741211</v>
       </c>
       <c r="G1727" t="n">
-        <v>48.6776237487793</v>
+        <v>48.6776275634766</v>
       </c>
       <c r="H1727" t="s">
         <v>8</v>
@@ -45297,7 +45297,7 @@
         <v>50.6500015258789</v>
       </c>
       <c r="G1728" t="n">
-        <v>48.7257308959961</v>
+        <v>48.7257347106934</v>
       </c>
       <c r="H1728" t="s">
         <v>8</v>
@@ -45349,7 +45349,7 @@
         <v>51.4500007629395</v>
       </c>
       <c r="G1730" t="n">
-        <v>49.4953346252441</v>
+        <v>49.4953384399414</v>
       </c>
       <c r="H1730" t="s">
         <v>8</v>
@@ -45453,7 +45453,7 @@
         <v>57</v>
       </c>
       <c r="G1734" t="n">
-        <v>54.8344802856445</v>
+        <v>54.8344841003418</v>
       </c>
       <c r="H1734" t="s">
         <v>8</v>
@@ -45505,7 +45505,7 @@
         <v>61.7999992370605</v>
       </c>
       <c r="G1736" t="n">
-        <v>59.4521217346191</v>
+        <v>59.4521255493164</v>
       </c>
       <c r="H1736" t="s">
         <v>8</v>
@@ -45531,7 +45531,7 @@
         <v>60.0499992370605</v>
       </c>
       <c r="G1737" t="n">
-        <v>57.7686042785645</v>
+        <v>57.7686080932617</v>
       </c>
       <c r="H1737" t="s">
         <v>8</v>
@@ -45609,7 +45609,7 @@
         <v>58.8499984741211</v>
       </c>
       <c r="G1740" t="n">
-        <v>56.6141929626465</v>
+        <v>56.6141967773438</v>
       </c>
       <c r="H1740" t="s">
         <v>8</v>
@@ -45661,7 +45661,7 @@
         <v>56.5999984741211</v>
       </c>
       <c r="G1742" t="n">
-        <v>54.4496765136719</v>
+        <v>54.4496803283691</v>
       </c>
       <c r="H1742" t="s">
         <v>8</v>
@@ -45713,7 +45713,7 @@
         <v>57</v>
       </c>
       <c r="G1744" t="n">
-        <v>54.8344802856445</v>
+        <v>54.8344841003418</v>
       </c>
       <c r="H1744" t="s">
         <v>8</v>
@@ -45999,7 +45999,7 @@
         <v>60.7999992370605</v>
       </c>
       <c r="G1755" t="n">
-        <v>58.4901123046875</v>
+        <v>58.4901161193848</v>
       </c>
       <c r="H1755" t="s">
         <v>8</v>
@@ -46337,7 +46337,7 @@
         <v>69.25</v>
       </c>
       <c r="G1768" t="n">
-        <v>66.6190872192383</v>
+        <v>66.6190795898438</v>
       </c>
       <c r="H1768" t="s">
         <v>8</v>
@@ -46415,7 +46415,7 @@
         <v>72.1999969482422</v>
       </c>
       <c r="G1771" t="n">
-        <v>69.4570159912109</v>
+        <v>69.4570083618164</v>
       </c>
       <c r="H1771" t="s">
         <v>8</v>
@@ -46493,7 +46493,7 @@
         <v>70.75</v>
       </c>
       <c r="G1774" t="n">
-        <v>68.0621032714844</v>
+        <v>68.0620956420898</v>
       </c>
       <c r="H1774" t="s">
         <v>8</v>
@@ -46701,7 +46701,7 @@
         <v>69.0999984741211</v>
       </c>
       <c r="G1782" t="n">
-        <v>66.4747848510742</v>
+        <v>66.4747772216797</v>
       </c>
       <c r="H1782" t="s">
         <v>8</v>
@@ -46727,7 +46727,7 @@
         <v>67.1999969482422</v>
       </c>
       <c r="G1783" t="n">
-        <v>64.6469573974609</v>
+        <v>64.6469650268555</v>
       </c>
       <c r="H1783" t="s">
         <v>8</v>
@@ -46805,7 +46805,7 @@
         <v>70.0500030517578</v>
       </c>
       <c r="G1786" t="n">
-        <v>67.3887023925781</v>
+        <v>67.3886947631836</v>
       </c>
       <c r="H1786" t="s">
         <v>8</v>
@@ -46831,7 +46831,7 @@
         <v>70.0500030517578</v>
       </c>
       <c r="G1787" t="n">
-        <v>67.3887023925781</v>
+        <v>67.3886947631836</v>
       </c>
       <c r="H1787" t="s">
         <v>8</v>
@@ -46857,7 +46857,7 @@
         <v>71.5</v>
       </c>
       <c r="G1788" t="n">
-        <v>68.7836074829102</v>
+        <v>68.7835998535156</v>
       </c>
       <c r="H1788" t="s">
         <v>8</v>
@@ -46961,7 +46961,7 @@
         <v>68.6500015258789</v>
       </c>
       <c r="G1792" t="n">
-        <v>66.0418853759766</v>
+        <v>66.0418930053711</v>
       </c>
       <c r="H1792" t="s">
         <v>8</v>
@@ -47247,7 +47247,7 @@
         <v>77</v>
       </c>
       <c r="G1803" t="n">
-        <v>74.0746536254883</v>
+        <v>74.0746459960938</v>
       </c>
       <c r="H1803" t="s">
         <v>8</v>
@@ -47403,7 +47403,7 @@
         <v>79.3000030517578</v>
       </c>
       <c r="G1809" t="n">
-        <v>76.2872695922852</v>
+        <v>76.2872772216797</v>
       </c>
       <c r="H1809" t="s">
         <v>8</v>
@@ -47429,7 +47429,7 @@
         <v>79.3000030517578</v>
       </c>
       <c r="G1810" t="n">
-        <v>76.2872695922852</v>
+        <v>76.2872772216797</v>
       </c>
       <c r="H1810" t="s">
         <v>8</v>
@@ -47507,7 +47507,7 @@
         <v>78.9499969482422</v>
       </c>
       <c r="G1813" t="n">
-        <v>75.950569152832</v>
+        <v>75.9505615234375</v>
       </c>
       <c r="H1813" t="s">
         <v>8</v>
@@ -47663,7 +47663,7 @@
         <v>80.1999969482422</v>
       </c>
       <c r="G1819" t="n">
-        <v>77.1530838012695</v>
+        <v>77.153076171875</v>
       </c>
       <c r="H1819" t="s">
         <v>8</v>
@@ -47793,7 +47793,7 @@
         <v>79.6999969482422</v>
       </c>
       <c r="G1824" t="n">
-        <v>76.6720657348633</v>
+        <v>76.6720733642578</v>
       </c>
       <c r="H1824" t="s">
         <v>8</v>
@@ -47871,7 +47871,7 @@
         <v>80.3499984741211</v>
       </c>
       <c r="G1827" t="n">
-        <v>77.2973861694336</v>
+        <v>77.2973785400391</v>
       </c>
       <c r="H1827" t="s">
         <v>8</v>
@@ -47949,7 +47949,7 @@
         <v>79.8499984741211</v>
       </c>
       <c r="G1830" t="n">
-        <v>76.8163681030273</v>
+        <v>76.8163757324219</v>
       </c>
       <c r="H1830" t="s">
         <v>8</v>
@@ -48001,7 +48001,7 @@
         <v>79.5</v>
       </c>
       <c r="G1832" t="n">
-        <v>76.4796752929688</v>
+        <v>76.4796676635742</v>
       </c>
       <c r="H1832" t="s">
         <v>8</v>
@@ -48183,7 +48183,7 @@
         <v>82.5</v>
       </c>
       <c r="G1839" t="n">
-        <v>79.3656921386719</v>
+        <v>79.3656997680664</v>
       </c>
       <c r="H1839" t="s">
         <v>8</v>
@@ -48417,7 +48417,7 @@
         <v>90.25</v>
       </c>
       <c r="G1848" t="n">
-        <v>86.8212585449219</v>
+        <v>86.8212661743164</v>
       </c>
       <c r="H1848" t="s">
         <v>8</v>
@@ -48599,7 +48599,7 @@
         <v>92.6500015258789</v>
       </c>
       <c r="G1855" t="n">
-        <v>89.1300811767578</v>
+        <v>89.1300888061523</v>
       </c>
       <c r="H1855" t="s">
         <v>8</v>
@@ -48651,7 +48651,7 @@
         <v>91.6999969482422</v>
       </c>
       <c r="G1857" t="n">
-        <v>88.2161712646484</v>
+        <v>88.216178894043</v>
       </c>
       <c r="H1857" t="s">
         <v>8</v>
@@ -48677,7 +48677,7 @@
         <v>88.3499984741211</v>
       </c>
       <c r="G1858" t="n">
-        <v>84.9934463500977</v>
+        <v>84.9934387207031</v>
       </c>
       <c r="H1858" t="s">
         <v>8</v>
@@ -48755,7 +48755,7 @@
         <v>90.25</v>
       </c>
       <c r="G1861" t="n">
-        <v>86.8212585449219</v>
+        <v>86.8212661743164</v>
       </c>
       <c r="H1861" t="s">
         <v>8</v>
@@ -48781,7 +48781,7 @@
         <v>90.75</v>
       </c>
       <c r="G1862" t="n">
-        <v>87.3022689819336</v>
+        <v>87.3022613525391</v>
       </c>
       <c r="H1862" t="s">
         <v>8</v>
@@ -48885,7 +48885,7 @@
         <v>84.25</v>
       </c>
       <c r="G1866" t="n">
-        <v>81.0492172241211</v>
+        <v>81.0492248535156</v>
       </c>
       <c r="H1866" t="s">
         <v>8</v>
@@ -48989,7 +48989,7 @@
         <v>87.8499984741211</v>
       </c>
       <c r="G1870" t="n">
-        <v>84.5124359130859</v>
+        <v>84.5124435424805</v>
       </c>
       <c r="H1870" t="s">
         <v>8</v>
@@ -49041,7 +49041,7 @@
         <v>82.8000030517578</v>
       </c>
       <c r="G1872" t="n">
-        <v>79.654296875</v>
+        <v>79.6543045043945</v>
       </c>
       <c r="H1872" t="s">
         <v>8</v>
@@ -49171,7 +49171,7 @@
         <v>81.3000030517578</v>
       </c>
       <c r="G1877" t="n">
-        <v>78.2112884521484</v>
+        <v>78.211296081543</v>
       </c>
       <c r="H1877" t="s">
         <v>8</v>
@@ -49223,7 +49223,7 @@
         <v>82</v>
       </c>
       <c r="G1879" t="n">
-        <v>78.8846969604492</v>
+        <v>78.8847045898438</v>
       </c>
       <c r="H1879" t="s">
         <v>8</v>
@@ -71274,6 +71274,32 @@
         <v>81.3199996948242</v>
       </c>
       <c r="H2727" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2728">
+      <c r="A2728" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B2728" t="n">
+        <v>172851</v>
+      </c>
+      <c r="C2728" t="n">
+        <v>81.620002746582</v>
+      </c>
+      <c r="D2728" t="n">
+        <v>79.7399978637695</v>
+      </c>
+      <c r="E2728" t="n">
+        <v>80.9599990844727</v>
+      </c>
+      <c r="F2728" t="n">
+        <v>80.9599990844727</v>
+      </c>
+      <c r="G2728" t="n">
+        <v>80.9599990844727</v>
+      </c>
+      <c r="H2728" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/BC.MI.xlsx
+++ b/data/BC.MI.xlsx
@@ -447,7 +447,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G3" t="n">
-        <v>14.6633539199829</v>
+        <v>14.6633520126343</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>15.1700000762939</v>
       </c>
       <c r="G5" t="n">
-        <v>13.9901294708252</v>
+        <v>13.9901304244995</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>14.9300003051758</v>
       </c>
       <c r="G6" t="n">
-        <v>13.7687978744507</v>
+        <v>13.7687959671021</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>14.9099998474121</v>
       </c>
       <c r="G7" t="n">
-        <v>13.7503528594971</v>
+        <v>13.7503509521484</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G9" t="n">
-        <v>14.8477973937988</v>
+        <v>14.8477983474731</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G10" t="n">
-        <v>15.1244640350342</v>
+        <v>15.1244621276855</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>16.3799991607666</v>
       </c>
       <c r="G11" t="n">
-        <v>15.1060218811035</v>
+        <v>15.1060199737549</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>15.460000038147</v>
       </c>
       <c r="G12" t="n">
-        <v>14.2575759887695</v>
+        <v>14.2575740814209</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>15.0299997329712</v>
       </c>
       <c r="G15" t="n">
-        <v>13.8610181808472</v>
+        <v>13.8610191345215</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G17" t="n">
-        <v>14.1561317443848</v>
+        <v>14.1561298370361</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>15.8100004196167</v>
       </c>
       <c r="G18" t="n">
-        <v>14.5803527832031</v>
+        <v>14.5803546905518</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>14.9799995422363</v>
       </c>
       <c r="G20" t="n">
-        <v>13.8149070739746</v>
+        <v>13.8149089813232</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G21" t="n">
-        <v>14.2391300201416</v>
+        <v>14.2391290664673</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>15.460000038147</v>
       </c>
       <c r="G23" t="n">
-        <v>14.2575759887695</v>
+        <v>14.2575740814209</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>14.9700002670288</v>
       </c>
       <c r="G24" t="n">
-        <v>13.8056859970093</v>
+        <v>13.8056879043579</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>15.1700000762939</v>
       </c>
       <c r="G25" t="n">
-        <v>13.9901294708252</v>
+        <v>13.9901304244995</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>14.9899997711182</v>
       </c>
       <c r="G26" t="n">
-        <v>13.8241310119629</v>
+        <v>13.8241300582886</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>14.3800001144409</v>
       </c>
       <c r="G27" t="n">
-        <v>13.2615747451782</v>
+        <v>13.2615737915039</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G28" t="n">
-        <v>12.5422401428223</v>
+        <v>12.5422391891479</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>13.7200002670288</v>
       </c>
       <c r="G31" t="n">
-        <v>12.6529064178467</v>
+        <v>12.6529083251953</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>14.5</v>
       </c>
       <c r="G32" t="n">
-        <v>13.3722400665283</v>
+        <v>13.3722410202026</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>14.5200004577637</v>
       </c>
       <c r="G34" t="n">
-        <v>13.3906860351562</v>
+        <v>13.3906841278076</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G35" t="n">
-        <v>13.233907699585</v>
+        <v>13.2339067459106</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>14.3199996948242</v>
       </c>
       <c r="G36" t="n">
-        <v>13.2062406539917</v>
+        <v>13.2062397003174</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>15.0200004577637</v>
       </c>
       <c r="G39" t="n">
-        <v>13.8517951965332</v>
+        <v>13.8517980575562</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>14.7299995422363</v>
       </c>
       <c r="G41" t="n">
-        <v>13.5843524932861</v>
+        <v>13.5843515396118</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G45" t="n">
-        <v>14.2391300201416</v>
+        <v>14.2391290664673</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>16.5</v>
       </c>
       <c r="G51" t="n">
-        <v>15.2166862487793</v>
+        <v>15.2166891098022</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G52" t="n">
-        <v>15.4011325836182</v>
+        <v>15.4011344909668</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>16.3199996948242</v>
       </c>
       <c r="G53" t="n">
-        <v>15.0506896972656</v>
+        <v>15.0506868362427</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>16.4599990844727</v>
       </c>
       <c r="G56" t="n">
-        <v>15.1797971725464</v>
+        <v>15.1797981262207</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>16.5699996948242</v>
       </c>
       <c r="G57" t="n">
-        <v>15.2812404632568</v>
+        <v>15.2812433242798</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G58" t="n">
-        <v>15.4011325836182</v>
+        <v>15.4011344909668</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>16.7399997711182</v>
       </c>
       <c r="G59" t="n">
-        <v>15.4380197525024</v>
+        <v>15.4380216598511</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>16.6399993896484</v>
       </c>
       <c r="G60" t="n">
-        <v>15.345799446106</v>
+        <v>15.3457975387573</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G61" t="n">
-        <v>15.1244640350342</v>
+        <v>15.1244621276855</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>16.6399993896484</v>
       </c>
       <c r="G63" t="n">
-        <v>15.345799446106</v>
+        <v>15.3457975387573</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>16.7099990844727</v>
       </c>
       <c r="G64" t="n">
-        <v>15.4103546142578</v>
+        <v>15.4103536605835</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>16.5900001525879</v>
       </c>
       <c r="G65" t="n">
-        <v>15.2996883392334</v>
+        <v>15.2996873855591</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G66" t="n">
-        <v>14.89391040802</v>
+        <v>14.8939085006714</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G68" t="n">
-        <v>14.4327974319458</v>
+        <v>14.4327964782715</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>16.2199993133545</v>
       </c>
       <c r="G69" t="n">
-        <v>14.9584646224976</v>
+        <v>14.9584617614746</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>16.6900005340576</v>
       </c>
       <c r="G71" t="n">
-        <v>15.3919095993042</v>
+        <v>15.3919105529785</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G73" t="n">
-        <v>15.5394659042358</v>
+        <v>15.5394678115845</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>16.9400005340576</v>
       </c>
       <c r="G74" t="n">
-        <v>15.6224699020386</v>
+        <v>15.6224679946899</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>17.5</v>
       </c>
       <c r="G78" t="n">
-        <v>16.1389083862305</v>
+        <v>16.1389122009277</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G79" t="n">
-        <v>16.0466899871826</v>
+        <v>16.046688079834</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>17.5699996948242</v>
       </c>
       <c r="G80" t="n">
-        <v>16.2034664154053</v>
+        <v>16.2034645080566</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G81" t="n">
-        <v>16.0835800170898</v>
+        <v>16.0835762023926</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>17.5200004577637</v>
       </c>
       <c r="G82" t="n">
-        <v>16.1573543548584</v>
+        <v>16.157356262207</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>17.5200004577637</v>
       </c>
       <c r="G83" t="n">
-        <v>16.1573543548584</v>
+        <v>16.157356262207</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G84" t="n">
-        <v>15.8161325454712</v>
+        <v>15.8161306381226</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>17.3600006103516</v>
       </c>
       <c r="G85" t="n">
-        <v>16.0097980499268</v>
+        <v>16.009801864624</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>17.5</v>
       </c>
       <c r="G88" t="n">
-        <v>16.1389083862305</v>
+        <v>16.1389122009277</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>17.25</v>
       </c>
       <c r="G90" t="n">
-        <v>15.9083557128906</v>
+        <v>15.9083566665649</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>17.5900001525879</v>
       </c>
       <c r="G94" t="n">
-        <v>16.2219123840332</v>
+        <v>16.2219104766846</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>17.7800006866455</v>
       </c>
       <c r="G96" t="n">
-        <v>16.3971328735352</v>
+        <v>16.3971347808838</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G98" t="n">
-        <v>16.4155750274658</v>
+        <v>16.4155788421631</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G99" t="n">
-        <v>16.2311363220215</v>
+        <v>16.2311325073242</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>17.6599998474121</v>
       </c>
       <c r="G103" t="n">
-        <v>16.407657623291</v>
+        <v>16.4076595306396</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>17.6399993896484</v>
       </c>
       <c r="G105" t="n">
-        <v>16.3890781402588</v>
+        <v>16.3890762329102</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>17.5799999237061</v>
       </c>
       <c r="G109" t="n">
-        <v>16.3333339691162</v>
+        <v>16.3333320617676</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G111" t="n">
-        <v>16.4448261260986</v>
+        <v>16.4448223114014</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>17.8799991607666</v>
       </c>
       <c r="G112" t="n">
-        <v>16.6120567321777</v>
+        <v>16.612060546875</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>16.6700000762939</v>
       </c>
       <c r="G115" t="n">
-        <v>15.4878644943237</v>
+        <v>15.487865447998</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>16.4400005340576</v>
       </c>
       <c r="G116" t="n">
-        <v>15.2741737365723</v>
+        <v>15.2741746902466</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>16.6900005340576</v>
       </c>
       <c r="G117" t="n">
-        <v>15.5064468383789</v>
+        <v>15.5064477920532</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G118" t="n">
-        <v>15.144100189209</v>
+        <v>15.1441040039062</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>17.6200008392334</v>
       </c>
       <c r="G119" t="n">
-        <v>16.3704967498779</v>
+        <v>16.3704929351807</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G120" t="n">
-        <v>16.3983688354492</v>
+        <v>16.3983669281006</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G121" t="n">
-        <v>16.2218418121338</v>
+        <v>16.2218437194824</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>17.2700004577637</v>
       </c>
       <c r="G122" t="n">
-        <v>16.0453205108643</v>
+        <v>16.0453186035156</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G123" t="n">
-        <v>16.3519153594971</v>
+        <v>16.3519134521484</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>16.5</v>
       </c>
       <c r="G124" t="n">
-        <v>15.3299198150635</v>
+        <v>15.3299207687378</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>15.710000038147</v>
       </c>
       <c r="G131" t="n">
-        <v>14.5959415435791</v>
+        <v>14.5959434509277</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>15.210000038147</v>
       </c>
       <c r="G132" t="n">
-        <v>14.1313991546631</v>
+        <v>14.1313982009888</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G133" t="n">
-        <v>14.4565801620483</v>
+        <v>14.4565811157227</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G135" t="n">
-        <v>14.7260150909424</v>
+        <v>14.7260131835938</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>16.5100002288818</v>
       </c>
       <c r="G136" t="n">
-        <v>15.3392105102539</v>
+        <v>15.3392114639282</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G139" t="n">
-        <v>15.2370100021362</v>
+        <v>15.2370080947876</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>16.5</v>
       </c>
       <c r="G140" t="n">
-        <v>15.3299198150635</v>
+        <v>15.3299207687378</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>16.5599994659424</v>
       </c>
       <c r="G141" t="n">
-        <v>15.3856649398804</v>
+        <v>15.3856658935547</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G142" t="n">
-        <v>15.7015542984009</v>
+        <v>15.7015552520752</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>16.8199996948242</v>
       </c>
       <c r="G143" t="n">
-        <v>15.6272277832031</v>
+        <v>15.6272249221802</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>16.9899997711182</v>
       </c>
       <c r="G144" t="n">
-        <v>15.7851724624634</v>
+        <v>15.7851715087891</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>16.7800006866455</v>
       </c>
       <c r="G145" t="n">
-        <v>15.5900650024414</v>
+        <v>15.5900640487671</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>16.5200004577637</v>
       </c>
       <c r="G146" t="n">
-        <v>15.3485021591187</v>
+        <v>15.3485040664673</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>16.9300003051758</v>
       </c>
       <c r="G147" t="n">
-        <v>15.7294263839722</v>
+        <v>15.7294273376465</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>16.6900005340576</v>
       </c>
       <c r="G148" t="n">
-        <v>15.5064468383789</v>
+        <v>15.5064477920532</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>16.6900005340576</v>
       </c>
       <c r="G149" t="n">
-        <v>15.5064468383789</v>
+        <v>15.5064477920532</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G150" t="n">
-        <v>15.4692831039429</v>
+        <v>15.4692821502686</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G151" t="n">
-        <v>15.1812658309937</v>
+        <v>15.1812686920166</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>16.4699993133545</v>
       </c>
       <c r="G152" t="n">
-        <v>15.3020467758179</v>
+        <v>15.3020477294922</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>16.9099998474121</v>
       </c>
       <c r="G155" t="n">
-        <v>15.7108449935913</v>
+        <v>15.7108459472656</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>17.0300006866455</v>
       </c>
       <c r="G156" t="n">
-        <v>15.8223361968994</v>
+        <v>15.8223342895508</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G158" t="n">
-        <v>16.1103553771973</v>
+        <v>16.1103515625</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G159" t="n">
-        <v>16.0731868743896</v>
+        <v>16.0731887817383</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>17.1700000762939</v>
       </c>
       <c r="G160" t="n">
-        <v>15.9524097442627</v>
+        <v>15.9524087905884</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>17.5400009155273</v>
       </c>
       <c r="G164" t="n">
-        <v>16.2961711883545</v>
+        <v>16.2961692810059</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>17.6700000762939</v>
       </c>
       <c r="G166" t="n">
-        <v>16.4169521331787</v>
+        <v>16.4169502258301</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>17.5</v>
       </c>
       <c r="G169" t="n">
-        <v>16.2590084075928</v>
+        <v>16.2590065002441</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>17.8299999237061</v>
       </c>
       <c r="G170" t="n">
-        <v>16.5656070709229</v>
+        <v>16.5656032562256</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>17.8799991607666</v>
       </c>
       <c r="G171" t="n">
-        <v>16.6120567321777</v>
+        <v>16.612060546875</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>17.9099998474121</v>
       </c>
       <c r="G172" t="n">
-        <v>16.6399307250977</v>
+        <v>16.6399326324463</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>18.0799999237061</v>
       </c>
       <c r="G174" t="n">
-        <v>16.7978744506836</v>
+        <v>16.7978763580322</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>18</v>
       </c>
       <c r="G175" t="n">
-        <v>16.7235488891602</v>
+        <v>16.7235469818115</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>18</v>
       </c>
       <c r="G177" t="n">
-        <v>16.7235488891602</v>
+        <v>16.7235469818115</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>17.9899997711182</v>
       </c>
       <c r="G178" t="n">
-        <v>16.7142581939697</v>
+        <v>16.7142601013184</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>18.0400009155273</v>
       </c>
       <c r="G179" t="n">
-        <v>16.7607116699219</v>
+        <v>16.7607135772705</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>18</v>
       </c>
       <c r="G180" t="n">
-        <v>16.7235488891602</v>
+        <v>16.7235469818115</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G181" t="n">
-        <v>16.6306400299072</v>
+        <v>16.6306419372559</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G182" t="n">
-        <v>16.6306400299072</v>
+        <v>16.6306419372559</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>18</v>
       </c>
       <c r="G183" t="n">
-        <v>16.7235488891602</v>
+        <v>16.7235469818115</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G185" t="n">
-        <v>16.481990814209</v>
+        <v>16.4819869995117</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>17.9699993133545</v>
       </c>
       <c r="G186" t="n">
-        <v>16.6956748962402</v>
+        <v>16.6956768035889</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>17.8199996948242</v>
       </c>
       <c r="G187" t="n">
-        <v>16.5563125610352</v>
+        <v>16.5563144683838</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G188" t="n">
-        <v>16.6306400299072</v>
+        <v>16.6306419372559</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G189" t="n">
-        <v>16.5934772491455</v>
+        <v>16.5934810638428</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G193" t="n">
-        <v>16.0731868743896</v>
+        <v>16.0731887817383</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G195" t="n">
-        <v>16.6306400299072</v>
+        <v>16.6306419372559</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>18</v>
       </c>
       <c r="G196" t="n">
-        <v>16.7235488891602</v>
+        <v>16.7235469818115</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>17.9400005340576</v>
       </c>
       <c r="G197" t="n">
-        <v>16.6678047180176</v>
+        <v>16.6678066253662</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>18</v>
       </c>
       <c r="G198" t="n">
-        <v>16.7235488891602</v>
+        <v>16.7235469818115</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>17.9099998474121</v>
       </c>
       <c r="G199" t="n">
-        <v>16.6399307250977</v>
+        <v>16.6399326324463</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>17.9400005340576</v>
       </c>
       <c r="G201" t="n">
-        <v>16.6678047180176</v>
+        <v>16.6678066253662</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>17.9699993133545</v>
       </c>
       <c r="G203" t="n">
-        <v>16.6956748962402</v>
+        <v>16.6956768035889</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>17.9599990844727</v>
       </c>
       <c r="G204" t="n">
-        <v>16.6863861083984</v>
+        <v>16.6863880157471</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G205" t="n">
-        <v>16.5934772491455</v>
+        <v>16.5934810638428</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G206" t="n">
-        <v>16.6306400299072</v>
+        <v>16.6306419372559</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G207" t="n">
-        <v>16.6306400299072</v>
+        <v>16.6306419372559</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>17.9899997711182</v>
       </c>
       <c r="G208" t="n">
-        <v>16.7142581939697</v>
+        <v>16.7142601013184</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>17.9899997711182</v>
       </c>
       <c r="G209" t="n">
-        <v>16.7142581939697</v>
+        <v>16.7142601013184</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>17.9899997711182</v>
       </c>
       <c r="G210" t="n">
-        <v>16.7142581939697</v>
+        <v>16.7142601013184</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>18</v>
       </c>
       <c r="G211" t="n">
-        <v>16.7235488891602</v>
+        <v>16.7235469818115</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>18.0400009155273</v>
       </c>
       <c r="G214" t="n">
-        <v>16.7607116699219</v>
+        <v>16.7607135772705</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>18</v>
       </c>
       <c r="G215" t="n">
-        <v>16.7235488891602</v>
+        <v>16.7235469818115</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>18</v>
       </c>
       <c r="G217" t="n">
-        <v>16.7235488891602</v>
+        <v>16.7235469818115</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>18</v>
       </c>
       <c r="G218" t="n">
-        <v>16.7235488891602</v>
+        <v>16.7235469818115</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>17.9599990844727</v>
       </c>
       <c r="G219" t="n">
-        <v>16.6863861083984</v>
+        <v>16.6863880157471</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>18.0799999237061</v>
       </c>
       <c r="G220" t="n">
-        <v>16.7978744506836</v>
+        <v>16.7978763580322</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>18.0799999237061</v>
       </c>
       <c r="G221" t="n">
-        <v>16.7978744506836</v>
+        <v>16.7978763580322</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>18</v>
       </c>
       <c r="G224" t="n">
-        <v>16.7235488891602</v>
+        <v>16.7235469818115</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>18</v>
       </c>
       <c r="G225" t="n">
-        <v>16.7235488891602</v>
+        <v>16.7235469818115</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>17.9899997711182</v>
       </c>
       <c r="G226" t="n">
-        <v>16.7142581939697</v>
+        <v>16.7142601013184</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>17.9400005340576</v>
       </c>
       <c r="G229" t="n">
-        <v>16.6678047180176</v>
+        <v>16.6678066253662</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>17.9200000762939</v>
       </c>
       <c r="G230" t="n">
-        <v>16.6492214202881</v>
+        <v>16.6492233276367</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>18</v>
       </c>
       <c r="G231" t="n">
-        <v>16.7235488891602</v>
+        <v>16.7235469818115</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>17.8299999237061</v>
       </c>
       <c r="G232" t="n">
-        <v>16.5656070709229</v>
+        <v>16.5656032562256</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>18</v>
       </c>
       <c r="G235" t="n">
-        <v>16.7235488891602</v>
+        <v>16.7235469818115</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>17.8099994659424</v>
       </c>
       <c r="G237" t="n">
-        <v>16.5470237731934</v>
+        <v>16.5470218658447</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>17.9099998474121</v>
       </c>
       <c r="G238" t="n">
-        <v>16.6399307250977</v>
+        <v>16.6399326324463</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>18.3099994659424</v>
       </c>
       <c r="G240" t="n">
-        <v>17.011568069458</v>
+        <v>17.0115642547607</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>18.1700000762939</v>
       </c>
       <c r="G241" t="n">
-        <v>16.8814926147461</v>
+        <v>16.8814945220947</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G242" t="n">
-        <v>16.9093685150146</v>
+        <v>16.9093647003174</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>18.3400001525879</v>
       </c>
       <c r="G243" t="n">
-        <v>17.039436340332</v>
+        <v>17.0394382476807</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>18.2900009155273</v>
       </c>
       <c r="G244" t="n">
-        <v>16.9929866790771</v>
+        <v>16.9929847717285</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>18.4400005340576</v>
       </c>
       <c r="G245" t="n">
-        <v>17.1323471069336</v>
+        <v>17.1323490142822</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>18.4500007629395</v>
       </c>
       <c r="G246" t="n">
-        <v>17.141637802124</v>
+        <v>17.1416397094727</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>18.3799991607666</v>
       </c>
       <c r="G248" t="n">
-        <v>17.0766010284424</v>
+        <v>17.076602935791</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G249" t="n">
-        <v>17.466817855835</v>
+        <v>17.4668140411377</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>19.8500003814697</v>
       </c>
       <c r="G254" t="n">
-        <v>18.4423599243164</v>
+        <v>18.4423580169678</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>19.9799995422363</v>
       </c>
       <c r="G255" t="n">
-        <v>18.563138961792</v>
+        <v>18.5631408691406</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>20.3400001525879</v>
       </c>
       <c r="G257" t="n">
-        <v>18.8976097106934</v>
+        <v>18.897611618042</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>20.5499992370605</v>
       </c>
       <c r="G258" t="n">
-        <v>19.092716217041</v>
+        <v>19.0927181243896</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>20.5900001525879</v>
       </c>
       <c r="G259" t="n">
-        <v>19.1298809051514</v>
+        <v>19.1298828125</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>20.4200000762939</v>
       </c>
       <c r="G261" t="n">
-        <v>18.9719371795654</v>
+        <v>18.9719390869141</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>20.7800006866455</v>
       </c>
       <c r="G262" t="n">
-        <v>19.3064079284668</v>
+        <v>19.3064117431641</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>20.6299991607666</v>
       </c>
       <c r="G263" t="n">
-        <v>19.1670455932617</v>
+        <v>19.1670436859131</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>21.5400009155273</v>
       </c>
       <c r="G264" t="n">
-        <v>20.0125160217285</v>
+        <v>20.0125141143799</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G265" t="n">
-        <v>20.1611671447754</v>
+        <v>20.161169052124</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>21.5</v>
       </c>
       <c r="G266" t="n">
-        <v>19.9753513336182</v>
+        <v>19.9753494262695</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>21.5200004577637</v>
       </c>
       <c r="G267" t="n">
-        <v>19.9939346313477</v>
+        <v>19.9939308166504</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>21.7800006866455</v>
       </c>
       <c r="G268" t="n">
-        <v>20.2354984283447</v>
+        <v>20.2354965209961</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>21.6299991607666</v>
       </c>
       <c r="G269" t="n">
-        <v>20.0961303710938</v>
+        <v>20.0961284637451</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G270" t="n">
-        <v>20.1611671447754</v>
+        <v>20.161169052124</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>21.9899997711182</v>
       </c>
       <c r="G273" t="n">
-        <v>20.4306049346924</v>
+        <v>20.4306011199951</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>21.6399993896484</v>
       </c>
       <c r="G274" t="n">
-        <v>20.1054191589355</v>
+        <v>20.1054229736328</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>21.3600006103516</v>
       </c>
       <c r="G275" t="n">
-        <v>19.8452758789062</v>
+        <v>19.8452816009521</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>21.0599994659424</v>
       </c>
       <c r="G276" t="n">
-        <v>19.5665531158447</v>
+        <v>19.5665512084961</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>20.9799995422363</v>
       </c>
       <c r="G277" t="n">
-        <v>19.4922256469727</v>
+        <v>19.4922275543213</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>20.7399997711182</v>
       </c>
       <c r="G278" t="n">
-        <v>19.2692470550537</v>
+        <v>19.2692432403564</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>21.0599994659424</v>
       </c>
       <c r="G280" t="n">
-        <v>19.5665531158447</v>
+        <v>19.5665512084961</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G281" t="n">
-        <v>19.4643516540527</v>
+        <v>19.46435546875</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>20.4799995422363</v>
       </c>
       <c r="G286" t="n">
-        <v>19.027681350708</v>
+        <v>19.0276832580566</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>20.6599998474121</v>
       </c>
       <c r="G287" t="n">
-        <v>19.1949195861816</v>
+        <v>19.1949157714844</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G288" t="n">
-        <v>19.1391735076904</v>
+        <v>19.1391754150391</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>20.6100006103516</v>
       </c>
       <c r="G290" t="n">
-        <v>19.1484661102295</v>
+        <v>19.1484642028809</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>20.2900009155273</v>
       </c>
       <c r="G291" t="n">
-        <v>18.8511562347412</v>
+        <v>18.8511581420898</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>20.1900005340576</v>
       </c>
       <c r="G292" t="n">
-        <v>18.7582473754883</v>
+        <v>18.7582454681396</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G293" t="n">
-        <v>18.8604488372803</v>
+        <v>18.860445022583</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>20.2800006866455</v>
       </c>
       <c r="G295" t="n">
-        <v>18.8418674468994</v>
+        <v>18.8418655395508</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G296" t="n">
-        <v>18.6281757354736</v>
+        <v>18.6281719207764</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>19.5</v>
       </c>
       <c r="G298" t="n">
-        <v>18.1171760559082</v>
+        <v>18.1171798706055</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>20.5900001525879</v>
       </c>
       <c r="G304" t="n">
-        <v>19.1298809051514</v>
+        <v>19.1298828125</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>20.6299991607666</v>
       </c>
       <c r="G305" t="n">
-        <v>19.1670455932617</v>
+        <v>19.1670436859131</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>20.7199993133545</v>
       </c>
       <c r="G306" t="n">
-        <v>19.2506618499756</v>
+        <v>19.2506637573242</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>20.9899997711182</v>
       </c>
       <c r="G307" t="n">
-        <v>19.5015182495117</v>
+        <v>19.5015163421631</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>21.0300006866455</v>
       </c>
       <c r="G308" t="n">
-        <v>19.5386791229248</v>
+        <v>19.5386810302734</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>21.3600006103516</v>
       </c>
       <c r="G310" t="n">
-        <v>19.8452758789062</v>
+        <v>19.8452816009521</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>21.8899993896484</v>
       </c>
       <c r="G311" t="n">
-        <v>20.3376941680908</v>
+        <v>20.3376960754395</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G313" t="n">
-        <v>20.5328025817871</v>
+        <v>20.5327987670898</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>22.0900001525879</v>
       </c>
       <c r="G314" t="n">
-        <v>20.523509979248</v>
+        <v>20.5235080718994</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G316" t="n">
-        <v>21.0902557373047</v>
+        <v>21.0902519226074</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>22.6299991607666</v>
       </c>
       <c r="G317" t="n">
-        <v>21.0252151489258</v>
+        <v>21.025218963623</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>22.3299999237061</v>
       </c>
       <c r="G319" t="n">
-        <v>20.7464904785156</v>
+        <v>20.7464923858643</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>22.3400001525879</v>
       </c>
       <c r="G322" t="n">
-        <v>20.7557849884033</v>
+        <v>20.7557830810547</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G323" t="n">
-        <v>20.7186164855957</v>
+        <v>20.7186183929443</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>22.5200004577637</v>
       </c>
       <c r="G324" t="n">
-        <v>20.9230194091797</v>
+        <v>20.9230213165283</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>22.9599990844727</v>
       </c>
       <c r="G328" t="n">
-        <v>21.3318157196045</v>
+        <v>21.3318176269531</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>22.6299991607666</v>
       </c>
       <c r="G331" t="n">
-        <v>21.0252151489258</v>
+        <v>21.025218963623</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>22.8899993896484</v>
       </c>
       <c r="G332" t="n">
-        <v>21.2667789459229</v>
+        <v>21.2667808532715</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G334" t="n">
-        <v>21.7406158447266</v>
+        <v>21.7406120300293</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>23.4200000762939</v>
       </c>
       <c r="G336" t="n">
-        <v>21.7591972351074</v>
+        <v>21.7591953277588</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>23.6499996185303</v>
       </c>
       <c r="G337" t="n">
-        <v>21.9728870391846</v>
+        <v>21.9728851318359</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>24.1000003814697</v>
       </c>
       <c r="G338" t="n">
-        <v>22.3909759521484</v>
+        <v>22.3909740447998</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>24.1700000762939</v>
       </c>
       <c r="G339" t="n">
-        <v>22.4560089111328</v>
+        <v>22.4560108184814</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>24.0400009155273</v>
       </c>
       <c r="G340" t="n">
-        <v>22.3352298736572</v>
+        <v>22.3352317810059</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>24.1499996185303</v>
       </c>
       <c r="G342" t="n">
-        <v>22.437427520752</v>
+        <v>22.4374294281006</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>24.5</v>
       </c>
       <c r="G343" t="n">
-        <v>22.7626094818115</v>
+        <v>22.7626075744629</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>24.5</v>
       </c>
       <c r="G344" t="n">
-        <v>22.7626094818115</v>
+        <v>22.7626075744629</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>23.6499996185303</v>
       </c>
       <c r="G345" t="n">
-        <v>21.9728870391846</v>
+        <v>21.9728851318359</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>24</v>
       </c>
       <c r="G346" t="n">
-        <v>22.2980690002441</v>
+        <v>22.2980670928955</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>23.7700004577637</v>
       </c>
       <c r="G347" t="n">
-        <v>22.0843772888184</v>
+        <v>22.0843753814697</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>23.3899993896484</v>
       </c>
       <c r="G348" t="n">
-        <v>21.7313213348389</v>
+        <v>21.7313232421875</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>23.2900009155273</v>
       </c>
       <c r="G350" t="n">
-        <v>21.6384162902832</v>
+        <v>21.6384124755859</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>23.1499996185303</v>
       </c>
       <c r="G351" t="n">
-        <v>21.5083408355713</v>
+        <v>21.5083389282227</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>22.6399993896484</v>
       </c>
       <c r="G352" t="n">
-        <v>21.0345096588135</v>
+        <v>21.0345058441162</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>22.6399993896484</v>
       </c>
       <c r="G353" t="n">
-        <v>21.0345096588135</v>
+        <v>21.0345058441162</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>23.5</v>
       </c>
       <c r="G354" t="n">
-        <v>21.8335208892822</v>
+        <v>21.8335247039795</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>23.3199996948242</v>
       </c>
       <c r="G355" t="n">
-        <v>21.8148136138916</v>
+        <v>21.8148155212402</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>23.3700008392334</v>
       </c>
       <c r="G356" t="n">
-        <v>21.8615894317627</v>
+        <v>21.8615856170654</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>23.3799991607666</v>
       </c>
       <c r="G357" t="n">
-        <v>21.8709392547607</v>
+        <v>21.8709411621094</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>23.3099994659424</v>
       </c>
       <c r="G361" t="n">
-        <v>21.8054599761963</v>
+        <v>21.8054580688477</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>22.9599990844727</v>
       </c>
       <c r="G362" t="n">
-        <v>21.478048324585</v>
+        <v>21.4780521392822</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>23.0400009155273</v>
       </c>
       <c r="G363" t="n">
-        <v>21.5528888702393</v>
+        <v>21.5528869628906</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>22.8799991607666</v>
       </c>
       <c r="G364" t="n">
-        <v>21.4032154083252</v>
+        <v>21.4032115936279</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>22.7700004577637</v>
       </c>
       <c r="G365" t="n">
-        <v>21.300313949585</v>
+        <v>21.3003158569336</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>22.9300003051758</v>
       </c>
       <c r="G366" t="n">
-        <v>21.4499893188477</v>
+        <v>21.4499855041504</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>22.7099990844727</v>
       </c>
       <c r="G369" t="n">
-        <v>21.2441883087158</v>
+        <v>21.2441825866699</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G370" t="n">
-        <v>20.8606472015381</v>
+        <v>20.8606491088867</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G371" t="n">
-        <v>21.1412868499756</v>
+        <v>21.1412887573242</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>23.0699996948242</v>
       </c>
       <c r="G372" t="n">
-        <v>21.5809478759766</v>
+        <v>21.5809497833252</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G373" t="n">
-        <v>21.1880588531494</v>
+        <v>21.1880569458008</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>23.8099994659424</v>
       </c>
       <c r="G376" t="n">
-        <v>22.2731857299805</v>
+        <v>22.2731876373291</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G378" t="n">
-        <v>22.2638320922852</v>
+        <v>22.2638301849365</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>23.8099994659424</v>
       </c>
       <c r="G380" t="n">
-        <v>22.2731857299805</v>
+        <v>22.2731876373291</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>23.9300003051758</v>
       </c>
       <c r="G381" t="n">
-        <v>22.3854427337646</v>
+        <v>22.385440826416</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>23.8400001525879</v>
       </c>
       <c r="G382" t="n">
-        <v>22.3012504577637</v>
+        <v>22.301248550415</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>23</v>
       </c>
       <c r="G383" t="n">
-        <v>21.5154666900635</v>
+        <v>21.5154705047607</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>23.0499992370605</v>
       </c>
       <c r="G385" t="n">
-        <v>21.5622406005859</v>
+        <v>21.5622425079346</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>22.8700008392334</v>
       </c>
       <c r="G386" t="n">
-        <v>21.3938617706299</v>
+        <v>21.3938598632812</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>22.7900009155273</v>
       </c>
       <c r="G387" t="n">
-        <v>21.3190231323242</v>
+        <v>21.3190212249756</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G388" t="n">
-        <v>21.1412868499756</v>
+        <v>21.1412887573242</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>23</v>
       </c>
       <c r="G389" t="n">
-        <v>21.5154666900635</v>
+        <v>21.5154705047607</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>23</v>
       </c>
       <c r="G390" t="n">
-        <v>21.5154666900635</v>
+        <v>21.5154705047607</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>22.7700004577637</v>
       </c>
       <c r="G391" t="n">
-        <v>21.300313949585</v>
+        <v>21.3003158569336</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>23.3199996948242</v>
       </c>
       <c r="G392" t="n">
-        <v>21.8148136138916</v>
+        <v>21.8148155212402</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>23.5599994659424</v>
       </c>
       <c r="G394" t="n">
-        <v>22.0393218994141</v>
+        <v>22.0393238067627</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G396" t="n">
-        <v>22.2638320922852</v>
+        <v>22.2638301849365</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>23.9500007629395</v>
       </c>
       <c r="G397" t="n">
-        <v>22.4041519165039</v>
+        <v>22.4041500091553</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>24.3099994659424</v>
       </c>
       <c r="G399" t="n">
-        <v>22.7409114837646</v>
+        <v>22.7409133911133</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>24.4899997711182</v>
       </c>
       <c r="G400" t="n">
-        <v>22.9092960357666</v>
+        <v>22.909294128418</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>24.5</v>
       </c>
       <c r="G401" t="n">
-        <v>22.9186477661133</v>
+        <v>22.9186496734619</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>24.4899997711182</v>
       </c>
       <c r="G403" t="n">
-        <v>22.9092960357666</v>
+        <v>22.909294128418</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>24.4099998474121</v>
       </c>
       <c r="G404" t="n">
-        <v>22.8344573974609</v>
+        <v>22.8344612121582</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>25</v>
       </c>
       <c r="G406" t="n">
-        <v>23.3863792419434</v>
+        <v>23.3863773345947</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>24.4200000762939</v>
       </c>
       <c r="G409" t="n">
-        <v>22.8438167572021</v>
+        <v>22.8438148498535</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>24.75</v>
       </c>
       <c r="G411" t="n">
-        <v>23.1525115966797</v>
+        <v>23.1525135040283</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>23.9799995422363</v>
       </c>
       <c r="G418" t="n">
-        <v>22.4322147369385</v>
+        <v>22.4322128295898</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>24.25</v>
       </c>
       <c r="G419" t="n">
-        <v>22.6847858428955</v>
+        <v>22.6847896575928</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G421" t="n">
-        <v>22.3573760986328</v>
+        <v>22.3573780059814</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G422" t="n">
-        <v>22.3573760986328</v>
+        <v>22.3573780059814</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>23.7199993133545</v>
       </c>
       <c r="G423" t="n">
-        <v>22.1889972686768</v>
+        <v>22.1889953613281</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>23.3799991607666</v>
       </c>
       <c r="G425" t="n">
-        <v>21.8709392547607</v>
+        <v>21.8709411621094</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G427" t="n">
-        <v>23.5734691619873</v>
+        <v>23.5734710693359</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>25.4500007629395</v>
       </c>
       <c r="G428" t="n">
-        <v>23.8073348999023</v>
+        <v>23.807336807251</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>24.9699993133545</v>
       </c>
       <c r="G429" t="n">
-        <v>23.3583164215088</v>
+        <v>23.3583145141602</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>24.4599990844727</v>
       </c>
       <c r="G431" t="n">
-        <v>22.8812313079834</v>
+        <v>22.881233215332</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>25</v>
       </c>
       <c r="G433" t="n">
-        <v>23.3863792419434</v>
+        <v>23.3863773345947</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>25.3500003814697</v>
       </c>
       <c r="G434" t="n">
-        <v>23.7137889862061</v>
+        <v>23.7137870788574</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>25.8500003814697</v>
       </c>
       <c r="G435" t="n">
-        <v>24.1815166473389</v>
+        <v>24.1815147399902</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>25.8700008392334</v>
       </c>
       <c r="G436" t="n">
-        <v>24.2002258300781</v>
+        <v>24.2002277374268</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>26</v>
       </c>
       <c r="G437" t="n">
-        <v>24.321834564209</v>
+        <v>24.3218307495117</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>25.9500007629395</v>
       </c>
       <c r="G439" t="n">
-        <v>24.2750606536865</v>
+        <v>24.2750625610352</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>26.1800003051758</v>
       </c>
       <c r="G442" t="n">
-        <v>24.4902172088623</v>
+        <v>24.4902153015137</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>26.1499996185303</v>
       </c>
       <c r="G443" t="n">
-        <v>24.4621524810791</v>
+        <v>24.4621543884277</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>26.0900001525879</v>
       </c>
       <c r="G444" t="n">
-        <v>24.4060249328613</v>
+        <v>24.40602684021</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G445" t="n">
-        <v>24.2282867431641</v>
+        <v>24.2282886505127</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>26</v>
       </c>
       <c r="G447" t="n">
-        <v>24.321834564209</v>
+        <v>24.3218307495117</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>26.2399997711182</v>
       </c>
       <c r="G448" t="n">
-        <v>24.5463428497314</v>
+        <v>24.5463447570801</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>27.1800003051758</v>
       </c>
       <c r="G449" t="n">
-        <v>25.4256725311279</v>
+        <v>25.4256687164307</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>27.1800003051758</v>
       </c>
       <c r="G450" t="n">
-        <v>25.4256725311279</v>
+        <v>25.4256687164307</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>27.1900005340576</v>
       </c>
       <c r="G451" t="n">
-        <v>25.435022354126</v>
+        <v>25.4350261688232</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>26.9599990844727</v>
       </c>
       <c r="G452" t="n">
-        <v>25.2198715209961</v>
+        <v>25.2198696136475</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>26.6900005340576</v>
       </c>
       <c r="G453" t="n">
-        <v>24.9672985076904</v>
+        <v>24.9672966003418</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>27.1800003051758</v>
       </c>
       <c r="G457" t="n">
-        <v>25.4256725311279</v>
+        <v>25.4256687164307</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>27.1900005340576</v>
       </c>
       <c r="G458" t="n">
-        <v>25.435022354126</v>
+        <v>25.4350261688232</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>26.7900009155273</v>
       </c>
       <c r="G459" t="n">
-        <v>25.0608444213867</v>
+        <v>25.0608463287354</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>26.75</v>
       </c>
       <c r="G460" t="n">
-        <v>25.0234241485596</v>
+        <v>25.0234279632568</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>26.7299995422363</v>
       </c>
       <c r="G461" t="n">
-        <v>25.0047149658203</v>
+        <v>25.0047168731689</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>26.4699993133545</v>
       </c>
       <c r="G462" t="n">
-        <v>24.7614994049072</v>
+        <v>24.76149559021</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>26.75</v>
       </c>
       <c r="G463" t="n">
-        <v>25.0234241485596</v>
+        <v>25.0234279632568</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>27.1499996185303</v>
       </c>
       <c r="G465" t="n">
-        <v>25.3976058959961</v>
+        <v>25.3976078033447</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>27.0799999237061</v>
       </c>
       <c r="G466" t="n">
-        <v>25.332124710083</v>
+        <v>25.3321266174316</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>27.7600002288818</v>
       </c>
       <c r="G468" t="n">
-        <v>25.9682350158691</v>
+        <v>25.9682331085205</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>28.3500003814697</v>
       </c>
       <c r="G469" t="n">
-        <v>26.5201549530029</v>
+        <v>26.5201530456543</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>28.8199996948242</v>
       </c>
       <c r="G470" t="n">
-        <v>26.9598178863525</v>
+        <v>26.9598159790039</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G471" t="n">
-        <v>26.5669269561768</v>
+        <v>26.5669250488281</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>28.1499996185303</v>
       </c>
       <c r="G473" t="n">
-        <v>26.3330593109131</v>
+        <v>26.3330612182617</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>28.4899997711182</v>
       </c>
       <c r="G474" t="n">
-        <v>26.6511154174805</v>
+        <v>26.6511192321777</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>28.6700000762939</v>
       </c>
       <c r="G475" t="n">
-        <v>26.8194999694824</v>
+        <v>26.8195018768311</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>26.4300003051758</v>
       </c>
       <c r="G478" t="n">
-        <v>24.7240791320801</v>
+        <v>24.7240810394287</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>26.5699996948242</v>
       </c>
       <c r="G479" t="n">
-        <v>24.8550415039062</v>
+        <v>24.8550395965576</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>26.5699996948242</v>
       </c>
       <c r="G481" t="n">
-        <v>24.8550415039062</v>
+        <v>24.8550395965576</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>26.9300003051758</v>
       </c>
       <c r="G482" t="n">
-        <v>25.1918067932129</v>
+        <v>25.1918087005615</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>26.9500007629395</v>
       </c>
       <c r="G484" t="n">
-        <v>25.2105159759521</v>
+        <v>25.2105178833008</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>27.3700008392334</v>
       </c>
       <c r="G485" t="n">
-        <v>25.6034069061279</v>
+        <v>25.6034088134766</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>26.5499992370605</v>
       </c>
       <c r="G487" t="n">
-        <v>24.8363342285156</v>
+        <v>24.836332321167</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G492" t="n">
-        <v>24.8831062316895</v>
+        <v>24.8831043243408</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>26.4899997711182</v>
       </c>
       <c r="G493" t="n">
-        <v>24.7802066802979</v>
+        <v>24.7802047729492</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>27.1800003051758</v>
       </c>
       <c r="G495" t="n">
-        <v>25.4256725311279</v>
+        <v>25.4256687164307</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>27.0200004577637</v>
       </c>
       <c r="G496" t="n">
-        <v>25.2759971618652</v>
+        <v>25.2759990692139</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>27.2900009155273</v>
       </c>
       <c r="G497" t="n">
-        <v>25.5285682678223</v>
+        <v>25.5285720825195</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>27.7900009155273</v>
       </c>
       <c r="G498" t="n">
-        <v>25.9962997436523</v>
+        <v>25.9962978363037</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>26.7700004577637</v>
       </c>
       <c r="G503" t="n">
-        <v>25.0421352386475</v>
+        <v>25.0421333312988</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>26.6900005340576</v>
       </c>
       <c r="G504" t="n">
-        <v>24.9672985076904</v>
+        <v>24.9672966003418</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>27.1499996185303</v>
       </c>
       <c r="G506" t="n">
-        <v>25.3976058959961</v>
+        <v>25.3976078033447</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>27.3700008392334</v>
       </c>
       <c r="G507" t="n">
-        <v>25.6034069061279</v>
+        <v>25.6034088134766</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>27.0400009155273</v>
       </c>
       <c r="G509" t="n">
-        <v>25.2947063446045</v>
+        <v>25.2947082519531</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>27.1299991607666</v>
       </c>
       <c r="G512" t="n">
-        <v>25.3788967132568</v>
+        <v>25.3788948059082</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G515" t="n">
-        <v>26.4733791351318</v>
+        <v>26.4733810424805</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G520" t="n">
-        <v>25.5379238128662</v>
+        <v>25.5379257202148</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>27.25</v>
       </c>
       <c r="G524" t="n">
-        <v>25.4911518096924</v>
+        <v>25.491153717041</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>27.0499992370605</v>
       </c>
       <c r="G529" t="n">
-        <v>25.3040618896484</v>
+        <v>25.3040599822998</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>27.1499996185303</v>
       </c>
       <c r="G531" t="n">
-        <v>25.3976058959961</v>
+        <v>25.3976078033447</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G534" t="n">
-        <v>24.8831062316895</v>
+        <v>24.8831043243408</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>26.1000003814697</v>
       </c>
       <c r="G535" t="n">
-        <v>24.4153804779053</v>
+        <v>24.4153823852539</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G536" t="n">
-        <v>24.2282867431641</v>
+        <v>24.2282886505127</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G537" t="n">
-        <v>23.6670169830322</v>
+        <v>23.6670150756836</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>26</v>
       </c>
       <c r="G538" t="n">
-        <v>24.321834564209</v>
+        <v>24.3218307495117</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G539" t="n">
-        <v>23.5734691619873</v>
+        <v>23.5734710693359</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>25.75</v>
       </c>
       <c r="G541" t="n">
-        <v>24.0879707336426</v>
+        <v>24.0879688262939</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G542" t="n">
-        <v>23.7605628967285</v>
+        <v>23.7605590820312</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G544" t="n">
-        <v>24.5089282989502</v>
+        <v>24.5089244842529</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>26.1499996185303</v>
       </c>
       <c r="G546" t="n">
-        <v>24.4621524810791</v>
+        <v>24.4621543884277</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G548" t="n">
-        <v>24.2282867431641</v>
+        <v>24.2282886505127</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G549" t="n">
-        <v>23.7605628967285</v>
+        <v>23.7605590820312</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>25.4500007629395</v>
       </c>
       <c r="G550" t="n">
-        <v>23.8073348999023</v>
+        <v>23.807336807251</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>25.4500007629395</v>
       </c>
       <c r="G552" t="n">
-        <v>23.8073348999023</v>
+        <v>23.807336807251</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>25.75</v>
       </c>
       <c r="G554" t="n">
-        <v>24.0879707336426</v>
+        <v>24.0879688262939</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>25.1000003814697</v>
       </c>
       <c r="G555" t="n">
-        <v>23.479923248291</v>
+        <v>23.4799251556396</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G556" t="n">
-        <v>23.6670169830322</v>
+        <v>23.6670150756836</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>25.3500003814697</v>
       </c>
       <c r="G557" t="n">
-        <v>23.7137889862061</v>
+        <v>23.7137870788574</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G558" t="n">
-        <v>23.9476528167725</v>
+        <v>23.9476509094238</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>26.1000003814697</v>
       </c>
       <c r="G560" t="n">
-        <v>24.4153804779053</v>
+        <v>24.4153823852539</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G562" t="n">
-        <v>24.6960144042969</v>
+        <v>24.6960124969482</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>26.1000003814697</v>
       </c>
       <c r="G563" t="n">
-        <v>24.4153804779053</v>
+        <v>24.4153823852539</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>26</v>
       </c>
       <c r="G565" t="n">
-        <v>24.321834564209</v>
+        <v>24.3218307495117</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>26.3500003814697</v>
       </c>
       <c r="G567" t="n">
-        <v>24.6492443084717</v>
+        <v>24.649242401123</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>26.3500003814697</v>
       </c>
       <c r="G568" t="n">
-        <v>24.6492443084717</v>
+        <v>24.649242401123</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>25.8500003814697</v>
       </c>
       <c r="G569" t="n">
-        <v>24.1815166473389</v>
+        <v>24.1815147399902</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>25.8500003814697</v>
       </c>
       <c r="G570" t="n">
-        <v>24.1815166473389</v>
+        <v>24.1815147399902</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>25.25</v>
       </c>
       <c r="G571" t="n">
-        <v>23.6202449798584</v>
+        <v>23.6202411651611</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>25.25</v>
       </c>
       <c r="G572" t="n">
-        <v>23.6202449798584</v>
+        <v>23.6202411651611</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>25.1000003814697</v>
       </c>
       <c r="G573" t="n">
-        <v>23.479923248291</v>
+        <v>23.4799251556396</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>26.1499996185303</v>
       </c>
       <c r="G575" t="n">
-        <v>24.4621524810791</v>
+        <v>24.4621543884277</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>25.9500007629395</v>
       </c>
       <c r="G576" t="n">
-        <v>24.2750606536865</v>
+        <v>24.2750625610352</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G586" t="n">
-        <v>26.0056495666504</v>
+        <v>26.0056533813477</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>27.4500007629395</v>
       </c>
       <c r="G588" t="n">
-        <v>25.678243637085</v>
+        <v>25.6782455444336</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G590" t="n">
-        <v>26.0056495666504</v>
+        <v>26.0056533813477</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G592" t="n">
-        <v>25.8185634613037</v>
+        <v>25.8185615539551</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G594" t="n">
-        <v>25.8185634613037</v>
+        <v>25.8185615539551</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G595" t="n">
-        <v>25.8185634613037</v>
+        <v>25.8185615539551</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>28</v>
       </c>
       <c r="G599" t="n">
-        <v>26.1927433013916</v>
+        <v>26.1927452087402</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>28.4500007629395</v>
       </c>
       <c r="G600" t="n">
-        <v>26.6137008666992</v>
+        <v>26.613697052002</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>28.25</v>
       </c>
       <c r="G601" t="n">
-        <v>26.426607131958</v>
+        <v>26.4266052246094</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>30.5499992370605</v>
       </c>
       <c r="G602" t="n">
-        <v>28.5781555175781</v>
+        <v>28.5781536102295</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G604" t="n">
-        <v>28.437837600708</v>
+        <v>28.4378356933594</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>30.25</v>
       </c>
       <c r="G605" t="n">
-        <v>28.2975158691406</v>
+        <v>28.2975177764893</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>30.9500007629395</v>
       </c>
       <c r="G606" t="n">
-        <v>28.952335357666</v>
+        <v>28.9523391723633</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>30.8500003814697</v>
       </c>
       <c r="G607" t="n">
-        <v>28.8587913513184</v>
+        <v>28.858793258667</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>31.5</v>
       </c>
       <c r="G614" t="n">
-        <v>29.7270107269287</v>
+        <v>29.7270088195801</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>35.2000007629395</v>
       </c>
       <c r="G617" t="n">
-        <v>33.2187538146973</v>
+        <v>33.21875</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>35.6500015258789</v>
       </c>
       <c r="G618" t="n">
-        <v>33.6434288024902</v>
+        <v>33.643424987793</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>36.7999992370605</v>
       </c>
       <c r="G619" t="n">
-        <v>34.7286987304688</v>
+        <v>34.7286949157715</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>36</v>
       </c>
       <c r="G621" t="n">
-        <v>33.9737281799316</v>
+        <v>33.9737243652344</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>35.5</v>
       </c>
       <c r="G622" t="n">
-        <v>33.5018653869629</v>
+        <v>33.5018692016602</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>35.5</v>
       </c>
       <c r="G624" t="n">
-        <v>33.5018653869629</v>
+        <v>33.5018692016602</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>36.5999984741211</v>
       </c>
       <c r="G625" t="n">
-        <v>34.5399475097656</v>
+        <v>34.5399513244629</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>37.4000015258789</v>
       </c>
       <c r="G626" t="n">
-        <v>35.2949256896973</v>
+        <v>35.2949295043945</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>36.7000007629395</v>
       </c>
       <c r="G629" t="n">
-        <v>34.6343269348145</v>
+        <v>34.6343307495117</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>36.9000015258789</v>
       </c>
       <c r="G631" t="n">
-        <v>34.823070526123</v>
+        <v>34.8230667114258</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>38.0999984741211</v>
       </c>
       <c r="G632" t="n">
-        <v>35.9555244445801</v>
+        <v>35.9555206298828</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>38</v>
       </c>
       <c r="G634" t="n">
-        <v>35.861156463623</v>
+        <v>35.8611526489258</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>37.0499992370605</v>
       </c>
       <c r="G636" t="n">
-        <v>34.9646224975586</v>
+        <v>34.9646263122559</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>38.25</v>
       </c>
       <c r="G637" t="n">
-        <v>36.0970840454102</v>
+        <v>36.0970802307129</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>37.4000015258789</v>
       </c>
       <c r="G639" t="n">
-        <v>35.2949256896973</v>
+        <v>35.2949295043945</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G640" t="n">
-        <v>30.3876094818115</v>
+        <v>30.3876113891602</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>32.5499992370605</v>
       </c>
       <c r="G641" t="n">
-        <v>30.7179069519043</v>
+        <v>30.7179126739502</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>32.8499984741211</v>
       </c>
       <c r="G642" t="n">
-        <v>31.0010223388672</v>
+        <v>31.0010204315186</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>33.0499992370605</v>
       </c>
       <c r="G643" t="n">
-        <v>31.1897678375244</v>
+        <v>31.1897640228271</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G644" t="n">
-        <v>30.9538383483887</v>
+        <v>30.9538326263428</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G645" t="n">
-        <v>30.3876094818115</v>
+        <v>30.3876113891602</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>32.6500015258789</v>
       </c>
       <c r="G646" t="n">
-        <v>30.8122787475586</v>
+        <v>30.8122806549072</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>34.5499992370605</v>
       </c>
       <c r="G647" t="n">
-        <v>32.6053314208984</v>
+        <v>32.6053352355957</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>35.3499984741211</v>
       </c>
       <c r="G648" t="n">
-        <v>33.3603134155273</v>
+        <v>33.3603096008301</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>36</v>
       </c>
       <c r="G651" t="n">
-        <v>33.9737281799316</v>
+        <v>33.9737243652344</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>36.6500015258789</v>
       </c>
       <c r="G655" t="n">
-        <v>34.5871429443359</v>
+        <v>34.5871391296387</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>36.2000007629395</v>
       </c>
       <c r="G656" t="n">
-        <v>34.162467956543</v>
+        <v>34.1624717712402</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>36</v>
       </c>
       <c r="G657" t="n">
-        <v>33.9737281799316</v>
+        <v>33.9737243652344</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>35.5</v>
       </c>
       <c r="G659" t="n">
-        <v>33.5018653869629</v>
+        <v>33.5018692016602</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>36.0499992370605</v>
       </c>
       <c r="G660" t="n">
-        <v>34.0209083557129</v>
+        <v>34.0209159851074</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>35.4000015258789</v>
       </c>
       <c r="G661" t="n">
-        <v>33.4074974060059</v>
+        <v>33.4074935913086</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>35.4000015258789</v>
       </c>
       <c r="G662" t="n">
-        <v>33.4074974060059</v>
+        <v>33.4074935913086</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>36.6500015258789</v>
       </c>
       <c r="G663" t="n">
-        <v>34.5871429443359</v>
+        <v>34.5871391296387</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>36.2000007629395</v>
       </c>
       <c r="G664" t="n">
-        <v>34.162467956543</v>
+        <v>34.1624717712402</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>36.7999992370605</v>
       </c>
       <c r="G666" t="n">
-        <v>34.7286987304688</v>
+        <v>34.7286949157715</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>36.3499984741211</v>
       </c>
       <c r="G667" t="n">
-        <v>34.304027557373</v>
+        <v>34.3040237426758</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>36.7000007629395</v>
       </c>
       <c r="G668" t="n">
-        <v>34.6343269348145</v>
+        <v>34.6343307495117</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>37.7000007629395</v>
       </c>
       <c r="G670" t="n">
-        <v>35.5780448913574</v>
+        <v>35.5780372619629</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>37.7000007629395</v>
       </c>
       <c r="G671" t="n">
-        <v>35.5780448913574</v>
+        <v>35.5780372619629</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>40.7999992370605</v>
       </c>
       <c r="G674" t="n">
-        <v>38.5035552978516</v>
+        <v>38.5035591125488</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>39.5999984741211</v>
       </c>
       <c r="G678" t="n">
-        <v>37.3710899353027</v>
+        <v>37.3710975646973</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>38</v>
       </c>
       <c r="G680" t="n">
-        <v>35.861156463623</v>
+        <v>35.8611526489258</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>38.9500007629395</v>
       </c>
       <c r="G682" t="n">
-        <v>36.7576789855957</v>
+        <v>36.757682800293</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>37.7000007629395</v>
       </c>
       <c r="G683" t="n">
-        <v>35.5780448913574</v>
+        <v>35.5780372619629</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>36.5</v>
       </c>
       <c r="G684" t="n">
-        <v>34.4455795288086</v>
+        <v>34.4455757141113</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>36.1500015258789</v>
       </c>
       <c r="G685" t="n">
-        <v>34.1152801513672</v>
+        <v>34.1152839660645</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>35.4000015258789</v>
       </c>
       <c r="G686" t="n">
-        <v>33.4074974060059</v>
+        <v>33.4074935913086</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>35.0499992370605</v>
       </c>
       <c r="G688" t="n">
-        <v>33.0771980285645</v>
+        <v>33.0771942138672</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>34.7999992370605</v>
       </c>
       <c r="G689" t="n">
-        <v>32.8412666320801</v>
+        <v>32.8412628173828</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>33.75</v>
       </c>
       <c r="G690" t="n">
-        <v>31.8503684997559</v>
+        <v>31.8503704071045</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>34.5</v>
       </c>
       <c r="G691" t="n">
-        <v>32.5581474304199</v>
+        <v>32.5581550598145</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>34.9000015258789</v>
       </c>
       <c r="G692" t="n">
-        <v>32.9356384277344</v>
+        <v>32.9356422424316</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>34.2999992370605</v>
       </c>
       <c r="G693" t="n">
-        <v>32.3694114685059</v>
+        <v>32.3694076538086</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>34.3499984741211</v>
       </c>
       <c r="G694" t="n">
-        <v>32.4165992736816</v>
+        <v>32.4165954589844</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>34.0999984741211</v>
       </c>
       <c r="G695" t="n">
-        <v>32.1806678771973</v>
+        <v>32.1806640625</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>34</v>
       </c>
       <c r="G696" t="n">
-        <v>32.0862998962402</v>
+        <v>32.0862922668457</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>34.75</v>
       </c>
       <c r="G697" t="n">
-        <v>32.7940826416016</v>
+        <v>32.7940788269043</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>34.1500015258789</v>
       </c>
       <c r="G698" t="n">
-        <v>32.227855682373</v>
+        <v>32.2278518676758</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>33.8499984741211</v>
       </c>
       <c r="G699" t="n">
-        <v>31.9447326660156</v>
+        <v>31.9447402954102</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>33.5499992370605</v>
       </c>
       <c r="G701" t="n">
-        <v>31.66162109375</v>
+        <v>31.6616249084473</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>33.75</v>
       </c>
       <c r="G702" t="n">
-        <v>31.8503684997559</v>
+        <v>31.8503704071045</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>33.25</v>
       </c>
       <c r="G703" t="n">
-        <v>31.378511428833</v>
+        <v>31.3785095214844</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G704" t="n">
-        <v>31.4256954193115</v>
+        <v>31.4256935119629</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>32.5</v>
       </c>
       <c r="G705" t="n">
-        <v>30.6707210540771</v>
+        <v>30.6707248687744</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>33.5</v>
       </c>
       <c r="G706" t="n">
-        <v>31.6144351959229</v>
+        <v>31.6144371032715</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>32.4500007629395</v>
       </c>
       <c r="G707" t="n">
-        <v>30.6235408782959</v>
+        <v>30.6235389709473</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>33.3499984741211</v>
       </c>
       <c r="G708" t="n">
-        <v>31.4728832244873</v>
+        <v>31.4728775024414</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>29.5499992370605</v>
       </c>
       <c r="G714" t="n">
-        <v>27.8867664337158</v>
+        <v>27.8867645263672</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>28.8500003814697</v>
       </c>
       <c r="G716" t="n">
-        <v>27.2261638641357</v>
+        <v>27.226167678833</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>29.25</v>
       </c>
       <c r="G720" t="n">
-        <v>27.6036510467529</v>
+        <v>27.6036491394043</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>30.3500003814697</v>
       </c>
       <c r="G723" t="n">
-        <v>28.6417369842529</v>
+        <v>28.6417388916016</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>30.25</v>
       </c>
       <c r="G724" t="n">
-        <v>28.5473670959473</v>
+        <v>28.5473651885986</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>30.5499992370605</v>
       </c>
       <c r="G725" t="n">
-        <v>28.8304805755615</v>
+        <v>28.8304786682129</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G726" t="n">
-        <v>30.1044940948486</v>
+        <v>30.1044960021973</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>30.9500007629395</v>
       </c>
       <c r="G727" t="n">
-        <v>29.2079658508301</v>
+        <v>29.2079677581787</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>30.5499992370605</v>
       </c>
       <c r="G728" t="n">
-        <v>28.8304805755615</v>
+        <v>28.8304786682129</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G730" t="n">
-        <v>29.6326370239258</v>
+        <v>29.6326389312744</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G731" t="n">
-        <v>29.0664043426514</v>
+        <v>29.0664081573486</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>30.5499992370605</v>
       </c>
       <c r="G732" t="n">
-        <v>28.8304805755615</v>
+        <v>28.8304786682129</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>31.0499992370605</v>
       </c>
       <c r="G733" t="n">
-        <v>29.302339553833</v>
+        <v>29.3023376464844</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>30.9500007629395</v>
       </c>
       <c r="G734" t="n">
-        <v>29.2079658508301</v>
+        <v>29.2079677581787</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>30.5499992370605</v>
       </c>
       <c r="G735" t="n">
-        <v>28.8304805755615</v>
+        <v>28.8304786682129</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>30.9500007629395</v>
       </c>
       <c r="G736" t="n">
-        <v>29.2079658508301</v>
+        <v>29.2079677581787</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G737" t="n">
-        <v>28.2170658111572</v>
+        <v>28.2170639038086</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G739" t="n">
-        <v>26.0465202331543</v>
+        <v>26.0465221405029</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G742" t="n">
-        <v>27.4620933532715</v>
+        <v>27.4620952606201</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>29</v>
       </c>
       <c r="G743" t="n">
-        <v>27.3677215576172</v>
+        <v>27.3677234649658</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>31</v>
       </c>
       <c r="G747" t="n">
-        <v>29.2551536560059</v>
+        <v>29.2551517486572</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G749" t="n">
-        <v>29.6326370239258</v>
+        <v>29.6326389312744</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>30.3500003814697</v>
       </c>
       <c r="G750" t="n">
-        <v>28.6417369842529</v>
+        <v>28.6417388916016</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G751" t="n">
-        <v>28.2170658111572</v>
+        <v>28.2170639038086</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G756" t="n">
-        <v>25.76340675354</v>
+        <v>25.7634086608887</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G758" t="n">
-        <v>25.857780456543</v>
+        <v>25.8577785491943</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>27.8500003814697</v>
       </c>
       <c r="G759" t="n">
-        <v>26.2824535369873</v>
+        <v>26.2824516296387</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G760" t="n">
-        <v>25.3859233856201</v>
+        <v>25.3859214782715</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>30.0499992370605</v>
       </c>
       <c r="G763" t="n">
-        <v>28.35862159729</v>
+        <v>28.3586235046387</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>30</v>
       </c>
       <c r="G765" t="n">
-        <v>28.3114395141602</v>
+        <v>28.3114376068115</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G768" t="n">
-        <v>26.3296337127686</v>
+        <v>26.3296356201172</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G771" t="n">
-        <v>26.1408958435059</v>
+        <v>26.1408939361572</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G772" t="n">
-        <v>25.857780456543</v>
+        <v>25.8577785491943</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G773" t="n">
-        <v>26.3296337127686</v>
+        <v>26.3296356201172</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>28.6499996185303</v>
       </c>
       <c r="G775" t="n">
-        <v>27.0374221801758</v>
+        <v>27.0374202728271</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G776" t="n">
-        <v>27.4620933532715</v>
+        <v>27.4620952606201</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>29.25</v>
       </c>
       <c r="G777" t="n">
-        <v>27.6036510467529</v>
+        <v>27.6036491394043</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>29</v>
       </c>
       <c r="G778" t="n">
-        <v>27.3677215576172</v>
+        <v>27.3677234649658</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G780" t="n">
-        <v>29.0664043426514</v>
+        <v>29.0664081573486</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>30.5499992370605</v>
       </c>
       <c r="G781" t="n">
-        <v>28.8304805755615</v>
+        <v>28.8304786682129</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>30.5499992370605</v>
       </c>
       <c r="G782" t="n">
-        <v>28.8304805755615</v>
+        <v>28.8304786682129</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>31.5499992370605</v>
       </c>
       <c r="G785" t="n">
-        <v>29.7741928100586</v>
+        <v>29.7741947174072</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>31.75</v>
       </c>
       <c r="G786" t="n">
-        <v>29.9629383087158</v>
+        <v>29.9629344940186</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>31.5499992370605</v>
       </c>
       <c r="G787" t="n">
-        <v>29.7741928100586</v>
+        <v>29.7741947174072</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>32.75</v>
       </c>
       <c r="G788" t="n">
-        <v>30.9066524505615</v>
+        <v>30.9066543579102</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>33.25</v>
       </c>
       <c r="G789" t="n">
-        <v>31.378511428833</v>
+        <v>31.3785095214844</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>33.25</v>
       </c>
       <c r="G791" t="n">
-        <v>31.378511428833</v>
+        <v>31.3785095214844</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>33.25</v>
       </c>
       <c r="G792" t="n">
-        <v>31.378511428833</v>
+        <v>31.3785095214844</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>34</v>
       </c>
       <c r="G793" t="n">
-        <v>32.0862998962402</v>
+        <v>32.0862922668457</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>34.3499984741211</v>
       </c>
       <c r="G794" t="n">
-        <v>32.4165992736816</v>
+        <v>32.4165954589844</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>34.0999984741211</v>
       </c>
       <c r="G795" t="n">
-        <v>32.1806678771973</v>
+        <v>32.1806640625</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>33.75</v>
       </c>
       <c r="G796" t="n">
-        <v>31.8503684997559</v>
+        <v>31.8503704071045</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>33.9500007629395</v>
       </c>
       <c r="G797" t="n">
-        <v>32.0391082763672</v>
+        <v>32.0391120910645</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>33.7000007629395</v>
       </c>
       <c r="G801" t="n">
-        <v>31.8031845092773</v>
+        <v>31.803186416626</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>33.8499984741211</v>
       </c>
       <c r="G803" t="n">
-        <v>31.9447326660156</v>
+        <v>31.9447402954102</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>33.8499984741211</v>
       </c>
       <c r="G804" t="n">
-        <v>31.9447326660156</v>
+        <v>31.9447402954102</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>35.0499992370605</v>
       </c>
       <c r="G806" t="n">
-        <v>33.0771980285645</v>
+        <v>33.0771942138672</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>35.4000015258789</v>
       </c>
       <c r="G808" t="n">
-        <v>33.4074974060059</v>
+        <v>33.4074935913086</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>34.9000015258789</v>
       </c>
       <c r="G809" t="n">
-        <v>32.9356384277344</v>
+        <v>32.9356422424316</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>34.7999992370605</v>
       </c>
       <c r="G810" t="n">
-        <v>32.8412666320801</v>
+        <v>32.8412628173828</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>34.2999992370605</v>
       </c>
       <c r="G811" t="n">
-        <v>32.3694114685059</v>
+        <v>32.3694076538086</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>34.7999992370605</v>
       </c>
       <c r="G812" t="n">
-        <v>32.8412666320801</v>
+        <v>32.8412628173828</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>34.7000007629395</v>
       </c>
       <c r="G813" t="n">
-        <v>32.746898651123</v>
+        <v>32.7469024658203</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>35.0999984741211</v>
       </c>
       <c r="G814" t="n">
-        <v>33.124382019043</v>
+        <v>33.1243782043457</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>31.5</v>
       </c>
       <c r="G816" t="n">
-        <v>29.7270107269287</v>
+        <v>29.7270088195801</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G821" t="n">
-        <v>29.6326370239258</v>
+        <v>29.6326389312744</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>30.9500007629395</v>
       </c>
       <c r="G823" t="n">
-        <v>29.2079658508301</v>
+        <v>29.2079677581787</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>31.3199996948242</v>
       </c>
       <c r="G827" t="n">
-        <v>29.5571384429932</v>
+        <v>29.5571403503418</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>32.060001373291</v>
       </c>
       <c r="G829" t="n">
-        <v>30.2554893493652</v>
+        <v>30.2554912567139</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>32.2400016784668</v>
       </c>
       <c r="G830" t="n">
-        <v>30.4253616333008</v>
+        <v>30.4253578186035</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G831" t="n">
-        <v>30.5763549804688</v>
+        <v>30.5763530731201</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>31.5</v>
       </c>
       <c r="G833" t="n">
-        <v>29.7270107269287</v>
+        <v>29.7270088195801</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>31.4599990844727</v>
       </c>
       <c r="G834" t="n">
-        <v>29.6892604827881</v>
+        <v>29.6892585754395</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>31.4599990844727</v>
       </c>
       <c r="G837" t="n">
-        <v>29.6892604827881</v>
+        <v>29.6892585754395</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G840" t="n">
-        <v>29.4438972473145</v>
+        <v>29.4438953399658</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>31.5</v>
       </c>
       <c r="G841" t="n">
-        <v>29.7270107269287</v>
+        <v>29.7270088195801</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>32.060001373291</v>
       </c>
       <c r="G842" t="n">
-        <v>30.2554893493652</v>
+        <v>30.2554912567139</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>31.0799999237061</v>
       </c>
       <c r="G851" t="n">
-        <v>29.3306484222412</v>
+        <v>29.3306465148926</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>30.1399993896484</v>
       </c>
       <c r="G852" t="n">
-        <v>28.4435558319092</v>
+        <v>28.4435577392578</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>30.8799991607666</v>
       </c>
       <c r="G853" t="n">
-        <v>29.1419067382812</v>
+        <v>29.141902923584</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G854" t="n">
-        <v>28.1226921081543</v>
+        <v>28.1226940155029</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>30.0400009155273</v>
       </c>
       <c r="G855" t="n">
-        <v>28.3491878509521</v>
+        <v>28.3491859436035</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>30.8400001525879</v>
       </c>
       <c r="G856" t="n">
-        <v>29.1041564941406</v>
+        <v>29.1041584014893</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>30.5200004577637</v>
       </c>
       <c r="G857" t="n">
-        <v>28.8021717071533</v>
+        <v>28.8021697998047</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>29.3199996948242</v>
       </c>
       <c r="G862" t="n">
-        <v>27.9429473876953</v>
+        <v>27.9429492950439</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>29.5400009155273</v>
       </c>
       <c r="G864" t="n">
-        <v>28.1526165008545</v>
+        <v>28.1526184082031</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>28.1599998474121</v>
       </c>
       <c r="G868" t="n">
-        <v>26.8374271392822</v>
+        <v>26.8374290466309</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>28.1800003051758</v>
       </c>
       <c r="G870" t="n">
-        <v>26.8564891815186</v>
+        <v>26.8564910888672</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>28.5200004577637</v>
       </c>
       <c r="G872" t="n">
-        <v>27.1805229187012</v>
+        <v>27.1805210113525</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>28.6399993896484</v>
       </c>
       <c r="G873" t="n">
-        <v>27.294885635376</v>
+        <v>27.2948837280273</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>28.6399993896484</v>
       </c>
       <c r="G874" t="n">
-        <v>27.294885635376</v>
+        <v>27.2948837280273</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>28.7800006866455</v>
       </c>
       <c r="G878" t="n">
-        <v>27.4283103942871</v>
+        <v>27.4283123016357</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>28.5200004577637</v>
       </c>
       <c r="G879" t="n">
-        <v>27.1805229187012</v>
+        <v>27.1805210113525</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>29.0599994659424</v>
       </c>
       <c r="G880" t="n">
-        <v>27.6951560974121</v>
+        <v>27.6951580047607</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>29</v>
       </c>
       <c r="G881" t="n">
-        <v>27.637975692749</v>
+        <v>27.6379776000977</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>29.2600002288818</v>
       </c>
       <c r="G883" t="n">
-        <v>27.8857669830322</v>
+        <v>27.885763168335</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>29.3400001525879</v>
       </c>
       <c r="G884" t="n">
-        <v>27.9620094299316</v>
+        <v>27.9620113372803</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>28.8400001525879</v>
       </c>
       <c r="G885" t="n">
-        <v>27.4854927062988</v>
+        <v>27.4854907989502</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G886" t="n">
-        <v>27.5426750183105</v>
+        <v>27.5426731109619</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>29.6599998474121</v>
       </c>
       <c r="G888" t="n">
-        <v>28.2669773101807</v>
+        <v>28.2669792175293</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>30.1599998474121</v>
       </c>
       <c r="G889" t="n">
-        <v>28.7434940338135</v>
+        <v>28.7434978485107</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>30.3199996948242</v>
       </c>
       <c r="G891" t="n">
-        <v>28.8959808349609</v>
+        <v>28.8959827423096</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G892" t="n">
-        <v>29.4487400054932</v>
+        <v>29.4487419128418</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>30.9799995422363</v>
       </c>
       <c r="G893" t="n">
-        <v>29.5249824523926</v>
+        <v>29.5249843597412</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>30.8199996948242</v>
       </c>
       <c r="G895" t="n">
-        <v>29.3724975585938</v>
+        <v>29.3724994659424</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G896" t="n">
-        <v>29.8299522399902</v>
+        <v>29.8299541473389</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>31.7800006866455</v>
       </c>
       <c r="G898" t="n">
-        <v>30.287410736084</v>
+        <v>30.2874126434326</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>30.4200000762939</v>
       </c>
       <c r="G899" t="n">
-        <v>28.9912853240967</v>
+        <v>28.991283416748</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G903" t="n">
-        <v>28.8769226074219</v>
+        <v>28.8769207000732</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>29.9400005340576</v>
       </c>
       <c r="G906" t="n">
-        <v>28.5338306427002</v>
+        <v>28.5338325500488</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>29.7199993133545</v>
       </c>
       <c r="G908" t="n">
-        <v>28.3241634368896</v>
+        <v>28.3241596221924</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>29.5</v>
       </c>
       <c r="G909" t="n">
-        <v>28.1144962310791</v>
+        <v>28.1144943237305</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>28.7800006866455</v>
       </c>
       <c r="G910" t="n">
-        <v>27.4283103942871</v>
+        <v>27.4283123016357</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>28.6399993896484</v>
       </c>
       <c r="G911" t="n">
-        <v>27.294885635376</v>
+        <v>27.2948837280273</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>28.1399993896484</v>
       </c>
       <c r="G913" t="n">
-        <v>26.8183708190918</v>
+        <v>26.8183670043945</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>28.1800003051758</v>
       </c>
       <c r="G918" t="n">
-        <v>26.8564891815186</v>
+        <v>26.8564910888672</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>28.1800003051758</v>
       </c>
       <c r="G920" t="n">
-        <v>26.8564891815186</v>
+        <v>26.8564910888672</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>27.6399993896484</v>
       </c>
       <c r="G921" t="n">
-        <v>26.3418521881104</v>
+        <v>26.3418502807617</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>28.5200004577637</v>
       </c>
       <c r="G923" t="n">
-        <v>27.1805229187012</v>
+        <v>27.1805210113525</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>28.8799991607666</v>
       </c>
       <c r="G924" t="n">
-        <v>27.5236148834229</v>
+        <v>27.5236129760742</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>29.2600002288818</v>
       </c>
       <c r="G927" t="n">
-        <v>27.8857669830322</v>
+        <v>27.885763168335</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>28.2399997711182</v>
       </c>
       <c r="G932" t="n">
-        <v>26.9136695861816</v>
+        <v>26.9136714935303</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>28</v>
       </c>
       <c r="G933" t="n">
-        <v>26.6849422454834</v>
+        <v>26.684944152832</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>27.5799999237061</v>
       </c>
       <c r="G934" t="n">
-        <v>26.28466796875</v>
+        <v>26.2846698760986</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>28.1399993896484</v>
       </c>
       <c r="G935" t="n">
-        <v>26.8183708190918</v>
+        <v>26.8183670043945</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>28.8400001525879</v>
       </c>
       <c r="G938" t="n">
-        <v>27.4854927062988</v>
+        <v>27.4854907989502</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>29.3199996948242</v>
       </c>
       <c r="G940" t="n">
-        <v>27.9429473876953</v>
+        <v>27.9429492950439</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>29</v>
       </c>
       <c r="G941" t="n">
-        <v>27.637975692749</v>
+        <v>27.6379776000977</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>27.9599990844727</v>
       </c>
       <c r="G947" t="n">
-        <v>26.6468200683594</v>
+        <v>26.6468181610107</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>27.9599990844727</v>
       </c>
       <c r="G948" t="n">
-        <v>26.6468200683594</v>
+        <v>26.6468181610107</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>28.0200004577637</v>
       </c>
       <c r="G949" t="n">
-        <v>26.7040042877197</v>
+        <v>26.7040061950684</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>28.5799999237061</v>
       </c>
       <c r="G953" t="n">
-        <v>27.2377014160156</v>
+        <v>27.2377033233643</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G954" t="n">
-        <v>27.256763458252</v>
+        <v>27.2567653656006</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>28.1399993896484</v>
       </c>
       <c r="G955" t="n">
-        <v>26.8183708190918</v>
+        <v>26.8183670043945</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>28</v>
       </c>
       <c r="G957" t="n">
-        <v>26.6849422454834</v>
+        <v>26.684944152832</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>27.6399993896484</v>
       </c>
       <c r="G958" t="n">
-        <v>26.3418521881104</v>
+        <v>26.3418502807617</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>26.8600006103516</v>
       </c>
       <c r="G960" t="n">
-        <v>25.5984859466553</v>
+        <v>25.5984878540039</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G962" t="n">
-        <v>25.5412998199463</v>
+        <v>25.5413017272949</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>28.2800006866455</v>
       </c>
       <c r="G964" t="n">
-        <v>26.9517955780029</v>
+        <v>26.9517936706543</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>27.6399993896484</v>
       </c>
       <c r="G969" t="n">
-        <v>26.3418521881104</v>
+        <v>26.3418502807617</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>26.8400001525879</v>
       </c>
       <c r="G971" t="n">
-        <v>25.5794239044189</v>
+        <v>25.5794277191162</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>27.6599998474121</v>
       </c>
       <c r="G972" t="n">
-        <v>26.3609104156494</v>
+        <v>26.3609142303467</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>27.9599990844727</v>
       </c>
       <c r="G975" t="n">
-        <v>26.6468200683594</v>
+        <v>26.6468181610107</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>28.0799999237061</v>
       </c>
       <c r="G976" t="n">
-        <v>26.7611846923828</v>
+        <v>26.7611885070801</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>28.8400001525879</v>
       </c>
       <c r="G977" t="n">
-        <v>27.4854927062988</v>
+        <v>27.4854907989502</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>29.1399993896484</v>
       </c>
       <c r="G978" t="n">
-        <v>27.7714042663574</v>
+        <v>27.7714023590088</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>29.9799995422363</v>
       </c>
       <c r="G983" t="n">
-        <v>28.571949005127</v>
+        <v>28.5719509124756</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>30.4599990844727</v>
       </c>
       <c r="G984" t="n">
-        <v>29.0294055938721</v>
+        <v>29.0294036865234</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>29.8400001525879</v>
       </c>
       <c r="G985" t="n">
-        <v>28.4385261535645</v>
+        <v>28.4385242462158</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>29.8600006103516</v>
       </c>
       <c r="G989" t="n">
-        <v>28.4575862884521</v>
+        <v>28.4575843811035</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>29.6200008392334</v>
       </c>
       <c r="G991" t="n">
-        <v>28.2288589477539</v>
+        <v>28.2288570404053</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>33.0800018310547</v>
       </c>
       <c r="G995" t="n">
-        <v>31.5263576507568</v>
+        <v>31.5263557434082</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>33.4599990844727</v>
       </c>
       <c r="G996" t="n">
-        <v>31.8885078430176</v>
+        <v>31.8885040283203</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G1000" t="n">
-        <v>30.7829856872559</v>
+        <v>30.7829875946045</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G1001" t="n">
-        <v>31.2595062255859</v>
+        <v>31.25950050354</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>32.3800010681152</v>
       </c>
       <c r="G1003" t="n">
-        <v>30.8592338562012</v>
+        <v>30.8592319488525</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>32.3800010681152</v>
       </c>
       <c r="G1006" t="n">
-        <v>30.8592338562012</v>
+        <v>30.8592319488525</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>32.060001373291</v>
       </c>
       <c r="G1007" t="n">
-        <v>30.5542602539062</v>
+        <v>30.5542621612549</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>32.4799995422363</v>
       </c>
       <c r="G1009" t="n">
-        <v>30.954532623291</v>
+        <v>30.9545345306396</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>31.9599990844727</v>
       </c>
       <c r="G1010" t="n">
-        <v>30.4589557647705</v>
+        <v>30.4589576721191</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>31.9200000762939</v>
       </c>
       <c r="G1012" t="n">
-        <v>30.4208354949951</v>
+        <v>30.4208374023438</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>32.4799995422363</v>
       </c>
       <c r="G1013" t="n">
-        <v>30.954532623291</v>
+        <v>30.9545345306396</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>32.4599990844727</v>
       </c>
       <c r="G1014" t="n">
-        <v>30.935474395752</v>
+        <v>30.9354724884033</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>31.5599994659424</v>
       </c>
       <c r="G1015" t="n">
-        <v>30.0777416229248</v>
+        <v>30.0777454376221</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>32.1199989318848</v>
       </c>
       <c r="G1017" t="n">
-        <v>30.611442565918</v>
+        <v>30.6114406585693</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G1018" t="n">
-        <v>30.3064708709717</v>
+        <v>30.306468963623</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>34.2000007629395</v>
       </c>
       <c r="G1019" t="n">
-        <v>32.5937538146973</v>
+        <v>32.5937576293945</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>34.560001373291</v>
       </c>
       <c r="G1020" t="n">
-        <v>32.9368515014648</v>
+        <v>32.9368476867676</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>36.1399993896484</v>
       </c>
       <c r="G1023" t="n">
-        <v>34.4426422119141</v>
+        <v>34.4426383972168</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>37.8400001525879</v>
       </c>
       <c r="G1026" t="n">
-        <v>36.0627975463867</v>
+        <v>36.0627937316895</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>38.2799987792969</v>
       </c>
       <c r="G1027" t="n">
-        <v>36.4821319580078</v>
+        <v>36.4821281433105</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>38.5400009155273</v>
       </c>
       <c r="G1028" t="n">
-        <v>36.7299194335938</v>
+        <v>36.7299156188965</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>36.9799995422363</v>
       </c>
       <c r="G1029" t="n">
-        <v>35.2431831359863</v>
+        <v>35.2431869506836</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27149,7 +27149,7 @@
         <v>37.0999984741211</v>
       </c>
       <c r="G1030" t="n">
-        <v>35.3575477600098</v>
+        <v>35.357551574707</v>
       </c>
       <c r="H1030" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>34.0999984741211</v>
       </c>
       <c r="G1035" t="n">
-        <v>32.4984512329102</v>
+        <v>32.4984474182129</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>32.8199996948242</v>
       </c>
       <c r="G1037" t="n">
-        <v>31.2785663604736</v>
+        <v>31.2785625457764</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>33.0200004577637</v>
       </c>
       <c r="G1038" t="n">
-        <v>31.4691715240479</v>
+        <v>31.4691734313965</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>33.5200004577637</v>
       </c>
       <c r="G1039" t="n">
-        <v>31.9456939697266</v>
+        <v>31.9456901550293</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>34.5800018310547</v>
       </c>
       <c r="G1040" t="n">
-        <v>32.9559097290039</v>
+        <v>32.9559059143066</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G1042" t="n">
-        <v>31.2595062255859</v>
+        <v>31.25950050354</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>34</v>
       </c>
       <c r="G1045" t="n">
-        <v>32.4031448364258</v>
+        <v>32.4031410217285</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>33.7000007629395</v>
       </c>
       <c r="G1048" t="n">
-        <v>32.1172370910645</v>
+        <v>32.1172409057617</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>33.6399993896484</v>
       </c>
       <c r="G1049" t="n">
-        <v>32.0600509643555</v>
+        <v>32.0600471496582</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>33.0800018310547</v>
       </c>
       <c r="G1052" t="n">
-        <v>31.5263576507568</v>
+        <v>31.5263557434082</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27799,7 +27799,7 @@
         <v>30.8799991607666</v>
       </c>
       <c r="G1055" t="n">
-        <v>29.4296817779541</v>
+        <v>29.4296779632568</v>
       </c>
       <c r="H1055" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>29.5400009155273</v>
       </c>
       <c r="G1056" t="n">
-        <v>28.1526165008545</v>
+        <v>28.1526184082031</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>30</v>
       </c>
       <c r="G1057" t="n">
-        <v>28.5910129547119</v>
+        <v>28.5910110473633</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>31.0799999237061</v>
       </c>
       <c r="G1060" t="n">
-        <v>29.6202869415283</v>
+        <v>29.6202850341797</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>27.2199993133545</v>
       </c>
       <c r="G1064" t="n">
-        <v>25.941577911377</v>
+        <v>25.9415760040283</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>26.8400001525879</v>
       </c>
       <c r="G1069" t="n">
-        <v>25.5794239044189</v>
+        <v>25.5794277191162</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>28.0799999237061</v>
       </c>
       <c r="G1076" t="n">
-        <v>26.7611846923828</v>
+        <v>26.7611885070801</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28371,7 +28371,7 @@
         <v>26.7399997711182</v>
       </c>
       <c r="G1077" t="n">
-        <v>25.4841194152832</v>
+        <v>25.4841213226318</v>
       </c>
       <c r="H1077" t="s">
         <v>8</v>
@@ -28397,7 +28397,7 @@
         <v>26</v>
       </c>
       <c r="G1078" t="n">
-        <v>24.7788753509521</v>
+        <v>24.7788734436035</v>
       </c>
       <c r="H1078" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>27.6800003051758</v>
       </c>
       <c r="G1079" t="n">
-        <v>26.3799743652344</v>
+        <v>26.3799724578857</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>25.6800003051758</v>
       </c>
       <c r="G1082" t="n">
-        <v>24.4739055633545</v>
+        <v>24.4739074707031</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>24.6800003051758</v>
       </c>
       <c r="G1083" t="n">
-        <v>23.5208702087402</v>
+        <v>23.5208721160889</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>24.8799991607666</v>
       </c>
       <c r="G1084" t="n">
-        <v>23.7114772796631</v>
+        <v>23.7114791870117</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>25.3199996948242</v>
       </c>
       <c r="G1086" t="n">
-        <v>24.1308135986328</v>
+        <v>24.1308116912842</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>25.9400005340576</v>
       </c>
       <c r="G1088" t="n">
-        <v>24.7216949462891</v>
+        <v>24.7216930389404</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>28.6200008392334</v>
       </c>
       <c r="G1093" t="n">
-        <v>27.2758255004883</v>
+        <v>27.2758235931396</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>28.8199996948242</v>
       </c>
       <c r="G1095" t="n">
-        <v>27.4664287567139</v>
+        <v>27.4664306640625</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>28.7800006866455</v>
       </c>
       <c r="G1098" t="n">
-        <v>27.4283103942871</v>
+        <v>27.4283123016357</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>27.1800003051758</v>
       </c>
       <c r="G1104" t="n">
-        <v>25.9034557342529</v>
+        <v>25.9034538269043</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>26.6399993896484</v>
       </c>
       <c r="G1105" t="n">
-        <v>25.3888206481934</v>
+        <v>25.3888187408447</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1106" t="n">
-        <v>25.5412998199463</v>
+        <v>25.5413017272949</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>26.5</v>
       </c>
       <c r="G1108" t="n">
-        <v>25.255392074585</v>
+        <v>25.2553939819336</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29203,7 +29203,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1109" t="n">
-        <v>25.5412998199463</v>
+        <v>25.5413017272949</v>
       </c>
       <c r="H1109" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>26.8199996948242</v>
       </c>
       <c r="G1114" t="n">
-        <v>25.5603618621826</v>
+        <v>25.5603637695312</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>27</v>
       </c>
       <c r="G1115" t="n">
-        <v>25.7319087982178</v>
+        <v>25.7319107055664</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29463,7 +29463,7 @@
         <v>29.2600002288818</v>
       </c>
       <c r="G1119" t="n">
-        <v>27.8857669830322</v>
+        <v>27.885763168335</v>
       </c>
       <c r="H1119" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>29.0200004577637</v>
       </c>
       <c r="G1120" t="n">
-        <v>27.657039642334</v>
+        <v>27.6570377349854</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>29.9799995422363</v>
       </c>
       <c r="G1121" t="n">
-        <v>28.571949005127</v>
+        <v>28.5719509124756</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>31.0799999237061</v>
       </c>
       <c r="G1126" t="n">
-        <v>29.6202869415283</v>
+        <v>29.6202850341797</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>30.6599998474121</v>
       </c>
       <c r="G1127" t="n">
-        <v>29.2200107574463</v>
+        <v>29.2200126647949</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29697,7 +29697,7 @@
         <v>29.3199996948242</v>
       </c>
       <c r="G1128" t="n">
-        <v>27.9429473876953</v>
+        <v>27.9429492950439</v>
       </c>
       <c r="H1128" t="s">
         <v>8</v>
@@ -29775,7 +29775,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1131" t="n">
-        <v>27.256763458252</v>
+        <v>27.2567653656006</v>
       </c>
       <c r="H1131" t="s">
         <v>8</v>
@@ -29801,7 +29801,7 @@
         <v>28.6200008392334</v>
       </c>
       <c r="G1132" t="n">
-        <v>27.2758255004883</v>
+        <v>27.2758235931396</v>
       </c>
       <c r="H1132" t="s">
         <v>8</v>
@@ -29905,7 +29905,7 @@
         <v>28.0799999237061</v>
       </c>
       <c r="G1136" t="n">
-        <v>26.7611846923828</v>
+        <v>26.7611885070801</v>
       </c>
       <c r="H1136" t="s">
         <v>8</v>
@@ -29931,7 +29931,7 @@
         <v>27.5200004577637</v>
       </c>
       <c r="G1137" t="n">
-        <v>26.2274894714355</v>
+        <v>26.2274875640869</v>
       </c>
       <c r="H1137" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>26.4200000762939</v>
       </c>
       <c r="G1138" t="n">
-        <v>25.1791477203369</v>
+        <v>25.1791515350342</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -29983,7 +29983,7 @@
         <v>26.4200000762939</v>
       </c>
       <c r="G1139" t="n">
-        <v>25.1791477203369</v>
+        <v>25.1791515350342</v>
       </c>
       <c r="H1139" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>25.2800006866455</v>
       </c>
       <c r="G1142" t="n">
-        <v>24.0926933288574</v>
+        <v>24.0926914215088</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>25.3600006103516</v>
       </c>
       <c r="G1143" t="n">
-        <v>24.1689357757568</v>
+        <v>24.1689338684082</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30113,7 +30113,7 @@
         <v>25.5400009155273</v>
       </c>
       <c r="G1144" t="n">
-        <v>24.3404808044434</v>
+        <v>24.340482711792</v>
       </c>
       <c r="H1144" t="s">
         <v>8</v>
@@ -30191,7 +30191,7 @@
         <v>25.4599990844727</v>
       </c>
       <c r="G1147" t="n">
-        <v>24.2642364501953</v>
+        <v>24.2642383575439</v>
       </c>
       <c r="H1147" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>25.7399997711182</v>
       </c>
       <c r="G1148" t="n">
-        <v>24.5310878753662</v>
+        <v>24.5310859680176</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>25.2600002288818</v>
       </c>
       <c r="G1152" t="n">
-        <v>24.0736312866211</v>
+        <v>24.0736331939697</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>24.7399997711182</v>
       </c>
       <c r="G1153" t="n">
-        <v>23.5780544281006</v>
+        <v>23.578052520752</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30373,7 +30373,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G1154" t="n">
-        <v>23.6352348327637</v>
+        <v>23.6352367401123</v>
       </c>
       <c r="H1154" t="s">
         <v>8</v>
@@ -30425,7 +30425,7 @@
         <v>25.0200004577637</v>
       </c>
       <c r="G1156" t="n">
-        <v>23.8449058532715</v>
+        <v>23.8449039459229</v>
       </c>
       <c r="H1156" t="s">
         <v>8</v>
@@ -30477,7 +30477,7 @@
         <v>24.7600002288818</v>
       </c>
       <c r="G1158" t="n">
-        <v>23.5971126556396</v>
+        <v>23.5971145629883</v>
       </c>
       <c r="H1158" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>23.9799995422363</v>
       </c>
       <c r="G1159" t="n">
-        <v>22.8537502288818</v>
+        <v>22.8537464141846</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30555,7 +30555,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G1161" t="n">
-        <v>22.7775077819824</v>
+        <v>22.7775058746338</v>
       </c>
       <c r="H1161" t="s">
         <v>8</v>
@@ -30607,7 +30607,7 @@
         <v>24.4400005340576</v>
       </c>
       <c r="G1163" t="n">
-        <v>23.2921447753906</v>
+        <v>23.292142868042</v>
       </c>
       <c r="H1163" t="s">
         <v>8</v>
@@ -30633,7 +30633,7 @@
         <v>24.6399993896484</v>
       </c>
       <c r="G1164" t="n">
-        <v>23.4827499389648</v>
+        <v>23.4827480316162</v>
       </c>
       <c r="H1164" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>25.1399993896484</v>
       </c>
       <c r="G1165" t="n">
-        <v>23.9592666625977</v>
+        <v>23.959264755249</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30711,7 +30711,7 @@
         <v>25.9799995422363</v>
       </c>
       <c r="G1167" t="n">
-        <v>24.7598152160645</v>
+        <v>24.7598133087158</v>
       </c>
       <c r="H1167" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>27</v>
       </c>
       <c r="G1173" t="n">
-        <v>25.7319087982178</v>
+        <v>25.7319107055664</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -30997,7 +30997,7 @@
         <v>25.2600002288818</v>
       </c>
       <c r="G1178" t="n">
-        <v>24.0736312866211</v>
+        <v>24.0736331939697</v>
       </c>
       <c r="H1178" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>25.2600002288818</v>
       </c>
       <c r="G1180" t="n">
-        <v>24.0736312866211</v>
+        <v>24.0736331939697</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>25.3199996948242</v>
       </c>
       <c r="G1181" t="n">
-        <v>24.1308135986328</v>
+        <v>24.1308116912842</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>26</v>
       </c>
       <c r="G1182" t="n">
-        <v>24.7788753509521</v>
+        <v>24.7788734436035</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31127,7 +31127,7 @@
         <v>26.0200004577637</v>
       </c>
       <c r="G1183" t="n">
-        <v>24.7979393005371</v>
+        <v>24.7979373931885</v>
       </c>
       <c r="H1183" t="s">
         <v>8</v>
@@ -31153,7 +31153,7 @@
         <v>25.8400001525879</v>
       </c>
       <c r="G1184" t="n">
-        <v>24.6263904571533</v>
+        <v>24.626392364502</v>
       </c>
       <c r="H1184" t="s">
         <v>8</v>
@@ -31205,7 +31205,7 @@
         <v>25.3199996948242</v>
       </c>
       <c r="G1186" t="n">
-        <v>24.1308135986328</v>
+        <v>24.1308116912842</v>
       </c>
       <c r="H1186" t="s">
         <v>8</v>
@@ -31309,7 +31309,7 @@
         <v>25.9799995422363</v>
       </c>
       <c r="G1190" t="n">
-        <v>24.7598152160645</v>
+        <v>24.7598133087158</v>
       </c>
       <c r="H1190" t="s">
         <v>8</v>
@@ -31387,7 +31387,7 @@
         <v>25.2800006866455</v>
       </c>
       <c r="G1193" t="n">
-        <v>24.0926933288574</v>
+        <v>24.0926914215088</v>
       </c>
       <c r="H1193" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>25.8799991607666</v>
       </c>
       <c r="G1194" t="n">
-        <v>24.6645126342773</v>
+        <v>24.6645107269287</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>25.8199996948242</v>
       </c>
       <c r="G1195" t="n">
-        <v>24.6073322296143</v>
+        <v>24.6073303222656</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31569,7 +31569,7 @@
         <v>26.0200004577637</v>
       </c>
       <c r="G1200" t="n">
-        <v>24.7979393005371</v>
+        <v>24.7979373931885</v>
       </c>
       <c r="H1200" t="s">
         <v>8</v>
@@ -31595,7 +31595,7 @@
         <v>25.5</v>
       </c>
       <c r="G1201" t="n">
-        <v>24.3023586273193</v>
+        <v>24.302360534668</v>
       </c>
       <c r="H1201" t="s">
         <v>8</v>
@@ -31621,7 +31621,7 @@
         <v>25.8799991607666</v>
       </c>
       <c r="G1202" t="n">
-        <v>24.6645126342773</v>
+        <v>24.6645107269287</v>
       </c>
       <c r="H1202" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>25.2600002288818</v>
       </c>
       <c r="G1203" t="n">
-        <v>24.0736312866211</v>
+        <v>24.0736331939697</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31673,7 +31673,7 @@
         <v>25.3400001525879</v>
       </c>
       <c r="G1204" t="n">
-        <v>24.1498718261719</v>
+        <v>24.1498737335205</v>
       </c>
       <c r="H1204" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>26.0400009155273</v>
       </c>
       <c r="G1207" t="n">
-        <v>24.8169975280762</v>
+        <v>24.8169994354248</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31855,7 +31855,7 @@
         <v>27.7399997711182</v>
       </c>
       <c r="G1211" t="n">
-        <v>26.4371547698975</v>
+        <v>26.4371528625488</v>
       </c>
       <c r="H1211" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>27.6800003051758</v>
       </c>
       <c r="G1214" t="n">
-        <v>26.3799743652344</v>
+        <v>26.3799724578857</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -31959,7 +31959,7 @@
         <v>27.5599994659424</v>
       </c>
       <c r="G1215" t="n">
-        <v>26.2656097412109</v>
+        <v>26.2656078338623</v>
       </c>
       <c r="H1215" t="s">
         <v>8</v>
@@ -32037,7 +32037,7 @@
         <v>26.9799995422363</v>
       </c>
       <c r="G1218" t="n">
-        <v>25.7128505706787</v>
+        <v>25.7128486633301</v>
       </c>
       <c r="H1218" t="s">
         <v>8</v>
@@ -32089,7 +32089,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1220" t="n">
-        <v>25.9225158691406</v>
+        <v>25.9225177764893</v>
       </c>
       <c r="H1220" t="s">
         <v>8</v>
@@ -32141,7 +32141,7 @@
         <v>27.1399993896484</v>
       </c>
       <c r="G1222" t="n">
-        <v>25.8653354644775</v>
+        <v>25.8653335571289</v>
       </c>
       <c r="H1222" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1223" t="n">
-        <v>25.9225158691406</v>
+        <v>25.9225177764893</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32219,7 +32219,7 @@
         <v>26.7600002288818</v>
       </c>
       <c r="G1225" t="n">
-        <v>25.5031833648682</v>
+        <v>25.5031814575195</v>
       </c>
       <c r="H1225" t="s">
         <v>8</v>
@@ -32297,7 +32297,7 @@
         <v>25.4400005340576</v>
       </c>
       <c r="G1228" t="n">
-        <v>24.2451782226562</v>
+        <v>24.2451801300049</v>
       </c>
       <c r="H1228" t="s">
         <v>8</v>
@@ -32349,7 +32349,7 @@
         <v>25.6599998474121</v>
       </c>
       <c r="G1230" t="n">
-        <v>24.4548435211182</v>
+        <v>24.4548454284668</v>
       </c>
       <c r="H1230" t="s">
         <v>8</v>
@@ -32401,7 +32401,7 @@
         <v>26.7600002288818</v>
       </c>
       <c r="G1232" t="n">
-        <v>25.5031833648682</v>
+        <v>25.5031814575195</v>
       </c>
       <c r="H1232" t="s">
         <v>8</v>
@@ -32453,7 +32453,7 @@
         <v>27.1399993896484</v>
       </c>
       <c r="G1234" t="n">
-        <v>25.8653354644775</v>
+        <v>25.8653335571289</v>
       </c>
       <c r="H1234" t="s">
         <v>8</v>
@@ -32479,7 +32479,7 @@
         <v>27.6800003051758</v>
       </c>
       <c r="G1235" t="n">
-        <v>26.3799743652344</v>
+        <v>26.3799724578857</v>
       </c>
       <c r="H1235" t="s">
         <v>8</v>
@@ -32531,7 +32531,7 @@
         <v>29.1399993896484</v>
       </c>
       <c r="G1237" t="n">
-        <v>27.7714042663574</v>
+        <v>27.7714023590088</v>
       </c>
       <c r="H1237" t="s">
         <v>8</v>
@@ -32557,7 +32557,7 @@
         <v>27.9599990844727</v>
       </c>
       <c r="G1238" t="n">
-        <v>26.6468200683594</v>
+        <v>26.6468181610107</v>
       </c>
       <c r="H1238" t="s">
         <v>8</v>
@@ -32583,7 +32583,7 @@
         <v>28.2800006866455</v>
       </c>
       <c r="G1239" t="n">
-        <v>26.9517955780029</v>
+        <v>26.9517936706543</v>
       </c>
       <c r="H1239" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>29.9799995422363</v>
       </c>
       <c r="G1240" t="n">
-        <v>28.571949005127</v>
+        <v>28.5719509124756</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32635,7 +32635,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G1241" t="n">
-        <v>29.4487400054932</v>
+        <v>29.4487419128418</v>
       </c>
       <c r="H1241" t="s">
         <v>8</v>
@@ -32661,7 +32661,7 @@
         <v>31.0799999237061</v>
       </c>
       <c r="G1242" t="n">
-        <v>29.6202869415283</v>
+        <v>29.6202850341797</v>
       </c>
       <c r="H1242" t="s">
         <v>8</v>
@@ -32713,7 +32713,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G1244" t="n">
-        <v>31.354808807373</v>
+        <v>31.3548107147217</v>
       </c>
       <c r="H1244" t="s">
         <v>8</v>
@@ -32739,7 +32739,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1245" t="n">
-        <v>31.7360248565674</v>
+        <v>31.7360210418701</v>
       </c>
       <c r="H1245" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>33.1199989318848</v>
       </c>
       <c r="G1248" t="n">
-        <v>31.5644721984863</v>
+        <v>31.5644760131836</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32843,7 +32843,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G1249" t="n">
-        <v>31.5454139709473</v>
+        <v>31.5454158782959</v>
       </c>
       <c r="H1249" t="s">
         <v>8</v>
@@ -32895,7 +32895,7 @@
         <v>33.5400009155273</v>
       </c>
       <c r="G1251" t="n">
-        <v>31.9647483825684</v>
+        <v>31.9647521972656</v>
       </c>
       <c r="H1251" t="s">
         <v>8</v>
@@ -32921,7 +32921,7 @@
         <v>34.4599990844727</v>
       </c>
       <c r="G1252" t="n">
-        <v>32.8415412902832</v>
+        <v>32.8415374755859</v>
       </c>
       <c r="H1252" t="s">
         <v>8</v>
@@ -32973,7 +32973,7 @@
         <v>35.3800010681152</v>
       </c>
       <c r="G1254" t="n">
-        <v>33.7183380126953</v>
+        <v>33.7183303833008</v>
       </c>
       <c r="H1254" t="s">
         <v>8</v>
@@ -32999,7 +32999,7 @@
         <v>35.1399993896484</v>
       </c>
       <c r="G1255" t="n">
-        <v>33.4896087646484</v>
+        <v>33.4896049499512</v>
       </c>
       <c r="H1255" t="s">
         <v>8</v>
@@ -33051,7 +33051,7 @@
         <v>36.439998626709</v>
       </c>
       <c r="G1257" t="n">
-        <v>34.7285461425781</v>
+        <v>34.7285423278809</v>
       </c>
       <c r="H1257" t="s">
         <v>8</v>
@@ -33077,7 +33077,7 @@
         <v>36.6399993896484</v>
       </c>
       <c r="G1258" t="n">
-        <v>34.9191513061523</v>
+        <v>34.9191551208496</v>
       </c>
       <c r="H1258" t="s">
         <v>8</v>
@@ -33129,7 +33129,7 @@
         <v>35.8199996948242</v>
       </c>
       <c r="G1260" t="n">
-        <v>34.1376647949219</v>
+        <v>34.1376686096191</v>
       </c>
       <c r="H1260" t="s">
         <v>8</v>
@@ -33155,7 +33155,7 @@
         <v>36.5400009155273</v>
       </c>
       <c r="G1261" t="n">
-        <v>34.8238563537598</v>
+        <v>34.8238525390625</v>
       </c>
       <c r="H1261" t="s">
         <v>8</v>
@@ -33259,7 +33259,7 @@
         <v>36</v>
       </c>
       <c r="G1265" t="n">
-        <v>34.3092155456543</v>
+        <v>34.309211730957</v>
       </c>
       <c r="H1265" t="s">
         <v>8</v>
@@ -33285,7 +33285,7 @@
         <v>36.9199981689453</v>
       </c>
       <c r="G1266" t="n">
-        <v>35.1860008239746</v>
+        <v>35.1860046386719</v>
       </c>
       <c r="H1266" t="s">
         <v>8</v>
@@ -33337,7 +33337,7 @@
         <v>36.4799995422363</v>
       </c>
       <c r="G1268" t="n">
-        <v>34.7666664123535</v>
+        <v>34.7666702270508</v>
       </c>
       <c r="H1268" t="s">
         <v>8</v>
@@ -33389,7 +33389,7 @@
         <v>35.7000007629395</v>
       </c>
       <c r="G1270" t="n">
-        <v>34.0233001708984</v>
+        <v>34.0233039855957</v>
       </c>
       <c r="H1270" t="s">
         <v>8</v>
@@ -33415,7 +33415,7 @@
         <v>35.8400001525879</v>
       </c>
       <c r="G1271" t="n">
-        <v>34.1567306518555</v>
+        <v>34.1567268371582</v>
       </c>
       <c r="H1271" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>34.5800018310547</v>
       </c>
       <c r="G1272" t="n">
-        <v>32.9559097290039</v>
+        <v>32.9559059143066</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33467,7 +33467,7 @@
         <v>33.4199981689453</v>
       </c>
       <c r="G1273" t="n">
-        <v>31.8503875732422</v>
+        <v>31.8503837585449</v>
       </c>
       <c r="H1273" t="s">
         <v>8</v>
@@ -33519,7 +33519,7 @@
         <v>34.2400016784668</v>
       </c>
       <c r="G1275" t="n">
-        <v>32.6318740844727</v>
+        <v>32.6318778991699</v>
       </c>
       <c r="H1275" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>35.5200004577637</v>
       </c>
       <c r="G1278" t="n">
-        <v>33.8517608642578</v>
+        <v>33.8517570495605</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33675,7 +33675,7 @@
         <v>34.939998626709</v>
       </c>
       <c r="G1281" t="n">
-        <v>33.298999786377</v>
+        <v>33.2989959716797</v>
       </c>
       <c r="H1281" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>34.5</v>
       </c>
       <c r="G1282" t="n">
-        <v>32.8796615600586</v>
+        <v>32.8796653747559</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33727,7 +33727,7 @@
         <v>34.2400016784668</v>
       </c>
       <c r="G1283" t="n">
-        <v>32.6318740844727</v>
+        <v>32.6318778991699</v>
       </c>
       <c r="H1283" t="s">
         <v>8</v>
@@ -33753,7 +33753,7 @@
         <v>34.8400001525879</v>
       </c>
       <c r="G1284" t="n">
-        <v>33.2036933898926</v>
+        <v>33.2036895751953</v>
       </c>
       <c r="H1284" t="s">
         <v>8</v>
@@ -33805,7 +33805,7 @@
         <v>33.5400009155273</v>
       </c>
       <c r="G1286" t="n">
-        <v>31.9647483825684</v>
+        <v>31.9647521972656</v>
       </c>
       <c r="H1286" t="s">
         <v>8</v>
@@ -33831,7 +33831,7 @@
         <v>34.1399993896484</v>
       </c>
       <c r="G1287" t="n">
-        <v>32.5365753173828</v>
+        <v>32.5365715026855</v>
       </c>
       <c r="H1287" t="s">
         <v>8</v>
@@ -33883,7 +33883,7 @@
         <v>34</v>
       </c>
       <c r="G1289" t="n">
-        <v>32.4031448364258</v>
+        <v>32.4031410217285</v>
       </c>
       <c r="H1289" t="s">
         <v>8</v>
@@ -33909,7 +33909,7 @@
         <v>33.0400009155273</v>
       </c>
       <c r="G1290" t="n">
-        <v>31.4882354736328</v>
+        <v>31.4882373809814</v>
       </c>
       <c r="H1290" t="s">
         <v>8</v>
@@ -33935,7 +33935,7 @@
         <v>33.2200012207031</v>
       </c>
       <c r="G1291" t="n">
-        <v>31.6597785949707</v>
+        <v>31.659782409668</v>
       </c>
       <c r="H1291" t="s">
         <v>8</v>
@@ -33987,7 +33987,7 @@
         <v>33.5200004577637</v>
       </c>
       <c r="G1293" t="n">
-        <v>31.9456939697266</v>
+        <v>31.9456901550293</v>
       </c>
       <c r="H1293" t="s">
         <v>8</v>
@@ -34013,7 +34013,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G1294" t="n">
-        <v>32.0219268798828</v>
+        <v>32.0219306945801</v>
       </c>
       <c r="H1294" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>34.5400009155273</v>
       </c>
       <c r="G1295" t="n">
-        <v>32.917781829834</v>
+        <v>32.9177894592285</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34091,7 +34091,7 @@
         <v>35</v>
       </c>
       <c r="G1297" t="n">
-        <v>33.3561782836914</v>
+        <v>33.3561820983887</v>
       </c>
       <c r="H1297" t="s">
         <v>8</v>
@@ -34143,7 +34143,7 @@
         <v>35.2000007629395</v>
       </c>
       <c r="G1299" t="n">
-        <v>33.5467872619629</v>
+        <v>33.5467834472656</v>
       </c>
       <c r="H1299" t="s">
         <v>8</v>
@@ -34247,7 +34247,7 @@
         <v>34.5400009155273</v>
       </c>
       <c r="G1303" t="n">
-        <v>32.917781829834</v>
+        <v>32.9177894592285</v>
       </c>
       <c r="H1303" t="s">
         <v>8</v>
@@ -34273,7 +34273,7 @@
         <v>34.1399993896484</v>
       </c>
       <c r="G1304" t="n">
-        <v>32.5365753173828</v>
+        <v>32.5365715026855</v>
       </c>
       <c r="H1304" t="s">
         <v>8</v>
@@ -34299,7 +34299,7 @@
         <v>34.7999992370605</v>
       </c>
       <c r="G1305" t="n">
-        <v>33.1655731201172</v>
+        <v>33.1655693054199</v>
       </c>
       <c r="H1305" t="s">
         <v>8</v>
@@ -34351,7 +34351,7 @@
         <v>34.2599983215332</v>
       </c>
       <c r="G1307" t="n">
-        <v>32.6509323120117</v>
+        <v>32.650936126709</v>
       </c>
       <c r="H1307" t="s">
         <v>8</v>
@@ -34429,7 +34429,7 @@
         <v>34.1199989318848</v>
       </c>
       <c r="G1310" t="n">
-        <v>32.5175094604492</v>
+        <v>32.5175132751465</v>
       </c>
       <c r="H1310" t="s">
         <v>8</v>
@@ -34455,7 +34455,7 @@
         <v>34.6399993896484</v>
       </c>
       <c r="G1311" t="n">
-        <v>33.0130844116211</v>
+        <v>33.0130882263184</v>
       </c>
       <c r="H1311" t="s">
         <v>8</v>
@@ -34507,7 +34507,7 @@
         <v>35.1399993896484</v>
       </c>
       <c r="G1313" t="n">
-        <v>33.4896087646484</v>
+        <v>33.4896049499512</v>
       </c>
       <c r="H1313" t="s">
         <v>8</v>
@@ -34611,7 +34611,7 @@
         <v>34.2599983215332</v>
       </c>
       <c r="G1317" t="n">
-        <v>32.6509323120117</v>
+        <v>32.650936126709</v>
       </c>
       <c r="H1317" t="s">
         <v>8</v>
@@ -34637,7 +34637,7 @@
         <v>34.8400001525879</v>
       </c>
       <c r="G1318" t="n">
-        <v>33.2036933898926</v>
+        <v>33.2036895751953</v>
       </c>
       <c r="H1318" t="s">
         <v>8</v>
@@ -34663,7 +34663,7 @@
         <v>35.9199981689453</v>
       </c>
       <c r="G1319" t="n">
-        <v>34.232967376709</v>
+        <v>34.2329711914062</v>
       </c>
       <c r="H1319" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>38.4799995422363</v>
       </c>
       <c r="G1324" t="n">
-        <v>36.6727333068848</v>
+        <v>36.672737121582</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34845,7 +34845,7 @@
         <v>37.5999984741211</v>
       </c>
       <c r="G1326" t="n">
-        <v>35.8340644836426</v>
+        <v>35.8340606689453</v>
       </c>
       <c r="H1326" t="s">
         <v>8</v>
@@ -34897,7 +34897,7 @@
         <v>37</v>
       </c>
       <c r="G1328" t="n">
-        <v>35.2622528076172</v>
+        <v>35.2622489929199</v>
       </c>
       <c r="H1328" t="s">
         <v>8</v>
@@ -34923,7 +34923,7 @@
         <v>37</v>
       </c>
       <c r="G1329" t="n">
-        <v>35.2622528076172</v>
+        <v>35.2622489929199</v>
       </c>
       <c r="H1329" t="s">
         <v>8</v>
@@ -34949,7 +34949,7 @@
         <v>37.0999984741211</v>
       </c>
       <c r="G1330" t="n">
-        <v>35.3575477600098</v>
+        <v>35.357551574707</v>
       </c>
       <c r="H1330" t="s">
         <v>8</v>
@@ -35001,7 +35001,7 @@
         <v>36.8400001525879</v>
       </c>
       <c r="G1332" t="n">
-        <v>35.1097602844238</v>
+        <v>35.1097640991211</v>
       </c>
       <c r="H1332" t="s">
         <v>8</v>
@@ -35079,7 +35079,7 @@
         <v>39</v>
       </c>
       <c r="G1335" t="n">
-        <v>37.1683197021484</v>
+        <v>37.1683120727539</v>
       </c>
       <c r="H1335" t="s">
         <v>8</v>
@@ -35235,7 +35235,7 @@
         <v>40.9799995422363</v>
       </c>
       <c r="G1341" t="n">
-        <v>39.0553169250488</v>
+        <v>39.0553207397461</v>
       </c>
       <c r="H1341" t="s">
         <v>8</v>
@@ -35287,7 +35287,7 @@
         <v>41.3400001525879</v>
       </c>
       <c r="G1343" t="n">
-        <v>39.3984107971191</v>
+        <v>39.3984146118164</v>
       </c>
       <c r="H1343" t="s">
         <v>8</v>
@@ -35313,7 +35313,7 @@
         <v>41.6800003051758</v>
       </c>
       <c r="G1344" t="n">
-        <v>39.7224464416504</v>
+        <v>39.7224426269531</v>
       </c>
       <c r="H1344" t="s">
         <v>8</v>
@@ -35365,7 +35365,7 @@
         <v>42.4199981689453</v>
       </c>
       <c r="G1346" t="n">
-        <v>40.4276885986328</v>
+        <v>40.4276847839355</v>
       </c>
       <c r="H1346" t="s">
         <v>8</v>
@@ -35417,7 +35417,7 @@
         <v>43.2000007629395</v>
       </c>
       <c r="G1348" t="n">
-        <v>41.1710548400879</v>
+        <v>41.1710586547852</v>
       </c>
       <c r="H1348" t="s">
         <v>8</v>
@@ -35443,7 +35443,7 @@
         <v>43.9799995422363</v>
       </c>
       <c r="G1349" t="n">
-        <v>41.914421081543</v>
+        <v>41.9144172668457</v>
       </c>
       <c r="H1349" t="s">
         <v>8</v>
@@ -35469,7 +35469,7 @@
         <v>43.4599990844727</v>
       </c>
       <c r="G1350" t="n">
-        <v>41.4188423156738</v>
+        <v>41.4188461303711</v>
       </c>
       <c r="H1350" t="s">
         <v>8</v>
@@ -35521,7 +35521,7 @@
         <v>42.8199996948242</v>
       </c>
       <c r="G1352" t="n">
-        <v>40.8089027404785</v>
+        <v>40.8088989257812</v>
       </c>
       <c r="H1352" t="s">
         <v>8</v>
@@ -35599,7 +35599,7 @@
         <v>42.0800018310547</v>
       </c>
       <c r="G1355" t="n">
-        <v>40.1036567687988</v>
+        <v>40.1036605834961</v>
       </c>
       <c r="H1355" t="s">
         <v>8</v>
@@ -35625,7 +35625,7 @@
         <v>42.0800018310547</v>
       </c>
       <c r="G1356" t="n">
-        <v>40.1036567687988</v>
+        <v>40.1036605834961</v>
       </c>
       <c r="H1356" t="s">
         <v>8</v>
@@ -35677,7 +35677,7 @@
         <v>43.8600006103516</v>
       </c>
       <c r="G1358" t="n">
-        <v>41.8000602722168</v>
+        <v>41.8000564575195</v>
       </c>
       <c r="H1358" t="s">
         <v>8</v>
@@ -35703,7 +35703,7 @@
         <v>44</v>
       </c>
       <c r="G1359" t="n">
-        <v>41.9334869384766</v>
+        <v>41.9334831237793</v>
       </c>
       <c r="H1359" t="s">
         <v>8</v>
@@ -35859,7 +35859,7 @@
         <v>44.2000007629395</v>
       </c>
       <c r="G1365" t="n">
-        <v>42.1240882873535</v>
+        <v>42.1240844726562</v>
       </c>
       <c r="H1365" t="s">
         <v>8</v>
@@ -35937,7 +35937,7 @@
         <v>45.1399993896484</v>
       </c>
       <c r="G1368" t="n">
-        <v>43.0199432373047</v>
+        <v>43.0199394226074</v>
       </c>
       <c r="H1368" t="s">
         <v>8</v>
@@ -35963,7 +35963,7 @@
         <v>45.560001373291</v>
       </c>
       <c r="G1369" t="n">
-        <v>43.4202194213867</v>
+        <v>43.4202156066895</v>
       </c>
       <c r="H1369" t="s">
         <v>8</v>
@@ -35989,7 +35989,7 @@
         <v>45.1800003051758</v>
       </c>
       <c r="G1370" t="n">
-        <v>43.0580673217773</v>
+        <v>43.0580596923828</v>
       </c>
       <c r="H1370" t="s">
         <v>8</v>
@@ -36015,7 +36015,7 @@
         <v>45.4199981689453</v>
       </c>
       <c r="G1371" t="n">
-        <v>43.2867889404297</v>
+        <v>43.2867851257324</v>
       </c>
       <c r="H1371" t="s">
         <v>8</v>
@@ -36145,7 +36145,7 @@
         <v>50.2999992370605</v>
       </c>
       <c r="G1376" t="n">
-        <v>47.9375915527344</v>
+        <v>47.9375953674316</v>
       </c>
       <c r="H1376" t="s">
         <v>8</v>
@@ -36223,7 +36223,7 @@
         <v>50.4500007629395</v>
       </c>
       <c r="G1379" t="n">
-        <v>48.0805511474609</v>
+        <v>48.0805549621582</v>
       </c>
       <c r="H1379" t="s">
         <v>8</v>
@@ -36353,7 +36353,7 @@
         <v>47.7200012207031</v>
       </c>
       <c r="G1384" t="n">
-        <v>45.4787712097168</v>
+        <v>45.4787673950195</v>
       </c>
       <c r="H1384" t="s">
         <v>8</v>
@@ -36405,7 +36405,7 @@
         <v>48.7999992370605</v>
       </c>
       <c r="G1386" t="n">
-        <v>46.5080490112305</v>
+        <v>46.5080451965332</v>
       </c>
       <c r="H1386" t="s">
         <v>8</v>
@@ -36431,7 +36431,7 @@
         <v>49.0999984741211</v>
       </c>
       <c r="G1387" t="n">
-        <v>46.7939529418945</v>
+        <v>46.7939491271973</v>
       </c>
       <c r="H1387" t="s">
         <v>8</v>
@@ -36457,7 +36457,7 @@
         <v>49.7400016784668</v>
       </c>
       <c r="G1388" t="n">
-        <v>47.4038963317871</v>
+        <v>47.4039001464844</v>
       </c>
       <c r="H1388" t="s">
         <v>8</v>
@@ -36483,7 +36483,7 @@
         <v>50.0499992370605</v>
       </c>
       <c r="G1389" t="n">
-        <v>47.699333190918</v>
+        <v>47.6993370056152</v>
       </c>
       <c r="H1389" t="s">
         <v>8</v>
@@ -36587,7 +36587,7 @@
         <v>49.5</v>
       </c>
       <c r="G1393" t="n">
-        <v>47.1751670837402</v>
+        <v>47.175163269043</v>
       </c>
       <c r="H1393" t="s">
         <v>8</v>
@@ -36613,7 +36613,7 @@
         <v>48.7999992370605</v>
       </c>
       <c r="G1394" t="n">
-        <v>46.5080490112305</v>
+        <v>46.5080451965332</v>
       </c>
       <c r="H1394" t="s">
         <v>8</v>
@@ -36795,7 +36795,7 @@
         <v>52.3499984741211</v>
       </c>
       <c r="G1401" t="n">
-        <v>49.8913154602051</v>
+        <v>49.8913078308105</v>
       </c>
       <c r="H1401" t="s">
         <v>8</v>
@@ -36821,7 +36821,7 @@
         <v>49.560001373291</v>
       </c>
       <c r="G1402" t="n">
-        <v>47.2323532104492</v>
+        <v>47.2323455810547</v>
       </c>
       <c r="H1402" t="s">
         <v>8</v>
@@ -36899,7 +36899,7 @@
         <v>51.4500007629395</v>
       </c>
       <c r="G1405" t="n">
-        <v>49.0335845947266</v>
+        <v>49.0335807800293</v>
       </c>
       <c r="H1405" t="s">
         <v>8</v>
@@ -36951,7 +36951,7 @@
         <v>49.1199989318848</v>
       </c>
       <c r="G1407" t="n">
-        <v>46.8130149841309</v>
+        <v>46.8130111694336</v>
       </c>
       <c r="H1407" t="s">
         <v>8</v>
@@ -36977,7 +36977,7 @@
         <v>49.6599998474121</v>
       </c>
       <c r="G1408" t="n">
-        <v>47.3276596069336</v>
+        <v>47.3276557922363</v>
       </c>
       <c r="H1408" t="s">
         <v>8</v>
@@ -37055,7 +37055,7 @@
         <v>49.7000007629395</v>
       </c>
       <c r="G1411" t="n">
-        <v>47.3657760620117</v>
+        <v>47.365779876709</v>
       </c>
       <c r="H1411" t="s">
         <v>8</v>
@@ -37081,7 +37081,7 @@
         <v>51.1500015258789</v>
       </c>
       <c r="G1412" t="n">
-        <v>48.7476692199707</v>
+        <v>48.747673034668</v>
       </c>
       <c r="H1412" t="s">
         <v>8</v>
@@ -37159,7 +37159,7 @@
         <v>51.4500007629395</v>
       </c>
       <c r="G1415" t="n">
-        <v>49.0335845947266</v>
+        <v>49.0335807800293</v>
       </c>
       <c r="H1415" t="s">
         <v>8</v>
@@ -37185,7 +37185,7 @@
         <v>51.7999992370605</v>
       </c>
       <c r="G1416" t="n">
-        <v>49.3671493530273</v>
+        <v>49.3671455383301</v>
       </c>
       <c r="H1416" t="s">
         <v>8</v>
@@ -37211,7 +37211,7 @@
         <v>52.0999984741211</v>
       </c>
       <c r="G1417" t="n">
-        <v>49.6530570983887</v>
+        <v>49.6530532836914</v>
       </c>
       <c r="H1417" t="s">
         <v>8</v>
@@ -37237,7 +37237,7 @@
         <v>52.2999992370605</v>
       </c>
       <c r="G1418" t="n">
-        <v>49.8436584472656</v>
+        <v>49.8436660766602</v>
       </c>
       <c r="H1418" t="s">
         <v>8</v>
@@ -37263,7 +37263,7 @@
         <v>56.4500007629395</v>
       </c>
       <c r="G1419" t="n">
-        <v>53.798755645752</v>
+        <v>53.7987480163574</v>
       </c>
       <c r="H1419" t="s">
         <v>8</v>
@@ -37315,7 +37315,7 @@
         <v>54.2000007629395</v>
       </c>
       <c r="G1421" t="n">
-        <v>51.6544303894043</v>
+        <v>51.654426574707</v>
       </c>
       <c r="H1421" t="s">
         <v>8</v>
@@ -37341,7 +37341,7 @@
         <v>54.8499984741211</v>
       </c>
       <c r="G1422" t="n">
-        <v>52.2738914489746</v>
+        <v>52.2738952636719</v>
       </c>
       <c r="H1422" t="s">
         <v>8</v>
@@ -37367,7 +37367,7 @@
         <v>54.8499984741211</v>
       </c>
       <c r="G1423" t="n">
-        <v>52.2738914489746</v>
+        <v>52.2738952636719</v>
       </c>
       <c r="H1423" t="s">
         <v>8</v>
@@ -37471,7 +37471,7 @@
         <v>54.9000015258789</v>
       </c>
       <c r="G1427" t="n">
-        <v>52.3215560913086</v>
+        <v>52.3215522766113</v>
       </c>
       <c r="H1427" t="s">
         <v>8</v>
@@ -37575,7 +37575,7 @@
         <v>52.3499984741211</v>
       </c>
       <c r="G1431" t="n">
-        <v>49.8913154602051</v>
+        <v>49.8913078308105</v>
       </c>
       <c r="H1431" t="s">
         <v>8</v>
@@ -37601,7 +37601,7 @@
         <v>49.0999984741211</v>
       </c>
       <c r="G1432" t="n">
-        <v>46.7939529418945</v>
+        <v>46.7939491271973</v>
       </c>
       <c r="H1432" t="s">
         <v>8</v>
@@ -37731,7 +37731,7 @@
         <v>48.7999992370605</v>
       </c>
       <c r="G1437" t="n">
-        <v>46.5080490112305</v>
+        <v>46.5080451965332</v>
       </c>
       <c r="H1437" t="s">
         <v>8</v>
@@ -37835,7 +37835,7 @@
         <v>50.0499992370605</v>
       </c>
       <c r="G1441" t="n">
-        <v>47.699333190918</v>
+        <v>47.6993370056152</v>
       </c>
       <c r="H1441" t="s">
         <v>8</v>
@@ -37861,7 +37861,7 @@
         <v>50.0499992370605</v>
       </c>
       <c r="G1442" t="n">
-        <v>47.699333190918</v>
+        <v>47.6993370056152</v>
       </c>
       <c r="H1442" t="s">
         <v>8</v>
@@ -37913,7 +37913,7 @@
         <v>49.6800003051758</v>
       </c>
       <c r="G1444" t="n">
-        <v>47.3467140197754</v>
+        <v>47.3467178344727</v>
       </c>
       <c r="H1444" t="s">
         <v>8</v>
@@ -37965,7 +37965,7 @@
         <v>49.1399993896484</v>
       </c>
       <c r="G1446" t="n">
-        <v>46.8320732116699</v>
+        <v>46.8320770263672</v>
       </c>
       <c r="H1446" t="s">
         <v>8</v>
@@ -37991,7 +37991,7 @@
         <v>49.7000007629395</v>
       </c>
       <c r="G1447" t="n">
-        <v>47.3657760620117</v>
+        <v>47.365779876709</v>
       </c>
       <c r="H1447" t="s">
         <v>8</v>
@@ -38017,7 +38017,7 @@
         <v>49.4799995422363</v>
       </c>
       <c r="G1448" t="n">
-        <v>47.1561088562012</v>
+        <v>47.1561050415039</v>
       </c>
       <c r="H1448" t="s">
         <v>8</v>
@@ -38043,7 +38043,7 @@
         <v>48.5800018310547</v>
       </c>
       <c r="G1449" t="n">
-        <v>46.2983779907227</v>
+        <v>46.2983818054199</v>
       </c>
       <c r="H1449" t="s">
         <v>8</v>
@@ -38069,7 +38069,7 @@
         <v>48.0200004577637</v>
       </c>
       <c r="G1450" t="n">
-        <v>45.7646789550781</v>
+        <v>45.7646827697754</v>
       </c>
       <c r="H1450" t="s">
         <v>8</v>
@@ -38095,7 +38095,7 @@
         <v>46.7599983215332</v>
       </c>
       <c r="G1451" t="n">
-        <v>44.5638580322266</v>
+        <v>44.5638542175293</v>
       </c>
       <c r="H1451" t="s">
         <v>8</v>
@@ -38147,7 +38147,7 @@
         <v>47.9599990844727</v>
       </c>
       <c r="G1453" t="n">
-        <v>45.7075004577637</v>
+        <v>45.7074928283691</v>
       </c>
       <c r="H1453" t="s">
         <v>8</v>
@@ -38277,7 +38277,7 @@
         <v>49.5200004577637</v>
       </c>
       <c r="G1458" t="n">
-        <v>47.1942253112793</v>
+        <v>47.1942291259766</v>
       </c>
       <c r="H1458" t="s">
         <v>8</v>
@@ -38303,7 +38303,7 @@
         <v>48.5800018310547</v>
       </c>
       <c r="G1459" t="n">
-        <v>46.2983779907227</v>
+        <v>46.2983818054199</v>
       </c>
       <c r="H1459" t="s">
         <v>8</v>
@@ -38433,7 +38433,7 @@
         <v>47.2999992370605</v>
       </c>
       <c r="G1464" t="n">
-        <v>45.0784912109375</v>
+        <v>45.0784950256348</v>
       </c>
       <c r="H1464" t="s">
         <v>8</v>
@@ -38485,7 +38485,7 @@
         <v>46.939998626709</v>
       </c>
       <c r="G1466" t="n">
-        <v>44.7354011535645</v>
+        <v>44.7353973388672</v>
       </c>
       <c r="H1466" t="s">
         <v>8</v>
@@ -38511,7 +38511,7 @@
         <v>47.7200012207031</v>
       </c>
       <c r="G1467" t="n">
-        <v>45.4787712097168</v>
+        <v>45.4787673950195</v>
       </c>
       <c r="H1467" t="s">
         <v>8</v>
@@ -38537,7 +38537,7 @@
         <v>47.0400009155273</v>
       </c>
       <c r="G1468" t="n">
-        <v>44.8307037353516</v>
+        <v>44.8307075500488</v>
       </c>
       <c r="H1468" t="s">
         <v>8</v>
@@ -38667,7 +38667,7 @@
         <v>49.5200004577637</v>
       </c>
       <c r="G1473" t="n">
-        <v>47.1942253112793</v>
+        <v>47.1942291259766</v>
       </c>
       <c r="H1473" t="s">
         <v>8</v>
@@ -38745,7 +38745,7 @@
         <v>49.7599983215332</v>
       </c>
       <c r="G1476" t="n">
-        <v>47.4229545593262</v>
+        <v>47.4229583740234</v>
       </c>
       <c r="H1476" t="s">
         <v>8</v>
@@ -38823,7 +38823,7 @@
         <v>51.2000007629395</v>
       </c>
       <c r="G1479" t="n">
-        <v>48.7953262329102</v>
+        <v>48.7953224182129</v>
       </c>
       <c r="H1479" t="s">
         <v>8</v>
@@ -38875,7 +38875,7 @@
         <v>51.1500015258789</v>
       </c>
       <c r="G1481" t="n">
-        <v>48.7476692199707</v>
+        <v>48.747673034668</v>
       </c>
       <c r="H1481" t="s">
         <v>8</v>
@@ -38901,7 +38901,7 @@
         <v>51.7999992370605</v>
       </c>
       <c r="G1482" t="n">
-        <v>49.3671493530273</v>
+        <v>49.3671455383301</v>
       </c>
       <c r="H1482" t="s">
         <v>8</v>
@@ -38953,7 +38953,7 @@
         <v>54</v>
       </c>
       <c r="G1484" t="n">
-        <v>51.4638175964355</v>
+        <v>51.4638214111328</v>
       </c>
       <c r="H1484" t="s">
         <v>8</v>
@@ -38979,7 +38979,7 @@
         <v>53.5499992370605</v>
       </c>
       <c r="G1485" t="n">
-        <v>51.0349540710449</v>
+        <v>51.0349502563477</v>
       </c>
       <c r="H1485" t="s">
         <v>8</v>
@@ -39005,7 +39005,7 @@
         <v>54.9000015258789</v>
       </c>
       <c r="G1486" t="n">
-        <v>52.3215560913086</v>
+        <v>52.3215522766113</v>
       </c>
       <c r="H1486" t="s">
         <v>8</v>
@@ -39083,7 +39083,7 @@
         <v>62.2999992370605</v>
       </c>
       <c r="G1489" t="n">
-        <v>59.3740005493164</v>
+        <v>59.3739967346191</v>
       </c>
       <c r="H1489" t="s">
         <v>8</v>
@@ -39135,7 +39135,7 @@
         <v>61.8499984741211</v>
       </c>
       <c r="G1491" t="n">
-        <v>58.9451332092285</v>
+        <v>58.9451370239258</v>
       </c>
       <c r="H1491" t="s">
         <v>8</v>
@@ -39187,7 +39187,7 @@
         <v>63.4500007629395</v>
       </c>
       <c r="G1493" t="n">
-        <v>60.4699897766113</v>
+        <v>60.4699859619141</v>
       </c>
       <c r="H1493" t="s">
         <v>8</v>
@@ -39239,7 +39239,7 @@
         <v>62.4500007629395</v>
       </c>
       <c r="G1495" t="n">
-        <v>59.516960144043</v>
+        <v>59.5169525146484</v>
       </c>
       <c r="H1495" t="s">
         <v>8</v>
@@ -39291,7 +39291,7 @@
         <v>61.8499984741211</v>
       </c>
       <c r="G1497" t="n">
-        <v>58.9451332092285</v>
+        <v>58.9451370239258</v>
       </c>
       <c r="H1497" t="s">
         <v>8</v>
@@ -39317,7 +39317,7 @@
         <v>60.0999984741211</v>
       </c>
       <c r="G1498" t="n">
-        <v>57.2773208618164</v>
+        <v>57.2773246765137</v>
       </c>
       <c r="H1498" t="s">
         <v>8</v>
@@ -39343,7 +39343,7 @@
         <v>60.1500015258789</v>
       </c>
       <c r="G1499" t="n">
-        <v>57.3249778747559</v>
+        <v>57.3249740600586</v>
       </c>
       <c r="H1499" t="s">
         <v>8</v>
@@ -39369,7 +39369,7 @@
         <v>58.6500015258789</v>
       </c>
       <c r="G1500" t="n">
-        <v>55.8954315185547</v>
+        <v>55.8954277038574</v>
       </c>
       <c r="H1500" t="s">
         <v>8</v>
@@ -39395,7 +39395,7 @@
         <v>57.8499984741211</v>
       </c>
       <c r="G1501" t="n">
-        <v>55.1329956054688</v>
+        <v>55.132999420166</v>
       </c>
       <c r="H1501" t="s">
         <v>8</v>
@@ -39421,7 +39421,7 @@
         <v>58.2999992370605</v>
       </c>
       <c r="G1502" t="n">
-        <v>55.5618667602539</v>
+        <v>55.5618629455566</v>
       </c>
       <c r="H1502" t="s">
         <v>8</v>
@@ -39447,7 +39447,7 @@
         <v>55.3499984741211</v>
       </c>
       <c r="G1503" t="n">
-        <v>52.7504196166992</v>
+        <v>52.750415802002</v>
       </c>
       <c r="H1503" t="s">
         <v>8</v>
@@ -39603,7 +39603,7 @@
         <v>56.9000015258789</v>
       </c>
       <c r="G1509" t="n">
-        <v>54.2276191711426</v>
+        <v>54.2276153564453</v>
       </c>
       <c r="H1509" t="s">
         <v>8</v>
@@ -39681,7 +39681,7 @@
         <v>56.9000015258789</v>
       </c>
       <c r="G1512" t="n">
-        <v>54.2276191711426</v>
+        <v>54.2276153564453</v>
       </c>
       <c r="H1512" t="s">
         <v>8</v>
@@ -39707,7 +39707,7 @@
         <v>56.1500015258789</v>
       </c>
       <c r="G1513" t="n">
-        <v>53.5128402709961</v>
+        <v>53.5128440856934</v>
       </c>
       <c r="H1513" t="s">
         <v>8</v>
@@ -39759,7 +39759,7 @@
         <v>53.8499984741211</v>
       </c>
       <c r="G1515" t="n">
-        <v>51.3208618164062</v>
+        <v>51.320858001709</v>
       </c>
       <c r="H1515" t="s">
         <v>8</v>
@@ -39811,7 +39811,7 @@
         <v>56.9000015258789</v>
       </c>
       <c r="G1517" t="n">
-        <v>54.2276191711426</v>
+        <v>54.2276153564453</v>
       </c>
       <c r="H1517" t="s">
         <v>8</v>
@@ -39915,7 +39915,7 @@
         <v>56.9000015258789</v>
       </c>
       <c r="G1521" t="n">
-        <v>54.2276191711426</v>
+        <v>54.2276153564453</v>
       </c>
       <c r="H1521" t="s">
         <v>8</v>
@@ -39941,7 +39941,7 @@
         <v>56.9500007629395</v>
       </c>
       <c r="G1522" t="n">
-        <v>54.2752685546875</v>
+        <v>54.275276184082</v>
       </c>
       <c r="H1522" t="s">
         <v>8</v>
@@ -39967,7 +39967,7 @@
         <v>58.25</v>
       </c>
       <c r="G1523" t="n">
-        <v>55.5142097473145</v>
+        <v>55.514217376709</v>
       </c>
       <c r="H1523" t="s">
         <v>8</v>
@@ -40019,7 +40019,7 @@
         <v>60.5999984741211</v>
       </c>
       <c r="G1525" t="n">
-        <v>57.7538452148438</v>
+        <v>57.7538414001465</v>
       </c>
       <c r="H1525" t="s">
         <v>8</v>
@@ -40045,7 +40045,7 @@
         <v>60.7000007629395</v>
       </c>
       <c r="G1526" t="n">
-        <v>57.8491439819336</v>
+        <v>57.8491477966309</v>
       </c>
       <c r="H1526" t="s">
         <v>8</v>
@@ -40071,7 +40071,7 @@
         <v>63.1500015258789</v>
       </c>
       <c r="G1527" t="n">
-        <v>60.18408203125</v>
+        <v>60.1840858459473</v>
       </c>
       <c r="H1527" t="s">
         <v>8</v>
@@ -40123,7 +40123,7 @@
         <v>63.5</v>
       </c>
       <c r="G1529" t="n">
-        <v>60.5176429748535</v>
+        <v>60.517635345459</v>
       </c>
       <c r="H1529" t="s">
         <v>8</v>
@@ -40149,7 +40149,7 @@
         <v>62.5499992370605</v>
       </c>
       <c r="G1530" t="n">
-        <v>59.6122589111328</v>
+        <v>59.6122550964355</v>
       </c>
       <c r="H1530" t="s">
         <v>8</v>
@@ -40175,7 +40175,7 @@
         <v>60.7999992370605</v>
       </c>
       <c r="G1531" t="n">
-        <v>57.9444465637207</v>
+        <v>57.944450378418</v>
       </c>
       <c r="H1531" t="s">
         <v>8</v>
@@ -40253,7 +40253,7 @@
         <v>57.2000007629395</v>
       </c>
       <c r="G1534" t="n">
-        <v>54.5135269165039</v>
+        <v>54.5135307312012</v>
       </c>
       <c r="H1534" t="s">
         <v>8</v>
@@ -40279,7 +40279,7 @@
         <v>56</v>
       </c>
       <c r="G1535" t="n">
-        <v>53.3698844909668</v>
+        <v>53.3698883056641</v>
       </c>
       <c r="H1535" t="s">
         <v>8</v>
@@ -40305,7 +40305,7 @@
         <v>54.0999984741211</v>
       </c>
       <c r="G1536" t="n">
-        <v>51.5591239929199</v>
+        <v>51.5591201782227</v>
       </c>
       <c r="H1536" t="s">
         <v>8</v>
@@ -40383,7 +40383,7 @@
         <v>55.0499992370605</v>
       </c>
       <c r="G1539" t="n">
-        <v>52.4645042419434</v>
+        <v>52.4645004272461</v>
       </c>
       <c r="H1539" t="s">
         <v>8</v>
@@ -40435,7 +40435,7 @@
         <v>53.8499984741211</v>
       </c>
       <c r="G1541" t="n">
-        <v>51.3208618164062</v>
+        <v>51.320858001709</v>
       </c>
       <c r="H1541" t="s">
         <v>8</v>
@@ -40487,7 +40487,7 @@
         <v>52.6500015258789</v>
       </c>
       <c r="G1543" t="n">
-        <v>50.1772270202637</v>
+        <v>50.1772232055664</v>
       </c>
       <c r="H1543" t="s">
         <v>8</v>
@@ -40513,7 +40513,7 @@
         <v>53.75</v>
       </c>
       <c r="G1544" t="n">
-        <v>51.2255668640137</v>
+        <v>51.2255630493164</v>
       </c>
       <c r="H1544" t="s">
         <v>8</v>
@@ -40565,7 +40565,7 @@
         <v>51</v>
       </c>
       <c r="G1546" t="n">
-        <v>48.6047172546387</v>
+        <v>48.6047210693359</v>
       </c>
       <c r="H1546" t="s">
         <v>8</v>
@@ -40591,7 +40591,7 @@
         <v>51.1500015258789</v>
       </c>
       <c r="G1547" t="n">
-        <v>48.7476692199707</v>
+        <v>48.747673034668</v>
       </c>
       <c r="H1547" t="s">
         <v>8</v>
@@ -40669,7 +40669,7 @@
         <v>52.2999992370605</v>
       </c>
       <c r="G1550" t="n">
-        <v>49.8436584472656</v>
+        <v>49.8436660766602</v>
       </c>
       <c r="H1550" t="s">
         <v>8</v>
@@ -40721,7 +40721,7 @@
         <v>52.6500015258789</v>
       </c>
       <c r="G1552" t="n">
-        <v>50.1772270202637</v>
+        <v>50.1772232055664</v>
       </c>
       <c r="H1552" t="s">
         <v>8</v>
@@ -40747,7 +40747,7 @@
         <v>52.9500007629395</v>
       </c>
       <c r="G1553" t="n">
-        <v>50.463134765625</v>
+        <v>50.4631385803223</v>
       </c>
       <c r="H1553" t="s">
         <v>8</v>
@@ -40825,7 +40825,7 @@
         <v>52.1500015258789</v>
       </c>
       <c r="G1556" t="n">
-        <v>49.7007064819336</v>
+        <v>49.7007141113281</v>
       </c>
       <c r="H1556" t="s">
         <v>8</v>
@@ -40903,7 +40903,7 @@
         <v>52.6500015258789</v>
       </c>
       <c r="G1559" t="n">
-        <v>50.1772270202637</v>
+        <v>50.1772232055664</v>
       </c>
       <c r="H1559" t="s">
         <v>8</v>
@@ -41007,7 +41007,7 @@
         <v>51.4500007629395</v>
       </c>
       <c r="G1563" t="n">
-        <v>49.0335845947266</v>
+        <v>49.0335807800293</v>
       </c>
       <c r="H1563" t="s">
         <v>8</v>
@@ -41111,7 +41111,7 @@
         <v>50.2999992370605</v>
       </c>
       <c r="G1567" t="n">
-        <v>47.9375915527344</v>
+        <v>47.9375953674316</v>
       </c>
       <c r="H1567" t="s">
         <v>8</v>
@@ -41163,7 +41163,7 @@
         <v>48.060001373291</v>
       </c>
       <c r="G1569" t="n">
-        <v>45.8028030395508</v>
+        <v>45.8027992248535</v>
       </c>
       <c r="H1569" t="s">
         <v>8</v>
@@ -41215,7 +41215,7 @@
         <v>43.5999984741211</v>
       </c>
       <c r="G1571" t="n">
-        <v>41.5522651672363</v>
+        <v>41.5522727966309</v>
       </c>
       <c r="H1571" t="s">
         <v>8</v>
@@ -41241,7 +41241,7 @@
         <v>42.7200012207031</v>
       </c>
       <c r="G1572" t="n">
-        <v>40.7136001586914</v>
+        <v>40.7136039733887</v>
       </c>
       <c r="H1572" t="s">
         <v>8</v>
@@ -41345,7 +41345,7 @@
         <v>46.939998626709</v>
       </c>
       <c r="G1576" t="n">
-        <v>44.7354011535645</v>
+        <v>44.7353973388672</v>
       </c>
       <c r="H1576" t="s">
         <v>8</v>
@@ -41423,7 +41423,7 @@
         <v>51.2000007629395</v>
       </c>
       <c r="G1579" t="n">
-        <v>48.7953262329102</v>
+        <v>48.7953224182129</v>
       </c>
       <c r="H1579" t="s">
         <v>8</v>
@@ -41475,7 +41475,7 @@
         <v>54.0999984741211</v>
       </c>
       <c r="G1581" t="n">
-        <v>51.5591239929199</v>
+        <v>51.5591201782227</v>
       </c>
       <c r="H1581" t="s">
         <v>8</v>
@@ -41553,7 +41553,7 @@
         <v>51</v>
       </c>
       <c r="G1584" t="n">
-        <v>48.6047172546387</v>
+        <v>48.6047210693359</v>
       </c>
       <c r="H1584" t="s">
         <v>8</v>
@@ -41683,7 +41683,7 @@
         <v>54</v>
       </c>
       <c r="G1589" t="n">
-        <v>51.4638175964355</v>
+        <v>51.4638214111328</v>
       </c>
       <c r="H1589" t="s">
         <v>8</v>
@@ -41735,7 +41735,7 @@
         <v>52.6500015258789</v>
       </c>
       <c r="G1591" t="n">
-        <v>50.1772270202637</v>
+        <v>50.1772232055664</v>
       </c>
       <c r="H1591" t="s">
         <v>8</v>
@@ -41761,7 +41761,7 @@
         <v>53.6500015258789</v>
       </c>
       <c r="G1592" t="n">
-        <v>51.1302604675293</v>
+        <v>51.130256652832</v>
       </c>
       <c r="H1592" t="s">
         <v>8</v>
@@ -41813,7 +41813,7 @@
         <v>51.3499984741211</v>
       </c>
       <c r="G1594" t="n">
-        <v>48.9382820129395</v>
+        <v>48.9382743835449</v>
       </c>
       <c r="H1594" t="s">
         <v>8</v>
@@ -41839,7 +41839,7 @@
         <v>51</v>
       </c>
       <c r="G1595" t="n">
-        <v>48.6047172546387</v>
+        <v>48.6047210693359</v>
       </c>
       <c r="H1595" t="s">
         <v>8</v>
@@ -41969,7 +41969,7 @@
         <v>52.3499984741211</v>
       </c>
       <c r="G1600" t="n">
-        <v>49.8913154602051</v>
+        <v>49.8913078308105</v>
       </c>
       <c r="H1600" t="s">
         <v>8</v>
@@ -42021,7 +42021,7 @@
         <v>52.0999984741211</v>
       </c>
       <c r="G1602" t="n">
-        <v>49.6530570983887</v>
+        <v>49.6530532836914</v>
       </c>
       <c r="H1602" t="s">
         <v>8</v>
@@ -42073,7 +42073,7 @@
         <v>50.4500007629395</v>
       </c>
       <c r="G1604" t="n">
-        <v>48.0805511474609</v>
+        <v>48.0805549621582</v>
       </c>
       <c r="H1604" t="s">
         <v>8</v>
@@ -42099,7 +42099,7 @@
         <v>48.3199996948242</v>
       </c>
       <c r="G1605" t="n">
-        <v>46.0505867004395</v>
+        <v>46.0505905151367</v>
       </c>
       <c r="H1605" t="s">
         <v>8</v>
@@ -42255,7 +42255,7 @@
         <v>48.6800003051758</v>
       </c>
       <c r="G1611" t="n">
-        <v>46.3936767578125</v>
+        <v>46.3936805725098</v>
       </c>
       <c r="H1611" t="s">
         <v>8</v>
@@ -42307,7 +42307,7 @@
         <v>46.560001373291</v>
       </c>
       <c r="G1613" t="n">
-        <v>44.3732528686523</v>
+        <v>44.3732490539551</v>
       </c>
       <c r="H1613" t="s">
         <v>8</v>
@@ -42359,7 +42359,7 @@
         <v>43.1399993896484</v>
       </c>
       <c r="G1615" t="n">
-        <v>41.1138725280762</v>
+        <v>41.1138763427734</v>
       </c>
       <c r="H1615" t="s">
         <v>8</v>
@@ -42411,7 +42411,7 @@
         <v>46.7599983215332</v>
       </c>
       <c r="G1617" t="n">
-        <v>44.5638580322266</v>
+        <v>44.5638542175293</v>
       </c>
       <c r="H1617" t="s">
         <v>8</v>
@@ -42437,7 +42437,7 @@
         <v>45.7000007629395</v>
       </c>
       <c r="G1618" t="n">
-        <v>43.553638458252</v>
+        <v>43.5536422729492</v>
       </c>
       <c r="H1618" t="s">
         <v>8</v>
@@ -42463,7 +42463,7 @@
         <v>47.2599983215332</v>
       </c>
       <c r="G1619" t="n">
-        <v>45.0403709411621</v>
+        <v>45.0403747558594</v>
       </c>
       <c r="H1619" t="s">
         <v>8</v>
@@ -42593,7 +42593,7 @@
         <v>45.0200004577637</v>
       </c>
       <c r="G1624" t="n">
-        <v>42.9055786132812</v>
+        <v>42.905574798584</v>
       </c>
       <c r="H1624" t="s">
         <v>8</v>
@@ -42619,7 +42619,7 @@
         <v>45.2799987792969</v>
       </c>
       <c r="G1625" t="n">
-        <v>43.5597457885742</v>
+        <v>43.559741973877</v>
       </c>
       <c r="H1625" t="s">
         <v>8</v>
@@ -42645,7 +42645,7 @@
         <v>43.5</v>
       </c>
       <c r="G1626" t="n">
-        <v>41.8473663330078</v>
+        <v>41.8473701477051</v>
       </c>
       <c r="H1626" t="s">
         <v>8</v>
@@ -42671,7 +42671,7 @@
         <v>43.1399993896484</v>
       </c>
       <c r="G1627" t="n">
-        <v>41.5010452270508</v>
+        <v>41.501049041748</v>
       </c>
       <c r="H1627" t="s">
         <v>8</v>
@@ -42853,7 +42853,7 @@
         <v>46.8400001525879</v>
       </c>
       <c r="G1634" t="n">
-        <v>45.060474395752</v>
+        <v>45.0604782104492</v>
       </c>
       <c r="H1634" t="s">
         <v>8</v>
@@ -42905,7 +42905,7 @@
         <v>46.5800018310547</v>
       </c>
       <c r="G1636" t="n">
-        <v>44.8103561401367</v>
+        <v>44.8103523254395</v>
       </c>
       <c r="H1636" t="s">
         <v>8</v>
@@ -42957,7 +42957,7 @@
         <v>45.560001373291</v>
       </c>
       <c r="G1638" t="n">
-        <v>43.8291091918945</v>
+        <v>43.8291053771973</v>
       </c>
       <c r="H1638" t="s">
         <v>8</v>
@@ -43009,7 +43009,7 @@
         <v>42.0800018310547</v>
       </c>
       <c r="G1640" t="n">
-        <v>40.481315612793</v>
+        <v>40.4813194274902</v>
       </c>
       <c r="H1640" t="s">
         <v>8</v>
@@ -43139,7 +43139,7 @@
         <v>40.9199981689453</v>
       </c>
       <c r="G1645" t="n">
-        <v>39.3653831481934</v>
+        <v>39.3653869628906</v>
       </c>
       <c r="H1645" t="s">
         <v>8</v>
@@ -43165,7 +43165,7 @@
         <v>41.0800018310547</v>
       </c>
       <c r="G1646" t="n">
-        <v>39.5193061828613</v>
+        <v>39.5193099975586</v>
       </c>
       <c r="H1646" t="s">
         <v>8</v>
@@ -43269,7 +43269,7 @@
         <v>42.9599990844727</v>
       </c>
       <c r="G1650" t="n">
-        <v>41.3278846740723</v>
+        <v>41.327880859375</v>
       </c>
       <c r="H1650" t="s">
         <v>8</v>
@@ -43295,7 +43295,7 @@
         <v>43.9000015258789</v>
       </c>
       <c r="G1651" t="n">
-        <v>42.2321739196777</v>
+        <v>42.2321701049805</v>
       </c>
       <c r="H1651" t="s">
         <v>8</v>
@@ -43373,7 +43373,7 @@
         <v>42.0800018310547</v>
       </c>
       <c r="G1654" t="n">
-        <v>40.481315612793</v>
+        <v>40.4813194274902</v>
       </c>
       <c r="H1654" t="s">
         <v>8</v>
@@ -43399,7 +43399,7 @@
         <v>43.060001373291</v>
       </c>
       <c r="G1655" t="n">
-        <v>41.4240875244141</v>
+        <v>41.4240837097168</v>
       </c>
       <c r="H1655" t="s">
         <v>8</v>
@@ -43425,7 +43425,7 @@
         <v>42.0800018310547</v>
       </c>
       <c r="G1656" t="n">
-        <v>40.481315612793</v>
+        <v>40.4813194274902</v>
       </c>
       <c r="H1656" t="s">
         <v>8</v>
@@ -43477,7 +43477,7 @@
         <v>45.560001373291</v>
       </c>
       <c r="G1658" t="n">
-        <v>43.8291091918945</v>
+        <v>43.8291053771973</v>
       </c>
       <c r="H1658" t="s">
         <v>8</v>
@@ -43659,7 +43659,7 @@
         <v>48.6800003051758</v>
       </c>
       <c r="G1665" t="n">
-        <v>46.8305702209473</v>
+        <v>46.8305740356445</v>
       </c>
       <c r="H1665" t="s">
         <v>8</v>
@@ -43711,7 +43711,7 @@
         <v>51.4500007629395</v>
       </c>
       <c r="G1667" t="n">
-        <v>49.4953384399414</v>
+        <v>49.4953346252441</v>
       </c>
       <c r="H1667" t="s">
         <v>8</v>
@@ -43737,7 +43737,7 @@
         <v>52.1500015258789</v>
       </c>
       <c r="G1668" t="n">
-        <v>50.1687431335449</v>
+        <v>50.1687469482422</v>
       </c>
       <c r="H1668" t="s">
         <v>8</v>
@@ -43763,7 +43763,7 @@
         <v>52.5499992370605</v>
       </c>
       <c r="G1669" t="n">
-        <v>50.5535469055176</v>
+        <v>50.5535430908203</v>
       </c>
       <c r="H1669" t="s">
         <v>8</v>
@@ -43893,7 +43893,7 @@
         <v>56.4500007629395</v>
       </c>
       <c r="G1674" t="n">
-        <v>54.3053779602051</v>
+        <v>54.3053741455078</v>
       </c>
       <c r="H1674" t="s">
         <v>8</v>
@@ -44049,7 +44049,7 @@
         <v>56.3499984741211</v>
       </c>
       <c r="G1680" t="n">
-        <v>54.2091789245605</v>
+        <v>54.2091751098633</v>
       </c>
       <c r="H1680" t="s">
         <v>8</v>
@@ -44127,7 +44127,7 @@
         <v>56.5499992370605</v>
       </c>
       <c r="G1683" t="n">
-        <v>54.4015808105469</v>
+        <v>54.4015769958496</v>
       </c>
       <c r="H1683" t="s">
         <v>8</v>
@@ -44153,7 +44153,7 @@
         <v>56.6500015258789</v>
       </c>
       <c r="G1684" t="n">
-        <v>54.4977836608887</v>
+        <v>54.4977798461914</v>
       </c>
       <c r="H1684" t="s">
         <v>8</v>
@@ -44205,7 +44205,7 @@
         <v>56.8499984741211</v>
       </c>
       <c r="G1686" t="n">
-        <v>54.6901779174805</v>
+        <v>54.6901817321777</v>
       </c>
       <c r="H1686" t="s">
         <v>8</v>
@@ -44335,7 +44335,7 @@
         <v>56.5499992370605</v>
       </c>
       <c r="G1691" t="n">
-        <v>54.4015808105469</v>
+        <v>54.4015769958496</v>
       </c>
       <c r="H1691" t="s">
         <v>8</v>
@@ -44361,7 +44361,7 @@
         <v>56.3499984741211</v>
       </c>
       <c r="G1692" t="n">
-        <v>54.2091789245605</v>
+        <v>54.2091751098633</v>
       </c>
       <c r="H1692" t="s">
         <v>8</v>
@@ -44465,7 +44465,7 @@
         <v>51.7999992370605</v>
       </c>
       <c r="G1696" t="n">
-        <v>49.8320426940918</v>
+        <v>49.8320388793945</v>
       </c>
       <c r="H1696" t="s">
         <v>8</v>
@@ -44543,7 +44543,7 @@
         <v>52.2000007629395</v>
       </c>
       <c r="G1699" t="n">
-        <v>50.2168426513672</v>
+        <v>50.2168464660645</v>
       </c>
       <c r="H1699" t="s">
         <v>8</v>
@@ -44595,7 +44595,7 @@
         <v>51.7999992370605</v>
       </c>
       <c r="G1701" t="n">
-        <v>49.8320426940918</v>
+        <v>49.8320388793945</v>
       </c>
       <c r="H1701" t="s">
         <v>8</v>
@@ -44621,7 +44621,7 @@
         <v>52.3499984741211</v>
       </c>
       <c r="G1702" t="n">
-        <v>50.361141204834</v>
+        <v>50.3611373901367</v>
       </c>
       <c r="H1702" t="s">
         <v>8</v>
@@ -44699,7 +44699,7 @@
         <v>52.7999992370605</v>
       </c>
       <c r="G1705" t="n">
-        <v>50.7940483093262</v>
+        <v>50.7940444946289</v>
       </c>
       <c r="H1705" t="s">
         <v>8</v>
@@ -44725,7 +44725,7 @@
         <v>52.9500007629395</v>
       </c>
       <c r="G1706" t="n">
-        <v>50.938346862793</v>
+        <v>50.9383506774902</v>
       </c>
       <c r="H1706" t="s">
         <v>8</v>
@@ -44751,7 +44751,7 @@
         <v>52.2000007629395</v>
       </c>
       <c r="G1707" t="n">
-        <v>50.2168426513672</v>
+        <v>50.2168464660645</v>
       </c>
       <c r="H1707" t="s">
         <v>8</v>
@@ -44803,7 +44803,7 @@
         <v>51.4500007629395</v>
       </c>
       <c r="G1709" t="n">
-        <v>49.4953384399414</v>
+        <v>49.4953346252441</v>
       </c>
       <c r="H1709" t="s">
         <v>8</v>
@@ -44855,7 +44855,7 @@
         <v>52.1500015258789</v>
       </c>
       <c r="G1711" t="n">
-        <v>50.1687431335449</v>
+        <v>50.1687469482422</v>
       </c>
       <c r="H1711" t="s">
         <v>8</v>
@@ -44959,7 +44959,7 @@
         <v>48.060001373291</v>
       </c>
       <c r="G1715" t="n">
-        <v>46.2341270446777</v>
+        <v>46.2341232299805</v>
       </c>
       <c r="H1715" t="s">
         <v>8</v>
@@ -45011,7 +45011,7 @@
         <v>48.7799987792969</v>
       </c>
       <c r="G1717" t="n">
-        <v>46.9267692565918</v>
+        <v>46.9267730712891</v>
       </c>
       <c r="H1717" t="s">
         <v>8</v>
@@ -45141,7 +45141,7 @@
         <v>51.0499992370605</v>
       </c>
       <c r="G1722" t="n">
-        <v>49.1105308532715</v>
+        <v>49.1105346679688</v>
       </c>
       <c r="H1722" t="s">
         <v>8</v>
@@ -45349,7 +45349,7 @@
         <v>51.4500007629395</v>
       </c>
       <c r="G1730" t="n">
-        <v>49.4953384399414</v>
+        <v>49.4953346252441</v>
       </c>
       <c r="H1730" t="s">
         <v>8</v>
@@ -45375,7 +45375,7 @@
         <v>52.2000007629395</v>
       </c>
       <c r="G1731" t="n">
-        <v>50.2168426513672</v>
+        <v>50.2168464660645</v>
       </c>
       <c r="H1731" t="s">
         <v>8</v>
@@ -45427,7 +45427,7 @@
         <v>56.75</v>
       </c>
       <c r="G1733" t="n">
-        <v>54.5939788818359</v>
+        <v>54.5939826965332</v>
       </c>
       <c r="H1733" t="s">
         <v>8</v>
@@ -45479,7 +45479,7 @@
         <v>61</v>
       </c>
       <c r="G1735" t="n">
-        <v>58.6825180053711</v>
+        <v>58.6825141906738</v>
       </c>
       <c r="H1735" t="s">
         <v>8</v>
@@ -45583,7 +45583,7 @@
         <v>58.6500015258789</v>
       </c>
       <c r="G1739" t="n">
-        <v>56.4217987060547</v>
+        <v>56.4217948913574</v>
       </c>
       <c r="H1739" t="s">
         <v>8</v>
@@ -45739,7 +45739,7 @@
         <v>57.1500015258789</v>
       </c>
       <c r="G1745" t="n">
-        <v>54.9787826538086</v>
+        <v>54.9787864685059</v>
       </c>
       <c r="H1745" t="s">
         <v>8</v>
@@ -45765,7 +45765,7 @@
         <v>58.0499992370605</v>
       </c>
       <c r="G1746" t="n">
-        <v>55.8445892333984</v>
+        <v>55.8445930480957</v>
       </c>
       <c r="H1746" t="s">
         <v>8</v>
@@ -45791,7 +45791,7 @@
         <v>60.7000007629395</v>
       </c>
       <c r="G1747" t="n">
-        <v>58.393913269043</v>
+        <v>58.3939170837402</v>
       </c>
       <c r="H1747" t="s">
         <v>8</v>
@@ -45817,7 +45817,7 @@
         <v>62.4500007629395</v>
       </c>
       <c r="G1748" t="n">
-        <v>60.0774307250977</v>
+        <v>60.0774269104004</v>
       </c>
       <c r="H1748" t="s">
         <v>8</v>
@@ -45843,7 +45843,7 @@
         <v>62.5999984741211</v>
       </c>
       <c r="G1749" t="n">
-        <v>60.2217254638672</v>
+        <v>60.2217292785645</v>
       </c>
       <c r="H1749" t="s">
         <v>8</v>
@@ -45869,7 +45869,7 @@
         <v>62.5999984741211</v>
       </c>
       <c r="G1750" t="n">
-        <v>60.2217254638672</v>
+        <v>60.2217292785645</v>
       </c>
       <c r="H1750" t="s">
         <v>8</v>
@@ -45895,7 +45895,7 @@
         <v>60.3499984741211</v>
       </c>
       <c r="G1751" t="n">
-        <v>58.0572128295898</v>
+        <v>58.0572090148926</v>
       </c>
       <c r="H1751" t="s">
         <v>8</v>
@@ -45921,7 +45921,7 @@
         <v>60.3499984741211</v>
       </c>
       <c r="G1752" t="n">
-        <v>58.0572128295898</v>
+        <v>58.0572090148926</v>
       </c>
       <c r="H1752" t="s">
         <v>8</v>
@@ -46233,7 +46233,7 @@
         <v>64.6999969482422</v>
       </c>
       <c r="G1764" t="n">
-        <v>62.2419471740723</v>
+        <v>62.241943359375</v>
       </c>
       <c r="H1764" t="s">
         <v>8</v>
@@ -46285,7 +46285,7 @@
         <v>69.1999969482422</v>
       </c>
       <c r="G1766" t="n">
-        <v>66.5709762573242</v>
+        <v>66.5709838867188</v>
       </c>
       <c r="H1766" t="s">
         <v>8</v>
@@ -46337,7 +46337,7 @@
         <v>69.25</v>
       </c>
       <c r="G1768" t="n">
-        <v>66.6190795898438</v>
+        <v>66.6190872192383</v>
       </c>
       <c r="H1768" t="s">
         <v>8</v>
@@ -46363,7 +46363,7 @@
         <v>69.9000015258789</v>
       </c>
       <c r="G1769" t="n">
-        <v>67.2443923950195</v>
+        <v>67.2444000244141</v>
       </c>
       <c r="H1769" t="s">
         <v>8</v>
@@ -46389,7 +46389,7 @@
         <v>71.6500015258789</v>
       </c>
       <c r="G1770" t="n">
-        <v>68.9279098510742</v>
+        <v>68.9279174804688</v>
       </c>
       <c r="H1770" t="s">
         <v>8</v>
@@ -46441,7 +46441,7 @@
         <v>69.1999969482422</v>
       </c>
       <c r="G1772" t="n">
-        <v>66.5709762573242</v>
+        <v>66.5709838867188</v>
       </c>
       <c r="H1772" t="s">
         <v>8</v>
@@ -46467,7 +46467,7 @@
         <v>69.9000015258789</v>
       </c>
       <c r="G1773" t="n">
-        <v>67.2443923950195</v>
+        <v>67.2444000244141</v>
       </c>
       <c r="H1773" t="s">
         <v>8</v>
@@ -46545,7 +46545,7 @@
         <v>69.9000015258789</v>
       </c>
       <c r="G1776" t="n">
-        <v>67.2443923950195</v>
+        <v>67.2444000244141</v>
       </c>
       <c r="H1776" t="s">
         <v>8</v>
@@ -46571,7 +46571,7 @@
         <v>70.1999969482422</v>
       </c>
       <c r="G1777" t="n">
-        <v>67.5329971313477</v>
+        <v>67.5329895019531</v>
       </c>
       <c r="H1777" t="s">
         <v>8</v>
@@ -46597,7 +46597,7 @@
         <v>69.6500015258789</v>
       </c>
       <c r="G1778" t="n">
-        <v>67.0038909912109</v>
+        <v>67.0038986206055</v>
       </c>
       <c r="H1778" t="s">
         <v>8</v>
@@ -46623,7 +46623,7 @@
         <v>70.0999984741211</v>
       </c>
       <c r="G1779" t="n">
-        <v>67.4367904663086</v>
+        <v>67.4367980957031</v>
       </c>
       <c r="H1779" t="s">
         <v>8</v>
@@ -46675,7 +46675,7 @@
         <v>70.6999969482422</v>
       </c>
       <c r="G1781" t="n">
-        <v>68.0139999389648</v>
+        <v>68.0139923095703</v>
       </c>
       <c r="H1781" t="s">
         <v>8</v>
@@ -46727,7 +46727,7 @@
         <v>67.1999969482422</v>
       </c>
       <c r="G1783" t="n">
-        <v>64.6469650268555</v>
+        <v>64.64697265625</v>
       </c>
       <c r="H1783" t="s">
         <v>8</v>
@@ -46779,7 +46779,7 @@
         <v>69.9000015258789</v>
       </c>
       <c r="G1785" t="n">
-        <v>67.2443923950195</v>
+        <v>67.2444000244141</v>
       </c>
       <c r="H1785" t="s">
         <v>8</v>
@@ -46909,7 +46909,7 @@
         <v>68.25</v>
       </c>
       <c r="G1790" t="n">
-        <v>65.6570816040039</v>
+        <v>65.6570739746094</v>
       </c>
       <c r="H1790" t="s">
         <v>8</v>
@@ -46935,7 +46935,7 @@
         <v>67.8499984741211</v>
       </c>
       <c r="G1791" t="n">
-        <v>65.2722778320312</v>
+        <v>65.2722702026367</v>
       </c>
       <c r="H1791" t="s">
         <v>8</v>
@@ -46961,7 +46961,7 @@
         <v>68.6500015258789</v>
       </c>
       <c r="G1792" t="n">
-        <v>66.0418930053711</v>
+        <v>66.0418853759766</v>
       </c>
       <c r="H1792" t="s">
         <v>8</v>
@@ -46987,7 +46987,7 @@
         <v>68.8499984741211</v>
       </c>
       <c r="G1793" t="n">
-        <v>66.2342834472656</v>
+        <v>66.2342758178711</v>
       </c>
       <c r="H1793" t="s">
         <v>8</v>
@@ -47039,7 +47039,7 @@
         <v>70.4499969482422</v>
       </c>
       <c r="G1795" t="n">
-        <v>67.7734985351562</v>
+        <v>67.7734909057617</v>
       </c>
       <c r="H1795" t="s">
         <v>8</v>
@@ -47247,7 +47247,7 @@
         <v>77</v>
       </c>
       <c r="G1803" t="n">
-        <v>74.0746459960938</v>
+        <v>74.0746536254883</v>
       </c>
       <c r="H1803" t="s">
         <v>8</v>
@@ -47273,7 +47273,7 @@
         <v>76.25</v>
       </c>
       <c r="G1804" t="n">
-        <v>73.3531494140625</v>
+        <v>73.353141784668</v>
       </c>
       <c r="H1804" t="s">
         <v>8</v>
@@ -47533,7 +47533,7 @@
         <v>79.9000015258789</v>
       </c>
       <c r="G1814" t="n">
-        <v>76.8644790649414</v>
+        <v>76.8644866943359</v>
       </c>
       <c r="H1814" t="s">
         <v>8</v>
@@ -47637,7 +47637,7 @@
         <v>79.1999969482422</v>
       </c>
       <c r="G1818" t="n">
-        <v>76.1910629272461</v>
+        <v>76.1910705566406</v>
       </c>
       <c r="H1818" t="s">
         <v>8</v>
@@ -47663,7 +47663,7 @@
         <v>80.1999969482422</v>
       </c>
       <c r="G1819" t="n">
-        <v>77.153076171875</v>
+        <v>77.1530685424805</v>
       </c>
       <c r="H1819" t="s">
         <v>8</v>
@@ -47689,7 +47689,7 @@
         <v>80.0500030517578</v>
       </c>
       <c r="G1820" t="n">
-        <v>77.0087890625</v>
+        <v>77.0087814331055</v>
       </c>
       <c r="H1820" t="s">
         <v>8</v>
@@ -47715,7 +47715,7 @@
         <v>81.1999969482422</v>
       </c>
       <c r="G1821" t="n">
-        <v>78.1150817871094</v>
+        <v>78.1150894165039</v>
       </c>
       <c r="H1821" t="s">
         <v>8</v>
@@ -47741,7 +47741,7 @@
         <v>79.4499969482422</v>
       </c>
       <c r="G1822" t="n">
-        <v>76.4315643310547</v>
+        <v>76.4315719604492</v>
       </c>
       <c r="H1822" t="s">
         <v>8</v>
@@ -47845,7 +47845,7 @@
         <v>80.0500030517578</v>
       </c>
       <c r="G1826" t="n">
-        <v>77.0087890625</v>
+        <v>77.0087814331055</v>
       </c>
       <c r="H1826" t="s">
         <v>8</v>
@@ -47871,7 +47871,7 @@
         <v>80.3499984741211</v>
       </c>
       <c r="G1827" t="n">
-        <v>77.2973785400391</v>
+        <v>77.2973709106445</v>
       </c>
       <c r="H1827" t="s">
         <v>8</v>
@@ -47949,7 +47949,7 @@
         <v>79.8499984741211</v>
       </c>
       <c r="G1830" t="n">
-        <v>76.8163757324219</v>
+        <v>76.8163833618164</v>
       </c>
       <c r="H1830" t="s">
         <v>8</v>
@@ -48131,7 +48131,7 @@
         <v>77.8000030517578</v>
       </c>
       <c r="G1837" t="n">
-        <v>74.8442687988281</v>
+        <v>74.8442611694336</v>
       </c>
       <c r="H1837" t="s">
         <v>8</v>
@@ -48261,7 +48261,7 @@
         <v>83.5999984741211</v>
       </c>
       <c r="G1842" t="n">
-        <v>80.4239120483398</v>
+        <v>80.4239044189453</v>
       </c>
       <c r="H1842" t="s">
         <v>8</v>
@@ -48339,7 +48339,7 @@
         <v>87.5</v>
       </c>
       <c r="G1845" t="n">
-        <v>84.1757431030273</v>
+        <v>84.1757354736328</v>
       </c>
       <c r="H1845" t="s">
         <v>8</v>
@@ -48573,7 +48573,7 @@
         <v>90</v>
       </c>
       <c r="G1854" t="n">
-        <v>86.5807647705078</v>
+        <v>86.5807571411133</v>
       </c>
       <c r="H1854" t="s">
         <v>8</v>
@@ -48625,7 +48625,7 @@
         <v>90.1500015258789</v>
       </c>
       <c r="G1856" t="n">
-        <v>86.7250671386719</v>
+        <v>86.7250595092773</v>
       </c>
       <c r="H1856" t="s">
         <v>8</v>
@@ -48677,7 +48677,7 @@
         <v>88.3499984741211</v>
       </c>
       <c r="G1858" t="n">
-        <v>84.9934387207031</v>
+        <v>84.9934463500977</v>
       </c>
       <c r="H1858" t="s">
         <v>8</v>
@@ -48885,7 +48885,7 @@
         <v>84.25</v>
       </c>
       <c r="G1866" t="n">
-        <v>81.0492248535156</v>
+        <v>81.0492172241211</v>
       </c>
       <c r="H1866" t="s">
         <v>8</v>
@@ -49015,7 +49015,7 @@
         <v>86.0500030517578</v>
       </c>
       <c r="G1871" t="n">
-        <v>82.7808380126953</v>
+        <v>82.7808303833008</v>
       </c>
       <c r="H1871" t="s">
         <v>8</v>
@@ -49301,7 +49301,7 @@
         <v>78.5</v>
       </c>
       <c r="G1882" t="n">
-        <v>76.1210708618164</v>
+        <v>76.1210632324219</v>
       </c>
       <c r="H1882" t="s">
         <v>8</v>
@@ -49353,7 +49353,7 @@
         <v>80.0500030517578</v>
       </c>
       <c r="G1884" t="n">
-        <v>77.6240997314453</v>
+        <v>77.6240921020508</v>
       </c>
       <c r="H1884" t="s">
         <v>8</v>
@@ -49561,7 +49561,7 @@
         <v>81.1999969482422</v>
       </c>
       <c r="G1892" t="n">
-        <v>78.7392349243164</v>
+        <v>78.7392425537109</v>
       </c>
       <c r="H1892" t="s">
         <v>8</v>
@@ -49639,7 +49639,7 @@
         <v>84.25</v>
       </c>
       <c r="G1895" t="n">
-        <v>81.6968154907227</v>
+        <v>81.6968078613281</v>
       </c>
       <c r="H1895" t="s">
         <v>8</v>
@@ -49691,7 +49691,7 @@
         <v>85.1500015258789</v>
       </c>
       <c r="G1897" t="n">
-        <v>82.5695419311523</v>
+        <v>82.5695343017578</v>
       </c>
       <c r="H1897" t="s">
         <v>8</v>
@@ -49743,7 +49743,7 @@
         <v>85.4000015258789</v>
       </c>
       <c r="G1899" t="n">
-        <v>82.8119659423828</v>
+        <v>82.8119583129883</v>
       </c>
       <c r="H1899" t="s">
         <v>8</v>
@@ -49899,7 +49899,7 @@
         <v>80.75</v>
       </c>
       <c r="G1905" t="n">
-        <v>78.3028717041016</v>
+        <v>78.3028793334961</v>
       </c>
       <c r="H1905" t="s">
         <v>8</v>
@@ -50029,7 +50029,7 @@
         <v>78.5</v>
       </c>
       <c r="G1910" t="n">
-        <v>76.1210708618164</v>
+        <v>76.1210632324219</v>
       </c>
       <c r="H1910" t="s">
         <v>8</v>
@@ -50055,7 +50055,7 @@
         <v>78.25</v>
       </c>
       <c r="G1911" t="n">
-        <v>75.8786468505859</v>
+        <v>75.8786392211914</v>
       </c>
       <c r="H1911" t="s">
         <v>8</v>
@@ -50263,7 +50263,7 @@
         <v>80.3499984741211</v>
       </c>
       <c r="G1919" t="n">
-        <v>77.9150009155273</v>
+        <v>77.9149932861328</v>
       </c>
       <c r="H1919" t="s">
         <v>8</v>
@@ -50289,7 +50289,7 @@
         <v>77</v>
       </c>
       <c r="G1920" t="n">
-        <v>74.6665191650391</v>
+        <v>74.6665267944336</v>
       </c>
       <c r="H1920" t="s">
         <v>8</v>
@@ -50315,7 +50315,7 @@
         <v>76.4499969482422</v>
       </c>
       <c r="G1921" t="n">
-        <v>74.133186340332</v>
+        <v>74.1331787109375</v>
       </c>
       <c r="H1921" t="s">
         <v>8</v>
@@ -50341,7 +50341,7 @@
         <v>77.1999969482422</v>
       </c>
       <c r="G1922" t="n">
-        <v>74.8604507446289</v>
+        <v>74.8604583740234</v>
       </c>
       <c r="H1922" t="s">
         <v>8</v>
@@ -50393,7 +50393,7 @@
         <v>77.0500030517578</v>
       </c>
       <c r="G1924" t="n">
-        <v>74.7150039672852</v>
+        <v>74.7150115966797</v>
       </c>
       <c r="H1924" t="s">
         <v>8</v>
@@ -50419,7 +50419,7 @@
         <v>76.5</v>
       </c>
       <c r="G1925" t="n">
-        <v>74.1816787719727</v>
+        <v>74.1816711425781</v>
       </c>
       <c r="H1925" t="s">
         <v>8</v>
@@ -50445,7 +50445,7 @@
         <v>76.0500030517578</v>
       </c>
       <c r="G1926" t="n">
-        <v>73.7453155517578</v>
+        <v>73.7453079223633</v>
       </c>
       <c r="H1926" t="s">
         <v>8</v>
@@ -50497,7 +50497,7 @@
         <v>76.0500030517578</v>
       </c>
       <c r="G1928" t="n">
-        <v>73.7453155517578</v>
+        <v>73.7453079223633</v>
       </c>
       <c r="H1928" t="s">
         <v>8</v>
@@ -50575,7 +50575,7 @@
         <v>75.0500030517578</v>
       </c>
       <c r="G1931" t="n">
-        <v>72.7756118774414</v>
+        <v>72.7756195068359</v>
       </c>
       <c r="H1931" t="s">
         <v>8</v>
@@ -50757,7 +50757,7 @@
         <v>75.8000030517578</v>
       </c>
       <c r="G1938" t="n">
-        <v>73.5028915405273</v>
+        <v>73.5028839111328</v>
       </c>
       <c r="H1938" t="s">
         <v>8</v>
@@ -50939,7 +50939,7 @@
         <v>71</v>
       </c>
       <c r="G1945" t="n">
-        <v>68.8483428955078</v>
+        <v>68.8483505249023</v>
       </c>
       <c r="H1945" t="s">
         <v>8</v>
@@ -50991,7 +50991,7 @@
         <v>70.4499969482422</v>
       </c>
       <c r="G1947" t="n">
-        <v>68.3150177001953</v>
+        <v>68.3150100708008</v>
       </c>
       <c r="H1947" t="s">
         <v>8</v>
@@ -51017,7 +51017,7 @@
         <v>70.0999984741211</v>
       </c>
       <c r="G1948" t="n">
-        <v>67.9756240844727</v>
+        <v>67.9756317138672</v>
       </c>
       <c r="H1948" t="s">
         <v>8</v>
@@ -51043,7 +51043,7 @@
         <v>70.5</v>
       </c>
       <c r="G1949" t="n">
-        <v>68.3635101318359</v>
+        <v>68.3635025024414</v>
       </c>
       <c r="H1949" t="s">
         <v>8</v>
@@ -51095,7 +51095,7 @@
         <v>77.0500030517578</v>
       </c>
       <c r="G1951" t="n">
-        <v>74.7150039672852</v>
+        <v>74.7150115966797</v>
       </c>
       <c r="H1951" t="s">
         <v>8</v>
@@ -51173,7 +51173,7 @@
         <v>74.6999969482422</v>
       </c>
       <c r="G1954" t="n">
-        <v>72.4362182617188</v>
+        <v>72.4362258911133</v>
       </c>
       <c r="H1954" t="s">
         <v>8</v>
@@ -51355,7 +51355,7 @@
         <v>73.8499984741211</v>
       </c>
       <c r="G1961" t="n">
-        <v>71.6119842529297</v>
+        <v>71.6119766235352</v>
       </c>
       <c r="H1961" t="s">
         <v>8</v>
@@ -51407,7 +51407,7 @@
         <v>74.75</v>
       </c>
       <c r="G1963" t="n">
-        <v>72.4847030639648</v>
+        <v>72.4847106933594</v>
       </c>
       <c r="H1963" t="s">
         <v>8</v>
@@ -51459,7 +51459,7 @@
         <v>71.1999969482422</v>
       </c>
       <c r="G1965" t="n">
-        <v>69.0422821044922</v>
+        <v>69.0422897338867</v>
       </c>
       <c r="H1965" t="s">
         <v>8</v>
@@ -51485,7 +51485,7 @@
         <v>71.6500015258789</v>
       </c>
       <c r="G1966" t="n">
-        <v>69.4786529541016</v>
+        <v>69.4786605834961</v>
       </c>
       <c r="H1966" t="s">
         <v>8</v>
@@ -51537,7 +51537,7 @@
         <v>71.4499969482422</v>
       </c>
       <c r="G1968" t="n">
-        <v>69.2847061157227</v>
+        <v>69.2847137451172</v>
       </c>
       <c r="H1968" t="s">
         <v>8</v>
@@ -51589,7 +51589,7 @@
         <v>69.0500030517578</v>
       </c>
       <c r="G1970" t="n">
-        <v>66.9574432373047</v>
+        <v>66.9574508666992</v>
       </c>
       <c r="H1970" t="s">
         <v>8</v>
@@ -51615,7 +51615,7 @@
         <v>68.8499984741211</v>
       </c>
       <c r="G1971" t="n">
-        <v>66.7635040283203</v>
+        <v>66.7634963989258</v>
       </c>
       <c r="H1971" t="s">
         <v>8</v>
@@ -52031,7 +52031,7 @@
         <v>71.6500015258789</v>
       </c>
       <c r="G1987" t="n">
-        <v>69.4786529541016</v>
+        <v>69.4786605834961</v>
       </c>
       <c r="H1987" t="s">
         <v>8</v>
@@ -52135,7 +52135,7 @@
         <v>79</v>
       </c>
       <c r="G1991" t="n">
-        <v>76.6059036254883</v>
+        <v>76.6059112548828</v>
       </c>
       <c r="H1991" t="s">
         <v>8</v>
@@ -52187,7 +52187,7 @@
         <v>74.6999969482422</v>
       </c>
       <c r="G1993" t="n">
-        <v>72.4362182617188</v>
+        <v>72.4362258911133</v>
       </c>
       <c r="H1993" t="s">
         <v>8</v>
@@ -52213,7 +52213,7 @@
         <v>74.5</v>
       </c>
       <c r="G1994" t="n">
-        <v>72.2422866821289</v>
+        <v>72.2422790527344</v>
       </c>
       <c r="H1994" t="s">
         <v>8</v>
@@ -52239,7 +52239,7 @@
         <v>75.8499984741211</v>
       </c>
       <c r="G1995" t="n">
-        <v>73.5513763427734</v>
+        <v>73.5513687133789</v>
       </c>
       <c r="H1995" t="s">
         <v>8</v>
@@ -52369,7 +52369,7 @@
         <v>79.4499969482422</v>
       </c>
       <c r="G2000" t="n">
-        <v>77.0422668457031</v>
+        <v>77.0422744750977</v>
       </c>
       <c r="H2000" t="s">
         <v>8</v>
@@ -52473,7 +52473,7 @@
         <v>80.1500015258789</v>
       </c>
       <c r="G2004" t="n">
-        <v>77.721061706543</v>
+        <v>77.7210540771484</v>
       </c>
       <c r="H2004" t="s">
         <v>8</v>
@@ -52525,7 +52525,7 @@
         <v>81.1999969482422</v>
       </c>
       <c r="G2006" t="n">
-        <v>78.7392349243164</v>
+        <v>78.7392425537109</v>
       </c>
       <c r="H2006" t="s">
         <v>8</v>
@@ -52577,7 +52577,7 @@
         <v>77.3000030517578</v>
       </c>
       <c r="G2008" t="n">
-        <v>74.9574279785156</v>
+        <v>74.9574356079102</v>
       </c>
       <c r="H2008" t="s">
         <v>8</v>
@@ -52603,7 +52603,7 @@
         <v>77.5999984741211</v>
       </c>
       <c r="G2009" t="n">
-        <v>75.2483367919922</v>
+        <v>75.2483291625977</v>
       </c>
       <c r="H2009" t="s">
         <v>8</v>
@@ -52629,7 +52629,7 @@
         <v>77.5</v>
       </c>
       <c r="G2010" t="n">
-        <v>75.1513671875</v>
+        <v>75.1513748168945</v>
       </c>
       <c r="H2010" t="s">
         <v>8</v>
@@ -52707,7 +52707,7 @@
         <v>77.75</v>
       </c>
       <c r="G2013" t="n">
-        <v>75.3937911987305</v>
+        <v>75.3937835693359</v>
       </c>
       <c r="H2013" t="s">
         <v>8</v>
@@ -52785,7 +52785,7 @@
         <v>74.8000030517578</v>
       </c>
       <c r="G2016" t="n">
-        <v>72.5331878662109</v>
+        <v>72.5331954956055</v>
       </c>
       <c r="H2016" t="s">
         <v>8</v>
@@ -52837,7 +52837,7 @@
         <v>75.4000015258789</v>
       </c>
       <c r="G2018" t="n">
-        <v>73.1150131225586</v>
+        <v>73.1150054931641</v>
       </c>
       <c r="H2018" t="s">
         <v>8</v>
@@ -52863,7 +52863,7 @@
         <v>75.8499984741211</v>
       </c>
       <c r="G2019" t="n">
-        <v>73.5513763427734</v>
+        <v>73.5513687133789</v>
       </c>
       <c r="H2019" t="s">
         <v>8</v>
@@ -52889,7 +52889,7 @@
         <v>76.0500030517578</v>
       </c>
       <c r="G2020" t="n">
-        <v>73.7453155517578</v>
+        <v>73.7453079223633</v>
       </c>
       <c r="H2020" t="s">
         <v>8</v>
@@ -52915,7 +52915,7 @@
         <v>75.8000030517578</v>
       </c>
       <c r="G2021" t="n">
-        <v>73.5028915405273</v>
+        <v>73.5028839111328</v>
       </c>
       <c r="H2021" t="s">
         <v>8</v>
@@ -52941,7 +52941,7 @@
         <v>77</v>
       </c>
       <c r="G2022" t="n">
-        <v>74.6665191650391</v>
+        <v>74.6665267944336</v>
       </c>
       <c r="H2022" t="s">
         <v>8</v>
@@ -52967,7 +52967,7 @@
         <v>79.1999969482422</v>
       </c>
       <c r="G2023" t="n">
-        <v>76.7998428344727</v>
+        <v>76.7998504638672</v>
       </c>
       <c r="H2023" t="s">
         <v>8</v>
@@ -53071,7 +53071,7 @@
         <v>88</v>
       </c>
       <c r="G2027" t="n">
-        <v>85.3331680297852</v>
+        <v>85.3331604003906</v>
       </c>
       <c r="H2027" t="s">
         <v>8</v>
@@ -53123,7 +53123,7 @@
         <v>84.4000015258789</v>
       </c>
       <c r="G2029" t="n">
-        <v>81.8422622680664</v>
+        <v>81.8422698974609</v>
       </c>
       <c r="H2029" t="s">
         <v>8</v>
@@ -53149,7 +53149,7 @@
         <v>86.5500030517578</v>
       </c>
       <c r="G2030" t="n">
-        <v>83.9271087646484</v>
+        <v>83.927116394043</v>
       </c>
       <c r="H2030" t="s">
         <v>8</v>
@@ -53175,7 +53175,7 @@
         <v>87.25</v>
       </c>
       <c r="G2031" t="n">
-        <v>84.6058959960938</v>
+        <v>84.6059036254883</v>
       </c>
       <c r="H2031" t="s">
         <v>8</v>
@@ -53201,7 +53201,7 @@
         <v>88</v>
       </c>
       <c r="G2032" t="n">
-        <v>85.3331680297852</v>
+        <v>85.3331604003906</v>
       </c>
       <c r="H2032" t="s">
         <v>8</v>
@@ -53253,7 +53253,7 @@
         <v>88.3499984741211</v>
       </c>
       <c r="G2034" t="n">
-        <v>85.6725540161133</v>
+        <v>85.6725616455078</v>
       </c>
       <c r="H2034" t="s">
         <v>8</v>
@@ -53279,7 +53279,7 @@
         <v>88.3000030517578</v>
       </c>
       <c r="G2035" t="n">
-        <v>85.6240692138672</v>
+        <v>85.6240768432617</v>
       </c>
       <c r="H2035" t="s">
         <v>8</v>
@@ -53331,7 +53331,7 @@
         <v>87.5999984741211</v>
       </c>
       <c r="G2037" t="n">
-        <v>84.9452896118164</v>
+        <v>84.9452819824219</v>
       </c>
       <c r="H2037" t="s">
         <v>8</v>
@@ -53357,7 +53357,7 @@
         <v>84.4499969482422</v>
       </c>
       <c r="G2038" t="n">
-        <v>81.8907470703125</v>
+        <v>81.890754699707</v>
       </c>
       <c r="H2038" t="s">
         <v>8</v>
@@ -53435,7 +53435,7 @@
         <v>84.75</v>
       </c>
       <c r="G2041" t="n">
-        <v>82.1816482543945</v>
+        <v>82.1816558837891</v>
       </c>
       <c r="H2041" t="s">
         <v>8</v>
@@ -53487,7 +53487,7 @@
         <v>84.4000015258789</v>
       </c>
       <c r="G2043" t="n">
-        <v>81.8422622680664</v>
+        <v>81.8422698974609</v>
       </c>
       <c r="H2043" t="s">
         <v>8</v>
@@ -53513,7 +53513,7 @@
         <v>86.25</v>
       </c>
       <c r="G2044" t="n">
-        <v>83.6362075805664</v>
+        <v>83.6361999511719</v>
       </c>
       <c r="H2044" t="s">
         <v>8</v>
@@ -53591,7 +53591,7 @@
         <v>85.5500030517578</v>
       </c>
       <c r="G2047" t="n">
-        <v>82.9574203491211</v>
+        <v>82.9574127197266</v>
       </c>
       <c r="H2047" t="s">
         <v>8</v>
@@ -53617,7 +53617,7 @@
         <v>84.0500030517578</v>
       </c>
       <c r="G2048" t="n">
-        <v>81.5028762817383</v>
+        <v>81.5028686523438</v>
       </c>
       <c r="H2048" t="s">
         <v>8</v>
@@ -53643,7 +53643,7 @@
         <v>84.6500015258789</v>
       </c>
       <c r="G2049" t="n">
-        <v>82.0846862792969</v>
+        <v>82.0846939086914</v>
       </c>
       <c r="H2049" t="s">
         <v>8</v>
@@ -53669,7 +53669,7 @@
         <v>84.9499969482422</v>
       </c>
       <c r="G2050" t="n">
-        <v>82.3755950927734</v>
+        <v>82.3755874633789</v>
       </c>
       <c r="H2050" t="s">
         <v>8</v>
@@ -53695,7 +53695,7 @@
         <v>84.8499984741211</v>
       </c>
       <c r="G2051" t="n">
-        <v>82.2786254882812</v>
+        <v>82.2786331176758</v>
       </c>
       <c r="H2051" t="s">
         <v>8</v>
@@ -53721,7 +53721,7 @@
         <v>84.25</v>
       </c>
       <c r="G2052" t="n">
-        <v>81.6968154907227</v>
+        <v>81.6968078613281</v>
       </c>
       <c r="H2052" t="s">
         <v>8</v>
@@ -53929,7 +53929,7 @@
         <v>93.5999984741211</v>
       </c>
       <c r="G2060" t="n">
-        <v>90.7634658813477</v>
+        <v>90.7634582519531</v>
       </c>
       <c r="H2060" t="s">
         <v>8</v>
@@ -53981,7 +53981,7 @@
         <v>95.5500030517578</v>
       </c>
       <c r="G2062" t="n">
-        <v>92.6543731689453</v>
+        <v>92.6543655395508</v>
       </c>
       <c r="H2062" t="s">
         <v>8</v>
@@ -54111,7 +54111,7 @@
         <v>102.699996948242</v>
       </c>
       <c r="G2067" t="n">
-        <v>99.5876846313477</v>
+        <v>99.5876770019531</v>
       </c>
       <c r="H2067" t="s">
         <v>8</v>
@@ -54137,7 +54137,7 @@
         <v>104.699996948242</v>
       </c>
       <c r="G2068" t="n">
-        <v>101.527076721191</v>
+        <v>101.527069091797</v>
       </c>
       <c r="H2068" t="s">
         <v>8</v>
@@ -54163,7 +54163,7 @@
         <v>104.599998474121</v>
       </c>
       <c r="G2069" t="n">
-        <v>101.430099487305</v>
+        <v>101.430107116699</v>
       </c>
       <c r="H2069" t="s">
         <v>8</v>
@@ -54475,7 +54475,7 @@
         <v>113.300003051758</v>
       </c>
       <c r="G2081" t="n">
-        <v>109.866455078125</v>
+        <v>109.86644744873</v>
       </c>
       <c r="H2081" t="s">
         <v>8</v>
@@ -54527,7 +54527,7 @@
         <v>111.699996948242</v>
       </c>
       <c r="G2083" t="n">
-        <v>108.314933776855</v>
+        <v>108.31494140625</v>
       </c>
       <c r="H2083" t="s">
         <v>8</v>
@@ -54605,7 +54605,7 @@
         <v>111.900001525879</v>
       </c>
       <c r="G2086" t="n">
-        <v>108.50887298584</v>
+        <v>108.508880615234</v>
       </c>
       <c r="H2086" t="s">
         <v>8</v>
@@ -54657,7 +54657,7 @@
         <v>115.900001525879</v>
       </c>
       <c r="G2088" t="n">
-        <v>112.387657165527</v>
+        <v>112.387664794922</v>
       </c>
       <c r="H2088" t="s">
         <v>8</v>
@@ -54709,7 +54709,7 @@
         <v>107.5</v>
       </c>
       <c r="G2090" t="n">
-        <v>104.242225646973</v>
+        <v>104.242218017578</v>
       </c>
       <c r="H2090" t="s">
         <v>8</v>
@@ -54761,7 +54761,7 @@
         <v>105.5</v>
       </c>
       <c r="G2092" t="n">
-        <v>102.302833557129</v>
+        <v>102.302825927734</v>
       </c>
       <c r="H2092" t="s">
         <v>8</v>
@@ -54787,7 +54787,7 @@
         <v>106.300003051758</v>
       </c>
       <c r="G2093" t="n">
-        <v>103.078582763672</v>
+        <v>103.078590393066</v>
       </c>
       <c r="H2093" t="s">
         <v>8</v>
@@ -54813,7 +54813,7 @@
         <v>104.400001525879</v>
       </c>
       <c r="G2094" t="n">
-        <v>101.236167907715</v>
+        <v>101.236175537109</v>
       </c>
       <c r="H2094" t="s">
         <v>8</v>
@@ -55099,7 +55099,7 @@
         <v>97.3000030517578</v>
       </c>
       <c r="G2105" t="n">
-        <v>94.3513336181641</v>
+        <v>94.3513259887695</v>
       </c>
       <c r="H2105" t="s">
         <v>8</v>
@@ -55151,7 +55151,7 @@
         <v>98.0999984741211</v>
       </c>
       <c r="G2107" t="n">
-        <v>95.127082824707</v>
+        <v>95.1270904541016</v>
       </c>
       <c r="H2107" t="s">
         <v>8</v>
@@ -55229,7 +55229,7 @@
         <v>98.5500030517578</v>
       </c>
       <c r="G2110" t="n">
-        <v>95.5634460449219</v>
+        <v>95.5634536743164</v>
       </c>
       <c r="H2110" t="s">
         <v>8</v>
@@ -55359,7 +55359,7 @@
         <v>98.3000030517578</v>
       </c>
       <c r="G2115" t="n">
-        <v>95.3210220336914</v>
+        <v>95.3210296630859</v>
       </c>
       <c r="H2115" t="s">
         <v>8</v>
@@ -55385,7 +55385,7 @@
         <v>96.5500030517578</v>
       </c>
       <c r="G2116" t="n">
-        <v>93.6240615844727</v>
+        <v>93.6240692138672</v>
       </c>
       <c r="H2116" t="s">
         <v>8</v>
@@ -55411,7 +55411,7 @@
         <v>94.5999984741211</v>
       </c>
       <c r="G2117" t="n">
-        <v>91.7331466674805</v>
+        <v>91.733154296875</v>
       </c>
       <c r="H2117" t="s">
         <v>8</v>
@@ -55489,7 +55489,7 @@
         <v>96.0999984741211</v>
       </c>
       <c r="G2120" t="n">
-        <v>93.1876907348633</v>
+        <v>93.1876983642578</v>
       </c>
       <c r="H2120" t="s">
         <v>8</v>
@@ -55567,7 +55567,7 @@
         <v>96.5999984741211</v>
       </c>
       <c r="G2123" t="n">
-        <v>93.6725387573242</v>
+        <v>93.6725463867188</v>
       </c>
       <c r="H2123" t="s">
         <v>8</v>
@@ -55671,7 +55671,7 @@
         <v>95.1500015258789</v>
       </c>
       <c r="G2127" t="n">
-        <v>92.266487121582</v>
+        <v>92.2664794921875</v>
       </c>
       <c r="H2127" t="s">
         <v>8</v>
@@ -55697,7 +55697,7 @@
         <v>95.1500015258789</v>
       </c>
       <c r="G2128" t="n">
-        <v>92.266487121582</v>
+        <v>92.2664794921875</v>
       </c>
       <c r="H2128" t="s">
         <v>8</v>
@@ -55723,7 +55723,7 @@
         <v>96.1500015258789</v>
       </c>
       <c r="G2129" t="n">
-        <v>93.2361755371094</v>
+        <v>93.2361831665039</v>
       </c>
       <c r="H2129" t="s">
         <v>8</v>
@@ -55801,7 +55801,7 @@
         <v>96.1500015258789</v>
       </c>
       <c r="G2132" t="n">
-        <v>93.2361755371094</v>
+        <v>93.2361831665039</v>
       </c>
       <c r="H2132" t="s">
         <v>8</v>
@@ -71300,6 +71300,32 @@
         <v>80.9599990844727</v>
       </c>
       <c r="H2728" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2729">
+      <c r="A2729" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B2729" t="n">
+        <v>193562</v>
+      </c>
+      <c r="C2729" t="n">
+        <v>81.8000030517578</v>
+      </c>
+      <c r="D2729" t="n">
+        <v>80.7600021362305</v>
+      </c>
+      <c r="E2729" t="n">
+        <v>81.5</v>
+      </c>
+      <c r="F2729" t="n">
+        <v>80.8000030517578</v>
+      </c>
+      <c r="G2729" t="n">
+        <v>80.8000030517578</v>
+      </c>
+      <c r="H2729" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/BC.MI.xlsx
+++ b/data/BC.MI.xlsx
@@ -63270,8 +63270,31 @@
       <c r="E2735" t="n">
         <v>81.5</v>
       </c>
-      <c r="F2735"/>
+      <c r="F2735" t="n">
+        <v>80.4599990844727</v>
+      </c>
       <c r="G2735" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2736">
+      <c r="A2736" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2736" t="n">
+        <v>178523</v>
+      </c>
+      <c r="C2736" t="n">
+        <v>80.9000015258789</v>
+      </c>
+      <c r="D2736" t="n">
+        <v>79.3399963378906</v>
+      </c>
+      <c r="E2736" t="n">
+        <v>80.7200012207031</v>
+      </c>
+      <c r="F2736"/>
+      <c r="G2736" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/BC.MI.xlsx
+++ b/data/BC.MI.xlsx
@@ -63293,8 +63293,31 @@
       <c r="E2736" t="n">
         <v>80.7200012207031</v>
       </c>
-      <c r="F2736"/>
+      <c r="F2736" t="n">
+        <v>80.379997253418</v>
+      </c>
       <c r="G2736" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2737">
+      <c r="A2737" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2737" t="n">
+        <v>143666</v>
+      </c>
+      <c r="C2737" t="n">
+        <v>81.1399993896484</v>
+      </c>
+      <c r="D2737" t="n">
+        <v>79.5400009155273</v>
+      </c>
+      <c r="E2737" t="n">
+        <v>79.7200012207031</v>
+      </c>
+      <c r="F2737"/>
+      <c r="G2737" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/BC.MI.xlsx
+++ b/data/BC.MI.xlsx
@@ -63316,8 +63316,31 @@
       <c r="E2737" t="n">
         <v>79.7200012207031</v>
       </c>
-      <c r="F2737"/>
+      <c r="F2737" t="n">
+        <v>80.5599975585938</v>
+      </c>
       <c r="G2737" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2738">
+      <c r="A2738" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2738" t="n">
+        <v>108665</v>
+      </c>
+      <c r="C2738" t="n">
+        <v>80.6999969482422</v>
+      </c>
+      <c r="D2738" t="n">
+        <v>79.5199966430664</v>
+      </c>
+      <c r="E2738" t="n">
+        <v>80.3000030517578</v>
+      </c>
+      <c r="F2738"/>
+      <c r="G2738" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/BC.MI.xlsx
+++ b/data/BC.MI.xlsx
@@ -63339,8 +63339,31 @@
       <c r="E2738" t="n">
         <v>80.3000030517578</v>
       </c>
-      <c r="F2738"/>
+      <c r="F2738" t="n">
+        <v>80.0999984741211</v>
+      </c>
       <c r="G2738" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2739">
+      <c r="A2739" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B2739" t="n">
+        <v>153949</v>
+      </c>
+      <c r="C2739" t="n">
+        <v>81.8199996948242</v>
+      </c>
+      <c r="D2739" t="n">
+        <v>80.2600021362305</v>
+      </c>
+      <c r="E2739" t="n">
+        <v>80.4199981689453</v>
+      </c>
+      <c r="F2739"/>
+      <c r="G2739" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/BC.MI.xlsx
+++ b/data/BC.MI.xlsx
@@ -63369,6 +63369,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2740">
+      <c r="A2740" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2740" t="n">
+        <v>168924</v>
+      </c>
+      <c r="C2740" t="n">
+        <v>81.9000015258789</v>
+      </c>
+      <c r="D2740" t="n">
+        <v>80.7600021362305</v>
+      </c>
+      <c r="E2740" t="n">
+        <v>81</v>
+      </c>
+      <c r="F2740" t="n">
+        <v>81.1999969482422</v>
+      </c>
+      <c r="G2740" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/BC.MI.xlsx
+++ b/data/BC.MI.xlsx
@@ -456,7 +456,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G3" t="n">
-        <v>14.6633539199829</v>
+        <v>14.6633529663086</v>
       </c>
       <c r="H3" t="n">
         <v>61148</v>
@@ -485,7 +485,7 @@
         <v>15.5</v>
       </c>
       <c r="G4" t="n">
-        <v>14.2944641113281</v>
+        <v>14.2944650650024</v>
       </c>
       <c r="H4" t="n">
         <v>43332</v>
@@ -572,7 +572,7 @@
         <v>14.9099998474121</v>
       </c>
       <c r="G7" t="n">
-        <v>13.7503509521484</v>
+        <v>13.7503519058228</v>
       </c>
       <c r="H7" t="n">
         <v>42969</v>
@@ -630,7 +630,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G9" t="n">
-        <v>14.8477983474731</v>
+        <v>14.8477973937988</v>
       </c>
       <c r="H9" t="n">
         <v>95690</v>
@@ -688,7 +688,7 @@
         <v>16.3799991607666</v>
       </c>
       <c r="G11" t="n">
-        <v>15.1060209274292</v>
+        <v>15.1060199737549</v>
       </c>
       <c r="H11" t="n">
         <v>136177</v>
@@ -717,7 +717,7 @@
         <v>15.460000038147</v>
       </c>
       <c r="G12" t="n">
-        <v>14.2575750350952</v>
+        <v>14.2575759887695</v>
       </c>
       <c r="H12" t="n">
         <v>138274</v>
@@ -746,7 +746,7 @@
         <v>15.6700000762939</v>
       </c>
       <c r="G13" t="n">
-        <v>14.4512405395508</v>
+        <v>14.4512414932251</v>
       </c>
       <c r="H13" t="n">
         <v>81542</v>
@@ -804,7 +804,7 @@
         <v>15.0299997329712</v>
       </c>
       <c r="G15" t="n">
-        <v>13.8610191345215</v>
+        <v>13.8610200881958</v>
       </c>
       <c r="H15" t="n">
         <v>92946</v>
@@ -833,7 +833,7 @@
         <v>15.3299999237061</v>
       </c>
       <c r="G16" t="n">
-        <v>14.1376857757568</v>
+        <v>14.1376848220825</v>
       </c>
       <c r="H16" t="n">
         <v>88250</v>
@@ -891,7 +891,7 @@
         <v>15.8100004196167</v>
       </c>
       <c r="G18" t="n">
-        <v>14.5803556442261</v>
+        <v>14.5803537368774</v>
       </c>
       <c r="H18" t="n">
         <v>84219</v>
@@ -920,7 +920,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G19" t="n">
-        <v>14.2022409439087</v>
+        <v>14.202241897583</v>
       </c>
       <c r="H19" t="n">
         <v>37612</v>
@@ -978,7 +978,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G21" t="n">
-        <v>14.2391290664673</v>
+        <v>14.2391309738159</v>
       </c>
       <c r="H21" t="n">
         <v>85513</v>
@@ -1007,7 +1007,7 @@
         <v>15.4099998474121</v>
       </c>
       <c r="G22" t="n">
-        <v>14.211464881897</v>
+        <v>14.2114639282227</v>
       </c>
       <c r="H22" t="n">
         <v>53844</v>
@@ -1036,7 +1036,7 @@
         <v>15.460000038147</v>
       </c>
       <c r="G23" t="n">
-        <v>14.2575750350952</v>
+        <v>14.2575759887695</v>
       </c>
       <c r="H23" t="n">
         <v>45721</v>
@@ -1152,7 +1152,7 @@
         <v>14.3800001144409</v>
       </c>
       <c r="G27" t="n">
-        <v>13.2615737915039</v>
+        <v>13.2615747451782</v>
       </c>
       <c r="H27" t="n">
         <v>131505</v>
@@ -1181,7 +1181,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G28" t="n">
-        <v>12.5422391891479</v>
+        <v>12.5422401428223</v>
       </c>
       <c r="H28" t="n">
         <v>192594</v>
@@ -1210,7 +1210,7 @@
         <v>13.289999961853</v>
       </c>
       <c r="G29" t="n">
-        <v>12.2563505172729</v>
+        <v>12.2563495635986</v>
       </c>
       <c r="H29" t="n">
         <v>193785</v>
@@ -1239,7 +1239,7 @@
         <v>13.2799997329712</v>
       </c>
       <c r="G30" t="n">
-        <v>12.2471265792847</v>
+        <v>12.2471284866333</v>
       </c>
       <c r="H30" t="n">
         <v>169537</v>
@@ -1268,7 +1268,7 @@
         <v>13.7200002670288</v>
       </c>
       <c r="G31" t="n">
-        <v>12.6529064178467</v>
+        <v>12.652907371521</v>
       </c>
       <c r="H31" t="n">
         <v>92315</v>
@@ -1297,7 +1297,7 @@
         <v>14.5</v>
       </c>
       <c r="G32" t="n">
-        <v>13.3722400665283</v>
+        <v>13.3722410202026</v>
       </c>
       <c r="H32" t="n">
         <v>78017</v>
@@ -1326,7 +1326,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G33" t="n">
-        <v>13.0033512115479</v>
+        <v>13.0033521652222</v>
       </c>
       <c r="H33" t="n">
         <v>65263</v>
@@ -1355,7 +1355,7 @@
         <v>14.5200004577637</v>
       </c>
       <c r="G34" t="n">
-        <v>13.3906869888306</v>
+        <v>13.3906860351562</v>
       </c>
       <c r="H34" t="n">
         <v>88427</v>
@@ -1384,7 +1384,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G35" t="n">
-        <v>13.2339067459106</v>
+        <v>13.233907699585</v>
       </c>
       <c r="H35" t="n">
         <v>89305</v>
@@ -1442,7 +1442,7 @@
         <v>15.1199998855591</v>
       </c>
       <c r="G37" t="n">
-        <v>13.944019317627</v>
+        <v>13.9440183639526</v>
       </c>
       <c r="H37" t="n">
         <v>71838</v>
@@ -1471,7 +1471,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G38" t="n">
-        <v>13.7411298751831</v>
+        <v>13.7411279678345</v>
       </c>
       <c r="H38" t="n">
         <v>54002</v>
@@ -1500,7 +1500,7 @@
         <v>15.0200004577637</v>
       </c>
       <c r="G39" t="n">
-        <v>13.8517961502075</v>
+        <v>13.8517971038818</v>
       </c>
       <c r="H39" t="n">
         <v>101974</v>
@@ -1558,7 +1558,7 @@
         <v>14.7299995422363</v>
       </c>
       <c r="G41" t="n">
-        <v>13.5843505859375</v>
+        <v>13.5843524932861</v>
       </c>
       <c r="H41" t="n">
         <v>60662</v>
@@ -1587,7 +1587,7 @@
         <v>14.8100004196167</v>
       </c>
       <c r="G42" t="n">
-        <v>13.658130645752</v>
+        <v>13.6581315994263</v>
       </c>
       <c r="H42" t="n">
         <v>43184</v>
@@ -1616,7 +1616,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G43" t="n">
-        <v>13.9255752563477</v>
+        <v>13.925573348999</v>
       </c>
       <c r="H43" t="n">
         <v>32263</v>
@@ -1645,7 +1645,7 @@
         <v>15.2399997711182</v>
       </c>
       <c r="G44" t="n">
-        <v>14.0546855926514</v>
+        <v>14.0546865463257</v>
       </c>
       <c r="H44" t="n">
         <v>42717</v>
@@ -1674,7 +1674,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G45" t="n">
-        <v>14.2391290664673</v>
+        <v>14.2391309738159</v>
       </c>
       <c r="H45" t="n">
         <v>37387</v>
@@ -1703,7 +1703,7 @@
         <v>15.4700002670288</v>
       </c>
       <c r="G46" t="n">
-        <v>14.2667989730835</v>
+        <v>14.2667980194092</v>
       </c>
       <c r="H46" t="n">
         <v>56531</v>
@@ -1761,7 +1761,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G48" t="n">
-        <v>14.2022409439087</v>
+        <v>14.202241897583</v>
       </c>
       <c r="H48" t="n">
         <v>20507</v>
@@ -1790,7 +1790,7 @@
         <v>15.5</v>
       </c>
       <c r="G49" t="n">
-        <v>14.2944641113281</v>
+        <v>14.2944650650024</v>
       </c>
       <c r="H49" t="n">
         <v>33636</v>
@@ -1819,7 +1819,7 @@
         <v>15.4099998474121</v>
       </c>
       <c r="G50" t="n">
-        <v>14.211464881897</v>
+        <v>14.2114639282227</v>
       </c>
       <c r="H50" t="n">
         <v>44199</v>
@@ -1848,7 +1848,7 @@
         <v>16.5</v>
       </c>
       <c r="G51" t="n">
-        <v>15.216685295105</v>
+        <v>15.2166872024536</v>
       </c>
       <c r="H51" t="n">
         <v>169713</v>
@@ -1906,7 +1906,7 @@
         <v>16.3199996948242</v>
       </c>
       <c r="G53" t="n">
-        <v>15.0506858825684</v>
+        <v>15.050687789917</v>
       </c>
       <c r="H53" t="n">
         <v>20261</v>
@@ -1935,7 +1935,7 @@
         <v>16.1700000762939</v>
       </c>
       <c r="G54" t="n">
-        <v>14.912353515625</v>
+        <v>14.9123544692993</v>
       </c>
       <c r="H54" t="n">
         <v>25065</v>
@@ -1964,7 +1964,7 @@
         <v>15.6700000762939</v>
       </c>
       <c r="G55" t="n">
-        <v>14.4512405395508</v>
+        <v>14.4512414932251</v>
       </c>
       <c r="H55" t="n">
         <v>53719</v>
@@ -2022,7 +2022,7 @@
         <v>16.5699996948242</v>
       </c>
       <c r="G57" t="n">
-        <v>15.2812433242798</v>
+        <v>15.2812423706055</v>
       </c>
       <c r="H57" t="n">
         <v>62987</v>
@@ -2080,7 +2080,7 @@
         <v>16.7399997711182</v>
       </c>
       <c r="G59" t="n">
-        <v>15.4380216598511</v>
+        <v>15.4380197525024</v>
       </c>
       <c r="H59" t="n">
         <v>47008</v>
@@ -2109,7 +2109,7 @@
         <v>16.6399993896484</v>
       </c>
       <c r="G60" t="n">
-        <v>15.3457975387573</v>
+        <v>15.345799446106</v>
       </c>
       <c r="H60" t="n">
         <v>34625</v>
@@ -2167,7 +2167,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G62" t="n">
-        <v>15.4933519363403</v>
+        <v>15.4933547973633</v>
       </c>
       <c r="H62" t="n">
         <v>74447</v>
@@ -2196,7 +2196,7 @@
         <v>16.6399993896484</v>
       </c>
       <c r="G63" t="n">
-        <v>15.3457975387573</v>
+        <v>15.345799446106</v>
       </c>
       <c r="H63" t="n">
         <v>69018</v>
@@ -2225,7 +2225,7 @@
         <v>16.7099990844727</v>
       </c>
       <c r="G64" t="n">
-        <v>15.4103517532349</v>
+        <v>15.4103546142578</v>
       </c>
       <c r="H64" t="n">
         <v>39631</v>
@@ -2254,7 +2254,7 @@
         <v>16.5900001525879</v>
       </c>
       <c r="G65" t="n">
-        <v>15.2996873855591</v>
+        <v>15.2996883392334</v>
       </c>
       <c r="H65" t="n">
         <v>38532</v>
@@ -2283,7 +2283,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G66" t="n">
-        <v>14.89391040802</v>
+        <v>14.8939075469971</v>
       </c>
       <c r="H66" t="n">
         <v>17748</v>
@@ -2312,7 +2312,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G67" t="n">
-        <v>14.8016881942749</v>
+        <v>14.8016862869263</v>
       </c>
       <c r="H67" t="n">
         <v>16652</v>
@@ -2370,7 +2370,7 @@
         <v>16.2199993133545</v>
       </c>
       <c r="G69" t="n">
-        <v>14.9584655761719</v>
+        <v>14.9584636688232</v>
       </c>
       <c r="H69" t="n">
         <v>34539</v>
@@ -2399,7 +2399,7 @@
         <v>16.4099998474121</v>
       </c>
       <c r="G70" t="n">
-        <v>15.1336860656738</v>
+        <v>15.1336870193481</v>
       </c>
       <c r="H70" t="n">
         <v>16981</v>
@@ -2428,7 +2428,7 @@
         <v>16.6900005340576</v>
       </c>
       <c r="G71" t="n">
-        <v>15.3919115066528</v>
+        <v>15.3919095993042</v>
       </c>
       <c r="H71" t="n">
         <v>22512</v>
@@ -2457,7 +2457,7 @@
         <v>16.8299999237061</v>
       </c>
       <c r="G72" t="n">
-        <v>15.5210189819336</v>
+        <v>15.5210218429565</v>
       </c>
       <c r="H72" t="n">
         <v>49155</v>
@@ -2486,7 +2486,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G73" t="n">
-        <v>15.5394668579102</v>
+        <v>15.5394649505615</v>
       </c>
       <c r="H73" t="n">
         <v>32587</v>
@@ -2544,7 +2544,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G75" t="n">
-        <v>16.0928020477295</v>
+        <v>16.0928001403809</v>
       </c>
       <c r="H75" t="n">
         <v>93978</v>
@@ -2631,7 +2631,7 @@
         <v>17.5</v>
       </c>
       <c r="G78" t="n">
-        <v>16.1389122009277</v>
+        <v>16.1389102935791</v>
       </c>
       <c r="H78" t="n">
         <v>46268</v>
@@ -2660,7 +2660,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G79" t="n">
-        <v>16.046688079834</v>
+        <v>16.0466861724854</v>
       </c>
       <c r="H79" t="n">
         <v>71398</v>
@@ -2689,7 +2689,7 @@
         <v>17.5699996948242</v>
       </c>
       <c r="G80" t="n">
-        <v>16.2034664154053</v>
+        <v>16.2034645080566</v>
       </c>
       <c r="H80" t="n">
         <v>20430</v>
@@ -2718,7 +2718,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G81" t="n">
-        <v>16.0835800170898</v>
+        <v>16.0835762023926</v>
       </c>
       <c r="H81" t="n">
         <v>43461</v>
@@ -2747,7 +2747,7 @@
         <v>17.5200004577637</v>
       </c>
       <c r="G82" t="n">
-        <v>16.157356262207</v>
+        <v>16.1573581695557</v>
       </c>
       <c r="H82" t="n">
         <v>26608</v>
@@ -2776,7 +2776,7 @@
         <v>17.5200004577637</v>
       </c>
       <c r="G83" t="n">
-        <v>16.157356262207</v>
+        <v>16.1573581695557</v>
       </c>
       <c r="H83" t="n">
         <v>38824</v>
@@ -2805,7 +2805,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G84" t="n">
-        <v>15.8161325454712</v>
+        <v>15.8161315917969</v>
       </c>
       <c r="H84" t="n">
         <v>41283</v>
@@ -2834,7 +2834,7 @@
         <v>17.3600006103516</v>
       </c>
       <c r="G85" t="n">
-        <v>16.009801864624</v>
+        <v>16.0097999572754</v>
       </c>
       <c r="H85" t="n">
         <v>54654</v>
@@ -2863,7 +2863,7 @@
         <v>17.5300006866455</v>
       </c>
       <c r="G86" t="n">
-        <v>16.166576385498</v>
+        <v>16.1665802001953</v>
       </c>
       <c r="H86" t="n">
         <v>44977</v>
@@ -2892,7 +2892,7 @@
         <v>17.4899997711182</v>
       </c>
       <c r="G87" t="n">
-        <v>16.1296882629395</v>
+        <v>16.1296844482422</v>
       </c>
       <c r="H87" t="n">
         <v>30733</v>
@@ -2921,7 +2921,7 @@
         <v>17.5</v>
       </c>
       <c r="G88" t="n">
-        <v>16.1389122009277</v>
+        <v>16.1389102935791</v>
       </c>
       <c r="H88" t="n">
         <v>27579</v>
@@ -2979,7 +2979,7 @@
         <v>17.25</v>
       </c>
       <c r="G90" t="n">
-        <v>15.9083557128906</v>
+        <v>15.9083576202393</v>
       </c>
       <c r="H90" t="n">
         <v>27940</v>
@@ -3066,7 +3066,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G93" t="n">
-        <v>16.0651321411133</v>
+        <v>16.0651340484619</v>
       </c>
       <c r="H93" t="n">
         <v>122755</v>
@@ -3095,7 +3095,7 @@
         <v>17.5900001525879</v>
       </c>
       <c r="G94" t="n">
-        <v>16.2219104766846</v>
+        <v>16.2219123840332</v>
       </c>
       <c r="H94" t="n">
         <v>70873</v>
@@ -3124,7 +3124,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G95" t="n">
-        <v>16.0651321411133</v>
+        <v>16.0651340484619</v>
       </c>
       <c r="H95" t="n">
         <v>30279</v>
@@ -3153,7 +3153,7 @@
         <v>17.7800006866455</v>
       </c>
       <c r="G96" t="n">
-        <v>16.3971309661865</v>
+        <v>16.3971328735352</v>
       </c>
       <c r="H96" t="n">
         <v>84539</v>
@@ -3211,7 +3211,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G98" t="n">
-        <v>16.4155769348145</v>
+        <v>16.4155788421631</v>
       </c>
       <c r="H98" t="n">
         <v>44723</v>
@@ -3240,7 +3240,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G99" t="n">
-        <v>16.2311325073242</v>
+        <v>16.2311344146729</v>
       </c>
       <c r="H99" t="n">
         <v>37932</v>
@@ -3269,7 +3269,7 @@
         <v>17.5200004577637</v>
       </c>
       <c r="G100" t="n">
-        <v>16.277587890625</v>
+        <v>16.2775897979736</v>
       </c>
       <c r="H100" t="n">
         <v>32827</v>
@@ -3298,7 +3298,7 @@
         <v>17.6900005340576</v>
       </c>
       <c r="G101" t="n">
-        <v>16.4355316162109</v>
+        <v>16.4355354309082</v>
       </c>
       <c r="H101" t="n">
         <v>29377</v>
@@ -3356,7 +3356,7 @@
         <v>17.6599998474121</v>
       </c>
       <c r="G103" t="n">
-        <v>16.4076595306396</v>
+        <v>16.407657623291</v>
       </c>
       <c r="H103" t="n">
         <v>26666</v>
@@ -3385,7 +3385,7 @@
         <v>17.6900005340576</v>
       </c>
       <c r="G104" t="n">
-        <v>16.4355316162109</v>
+        <v>16.4355354309082</v>
       </c>
       <c r="H104" t="n">
         <v>34454</v>
@@ -3414,7 +3414,7 @@
         <v>17.6399993896484</v>
       </c>
       <c r="G105" t="n">
-        <v>16.3890781402588</v>
+        <v>16.3890800476074</v>
       </c>
       <c r="H105" t="n">
         <v>27324</v>
@@ -3443,7 +3443,7 @@
         <v>17.7299995422363</v>
       </c>
       <c r="G106" t="n">
-        <v>16.4726963043213</v>
+        <v>16.4726943969727</v>
       </c>
       <c r="H106" t="n">
         <v>80417</v>
@@ -3472,7 +3472,7 @@
         <v>17.75</v>
       </c>
       <c r="G107" t="n">
-        <v>16.4912796020508</v>
+        <v>16.4912776947021</v>
       </c>
       <c r="H107" t="n">
         <v>36469</v>
@@ -3646,7 +3646,7 @@
         <v>17.8700008392334</v>
       </c>
       <c r="G113" t="n">
-        <v>16.6027717590332</v>
+        <v>16.6027679443359</v>
       </c>
       <c r="H113" t="n">
         <v>50648</v>
@@ -3675,7 +3675,7 @@
         <v>17.2399997711182</v>
       </c>
       <c r="G114" t="n">
-        <v>16.0174427032471</v>
+        <v>16.0174446105957</v>
       </c>
       <c r="H114" t="n">
         <v>39248</v>
@@ -3733,7 +3733,7 @@
         <v>16.4400005340576</v>
       </c>
       <c r="G116" t="n">
-        <v>15.2741737365723</v>
+        <v>15.2741765975952</v>
       </c>
       <c r="H116" t="n">
         <v>59273</v>
@@ -3820,7 +3820,7 @@
         <v>17.6200008392334</v>
       </c>
       <c r="G119" t="n">
-        <v>16.3704986572266</v>
+        <v>16.3704967498779</v>
       </c>
       <c r="H119" t="n">
         <v>379982</v>
@@ -3878,7 +3878,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G121" t="n">
-        <v>16.2218437194824</v>
+        <v>16.2218399047852</v>
       </c>
       <c r="H121" t="n">
         <v>113681</v>
@@ -3907,7 +3907,7 @@
         <v>17.2700004577637</v>
       </c>
       <c r="G122" t="n">
-        <v>16.045316696167</v>
+        <v>16.0453186035156</v>
       </c>
       <c r="H122" t="n">
         <v>52719</v>
@@ -3936,7 +3936,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G123" t="n">
-        <v>16.3519172668457</v>
+        <v>16.3519153594971</v>
       </c>
       <c r="H123" t="n">
         <v>39776</v>
@@ -3965,7 +3965,7 @@
         <v>16.5</v>
       </c>
       <c r="G124" t="n">
-        <v>15.3299217224121</v>
+        <v>15.3299198150635</v>
       </c>
       <c r="H124" t="n">
         <v>149335</v>
@@ -3994,7 +3994,7 @@
         <v>15.8100004196167</v>
       </c>
       <c r="G125" t="n">
-        <v>14.688850402832</v>
+        <v>14.6888513565063</v>
       </c>
       <c r="H125" t="n">
         <v>78782</v>
@@ -4052,7 +4052,7 @@
         <v>16.2299995422363</v>
       </c>
       <c r="G127" t="n">
-        <v>15.0790672302246</v>
+        <v>15.0790662765503</v>
       </c>
       <c r="H127" t="n">
         <v>67626</v>
@@ -4081,7 +4081,7 @@
         <v>16.1599998474121</v>
       </c>
       <c r="G128" t="n">
-        <v>15.0140314102173</v>
+        <v>15.014030456543</v>
       </c>
       <c r="H128" t="n">
         <v>35273</v>
@@ -4110,7 +4110,7 @@
         <v>16.4799995422363</v>
       </c>
       <c r="G129" t="n">
-        <v>15.3113374710083</v>
+        <v>15.3113393783569</v>
       </c>
       <c r="H129" t="n">
         <v>51916</v>
@@ -4139,7 +4139,7 @@
         <v>16.1599998474121</v>
       </c>
       <c r="G130" t="n">
-        <v>15.0140314102173</v>
+        <v>15.014030456543</v>
       </c>
       <c r="H130" t="n">
         <v>27190</v>
@@ -4197,7 +4197,7 @@
         <v>15.210000038147</v>
       </c>
       <c r="G132" t="n">
-        <v>14.1313991546631</v>
+        <v>14.1314001083374</v>
       </c>
       <c r="H132" t="n">
         <v>98251</v>
@@ -4226,7 +4226,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G133" t="n">
-        <v>14.4565782546997</v>
+        <v>14.4565801620483</v>
       </c>
       <c r="H133" t="n">
         <v>58458</v>
@@ -4255,7 +4255,7 @@
         <v>15.8100004196167</v>
       </c>
       <c r="G134" t="n">
-        <v>14.688850402832</v>
+        <v>14.6888513565063</v>
       </c>
       <c r="H134" t="n">
         <v>17481</v>
@@ -4284,7 +4284,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G135" t="n">
-        <v>14.7260141372681</v>
+        <v>14.7260150909424</v>
       </c>
       <c r="H135" t="n">
         <v>16138</v>
@@ -4313,7 +4313,7 @@
         <v>16.5100002288818</v>
       </c>
       <c r="G136" t="n">
-        <v>15.3392105102539</v>
+        <v>15.3392114639282</v>
       </c>
       <c r="H136" t="n">
         <v>65544</v>
@@ -4342,7 +4342,7 @@
         <v>16.6299991607666</v>
       </c>
       <c r="G137" t="n">
-        <v>15.450701713562</v>
+        <v>15.4507007598877</v>
       </c>
       <c r="H137" t="n">
         <v>37720</v>
@@ -4371,7 +4371,7 @@
         <v>16.4899997711182</v>
       </c>
       <c r="G138" t="n">
-        <v>15.320629119873</v>
+        <v>15.3206300735474</v>
       </c>
       <c r="H138" t="n">
         <v>36885</v>
@@ -4429,7 +4429,7 @@
         <v>16.5</v>
       </c>
       <c r="G140" t="n">
-        <v>15.3299217224121</v>
+        <v>15.3299198150635</v>
       </c>
       <c r="H140" t="n">
         <v>28765</v>
@@ -4458,7 +4458,7 @@
         <v>16.5599994659424</v>
       </c>
       <c r="G141" t="n">
-        <v>15.3856658935547</v>
+        <v>15.3856649398804</v>
       </c>
       <c r="H141" t="n">
         <v>28734</v>
@@ -4574,7 +4574,7 @@
         <v>16.7800006866455</v>
       </c>
       <c r="G145" t="n">
-        <v>15.5900650024414</v>
+        <v>15.5900640487671</v>
       </c>
       <c r="H145" t="n">
         <v>25662</v>
@@ -4603,7 +4603,7 @@
         <v>16.5200004577637</v>
       </c>
       <c r="G146" t="n">
-        <v>15.348503112793</v>
+        <v>15.3485012054443</v>
       </c>
       <c r="H146" t="n">
         <v>38195</v>
@@ -4632,7 +4632,7 @@
         <v>16.9300003051758</v>
       </c>
       <c r="G147" t="n">
-        <v>15.7294273376465</v>
+        <v>15.7294263839722</v>
       </c>
       <c r="H147" t="n">
         <v>67259</v>
@@ -4719,7 +4719,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G150" t="n">
-        <v>15.4692821502686</v>
+        <v>15.4692831039429</v>
       </c>
       <c r="H150" t="n">
         <v>26455</v>
@@ -4748,7 +4748,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G151" t="n">
-        <v>15.1812677383423</v>
+        <v>15.1812648773193</v>
       </c>
       <c r="H151" t="n">
         <v>19807</v>
@@ -4777,7 +4777,7 @@
         <v>16.4699993133545</v>
       </c>
       <c r="G152" t="n">
-        <v>15.3020458221436</v>
+        <v>15.3020477294922</v>
       </c>
       <c r="H152" t="n">
         <v>23178</v>
@@ -4806,7 +4806,7 @@
         <v>16.4899997711182</v>
       </c>
       <c r="G153" t="n">
-        <v>15.320629119873</v>
+        <v>15.3206300735474</v>
       </c>
       <c r="H153" t="n">
         <v>11206</v>
@@ -4835,7 +4835,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G154" t="n">
-        <v>15.4414091110229</v>
+        <v>15.4414110183716</v>
       </c>
       <c r="H154" t="n">
         <v>25623</v>
@@ -4864,7 +4864,7 @@
         <v>16.9099998474121</v>
       </c>
       <c r="G155" t="n">
-        <v>15.7108478546143</v>
+        <v>15.7108469009399</v>
       </c>
       <c r="H155" t="n">
         <v>26232</v>
@@ -4893,7 +4893,7 @@
         <v>17.0300006866455</v>
       </c>
       <c r="G156" t="n">
-        <v>15.8223352432251</v>
+        <v>15.822338104248</v>
       </c>
       <c r="H156" t="n">
         <v>25098</v>
@@ -4922,7 +4922,7 @@
         <v>17.2900009155273</v>
       </c>
       <c r="G157" t="n">
-        <v>16.0638999938965</v>
+        <v>16.0638980865479</v>
       </c>
       <c r="H157" t="n">
         <v>66106</v>
@@ -4951,7 +4951,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G158" t="n">
-        <v>16.1103515625</v>
+        <v>16.1103534698486</v>
       </c>
       <c r="H158" t="n">
         <v>12768</v>
@@ -5009,7 +5009,7 @@
         <v>17.1700000762939</v>
       </c>
       <c r="G160" t="n">
-        <v>15.9524078369141</v>
+        <v>15.9524059295654</v>
       </c>
       <c r="H160" t="n">
         <v>20957</v>
@@ -5096,7 +5096,7 @@
         <v>17.4899997711182</v>
       </c>
       <c r="G163" t="n">
-        <v>16.2497138977051</v>
+        <v>16.2497119903564</v>
       </c>
       <c r="H163" t="n">
         <v>20591</v>
@@ -5154,7 +5154,7 @@
         <v>17.5200004577637</v>
       </c>
       <c r="G165" t="n">
-        <v>16.277587890625</v>
+        <v>16.2775897979736</v>
       </c>
       <c r="H165" t="n">
         <v>47902</v>
@@ -5183,7 +5183,7 @@
         <v>17.6700000762939</v>
       </c>
       <c r="G166" t="n">
-        <v>16.4169502258301</v>
+        <v>16.4169521331787</v>
       </c>
       <c r="H166" t="n">
         <v>28140</v>
@@ -5212,7 +5212,7 @@
         <v>17.75</v>
       </c>
       <c r="G167" t="n">
-        <v>16.4912796020508</v>
+        <v>16.4912776947021</v>
       </c>
       <c r="H167" t="n">
         <v>29338</v>
@@ -5241,7 +5241,7 @@
         <v>17.75</v>
       </c>
       <c r="G168" t="n">
-        <v>16.4912796020508</v>
+        <v>16.4912776947021</v>
       </c>
       <c r="H168" t="n">
         <v>102230</v>
@@ -5270,7 +5270,7 @@
         <v>17.5</v>
       </c>
       <c r="G169" t="n">
-        <v>16.2590084075928</v>
+        <v>16.2590065002441</v>
       </c>
       <c r="H169" t="n">
         <v>29226</v>
@@ -5444,7 +5444,7 @@
         <v>18</v>
       </c>
       <c r="G175" t="n">
-        <v>16.7235507965088</v>
+        <v>16.7235469818115</v>
       </c>
       <c r="H175" t="n">
         <v>54483</v>
@@ -5473,7 +5473,7 @@
         <v>17.8899993896484</v>
       </c>
       <c r="G176" t="n">
-        <v>16.6213531494141</v>
+        <v>16.6213493347168</v>
       </c>
       <c r="H176" t="n">
         <v>40727</v>
@@ -5502,7 +5502,7 @@
         <v>18</v>
       </c>
       <c r="G177" t="n">
-        <v>16.7235507965088</v>
+        <v>16.7235469818115</v>
       </c>
       <c r="H177" t="n">
         <v>33704</v>
@@ -5589,7 +5589,7 @@
         <v>18</v>
       </c>
       <c r="G180" t="n">
-        <v>16.7235507965088</v>
+        <v>16.7235469818115</v>
       </c>
       <c r="H180" t="n">
         <v>20891</v>
@@ -5618,7 +5618,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G181" t="n">
-        <v>16.6306419372559</v>
+        <v>16.6306381225586</v>
       </c>
       <c r="H181" t="n">
         <v>80243</v>
@@ -5647,7 +5647,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G182" t="n">
-        <v>16.6306419372559</v>
+        <v>16.6306381225586</v>
       </c>
       <c r="H182" t="n">
         <v>25269</v>
@@ -5676,7 +5676,7 @@
         <v>18</v>
       </c>
       <c r="G183" t="n">
-        <v>16.7235507965088</v>
+        <v>16.7235469818115</v>
       </c>
       <c r="H183" t="n">
         <v>30487</v>
@@ -5705,7 +5705,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G184" t="n">
-        <v>16.6770973205566</v>
+        <v>16.6770935058594</v>
       </c>
       <c r="H184" t="n">
         <v>42388</v>
@@ -5734,7 +5734,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G185" t="n">
-        <v>16.4819889068604</v>
+        <v>16.4819869995117</v>
       </c>
       <c r="H185" t="n">
         <v>62870</v>
@@ -5792,7 +5792,7 @@
         <v>17.8199996948242</v>
       </c>
       <c r="G187" t="n">
-        <v>16.5563144683838</v>
+        <v>16.5563125610352</v>
       </c>
       <c r="H187" t="n">
         <v>46775</v>
@@ -5821,7 +5821,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G188" t="n">
-        <v>16.6306419372559</v>
+        <v>16.6306381225586</v>
       </c>
       <c r="H188" t="n">
         <v>21870</v>
@@ -5850,7 +5850,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G189" t="n">
-        <v>16.5934772491455</v>
+        <v>16.5934791564941</v>
       </c>
       <c r="H189" t="n">
         <v>60441</v>
@@ -5995,7 +5995,7 @@
         <v>17.6900005340576</v>
       </c>
       <c r="G194" t="n">
-        <v>16.4355316162109</v>
+        <v>16.4355354309082</v>
       </c>
       <c r="H194" t="n">
         <v>23183</v>
@@ -6024,7 +6024,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G195" t="n">
-        <v>16.6306419372559</v>
+        <v>16.6306381225586</v>
       </c>
       <c r="H195" t="n">
         <v>47535</v>
@@ -6053,7 +6053,7 @@
         <v>18</v>
       </c>
       <c r="G196" t="n">
-        <v>16.7235507965088</v>
+        <v>16.7235469818115</v>
       </c>
       <c r="H196" t="n">
         <v>57924</v>
@@ -6082,7 +6082,7 @@
         <v>17.9400005340576</v>
       </c>
       <c r="G197" t="n">
-        <v>16.6678066253662</v>
+        <v>16.6678047180176</v>
       </c>
       <c r="H197" t="n">
         <v>30979</v>
@@ -6111,7 +6111,7 @@
         <v>18</v>
       </c>
       <c r="G198" t="n">
-        <v>16.7235507965088</v>
+        <v>16.7235469818115</v>
       </c>
       <c r="H198" t="n">
         <v>36332</v>
@@ -6198,7 +6198,7 @@
         <v>17.9400005340576</v>
       </c>
       <c r="G201" t="n">
-        <v>16.6678066253662</v>
+        <v>16.6678047180176</v>
       </c>
       <c r="H201" t="n">
         <v>52466</v>
@@ -6314,7 +6314,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G205" t="n">
-        <v>16.5934772491455</v>
+        <v>16.5934791564941</v>
       </c>
       <c r="H205" t="n">
         <v>25476</v>
@@ -6343,7 +6343,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G206" t="n">
-        <v>16.6306419372559</v>
+        <v>16.6306381225586</v>
       </c>
       <c r="H206" t="n">
         <v>24927</v>
@@ -6372,7 +6372,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G207" t="n">
-        <v>16.6306419372559</v>
+        <v>16.6306381225586</v>
       </c>
       <c r="H207" t="n">
         <v>42875</v>
@@ -6488,7 +6488,7 @@
         <v>18</v>
       </c>
       <c r="G211" t="n">
-        <v>16.7235507965088</v>
+        <v>16.7235469818115</v>
       </c>
       <c r="H211" t="n">
         <v>39388</v>
@@ -6517,7 +6517,7 @@
         <v>18.0699996948242</v>
       </c>
       <c r="G212" t="n">
-        <v>16.7885837554932</v>
+        <v>16.7885856628418</v>
       </c>
       <c r="H212" t="n">
         <v>160547</v>
@@ -6604,7 +6604,7 @@
         <v>18</v>
       </c>
       <c r="G215" t="n">
-        <v>16.7235507965088</v>
+        <v>16.7235469818115</v>
       </c>
       <c r="H215" t="n">
         <v>19589</v>
@@ -6633,7 +6633,7 @@
         <v>18.0599994659424</v>
       </c>
       <c r="G216" t="n">
-        <v>16.7792911529541</v>
+        <v>16.7792930603027</v>
       </c>
       <c r="H216" t="n">
         <v>55172</v>
@@ -6662,7 +6662,7 @@
         <v>18</v>
       </c>
       <c r="G217" t="n">
-        <v>16.7235507965088</v>
+        <v>16.7235469818115</v>
       </c>
       <c r="H217" t="n">
         <v>35574</v>
@@ -6691,7 +6691,7 @@
         <v>18</v>
       </c>
       <c r="G218" t="n">
-        <v>16.7235507965088</v>
+        <v>16.7235469818115</v>
       </c>
       <c r="H218" t="n">
         <v>43897</v>
@@ -6807,7 +6807,7 @@
         <v>18.1200008392334</v>
       </c>
       <c r="G222" t="n">
-        <v>16.8350410461426</v>
+        <v>16.8350391387939</v>
       </c>
       <c r="H222" t="n">
         <v>29793</v>
@@ -6836,7 +6836,7 @@
         <v>17.9300003051758</v>
       </c>
       <c r="G223" t="n">
-        <v>16.6585121154785</v>
+        <v>16.6585159301758</v>
       </c>
       <c r="H223" t="n">
         <v>26120</v>
@@ -6865,7 +6865,7 @@
         <v>18</v>
       </c>
       <c r="G224" t="n">
-        <v>16.7235507965088</v>
+        <v>16.7235469818115</v>
       </c>
       <c r="H224" t="n">
         <v>27459</v>
@@ -6894,7 +6894,7 @@
         <v>18</v>
       </c>
       <c r="G225" t="n">
-        <v>16.7235507965088</v>
+        <v>16.7235469818115</v>
       </c>
       <c r="H225" t="n">
         <v>25997</v>
@@ -6981,7 +6981,7 @@
         <v>18.0699996948242</v>
       </c>
       <c r="G228" t="n">
-        <v>16.7885837554932</v>
+        <v>16.7885856628418</v>
       </c>
       <c r="H228" t="n">
         <v>31227</v>
@@ -7010,7 +7010,7 @@
         <v>17.9400005340576</v>
       </c>
       <c r="G229" t="n">
-        <v>16.6678066253662</v>
+        <v>16.6678047180176</v>
       </c>
       <c r="H229" t="n">
         <v>16208</v>
@@ -7039,7 +7039,7 @@
         <v>17.9200000762939</v>
       </c>
       <c r="G230" t="n">
-        <v>16.6492233276367</v>
+        <v>16.6492214202881</v>
       </c>
       <c r="H230" t="n">
         <v>24873</v>
@@ -7068,7 +7068,7 @@
         <v>18</v>
       </c>
       <c r="G231" t="n">
-        <v>16.7235507965088</v>
+        <v>16.7235469818115</v>
       </c>
       <c r="H231" t="n">
         <v>41856</v>
@@ -7184,7 +7184,7 @@
         <v>18</v>
       </c>
       <c r="G235" t="n">
-        <v>16.7235507965088</v>
+        <v>16.7235469818115</v>
       </c>
       <c r="H235" t="n">
         <v>42310</v>
@@ -7213,7 +7213,7 @@
         <v>17.9500007629395</v>
       </c>
       <c r="G236" t="n">
-        <v>16.6770973205566</v>
+        <v>16.6770935058594</v>
       </c>
       <c r="H236" t="n">
         <v>29279</v>
@@ -7300,7 +7300,7 @@
         <v>18.1399993896484</v>
       </c>
       <c r="G239" t="n">
-        <v>16.8536186218262</v>
+        <v>16.8536205291748</v>
       </c>
       <c r="H239" t="n">
         <v>35465</v>
@@ -7329,7 +7329,7 @@
         <v>18.3099994659424</v>
       </c>
       <c r="G240" t="n">
-        <v>17.0115642547607</v>
+        <v>17.0115661621094</v>
       </c>
       <c r="H240" t="n">
         <v>92777</v>
@@ -7358,7 +7358,7 @@
         <v>18.1700000762939</v>
       </c>
       <c r="G241" t="n">
-        <v>16.8814945220947</v>
+        <v>16.8814926147461</v>
       </c>
       <c r="H241" t="n">
         <v>56239</v>
@@ -7387,7 +7387,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G242" t="n">
-        <v>16.909366607666</v>
+        <v>16.9093685150146</v>
       </c>
       <c r="H242" t="n">
         <v>23708</v>
@@ -7416,7 +7416,7 @@
         <v>18.3400001525879</v>
       </c>
       <c r="G243" t="n">
-        <v>17.0394401550293</v>
+        <v>17.039436340332</v>
       </c>
       <c r="H243" t="n">
         <v>32531</v>
@@ -7445,7 +7445,7 @@
         <v>18.2900009155273</v>
       </c>
       <c r="G244" t="n">
-        <v>16.9929847717285</v>
+        <v>16.9929866790771</v>
       </c>
       <c r="H244" t="n">
         <v>30928</v>
@@ -7561,7 +7561,7 @@
         <v>18.3799991607666</v>
       </c>
       <c r="G248" t="n">
-        <v>17.0765991210938</v>
+        <v>17.0766010284424</v>
       </c>
       <c r="H248" t="n">
         <v>49529</v>
@@ -7619,7 +7619,7 @@
         <v>18.9899997711182</v>
       </c>
       <c r="G250" t="n">
-        <v>17.643346786499</v>
+        <v>17.6433448791504</v>
       </c>
       <c r="H250" t="n">
         <v>157007</v>
@@ -7648,7 +7648,7 @@
         <v>19.9099998474121</v>
       </c>
       <c r="G251" t="n">
-        <v>18.4981021881104</v>
+        <v>18.498104095459</v>
       </c>
       <c r="H251" t="n">
         <v>255608</v>
@@ -7764,7 +7764,7 @@
         <v>19.9799995422363</v>
       </c>
       <c r="G255" t="n">
-        <v>18.563138961792</v>
+        <v>18.5631370544434</v>
       </c>
       <c r="H255" t="n">
         <v>86713</v>
@@ -7822,7 +7822,7 @@
         <v>20.3400001525879</v>
       </c>
       <c r="G257" t="n">
-        <v>18.897611618042</v>
+        <v>18.8976135253906</v>
       </c>
       <c r="H257" t="n">
         <v>65935</v>
@@ -7851,7 +7851,7 @@
         <v>20.5499992370605</v>
       </c>
       <c r="G258" t="n">
-        <v>19.0927181243896</v>
+        <v>19.092716217041</v>
       </c>
       <c r="H258" t="n">
         <v>79582</v>
@@ -7880,7 +7880,7 @@
         <v>20.5900001525879</v>
       </c>
       <c r="G259" t="n">
-        <v>19.1298847198486</v>
+        <v>19.1298789978027</v>
       </c>
       <c r="H259" t="n">
         <v>97936</v>
@@ -7938,7 +7938,7 @@
         <v>20.4200000762939</v>
       </c>
       <c r="G261" t="n">
-        <v>18.9719371795654</v>
+        <v>18.9719390869141</v>
       </c>
       <c r="H261" t="n">
         <v>71018</v>
@@ -7967,7 +7967,7 @@
         <v>20.7800006866455</v>
       </c>
       <c r="G262" t="n">
-        <v>19.3064079284668</v>
+        <v>19.3064098358154</v>
       </c>
       <c r="H262" t="n">
         <v>104291</v>
@@ -7996,7 +7996,7 @@
         <v>20.6299991607666</v>
       </c>
       <c r="G263" t="n">
-        <v>19.1670436859131</v>
+        <v>19.1670455932617</v>
       </c>
       <c r="H263" t="n">
         <v>116970</v>
@@ -8025,7 +8025,7 @@
         <v>21.5400009155273</v>
       </c>
       <c r="G264" t="n">
-        <v>20.0125141143799</v>
+        <v>20.0125179290771</v>
       </c>
       <c r="H264" t="n">
         <v>286077</v>
@@ -8054,7 +8054,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G265" t="n">
-        <v>20.1611671447754</v>
+        <v>20.1611728668213</v>
       </c>
       <c r="H265" t="n">
         <v>138588</v>
@@ -8083,7 +8083,7 @@
         <v>21.5</v>
       </c>
       <c r="G266" t="n">
-        <v>19.9753494262695</v>
+        <v>19.9753513336182</v>
       </c>
       <c r="H266" t="n">
         <v>68980</v>
@@ -8112,7 +8112,7 @@
         <v>21.5200004577637</v>
       </c>
       <c r="G267" t="n">
-        <v>19.993932723999</v>
+        <v>19.9939308166504</v>
       </c>
       <c r="H267" t="n">
         <v>63796</v>
@@ -8141,7 +8141,7 @@
         <v>21.7800006866455</v>
       </c>
       <c r="G268" t="n">
-        <v>20.2354984283447</v>
+        <v>20.2354965209961</v>
       </c>
       <c r="H268" t="n">
         <v>69766</v>
@@ -8170,7 +8170,7 @@
         <v>21.6299991607666</v>
       </c>
       <c r="G269" t="n">
-        <v>20.0961303710938</v>
+        <v>20.0961322784424</v>
       </c>
       <c r="H269" t="n">
         <v>70450</v>
@@ -8199,7 +8199,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G270" t="n">
-        <v>20.1611671447754</v>
+        <v>20.1611728668213</v>
       </c>
       <c r="H270" t="n">
         <v>47153</v>
@@ -8228,7 +8228,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G271" t="n">
-        <v>20.6257133483887</v>
+        <v>20.6257095336914</v>
       </c>
       <c r="H271" t="n">
         <v>112838</v>
@@ -8257,7 +8257,7 @@
         <v>21.9599990844727</v>
       </c>
       <c r="G272" t="n">
-        <v>20.4027328491211</v>
+        <v>20.4027271270752</v>
       </c>
       <c r="H272" t="n">
         <v>2386278</v>
@@ -8286,7 +8286,7 @@
         <v>21.9899997711182</v>
       </c>
       <c r="G273" t="n">
-        <v>20.4306030273438</v>
+        <v>20.4306049346924</v>
       </c>
       <c r="H273" t="n">
         <v>140248</v>
@@ -8460,7 +8460,7 @@
         <v>20.9200000762939</v>
       </c>
       <c r="G279" t="n">
-        <v>19.4364814758301</v>
+        <v>19.4364795684814</v>
       </c>
       <c r="H279" t="n">
         <v>50548</v>
@@ -8518,7 +8518,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G281" t="n">
-        <v>19.46435546875</v>
+        <v>19.4643535614014</v>
       </c>
       <c r="H281" t="n">
         <v>36070</v>
@@ -8605,7 +8605,7 @@
         <v>20.6800003051758</v>
       </c>
       <c r="G284" t="n">
-        <v>19.2134990692139</v>
+        <v>19.2135009765625</v>
       </c>
       <c r="H284" t="n">
         <v>44756</v>
@@ -8634,7 +8634,7 @@
         <v>20.6800003051758</v>
       </c>
       <c r="G285" t="n">
-        <v>19.2134990692139</v>
+        <v>19.2135009765625</v>
       </c>
       <c r="H285" t="n">
         <v>46336</v>
@@ -8692,7 +8692,7 @@
         <v>20.6599998474121</v>
       </c>
       <c r="G287" t="n">
-        <v>19.1949195861816</v>
+        <v>19.1949214935303</v>
       </c>
       <c r="H287" t="n">
         <v>19454</v>
@@ -8750,7 +8750,7 @@
         <v>20.5599994659424</v>
       </c>
       <c r="G289" t="n">
-        <v>19.1020088195801</v>
+        <v>19.1020107269287</v>
       </c>
       <c r="H289" t="n">
         <v>26530</v>
@@ -8779,7 +8779,7 @@
         <v>20.6100006103516</v>
       </c>
       <c r="G290" t="n">
-        <v>19.1484661102295</v>
+        <v>19.1484680175781</v>
       </c>
       <c r="H290" t="n">
         <v>29870</v>
@@ -8866,7 +8866,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G293" t="n">
-        <v>18.860445022583</v>
+        <v>18.8604469299316</v>
       </c>
       <c r="H293" t="n">
         <v>42087</v>
@@ -8953,7 +8953,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G296" t="n">
-        <v>18.6281757354736</v>
+        <v>18.6281776428223</v>
       </c>
       <c r="H296" t="n">
         <v>39061</v>
@@ -8982,7 +8982,7 @@
         <v>19.6499996185303</v>
       </c>
       <c r="G297" t="n">
-        <v>18.2565422058105</v>
+        <v>18.2565402984619</v>
       </c>
       <c r="H297" t="n">
         <v>46826</v>
@@ -9011,7 +9011,7 @@
         <v>19.5</v>
       </c>
       <c r="G298" t="n">
-        <v>18.1171779632568</v>
+        <v>18.1171760559082</v>
       </c>
       <c r="H298" t="n">
         <v>45781</v>
@@ -9040,7 +9040,7 @@
         <v>19.4300003051758</v>
       </c>
       <c r="G299" t="n">
-        <v>18.0521411895752</v>
+        <v>18.0521430969238</v>
       </c>
       <c r="H299" t="n">
         <v>78415</v>
@@ -9098,7 +9098,7 @@
         <v>20.4599990844727</v>
       </c>
       <c r="G301" t="n">
-        <v>19.0090980529785</v>
+        <v>19.0090999603271</v>
       </c>
       <c r="H301" t="n">
         <v>81372</v>
@@ -9127,7 +9127,7 @@
         <v>20.7299995422363</v>
       </c>
       <c r="G302" t="n">
-        <v>19.2599563598633</v>
+        <v>19.2599544525146</v>
       </c>
       <c r="H302" t="n">
         <v>66140</v>
@@ -9156,7 +9156,7 @@
         <v>20.4400005340576</v>
       </c>
       <c r="G303" t="n">
-        <v>18.9905223846436</v>
+        <v>18.9905204772949</v>
       </c>
       <c r="H303" t="n">
         <v>45086</v>
@@ -9185,7 +9185,7 @@
         <v>20.5900001525879</v>
       </c>
       <c r="G304" t="n">
-        <v>19.1298847198486</v>
+        <v>19.1298789978027</v>
       </c>
       <c r="H304" t="n">
         <v>77137</v>
@@ -9214,7 +9214,7 @@
         <v>20.6299991607666</v>
       </c>
       <c r="G305" t="n">
-        <v>19.1670436859131</v>
+        <v>19.1670455932617</v>
       </c>
       <c r="H305" t="n">
         <v>45808</v>
@@ -9272,7 +9272,7 @@
         <v>20.9899997711182</v>
       </c>
       <c r="G307" t="n">
-        <v>19.5015182495117</v>
+        <v>19.5015144348145</v>
       </c>
       <c r="H307" t="n">
         <v>253364</v>
@@ -9301,7 +9301,7 @@
         <v>21.0300006866455</v>
       </c>
       <c r="G308" t="n">
-        <v>19.5386829376221</v>
+        <v>19.5386810302734</v>
       </c>
       <c r="H308" t="n">
         <v>86620</v>
@@ -9475,7 +9475,7 @@
         <v>22.0900001525879</v>
       </c>
       <c r="G314" t="n">
-        <v>20.523509979248</v>
+        <v>20.5235118865967</v>
       </c>
       <c r="H314" t="n">
         <v>76185</v>
@@ -9504,7 +9504,7 @@
         <v>22.2299995422363</v>
       </c>
       <c r="G315" t="n">
-        <v>20.6535835266113</v>
+        <v>20.6535816192627</v>
       </c>
       <c r="H315" t="n">
         <v>64387</v>
@@ -9562,7 +9562,7 @@
         <v>22.6299991607666</v>
       </c>
       <c r="G317" t="n">
-        <v>21.0252170562744</v>
+        <v>21.0252151489258</v>
       </c>
       <c r="H317" t="n">
         <v>78624</v>
@@ -9620,7 +9620,7 @@
         <v>22.3299999237061</v>
       </c>
       <c r="G319" t="n">
-        <v>20.7464904785156</v>
+        <v>20.7464923858643</v>
       </c>
       <c r="H319" t="n">
         <v>77818</v>
@@ -9678,7 +9678,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G321" t="n">
-        <v>20.6257133483887</v>
+        <v>20.6257095336914</v>
       </c>
       <c r="H321" t="n">
         <v>68839</v>
@@ -9736,7 +9736,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G323" t="n">
-        <v>20.7186183929443</v>
+        <v>20.7186164855957</v>
       </c>
       <c r="H323" t="n">
         <v>58724</v>
@@ -9794,7 +9794,7 @@
         <v>22.6100006103516</v>
       </c>
       <c r="G325" t="n">
-        <v>21.0066375732422</v>
+        <v>21.0066356658936</v>
       </c>
       <c r="H325" t="n">
         <v>36814</v>
@@ -9823,7 +9823,7 @@
         <v>22.4300003051758</v>
       </c>
       <c r="G326" t="n">
-        <v>20.8393974304199</v>
+        <v>20.8394031524658</v>
       </c>
       <c r="H326" t="n">
         <v>69319</v>
@@ -9852,7 +9852,7 @@
         <v>22.75</v>
       </c>
       <c r="G327" t="n">
-        <v>21.1367092132568</v>
+        <v>21.1367111206055</v>
       </c>
       <c r="H327" t="n">
         <v>61182</v>
@@ -9968,7 +9968,7 @@
         <v>22.6299991607666</v>
       </c>
       <c r="G331" t="n">
-        <v>21.0252170562744</v>
+        <v>21.0252151489258</v>
       </c>
       <c r="H331" t="n">
         <v>36174</v>
@@ -10026,7 +10026,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G333" t="n">
-        <v>21.5547981262207</v>
+        <v>21.5548000335693</v>
       </c>
       <c r="H333" t="n">
         <v>73679</v>
@@ -10084,7 +10084,7 @@
         <v>23.1700000762939</v>
       </c>
       <c r="G335" t="n">
-        <v>21.5269260406494</v>
+        <v>21.5269241333008</v>
       </c>
       <c r="H335" t="n">
         <v>83152</v>
@@ -10113,7 +10113,7 @@
         <v>23.4200000762939</v>
       </c>
       <c r="G336" t="n">
-        <v>21.7591972351074</v>
+        <v>21.7591953277588</v>
       </c>
       <c r="H336" t="n">
         <v>36169</v>
@@ -10171,7 +10171,7 @@
         <v>24.1000003814697</v>
       </c>
       <c r="G338" t="n">
-        <v>22.3909778594971</v>
+        <v>22.3909740447998</v>
       </c>
       <c r="H338" t="n">
         <v>75292</v>
@@ -10200,7 +10200,7 @@
         <v>24.1700000762939</v>
       </c>
       <c r="G339" t="n">
-        <v>22.4560127258301</v>
+        <v>22.4560108184814</v>
       </c>
       <c r="H339" t="n">
         <v>51555</v>
@@ -10287,7 +10287,7 @@
         <v>24.1499996185303</v>
       </c>
       <c r="G342" t="n">
-        <v>22.4374294281006</v>
+        <v>22.4374256134033</v>
       </c>
       <c r="H342" t="n">
         <v>31908</v>
@@ -10403,7 +10403,7 @@
         <v>24</v>
       </c>
       <c r="G346" t="n">
-        <v>22.2980709075928</v>
+        <v>22.2980670928955</v>
       </c>
       <c r="H346" t="n">
         <v>191573</v>
@@ -10490,7 +10490,7 @@
         <v>23</v>
       </c>
       <c r="G349" t="n">
-        <v>21.3689804077148</v>
+        <v>21.3689785003662</v>
       </c>
       <c r="H349" t="n">
         <v>521646</v>
@@ -10519,7 +10519,7 @@
         <v>23.2900009155273</v>
       </c>
       <c r="G350" t="n">
-        <v>21.6384143829346</v>
+        <v>21.6384162902832</v>
       </c>
       <c r="H350" t="n">
         <v>144892</v>
@@ -10548,7 +10548,7 @@
         <v>23.1499996185303</v>
       </c>
       <c r="G351" t="n">
-        <v>21.5083446502686</v>
+        <v>21.5083427429199</v>
       </c>
       <c r="H351" t="n">
         <v>68100</v>
@@ -10577,7 +10577,7 @@
         <v>22.6399993896484</v>
       </c>
       <c r="G352" t="n">
-        <v>21.0345077514648</v>
+        <v>21.0345096588135</v>
       </c>
       <c r="H352" t="n">
         <v>65861</v>
@@ -10606,7 +10606,7 @@
         <v>22.6399993896484</v>
       </c>
       <c r="G353" t="n">
-        <v>21.0345077514648</v>
+        <v>21.0345096588135</v>
       </c>
       <c r="H353" t="n">
         <v>79444</v>
@@ -10693,7 +10693,7 @@
         <v>23.3700008392334</v>
       </c>
       <c r="G356" t="n">
-        <v>21.8615856170654</v>
+        <v>21.8615894317627</v>
       </c>
       <c r="H356" t="n">
         <v>60772</v>
@@ -10722,7 +10722,7 @@
         <v>23.3799991607666</v>
       </c>
       <c r="G357" t="n">
-        <v>21.8709392547607</v>
+        <v>21.8709411621094</v>
       </c>
       <c r="H357" t="n">
         <v>34706</v>
@@ -10751,7 +10751,7 @@
         <v>23.5</v>
       </c>
       <c r="G358" t="n">
-        <v>21.9831943511963</v>
+        <v>21.9831962585449</v>
       </c>
       <c r="H358" t="n">
         <v>43801</v>
@@ -10780,7 +10780,7 @@
         <v>23.2700004577637</v>
       </c>
       <c r="G359" t="n">
-        <v>21.7680435180664</v>
+        <v>21.7680416107178</v>
       </c>
       <c r="H359" t="n">
         <v>21518</v>
@@ -10838,7 +10838,7 @@
         <v>23.3099994659424</v>
       </c>
       <c r="G361" t="n">
-        <v>21.8054580688477</v>
+        <v>21.8054599761963</v>
       </c>
       <c r="H361" t="n">
         <v>33925</v>
@@ -10896,7 +10896,7 @@
         <v>23.0400009155273</v>
       </c>
       <c r="G363" t="n">
-        <v>21.5528888702393</v>
+        <v>21.5528869628906</v>
       </c>
       <c r="H363" t="n">
         <v>28984</v>
@@ -10925,7 +10925,7 @@
         <v>22.8799991607666</v>
       </c>
       <c r="G364" t="n">
-        <v>21.4032154083252</v>
+        <v>21.4032135009766</v>
       </c>
       <c r="H364" t="n">
         <v>41800</v>
@@ -10954,7 +10954,7 @@
         <v>22.7700004577637</v>
       </c>
       <c r="G365" t="n">
-        <v>21.3003120422363</v>
+        <v>21.3003158569336</v>
       </c>
       <c r="H365" t="n">
         <v>59039</v>
@@ -11041,7 +11041,7 @@
         <v>22.75</v>
       </c>
       <c r="G368" t="n">
-        <v>21.2816047668457</v>
+        <v>21.2816066741943</v>
       </c>
       <c r="H368" t="n">
         <v>30162</v>
@@ -11070,7 +11070,7 @@
         <v>22.7099990844727</v>
       </c>
       <c r="G369" t="n">
-        <v>21.2441864013672</v>
+        <v>21.2441844940186</v>
       </c>
       <c r="H369" t="n">
         <v>38172</v>
@@ -11099,7 +11099,7 @@
         <v>22.2999992370605</v>
       </c>
       <c r="G370" t="n">
-        <v>20.8606491088867</v>
+        <v>20.8606472015381</v>
       </c>
       <c r="H370" t="n">
         <v>40837</v>
@@ -11157,7 +11157,7 @@
         <v>23.0699996948242</v>
       </c>
       <c r="G372" t="n">
-        <v>21.5809497833252</v>
+        <v>21.5809459686279</v>
       </c>
       <c r="H372" t="n">
         <v>53257</v>
@@ -11186,7 +11186,7 @@
         <v>22.6499996185303</v>
       </c>
       <c r="G373" t="n">
-        <v>21.188060760498</v>
+        <v>21.1880588531494</v>
       </c>
       <c r="H373" t="n">
         <v>53750</v>
@@ -11215,7 +11215,7 @@
         <v>22.8600006103516</v>
       </c>
       <c r="G374" t="n">
-        <v>21.3845043182373</v>
+        <v>21.3845062255859</v>
       </c>
       <c r="H374" t="n">
         <v>79363</v>
@@ -11302,7 +11302,7 @@
         <v>23.6399993896484</v>
       </c>
       <c r="G377" t="n">
-        <v>22.1141586303711</v>
+        <v>22.1141624450684</v>
       </c>
       <c r="H377" t="n">
         <v>54988</v>
@@ -11331,7 +11331,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G378" t="n">
-        <v>22.2638320922852</v>
+        <v>22.2638301849365</v>
       </c>
       <c r="H378" t="n">
         <v>43149</v>
@@ -11447,7 +11447,7 @@
         <v>23.8400001525879</v>
       </c>
       <c r="G382" t="n">
-        <v>22.3012523651123</v>
+        <v>22.3012504577637</v>
       </c>
       <c r="H382" t="n">
         <v>38614</v>
@@ -11505,7 +11505,7 @@
         <v>23.0200004577637</v>
       </c>
       <c r="G384" t="n">
-        <v>21.5341777801514</v>
+        <v>21.5341796875</v>
       </c>
       <c r="H384" t="n">
         <v>46271</v>
@@ -11534,7 +11534,7 @@
         <v>23.0499992370605</v>
       </c>
       <c r="G385" t="n">
-        <v>21.5622425079346</v>
+        <v>21.5622386932373</v>
       </c>
       <c r="H385" t="n">
         <v>36282</v>
@@ -11563,7 +11563,7 @@
         <v>22.8700008392334</v>
       </c>
       <c r="G386" t="n">
-        <v>21.3938598632812</v>
+        <v>21.3938617706299</v>
       </c>
       <c r="H386" t="n">
         <v>34823</v>
@@ -11592,7 +11592,7 @@
         <v>22.7900009155273</v>
       </c>
       <c r="G387" t="n">
-        <v>21.3190231323242</v>
+        <v>21.3190250396729</v>
       </c>
       <c r="H387" t="n">
         <v>28915</v>
@@ -11708,7 +11708,7 @@
         <v>22.7700004577637</v>
       </c>
       <c r="G391" t="n">
-        <v>21.3003120422363</v>
+        <v>21.3003158569336</v>
       </c>
       <c r="H391" t="n">
         <v>20414</v>
@@ -11766,7 +11766,7 @@
         <v>23.7099990844727</v>
       </c>
       <c r="G393" t="n">
-        <v>22.1796417236328</v>
+        <v>22.1796398162842</v>
       </c>
       <c r="H393" t="n">
         <v>65074</v>
@@ -11853,7 +11853,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G396" t="n">
-        <v>22.2638320922852</v>
+        <v>22.2638301849365</v>
       </c>
       <c r="H396" t="n">
         <v>24021</v>
@@ -11882,7 +11882,7 @@
         <v>23.9500007629395</v>
       </c>
       <c r="G397" t="n">
-        <v>22.4041538238525</v>
+        <v>22.4041500091553</v>
       </c>
       <c r="H397" t="n">
         <v>38506</v>
@@ -11940,7 +11940,7 @@
         <v>24.3099994659424</v>
       </c>
       <c r="G399" t="n">
-        <v>22.7409133911133</v>
+        <v>22.7409114837646</v>
       </c>
       <c r="H399" t="n">
         <v>72743</v>
@@ -11969,7 +11969,7 @@
         <v>24.4899997711182</v>
       </c>
       <c r="G400" t="n">
-        <v>22.909294128418</v>
+        <v>22.9092960357666</v>
       </c>
       <c r="H400" t="n">
         <v>34117</v>
@@ -11998,7 +11998,7 @@
         <v>24.5</v>
       </c>
       <c r="G401" t="n">
-        <v>22.9186515808105</v>
+        <v>22.9186496734619</v>
       </c>
       <c r="H401" t="n">
         <v>26633</v>
@@ -12027,7 +12027,7 @@
         <v>24.2700004577637</v>
       </c>
       <c r="G402" t="n">
-        <v>22.7034950256348</v>
+        <v>22.7034969329834</v>
       </c>
       <c r="H402" t="n">
         <v>18355</v>
@@ -12056,7 +12056,7 @@
         <v>24.4899997711182</v>
       </c>
       <c r="G403" t="n">
-        <v>22.909294128418</v>
+        <v>22.9092960357666</v>
       </c>
       <c r="H403" t="n">
         <v>19649</v>
@@ -12085,7 +12085,7 @@
         <v>24.4099998474121</v>
       </c>
       <c r="G404" t="n">
-        <v>22.8344612121582</v>
+        <v>22.8344573974609</v>
       </c>
       <c r="H404" t="n">
         <v>20447</v>
@@ -12114,7 +12114,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G405" t="n">
-        <v>23.1992893218994</v>
+        <v>23.1992874145508</v>
       </c>
       <c r="H405" t="n">
         <v>45969</v>
@@ -12143,7 +12143,7 @@
         <v>25</v>
       </c>
       <c r="G406" t="n">
-        <v>23.3863792419434</v>
+        <v>23.386381149292</v>
       </c>
       <c r="H406" t="n">
         <v>57285</v>
@@ -12201,7 +12201,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G408" t="n">
-        <v>23.1992893218994</v>
+        <v>23.1992874145508</v>
       </c>
       <c r="H408" t="n">
         <v>24905</v>
@@ -12230,7 +12230,7 @@
         <v>24.4200000762939</v>
       </c>
       <c r="G409" t="n">
-        <v>22.8438129425049</v>
+        <v>22.8438148498535</v>
       </c>
       <c r="H409" t="n">
         <v>29814</v>
@@ -12259,7 +12259,7 @@
         <v>24.7000007629395</v>
       </c>
       <c r="G410" t="n">
-        <v>23.1057434082031</v>
+        <v>23.1057415008545</v>
       </c>
       <c r="H410" t="n">
         <v>22726</v>
@@ -12404,7 +12404,7 @@
         <v>24.2199993133545</v>
       </c>
       <c r="G415" t="n">
-        <v>22.6567249298096</v>
+        <v>22.6567230224609</v>
       </c>
       <c r="H415" t="n">
         <v>17762</v>
@@ -12462,7 +12462,7 @@
         <v>24.0100002288818</v>
       </c>
       <c r="G417" t="n">
-        <v>22.460277557373</v>
+        <v>22.4602832794189</v>
       </c>
       <c r="H417" t="n">
         <v>23444</v>
@@ -12520,7 +12520,7 @@
         <v>24.25</v>
       </c>
       <c r="G419" t="n">
-        <v>22.6847858428955</v>
+        <v>22.6847877502441</v>
       </c>
       <c r="H419" t="n">
         <v>13310</v>
@@ -12665,7 +12665,7 @@
         <v>23.4099998474121</v>
       </c>
       <c r="G424" t="n">
-        <v>21.8990020751953</v>
+        <v>21.8990039825439</v>
       </c>
       <c r="H424" t="n">
         <v>59524</v>
@@ -12694,7 +12694,7 @@
         <v>23.3799991607666</v>
       </c>
       <c r="G425" t="n">
-        <v>21.8709392547607</v>
+        <v>21.8709411621094</v>
       </c>
       <c r="H425" t="n">
         <v>69647</v>
@@ -12723,7 +12723,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G426" t="n">
-        <v>23.1992893218994</v>
+        <v>23.1992874145508</v>
       </c>
       <c r="H426" t="n">
         <v>169660</v>
@@ -12752,7 +12752,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G427" t="n">
-        <v>23.5734691619873</v>
+        <v>23.5734672546387</v>
       </c>
       <c r="H427" t="n">
         <v>217121</v>
@@ -12868,7 +12868,7 @@
         <v>24.4599990844727</v>
       </c>
       <c r="G431" t="n">
-        <v>22.8812313079834</v>
+        <v>22.881233215332</v>
       </c>
       <c r="H431" t="n">
         <v>46903</v>
@@ -12897,7 +12897,7 @@
         <v>24.1700000762939</v>
       </c>
       <c r="G432" t="n">
-        <v>22.6099529266357</v>
+        <v>22.6099491119385</v>
       </c>
       <c r="H432" t="n">
         <v>60787</v>
@@ -12926,7 +12926,7 @@
         <v>25</v>
       </c>
       <c r="G433" t="n">
-        <v>23.3863792419434</v>
+        <v>23.386381149292</v>
       </c>
       <c r="H433" t="n">
         <v>47419</v>
@@ -12955,7 +12955,7 @@
         <v>25.3500003814697</v>
       </c>
       <c r="G434" t="n">
-        <v>23.7137870788574</v>
+        <v>23.7137889862061</v>
       </c>
       <c r="H434" t="n">
         <v>71667</v>
@@ -12984,7 +12984,7 @@
         <v>25.8500003814697</v>
       </c>
       <c r="G435" t="n">
-        <v>24.1815147399902</v>
+        <v>24.1815185546875</v>
       </c>
       <c r="H435" t="n">
         <v>68457</v>
@@ -13042,7 +13042,7 @@
         <v>26</v>
       </c>
       <c r="G437" t="n">
-        <v>24.3218326568604</v>
+        <v>24.321834564209</v>
       </c>
       <c r="H437" t="n">
         <v>88936</v>
@@ -13129,7 +13129,7 @@
         <v>26.0699996948242</v>
       </c>
       <c r="G440" t="n">
-        <v>24.3873157501221</v>
+        <v>24.3873138427734</v>
       </c>
       <c r="H440" t="n">
         <v>83089</v>
@@ -13187,7 +13187,7 @@
         <v>26.1800003051758</v>
       </c>
       <c r="G442" t="n">
-        <v>24.4902153015137</v>
+        <v>24.4902172088623</v>
       </c>
       <c r="H442" t="n">
         <v>58401</v>
@@ -13216,7 +13216,7 @@
         <v>26.1499996185303</v>
       </c>
       <c r="G443" t="n">
-        <v>24.4621543884277</v>
+        <v>24.4621505737305</v>
       </c>
       <c r="H443" t="n">
         <v>46836</v>
@@ -13274,7 +13274,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G445" t="n">
-        <v>24.2282886505127</v>
+        <v>24.2282867431641</v>
       </c>
       <c r="H445" t="n">
         <v>44995</v>
@@ -13303,7 +13303,7 @@
         <v>25.5</v>
       </c>
       <c r="G446" t="n">
-        <v>23.8541049957275</v>
+        <v>23.8541088104248</v>
       </c>
       <c r="H446" t="n">
         <v>65967</v>
@@ -13332,7 +13332,7 @@
         <v>26</v>
       </c>
       <c r="G447" t="n">
-        <v>24.3218326568604</v>
+        <v>24.321834564209</v>
       </c>
       <c r="H447" t="n">
         <v>66842</v>
@@ -13361,7 +13361,7 @@
         <v>26.2399997711182</v>
       </c>
       <c r="G448" t="n">
-        <v>24.5463428497314</v>
+        <v>24.5463447570801</v>
       </c>
       <c r="H448" t="n">
         <v>46091</v>
@@ -13477,7 +13477,7 @@
         <v>26.9599990844727</v>
       </c>
       <c r="G452" t="n">
-        <v>25.2198715209961</v>
+        <v>25.2198696136475</v>
       </c>
       <c r="H452" t="n">
         <v>97214</v>
@@ -13506,7 +13506,7 @@
         <v>26.6900005340576</v>
       </c>
       <c r="G453" t="n">
-        <v>24.9672985076904</v>
+        <v>24.9672966003418</v>
       </c>
       <c r="H453" t="n">
         <v>156148</v>
@@ -13535,7 +13535,7 @@
         <v>26.8099994659424</v>
       </c>
       <c r="G454" t="n">
-        <v>25.079553604126</v>
+        <v>25.0795516967773</v>
       </c>
       <c r="H454" t="n">
         <v>67873</v>
@@ -13593,7 +13593,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G456" t="n">
-        <v>25.1637439727783</v>
+        <v>25.1637401580811</v>
       </c>
       <c r="H456" t="n">
         <v>162996</v>
@@ -13825,7 +13825,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G464" t="n">
-        <v>25.1637439727783</v>
+        <v>25.1637401580811</v>
       </c>
       <c r="H464" t="n">
         <v>56873</v>
@@ -13883,7 +13883,7 @@
         <v>27.0799999237061</v>
       </c>
       <c r="G466" t="n">
-        <v>25.3321266174316</v>
+        <v>25.332124710083</v>
       </c>
       <c r="H466" t="n">
         <v>62508</v>
@@ -13912,7 +13912,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G467" t="n">
-        <v>25.6314697265625</v>
+        <v>25.6314716339111</v>
       </c>
       <c r="H467" t="n">
         <v>83642</v>
@@ -14028,7 +14028,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G471" t="n">
-        <v>26.5669231414795</v>
+        <v>26.5669250488281</v>
       </c>
       <c r="H471" t="n">
         <v>54780</v>
@@ -14086,7 +14086,7 @@
         <v>28.1499996185303</v>
       </c>
       <c r="G473" t="n">
-        <v>26.3330631256104</v>
+        <v>26.3330612182617</v>
       </c>
       <c r="H473" t="n">
         <v>76970</v>
@@ -14144,7 +14144,7 @@
         <v>28.6700000762939</v>
       </c>
       <c r="G475" t="n">
-        <v>26.8194980621338</v>
+        <v>26.8194999694824</v>
       </c>
       <c r="H475" t="n">
         <v>54523</v>
@@ -14231,7 +14231,7 @@
         <v>26.4300003051758</v>
       </c>
       <c r="G478" t="n">
-        <v>24.7240791320801</v>
+        <v>24.7240810394287</v>
       </c>
       <c r="H478" t="n">
         <v>112998</v>
@@ -14260,7 +14260,7 @@
         <v>26.5699996948242</v>
       </c>
       <c r="G479" t="n">
-        <v>24.8550434112549</v>
+        <v>24.8550415039062</v>
       </c>
       <c r="H479" t="n">
         <v>104751</v>
@@ -14289,7 +14289,7 @@
         <v>26.5900001525879</v>
       </c>
       <c r="G480" t="n">
-        <v>24.8737506866455</v>
+        <v>24.8737525939941</v>
       </c>
       <c r="H480" t="n">
         <v>68260</v>
@@ -14318,7 +14318,7 @@
         <v>26.5699996948242</v>
       </c>
       <c r="G481" t="n">
-        <v>24.8550434112549</v>
+        <v>24.8550415039062</v>
       </c>
       <c r="H481" t="n">
         <v>62121</v>
@@ -14376,7 +14376,7 @@
         <v>26.5</v>
       </c>
       <c r="G483" t="n">
-        <v>24.7895603179932</v>
+        <v>24.7895584106445</v>
       </c>
       <c r="H483" t="n">
         <v>30313</v>
@@ -14405,7 +14405,7 @@
         <v>26.9500007629395</v>
       </c>
       <c r="G484" t="n">
-        <v>25.2105178833008</v>
+        <v>25.2105159759521</v>
       </c>
       <c r="H484" t="n">
         <v>42573</v>
@@ -14434,7 +14434,7 @@
         <v>27.3700008392334</v>
       </c>
       <c r="G485" t="n">
-        <v>25.6034088134766</v>
+        <v>25.6034069061279</v>
       </c>
       <c r="H485" t="n">
         <v>58230</v>
@@ -14492,7 +14492,7 @@
         <v>26.5499992370605</v>
       </c>
       <c r="G487" t="n">
-        <v>24.8363304138184</v>
+        <v>24.8363342285156</v>
       </c>
       <c r="H487" t="n">
         <v>40062</v>
@@ -14579,7 +14579,7 @@
         <v>26.5599994659424</v>
       </c>
       <c r="G490" t="n">
-        <v>24.8456859588623</v>
+        <v>24.8456878662109</v>
       </c>
       <c r="H490" t="n">
         <v>66953</v>
@@ -14637,7 +14637,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G492" t="n">
-        <v>24.8831062316895</v>
+        <v>24.8831100463867</v>
       </c>
       <c r="H492" t="n">
         <v>42203</v>
@@ -14666,7 +14666,7 @@
         <v>26.4899997711182</v>
       </c>
       <c r="G493" t="n">
-        <v>24.7802066802979</v>
+        <v>24.7802085876465</v>
       </c>
       <c r="H493" t="n">
         <v>50216</v>
@@ -14695,7 +14695,7 @@
         <v>27</v>
       </c>
       <c r="G494" t="n">
-        <v>25.257287979126</v>
+        <v>25.2572898864746</v>
       </c>
       <c r="H494" t="n">
         <v>39491</v>
@@ -14753,7 +14753,7 @@
         <v>27.0200004577637</v>
       </c>
       <c r="G496" t="n">
-        <v>25.2759990692139</v>
+        <v>25.2759971618652</v>
       </c>
       <c r="H496" t="n">
         <v>35572</v>
@@ -14782,7 +14782,7 @@
         <v>27.2900009155273</v>
       </c>
       <c r="G497" t="n">
-        <v>25.5285739898682</v>
+        <v>25.5285682678223</v>
       </c>
       <c r="H497" t="n">
         <v>39590</v>
@@ -14811,7 +14811,7 @@
         <v>27.7900009155273</v>
       </c>
       <c r="G498" t="n">
-        <v>25.9962997436523</v>
+        <v>25.9962978363037</v>
       </c>
       <c r="H498" t="n">
         <v>40230</v>
@@ -14840,7 +14840,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G499" t="n">
-        <v>25.9121074676514</v>
+        <v>25.912109375</v>
       </c>
       <c r="H499" t="n">
         <v>48701</v>
@@ -14869,7 +14869,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G500" t="n">
-        <v>26.0991973876953</v>
+        <v>26.0991992950439</v>
       </c>
       <c r="H500" t="n">
         <v>47641</v>
@@ -14985,7 +14985,7 @@
         <v>26.6900005340576</v>
       </c>
       <c r="G504" t="n">
-        <v>24.9672985076904</v>
+        <v>24.9672966003418</v>
       </c>
       <c r="H504" t="n">
         <v>77566</v>
@@ -15014,7 +15014,7 @@
         <v>26.7600002288818</v>
       </c>
       <c r="G505" t="n">
-        <v>25.0327816009521</v>
+        <v>25.0327796936035</v>
       </c>
       <c r="H505" t="n">
         <v>28901</v>
@@ -15072,7 +15072,7 @@
         <v>27.3700008392334</v>
       </c>
       <c r="G507" t="n">
-        <v>25.6034088134766</v>
+        <v>25.6034069061279</v>
       </c>
       <c r="H507" t="n">
         <v>36648</v>
@@ -15188,7 +15188,7 @@
         <v>27.0100002288818</v>
       </c>
       <c r="G511" t="n">
-        <v>25.2666416168213</v>
+        <v>25.2666435241699</v>
       </c>
       <c r="H511" t="n">
         <v>24856</v>
@@ -15217,7 +15217,7 @@
         <v>27.1299991607666</v>
       </c>
       <c r="G512" t="n">
-        <v>25.3788986206055</v>
+        <v>25.3788948059082</v>
       </c>
       <c r="H512" t="n">
         <v>35663</v>
@@ -15275,7 +15275,7 @@
         <v>27.5499992370605</v>
       </c>
       <c r="G514" t="n">
-        <v>25.7717876434326</v>
+        <v>25.7717895507812</v>
       </c>
       <c r="H514" t="n">
         <v>35840</v>
@@ -15362,7 +15362,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G517" t="n">
-        <v>27.0346546173096</v>
+        <v>27.0346527099609</v>
       </c>
       <c r="H517" t="n">
         <v>296513</v>
@@ -15391,7 +15391,7 @@
         <v>27</v>
       </c>
       <c r="G518" t="n">
-        <v>25.257287979126</v>
+        <v>25.2572898864746</v>
       </c>
       <c r="H518" t="n">
         <v>3959864</v>
@@ -15420,7 +15420,7 @@
         <v>27</v>
       </c>
       <c r="G519" t="n">
-        <v>25.257287979126</v>
+        <v>25.2572898864746</v>
       </c>
       <c r="H519" t="n">
         <v>237711</v>
@@ -15449,7 +15449,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G520" t="n">
-        <v>25.5379238128662</v>
+        <v>25.5379219055176</v>
       </c>
       <c r="H520" t="n">
         <v>247114</v>
@@ -15478,7 +15478,7 @@
         <v>27</v>
       </c>
       <c r="G521" t="n">
-        <v>25.257287979126</v>
+        <v>25.2572898864746</v>
       </c>
       <c r="H521" t="n">
         <v>121591</v>
@@ -15507,7 +15507,7 @@
         <v>27</v>
       </c>
       <c r="G522" t="n">
-        <v>25.257287979126</v>
+        <v>25.2572898864746</v>
       </c>
       <c r="H522" t="n">
         <v>80441</v>
@@ -15536,7 +15536,7 @@
         <v>27</v>
       </c>
       <c r="G523" t="n">
-        <v>25.257287979126</v>
+        <v>25.2572898864746</v>
       </c>
       <c r="H523" t="n">
         <v>160928</v>
@@ -15565,7 +15565,7 @@
         <v>27.25</v>
       </c>
       <c r="G524" t="n">
-        <v>25.491153717041</v>
+        <v>25.4911499023438</v>
       </c>
       <c r="H524" t="n">
         <v>78214</v>
@@ -15594,7 +15594,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G525" t="n">
-        <v>25.6314697265625</v>
+        <v>25.6314716339111</v>
       </c>
       <c r="H525" t="n">
         <v>78720</v>
@@ -15623,7 +15623,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G526" t="n">
-        <v>25.6314697265625</v>
+        <v>25.6314716339111</v>
       </c>
       <c r="H526" t="n">
         <v>57579</v>
@@ -15652,7 +15652,7 @@
         <v>27.3500003814697</v>
       </c>
       <c r="G527" t="n">
-        <v>25.58469581604</v>
+        <v>25.5846977233887</v>
       </c>
       <c r="H527" t="n">
         <v>34270</v>
@@ -15710,7 +15710,7 @@
         <v>27.0499992370605</v>
       </c>
       <c r="G529" t="n">
-        <v>25.3040618896484</v>
+        <v>25.3040637969971</v>
       </c>
       <c r="H529" t="n">
         <v>42047</v>
@@ -15739,7 +15739,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G530" t="n">
-        <v>25.6314697265625</v>
+        <v>25.6314716339111</v>
       </c>
       <c r="H530" t="n">
         <v>48724</v>
@@ -15797,7 +15797,7 @@
         <v>27</v>
       </c>
       <c r="G532" t="n">
-        <v>25.257287979126</v>
+        <v>25.2572898864746</v>
       </c>
       <c r="H532" t="n">
         <v>50007</v>
@@ -15826,7 +15826,7 @@
         <v>27</v>
       </c>
       <c r="G533" t="n">
-        <v>25.257287979126</v>
+        <v>25.2572898864746</v>
       </c>
       <c r="H533" t="n">
         <v>56747</v>
@@ -15855,7 +15855,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G534" t="n">
-        <v>24.8831062316895</v>
+        <v>24.8831100463867</v>
       </c>
       <c r="H534" t="n">
         <v>65991</v>
@@ -15884,7 +15884,7 @@
         <v>26.1000003814697</v>
       </c>
       <c r="G535" t="n">
-        <v>24.4153785705566</v>
+        <v>24.4153804779053</v>
       </c>
       <c r="H535" t="n">
         <v>106328</v>
@@ -15913,7 +15913,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G536" t="n">
-        <v>24.2282886505127</v>
+        <v>24.2282867431641</v>
       </c>
       <c r="H536" t="n">
         <v>105918</v>
@@ -15942,7 +15942,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G537" t="n">
-        <v>23.6670150756836</v>
+        <v>23.6670169830322</v>
       </c>
       <c r="H537" t="n">
         <v>94386</v>
@@ -15971,7 +15971,7 @@
         <v>26</v>
       </c>
       <c r="G538" t="n">
-        <v>24.3218326568604</v>
+        <v>24.321834564209</v>
       </c>
       <c r="H538" t="n">
         <v>78057</v>
@@ -16000,7 +16000,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G539" t="n">
-        <v>23.5734691619873</v>
+        <v>23.5734672546387</v>
       </c>
       <c r="H539" t="n">
         <v>42055</v>
@@ -16029,7 +16029,7 @@
         <v>25.5</v>
       </c>
       <c r="G540" t="n">
-        <v>23.8541049957275</v>
+        <v>23.8541088104248</v>
       </c>
       <c r="H540" t="n">
         <v>107364</v>
@@ -16058,7 +16058,7 @@
         <v>25.75</v>
       </c>
       <c r="G541" t="n">
-        <v>24.0879707336426</v>
+        <v>24.0879726409912</v>
       </c>
       <c r="H541" t="n">
         <v>53927</v>
@@ -16087,7 +16087,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G542" t="n">
-        <v>23.7605590820312</v>
+        <v>23.7605609893799</v>
       </c>
       <c r="H542" t="n">
         <v>52591</v>
@@ -16203,7 +16203,7 @@
         <v>26.1499996185303</v>
       </c>
       <c r="G546" t="n">
-        <v>24.4621543884277</v>
+        <v>24.4621505737305</v>
       </c>
       <c r="H546" t="n">
         <v>29654</v>
@@ -16261,7 +16261,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G548" t="n">
-        <v>24.2282886505127</v>
+        <v>24.2282867431641</v>
       </c>
       <c r="H548" t="n">
         <v>36475</v>
@@ -16290,7 +16290,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G549" t="n">
-        <v>23.7605590820312</v>
+        <v>23.7605609893799</v>
       </c>
       <c r="H549" t="n">
         <v>52236</v>
@@ -16348,7 +16348,7 @@
         <v>25.5</v>
       </c>
       <c r="G551" t="n">
-        <v>23.8541049957275</v>
+        <v>23.8541088104248</v>
       </c>
       <c r="H551" t="n">
         <v>47209</v>
@@ -16435,7 +16435,7 @@
         <v>25.75</v>
       </c>
       <c r="G554" t="n">
-        <v>24.0879707336426</v>
+        <v>24.0879726409912</v>
       </c>
       <c r="H554" t="n">
         <v>74847</v>
@@ -16464,7 +16464,7 @@
         <v>25.1000003814697</v>
       </c>
       <c r="G555" t="n">
-        <v>23.479923248291</v>
+        <v>23.4799213409424</v>
       </c>
       <c r="H555" t="n">
         <v>79109</v>
@@ -16493,7 +16493,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G556" t="n">
-        <v>23.6670150756836</v>
+        <v>23.6670169830322</v>
       </c>
       <c r="H556" t="n">
         <v>41306</v>
@@ -16522,7 +16522,7 @@
         <v>25.3500003814697</v>
       </c>
       <c r="G557" t="n">
-        <v>23.7137870788574</v>
+        <v>23.7137889862061</v>
       </c>
       <c r="H557" t="n">
         <v>46776</v>
@@ -16551,7 +16551,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G558" t="n">
-        <v>23.9476528167725</v>
+        <v>23.9476509094238</v>
       </c>
       <c r="H558" t="n">
         <v>82786</v>
@@ -16580,7 +16580,7 @@
         <v>26.4500007629395</v>
       </c>
       <c r="G559" t="n">
-        <v>24.7427883148193</v>
+        <v>24.742790222168</v>
       </c>
       <c r="H559" t="n">
         <v>305392</v>
@@ -16609,7 +16609,7 @@
         <v>26.1000003814697</v>
       </c>
       <c r="G560" t="n">
-        <v>24.4153785705566</v>
+        <v>24.4153804779053</v>
       </c>
       <c r="H560" t="n">
         <v>187713</v>
@@ -16696,7 +16696,7 @@
         <v>26.1000003814697</v>
       </c>
       <c r="G563" t="n">
-        <v>24.4153785705566</v>
+        <v>24.4153804779053</v>
       </c>
       <c r="H563" t="n">
         <v>135613</v>
@@ -16754,7 +16754,7 @@
         <v>26</v>
       </c>
       <c r="G565" t="n">
-        <v>24.3218326568604</v>
+        <v>24.321834564209</v>
       </c>
       <c r="H565" t="n">
         <v>146811</v>
@@ -16870,7 +16870,7 @@
         <v>25.8500003814697</v>
       </c>
       <c r="G569" t="n">
-        <v>24.1815147399902</v>
+        <v>24.1815185546875</v>
       </c>
       <c r="H569" t="n">
         <v>49044</v>
@@ -16899,7 +16899,7 @@
         <v>25.8500003814697</v>
       </c>
       <c r="G570" t="n">
-        <v>24.1815147399902</v>
+        <v>24.1815185546875</v>
       </c>
       <c r="H570" t="n">
         <v>63627</v>
@@ -16928,7 +16928,7 @@
         <v>25.25</v>
       </c>
       <c r="G571" t="n">
-        <v>23.6202449798584</v>
+        <v>23.6202430725098</v>
       </c>
       <c r="H571" t="n">
         <v>74468</v>
@@ -16957,7 +16957,7 @@
         <v>25.25</v>
       </c>
       <c r="G572" t="n">
-        <v>23.6202449798584</v>
+        <v>23.6202430725098</v>
       </c>
       <c r="H572" t="n">
         <v>65425</v>
@@ -16986,7 +16986,7 @@
         <v>25.1000003814697</v>
       </c>
       <c r="G573" t="n">
-        <v>23.479923248291</v>
+        <v>23.4799213409424</v>
       </c>
       <c r="H573" t="n">
         <v>95783</v>
@@ -17015,7 +17015,7 @@
         <v>25.5</v>
       </c>
       <c r="G574" t="n">
-        <v>23.8541049957275</v>
+        <v>23.8541088104248</v>
       </c>
       <c r="H574" t="n">
         <v>123453</v>
@@ -17044,7 +17044,7 @@
         <v>26.1499996185303</v>
       </c>
       <c r="G575" t="n">
-        <v>24.4621543884277</v>
+        <v>24.4621505737305</v>
       </c>
       <c r="H575" t="n">
         <v>63600</v>
@@ -17160,7 +17160,7 @@
         <v>27</v>
       </c>
       <c r="G579" t="n">
-        <v>25.257287979126</v>
+        <v>25.2572898864746</v>
       </c>
       <c r="H579" t="n">
         <v>447824</v>
@@ -17189,7 +17189,7 @@
         <v>27.5499992370605</v>
       </c>
       <c r="G580" t="n">
-        <v>25.7717876434326</v>
+        <v>25.7717895507812</v>
       </c>
       <c r="H580" t="n">
         <v>114357</v>
@@ -17276,7 +17276,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G583" t="n">
-        <v>25.6314697265625</v>
+        <v>25.6314716339111</v>
       </c>
       <c r="H583" t="n">
         <v>65464</v>
@@ -17363,7 +17363,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G586" t="n">
-        <v>26.005651473999</v>
+        <v>26.0056495666504</v>
       </c>
       <c r="H586" t="n">
         <v>154125</v>
@@ -17421,7 +17421,7 @@
         <v>27.4500007629395</v>
       </c>
       <c r="G588" t="n">
-        <v>25.678243637085</v>
+        <v>25.6782455444336</v>
       </c>
       <c r="H588" t="n">
         <v>81732</v>
@@ -17450,7 +17450,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G589" t="n">
-        <v>25.9121074676514</v>
+        <v>25.912109375</v>
       </c>
       <c r="H589" t="n">
         <v>39372</v>
@@ -17479,7 +17479,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G590" t="n">
-        <v>26.005651473999</v>
+        <v>26.0056495666504</v>
       </c>
       <c r="H590" t="n">
         <v>34713</v>
@@ -17508,7 +17508,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G591" t="n">
-        <v>26.0991973876953</v>
+        <v>26.0991992950439</v>
       </c>
       <c r="H591" t="n">
         <v>51015</v>
@@ -17537,7 +17537,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G592" t="n">
-        <v>25.8185615539551</v>
+        <v>25.8185634613037</v>
       </c>
       <c r="H592" t="n">
         <v>40658</v>
@@ -17566,7 +17566,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G593" t="n">
-        <v>25.6314697265625</v>
+        <v>25.6314716339111</v>
       </c>
       <c r="H593" t="n">
         <v>49760</v>
@@ -17595,7 +17595,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G594" t="n">
-        <v>25.8185615539551</v>
+        <v>25.8185634613037</v>
       </c>
       <c r="H594" t="n">
         <v>45451</v>
@@ -17624,7 +17624,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G595" t="n">
-        <v>25.8185615539551</v>
+        <v>25.8185634613037</v>
       </c>
       <c r="H595" t="n">
         <v>75988</v>
@@ -17653,7 +17653,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G596" t="n">
-        <v>26.0991973876953</v>
+        <v>26.0991992950439</v>
       </c>
       <c r="H596" t="n">
         <v>32026</v>
@@ -17740,7 +17740,7 @@
         <v>28</v>
       </c>
       <c r="G599" t="n">
-        <v>26.1927452087402</v>
+        <v>26.1927433013916</v>
       </c>
       <c r="H599" t="n">
         <v>98539</v>
@@ -17769,7 +17769,7 @@
         <v>28.4500007629395</v>
       </c>
       <c r="G600" t="n">
-        <v>26.6136989593506</v>
+        <v>26.6137008666992</v>
       </c>
       <c r="H600" t="n">
         <v>74029</v>
@@ -17798,7 +17798,7 @@
         <v>28.25</v>
       </c>
       <c r="G601" t="n">
-        <v>26.426607131958</v>
+        <v>26.4266090393066</v>
       </c>
       <c r="H601" t="n">
         <v>51142</v>
@@ -17827,7 +17827,7 @@
         <v>30.5499992370605</v>
       </c>
       <c r="G602" t="n">
-        <v>28.5781555175781</v>
+        <v>28.5781536102295</v>
       </c>
       <c r="H602" t="n">
         <v>285606</v>
@@ -17856,7 +17856,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G603" t="n">
-        <v>28.2507476806641</v>
+        <v>28.2507457733154</v>
       </c>
       <c r="H603" t="n">
         <v>163024</v>
@@ -17914,7 +17914,7 @@
         <v>30.25</v>
       </c>
       <c r="G605" t="n">
-        <v>28.2975177764893</v>
+        <v>28.2975158691406</v>
       </c>
       <c r="H605" t="n">
         <v>127931</v>
@@ -18030,7 +18030,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G609" t="n">
-        <v>29.8213806152344</v>
+        <v>29.821382522583</v>
       </c>
       <c r="H609" t="n">
         <v>103237</v>
@@ -18175,7 +18175,7 @@
         <v>31.5</v>
       </c>
       <c r="G614" t="n">
-        <v>29.7270088195801</v>
+        <v>29.7270107269287</v>
       </c>
       <c r="H614" t="n">
         <v>179319</v>
@@ -18291,7 +18291,7 @@
         <v>35.6500015258789</v>
       </c>
       <c r="G618" t="n">
-        <v>33.6434288024902</v>
+        <v>33.6434326171875</v>
       </c>
       <c r="H618" t="n">
         <v>510094</v>
@@ -18407,7 +18407,7 @@
         <v>35.5</v>
       </c>
       <c r="G622" t="n">
-        <v>33.5018653869629</v>
+        <v>33.5018692016602</v>
       </c>
       <c r="H622" t="n">
         <v>278652</v>
@@ -18465,7 +18465,7 @@
         <v>35.5</v>
       </c>
       <c r="G624" t="n">
-        <v>33.5018653869629</v>
+        <v>33.5018692016602</v>
       </c>
       <c r="H624" t="n">
         <v>131788</v>
@@ -18494,7 +18494,7 @@
         <v>36.5999984741211</v>
       </c>
       <c r="G625" t="n">
-        <v>34.5399551391602</v>
+        <v>34.5399513244629</v>
       </c>
       <c r="H625" t="n">
         <v>59256</v>
@@ -18523,7 +18523,7 @@
         <v>37.4000015258789</v>
       </c>
       <c r="G626" t="n">
-        <v>35.2949256896973</v>
+        <v>35.2949333190918</v>
       </c>
       <c r="H626" t="n">
         <v>83167</v>
@@ -18581,7 +18581,7 @@
         <v>36.8499984741211</v>
       </c>
       <c r="G628" t="n">
-        <v>34.77587890625</v>
+        <v>34.7758827209473</v>
       </c>
       <c r="H628" t="n">
         <v>78088</v>
@@ -18610,7 +18610,7 @@
         <v>36.7000007629395</v>
       </c>
       <c r="G629" t="n">
-        <v>34.6343269348145</v>
+        <v>34.6343231201172</v>
       </c>
       <c r="H629" t="n">
         <v>63966</v>
@@ -18697,7 +18697,7 @@
         <v>38.0999984741211</v>
       </c>
       <c r="G632" t="n">
-        <v>35.9555282592773</v>
+        <v>35.9555244445801</v>
       </c>
       <c r="H632" t="n">
         <v>91116</v>
@@ -18755,7 +18755,7 @@
         <v>38</v>
       </c>
       <c r="G634" t="n">
-        <v>35.861156463623</v>
+        <v>35.8611602783203</v>
       </c>
       <c r="H634" t="n">
         <v>60303</v>
@@ -18813,7 +18813,7 @@
         <v>37.0499992370605</v>
       </c>
       <c r="G636" t="n">
-        <v>34.9646263122559</v>
+        <v>34.9646224975586</v>
       </c>
       <c r="H636" t="n">
         <v>91025</v>
@@ -18900,7 +18900,7 @@
         <v>37.4000015258789</v>
       </c>
       <c r="G639" t="n">
-        <v>35.2949256896973</v>
+        <v>35.2949333190918</v>
       </c>
       <c r="H639" t="n">
         <v>158356</v>
@@ -18929,7 +18929,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G640" t="n">
-        <v>30.3876132965088</v>
+        <v>30.3876094818115</v>
       </c>
       <c r="H640" t="n">
         <v>473865</v>
@@ -18958,7 +18958,7 @@
         <v>32.5499992370605</v>
       </c>
       <c r="G641" t="n">
-        <v>30.7179088592529</v>
+        <v>30.7179107666016</v>
       </c>
       <c r="H641" t="n">
         <v>398010</v>
@@ -19016,7 +19016,7 @@
         <v>33.0499992370605</v>
       </c>
       <c r="G643" t="n">
-        <v>31.1897621154785</v>
+        <v>31.1897659301758</v>
       </c>
       <c r="H643" t="n">
         <v>114298</v>
@@ -19045,7 +19045,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G644" t="n">
-        <v>30.95383644104</v>
+        <v>30.9538345336914</v>
       </c>
       <c r="H644" t="n">
         <v>110384</v>
@@ -19074,7 +19074,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G645" t="n">
-        <v>30.3876132965088</v>
+        <v>30.3876094818115</v>
       </c>
       <c r="H645" t="n">
         <v>46882</v>
@@ -19132,7 +19132,7 @@
         <v>34.5499992370605</v>
       </c>
       <c r="G647" t="n">
-        <v>32.6053352355957</v>
+        <v>32.6053314208984</v>
       </c>
       <c r="H647" t="n">
         <v>240196</v>
@@ -19219,7 +19219,7 @@
         <v>36.4000015258789</v>
       </c>
       <c r="G650" t="n">
-        <v>34.3512115478516</v>
+        <v>34.3512153625488</v>
       </c>
       <c r="H650" t="n">
         <v>105258</v>
@@ -19277,7 +19277,7 @@
         <v>35.9500007629395</v>
       </c>
       <c r="G652" t="n">
-        <v>33.9265403747559</v>
+        <v>33.9265365600586</v>
       </c>
       <c r="H652" t="n">
         <v>172656</v>
@@ -19335,7 +19335,7 @@
         <v>36.25</v>
       </c>
       <c r="G654" t="n">
-        <v>34.2096519470215</v>
+        <v>34.2096557617188</v>
       </c>
       <c r="H654" t="n">
         <v>125137</v>
@@ -19364,7 +19364,7 @@
         <v>36.6500015258789</v>
       </c>
       <c r="G655" t="n">
-        <v>34.5871391296387</v>
+        <v>34.5871429443359</v>
       </c>
       <c r="H655" t="n">
         <v>47496</v>
@@ -19393,7 +19393,7 @@
         <v>36.2000007629395</v>
       </c>
       <c r="G656" t="n">
-        <v>34.162467956543</v>
+        <v>34.1624641418457</v>
       </c>
       <c r="H656" t="n">
         <v>85959</v>
@@ -19451,7 +19451,7 @@
         <v>36.25</v>
       </c>
       <c r="G658" t="n">
-        <v>34.2096519470215</v>
+        <v>34.2096557617188</v>
       </c>
       <c r="H658" t="n">
         <v>61678</v>
@@ -19480,7 +19480,7 @@
         <v>35.5</v>
       </c>
       <c r="G659" t="n">
-        <v>33.5018653869629</v>
+        <v>33.5018692016602</v>
       </c>
       <c r="H659" t="n">
         <v>117716</v>
@@ -19509,7 +19509,7 @@
         <v>36.0499992370605</v>
       </c>
       <c r="G660" t="n">
-        <v>34.0209083557129</v>
+        <v>34.0209045410156</v>
       </c>
       <c r="H660" t="n">
         <v>151660</v>
@@ -19596,7 +19596,7 @@
         <v>36.6500015258789</v>
       </c>
       <c r="G663" t="n">
-        <v>34.5871391296387</v>
+        <v>34.5871429443359</v>
       </c>
       <c r="H663" t="n">
         <v>92418</v>
@@ -19625,7 +19625,7 @@
         <v>36.2000007629395</v>
       </c>
       <c r="G664" t="n">
-        <v>34.162467956543</v>
+        <v>34.1624641418457</v>
       </c>
       <c r="H664" t="n">
         <v>61302</v>
@@ -19654,7 +19654,7 @@
         <v>36.25</v>
       </c>
       <c r="G665" t="n">
-        <v>34.2096519470215</v>
+        <v>34.2096557617188</v>
       </c>
       <c r="H665" t="n">
         <v>96828</v>
@@ -19712,7 +19712,7 @@
         <v>36.3499984741211</v>
       </c>
       <c r="G667" t="n">
-        <v>34.3040237426758</v>
+        <v>34.3040199279785</v>
       </c>
       <c r="H667" t="n">
         <v>65013</v>
@@ -19741,7 +19741,7 @@
         <v>36.7000007629395</v>
       </c>
       <c r="G668" t="n">
-        <v>34.6343269348145</v>
+        <v>34.6343231201172</v>
       </c>
       <c r="H668" t="n">
         <v>42893</v>
@@ -19770,7 +19770,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G669" t="n">
-        <v>35.1061859130859</v>
+        <v>35.1061820983887</v>
       </c>
       <c r="H669" t="n">
         <v>135641</v>
@@ -19944,7 +19944,7 @@
         <v>39.0499992370605</v>
       </c>
       <c r="G675" t="n">
-        <v>36.85205078125</v>
+        <v>36.8520545959473</v>
       </c>
       <c r="H675" t="n">
         <v>142986</v>
@@ -20002,7 +20002,7 @@
         <v>39.1500015258789</v>
       </c>
       <c r="G677" t="n">
-        <v>36.9464263916016</v>
+        <v>36.9464302062988</v>
       </c>
       <c r="H677" t="n">
         <v>91637</v>
@@ -20089,7 +20089,7 @@
         <v>38</v>
       </c>
       <c r="G680" t="n">
-        <v>35.861156463623</v>
+        <v>35.8611602783203</v>
       </c>
       <c r="H680" t="n">
         <v>152741</v>
@@ -20147,7 +20147,7 @@
         <v>38.9500007629395</v>
       </c>
       <c r="G682" t="n">
-        <v>36.7576866149902</v>
+        <v>36.757682800293</v>
       </c>
       <c r="H682" t="n">
         <v>124061</v>
@@ -20321,7 +20321,7 @@
         <v>35.0499992370605</v>
       </c>
       <c r="G688" t="n">
-        <v>33.0771980285645</v>
+        <v>33.0771942138672</v>
       </c>
       <c r="H688" t="n">
         <v>77759</v>
@@ -20350,7 +20350,7 @@
         <v>34.7999992370605</v>
       </c>
       <c r="G689" t="n">
-        <v>32.8412704467773</v>
+        <v>32.8412628173828</v>
       </c>
       <c r="H689" t="n">
         <v>116986</v>
@@ -20379,7 +20379,7 @@
         <v>33.75</v>
       </c>
       <c r="G690" t="n">
-        <v>31.8503646850586</v>
+        <v>31.8503684997559</v>
       </c>
       <c r="H690" t="n">
         <v>137232</v>
@@ -20408,7 +20408,7 @@
         <v>34.5</v>
       </c>
       <c r="G691" t="n">
-        <v>32.5581512451172</v>
+        <v>32.5581550598145</v>
       </c>
       <c r="H691" t="n">
         <v>129800</v>
@@ -20437,7 +20437,7 @@
         <v>34.9000015258789</v>
       </c>
       <c r="G692" t="n">
-        <v>32.9356346130371</v>
+        <v>32.9356422424316</v>
       </c>
       <c r="H692" t="n">
         <v>153075</v>
@@ -20495,7 +20495,7 @@
         <v>34.3499984741211</v>
       </c>
       <c r="G694" t="n">
-        <v>32.4165916442871</v>
+        <v>32.4165954589844</v>
       </c>
       <c r="H694" t="n">
         <v>46973</v>
@@ -20524,7 +20524,7 @@
         <v>34.0999984741211</v>
       </c>
       <c r="G695" t="n">
-        <v>32.1806678771973</v>
+        <v>32.1806640625</v>
       </c>
       <c r="H695" t="n">
         <v>109117</v>
@@ -20611,7 +20611,7 @@
         <v>34.1500015258789</v>
       </c>
       <c r="G698" t="n">
-        <v>32.227855682373</v>
+        <v>32.2278594970703</v>
       </c>
       <c r="H698" t="n">
         <v>532587</v>
@@ -20698,7 +20698,7 @@
         <v>33.5499992370605</v>
       </c>
       <c r="G701" t="n">
-        <v>31.6616268157959</v>
+        <v>31.66162109375</v>
       </c>
       <c r="H701" t="n">
         <v>86649</v>
@@ -20727,7 +20727,7 @@
         <v>33.75</v>
       </c>
       <c r="G702" t="n">
-        <v>31.8503646850586</v>
+        <v>31.8503684997559</v>
       </c>
       <c r="H702" t="n">
         <v>110268</v>
@@ -20756,7 +20756,7 @@
         <v>33.25</v>
       </c>
       <c r="G703" t="n">
-        <v>31.3785076141357</v>
+        <v>31.3785133361816</v>
       </c>
       <c r="H703" t="n">
         <v>68703</v>
@@ -20785,7 +20785,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G704" t="n">
-        <v>31.4256973266602</v>
+        <v>31.4256935119629</v>
       </c>
       <c r="H704" t="n">
         <v>66734</v>
@@ -20814,7 +20814,7 @@
         <v>32.5</v>
       </c>
       <c r="G705" t="n">
-        <v>30.6707229614258</v>
+        <v>30.6707210540771</v>
       </c>
       <c r="H705" t="n">
         <v>69778</v>
@@ -20872,7 +20872,7 @@
         <v>32.4500007629395</v>
       </c>
       <c r="G707" t="n">
-        <v>30.62353515625</v>
+        <v>30.6235370635986</v>
       </c>
       <c r="H707" t="n">
         <v>92299</v>
@@ -20901,7 +20901,7 @@
         <v>33.3499984741211</v>
       </c>
       <c r="G708" t="n">
-        <v>31.4728813171387</v>
+        <v>31.47287940979</v>
       </c>
       <c r="H708" t="n">
         <v>145812</v>
@@ -20930,7 +20930,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G709" t="n">
-        <v>28.5001811981201</v>
+        <v>28.5001792907715</v>
       </c>
       <c r="H709" t="n">
         <v>247286</v>
@@ -20988,7 +20988,7 @@
         <v>29.5</v>
       </c>
       <c r="G711" t="n">
-        <v>27.8395805358887</v>
+        <v>27.8395824432373</v>
       </c>
       <c r="H711" t="n">
         <v>127879</v>
@@ -21017,7 +21017,7 @@
         <v>29.0499992370605</v>
       </c>
       <c r="G712" t="n">
-        <v>27.4149074554443</v>
+        <v>27.414909362793</v>
       </c>
       <c r="H712" t="n">
         <v>118586</v>
@@ -21104,7 +21104,7 @@
         <v>29.5</v>
       </c>
       <c r="G715" t="n">
-        <v>27.8395805358887</v>
+        <v>27.8395824432373</v>
       </c>
       <c r="H715" t="n">
         <v>147869</v>
@@ -21220,7 +21220,7 @@
         <v>29.0499992370605</v>
       </c>
       <c r="G719" t="n">
-        <v>27.4149074554443</v>
+        <v>27.414909362793</v>
       </c>
       <c r="H719" t="n">
         <v>144649</v>
@@ -21278,7 +21278,7 @@
         <v>29.0499992370605</v>
       </c>
       <c r="G721" t="n">
-        <v>27.4149074554443</v>
+        <v>27.414909362793</v>
       </c>
       <c r="H721" t="n">
         <v>92529</v>
@@ -21307,7 +21307,7 @@
         <v>29.6499996185303</v>
       </c>
       <c r="G722" t="n">
-        <v>27.9811363220215</v>
+        <v>27.9811382293701</v>
       </c>
       <c r="H722" t="n">
         <v>86989</v>
@@ -21539,7 +21539,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G730" t="n">
-        <v>29.6326389312744</v>
+        <v>29.6326370239258</v>
       </c>
       <c r="H730" t="n">
         <v>141037</v>
@@ -21568,7 +21568,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G731" t="n">
-        <v>29.0664081573486</v>
+        <v>29.06640625</v>
       </c>
       <c r="H731" t="n">
         <v>105082</v>
@@ -21626,7 +21626,7 @@
         <v>31.0499992370605</v>
       </c>
       <c r="G733" t="n">
-        <v>29.3023357391357</v>
+        <v>29.3023376464844</v>
       </c>
       <c r="H733" t="n">
         <v>142789</v>
@@ -21829,7 +21829,7 @@
         <v>28.5499992370605</v>
       </c>
       <c r="G740" t="n">
-        <v>26.9430484771729</v>
+        <v>26.9430503845215</v>
       </c>
       <c r="H740" t="n">
         <v>150449</v>
@@ -21858,7 +21858,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G741" t="n">
-        <v>27.0846099853516</v>
+        <v>27.0846080780029</v>
       </c>
       <c r="H741" t="n">
         <v>79691</v>
@@ -21974,7 +21974,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G745" t="n">
-        <v>28.5001811981201</v>
+        <v>28.5001792907715</v>
       </c>
       <c r="H745" t="n">
         <v>156847</v>
@@ -22061,7 +22061,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G748" t="n">
-        <v>29.8213806152344</v>
+        <v>29.821382522583</v>
       </c>
       <c r="H748" t="n">
         <v>88713</v>
@@ -22090,7 +22090,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G749" t="n">
-        <v>29.6326389312744</v>
+        <v>29.6326370239258</v>
       </c>
       <c r="H749" t="n">
         <v>60850</v>
@@ -22177,7 +22177,7 @@
         <v>28.3500003814697</v>
       </c>
       <c r="G752" t="n">
-        <v>26.7543087005615</v>
+        <v>26.7543067932129</v>
       </c>
       <c r="H752" t="n">
         <v>97659</v>
@@ -22206,7 +22206,7 @@
         <v>28.1000003814697</v>
       </c>
       <c r="G753" t="n">
-        <v>26.5183811187744</v>
+        <v>26.5183792114258</v>
       </c>
       <c r="H753" t="n">
         <v>106831</v>
@@ -22235,7 +22235,7 @@
         <v>28.75</v>
       </c>
       <c r="G754" t="n">
-        <v>27.1317939758301</v>
+        <v>27.1317958831787</v>
       </c>
       <c r="H754" t="n">
         <v>80259</v>
@@ -22264,7 +22264,7 @@
         <v>28.25</v>
       </c>
       <c r="G755" t="n">
-        <v>26.6599349975586</v>
+        <v>26.6599369049072</v>
       </c>
       <c r="H755" t="n">
         <v>101429</v>
@@ -22293,7 +22293,7 @@
         <v>27.2999992370605</v>
       </c>
       <c r="G756" t="n">
-        <v>25.7634048461914</v>
+        <v>25.76340675354</v>
       </c>
       <c r="H756" t="n">
         <v>115028</v>
@@ -22351,7 +22351,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G758" t="n">
-        <v>25.857780456543</v>
+        <v>25.8577785491943</v>
       </c>
       <c r="H758" t="n">
         <v>76488</v>
@@ -22380,7 +22380,7 @@
         <v>27.8500003814697</v>
       </c>
       <c r="G759" t="n">
-        <v>26.28244972229</v>
+        <v>26.2824516296387</v>
       </c>
       <c r="H759" t="n">
         <v>104313</v>
@@ -22409,7 +22409,7 @@
         <v>26.8999996185303</v>
       </c>
       <c r="G760" t="n">
-        <v>25.3859214782715</v>
+        <v>25.3859195709229</v>
       </c>
       <c r="H760" t="n">
         <v>64205</v>
@@ -22467,7 +22467,7 @@
         <v>28</v>
       </c>
       <c r="G762" t="n">
-        <v>26.4240093231201</v>
+        <v>26.4240112304688</v>
       </c>
       <c r="H762" t="n">
         <v>122045</v>
@@ -22554,7 +22554,7 @@
         <v>30</v>
       </c>
       <c r="G765" t="n">
-        <v>28.3114376068115</v>
+        <v>28.3114395141602</v>
       </c>
       <c r="H765" t="n">
         <v>124616</v>
@@ -22612,7 +22612,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G767" t="n">
-        <v>29.8213806152344</v>
+        <v>29.821382522583</v>
       </c>
       <c r="H767" t="n">
         <v>167889</v>
@@ -22699,7 +22699,7 @@
         <v>28.0499992370605</v>
       </c>
       <c r="G770" t="n">
-        <v>26.4711933135986</v>
+        <v>26.47119140625</v>
       </c>
       <c r="H770" t="n">
         <v>222777</v>
@@ -22728,7 +22728,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G771" t="n">
-        <v>26.1408939361572</v>
+        <v>26.1408958435059</v>
       </c>
       <c r="H771" t="n">
         <v>123243</v>
@@ -22757,7 +22757,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G772" t="n">
-        <v>25.857780456543</v>
+        <v>25.8577785491943</v>
       </c>
       <c r="H772" t="n">
         <v>178129</v>
@@ -22815,7 +22815,7 @@
         <v>28.7000007629395</v>
       </c>
       <c r="G774" t="n">
-        <v>27.0846099853516</v>
+        <v>27.0846080780029</v>
       </c>
       <c r="H774" t="n">
         <v>140182</v>
@@ -22844,7 +22844,7 @@
         <v>28.6499996185303</v>
       </c>
       <c r="G775" t="n">
-        <v>27.0374240875244</v>
+        <v>27.0374221801758</v>
       </c>
       <c r="H775" t="n">
         <v>79269</v>
@@ -22960,7 +22960,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G779" t="n">
-        <v>28.5001811981201</v>
+        <v>28.5001792907715</v>
       </c>
       <c r="H779" t="n">
         <v>163478</v>
@@ -22989,7 +22989,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G780" t="n">
-        <v>29.0664081573486</v>
+        <v>29.06640625</v>
       </c>
       <c r="H780" t="n">
         <v>129472</v>
@@ -23105,7 +23105,7 @@
         <v>31.25</v>
       </c>
       <c r="G784" t="n">
-        <v>29.491081237793</v>
+        <v>29.4910793304443</v>
       </c>
       <c r="H784" t="n">
         <v>136741</v>
@@ -23134,7 +23134,7 @@
         <v>31.5499992370605</v>
       </c>
       <c r="G785" t="n">
-        <v>29.7741966247559</v>
+        <v>29.7741928100586</v>
       </c>
       <c r="H785" t="n">
         <v>117895</v>
@@ -23163,7 +23163,7 @@
         <v>31.75</v>
       </c>
       <c r="G786" t="n">
-        <v>29.9629364013672</v>
+        <v>29.9629383087158</v>
       </c>
       <c r="H786" t="n">
         <v>133684</v>
@@ -23192,7 +23192,7 @@
         <v>31.5499992370605</v>
       </c>
       <c r="G787" t="n">
-        <v>29.7741966247559</v>
+        <v>29.7741928100586</v>
       </c>
       <c r="H787" t="n">
         <v>49223</v>
@@ -23221,7 +23221,7 @@
         <v>32.75</v>
       </c>
       <c r="G788" t="n">
-        <v>30.9066505432129</v>
+        <v>30.9066543579102</v>
       </c>
       <c r="H788" t="n">
         <v>79600</v>
@@ -23250,7 +23250,7 @@
         <v>33.25</v>
       </c>
       <c r="G789" t="n">
-        <v>31.3785076141357</v>
+        <v>31.3785133361816</v>
       </c>
       <c r="H789" t="n">
         <v>119809</v>
@@ -23279,7 +23279,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G790" t="n">
-        <v>31.0482120513916</v>
+        <v>31.048210144043</v>
       </c>
       <c r="H790" t="n">
         <v>173592</v>
@@ -23308,7 +23308,7 @@
         <v>33.25</v>
       </c>
       <c r="G791" t="n">
-        <v>31.3785076141357</v>
+        <v>31.3785133361816</v>
       </c>
       <c r="H791" t="n">
         <v>101328</v>
@@ -23337,7 +23337,7 @@
         <v>33.25</v>
       </c>
       <c r="G792" t="n">
-        <v>31.3785076141357</v>
+        <v>31.3785133361816</v>
       </c>
       <c r="H792" t="n">
         <v>78594</v>
@@ -23395,7 +23395,7 @@
         <v>34.3499984741211</v>
       </c>
       <c r="G794" t="n">
-        <v>32.4165916442871</v>
+        <v>32.4165954589844</v>
       </c>
       <c r="H794" t="n">
         <v>126536</v>
@@ -23424,7 +23424,7 @@
         <v>34.0999984741211</v>
       </c>
       <c r="G795" t="n">
-        <v>32.1806678771973</v>
+        <v>32.1806640625</v>
       </c>
       <c r="H795" t="n">
         <v>125918</v>
@@ -23453,7 +23453,7 @@
         <v>33.75</v>
       </c>
       <c r="G796" t="n">
-        <v>31.8503646850586</v>
+        <v>31.8503684997559</v>
       </c>
       <c r="H796" t="n">
         <v>163016</v>
@@ -23482,7 +23482,7 @@
         <v>33.9500007629395</v>
       </c>
       <c r="G797" t="n">
-        <v>32.0391120910645</v>
+        <v>32.0391082763672</v>
       </c>
       <c r="H797" t="n">
         <v>213453</v>
@@ -23627,7 +23627,7 @@
         <v>35.1500015258789</v>
       </c>
       <c r="G802" t="n">
-        <v>33.1715660095215</v>
+        <v>33.1715698242188</v>
       </c>
       <c r="H802" t="n">
         <v>436803</v>
@@ -23743,7 +23743,7 @@
         <v>35.0499992370605</v>
       </c>
       <c r="G806" t="n">
-        <v>33.0771980285645</v>
+        <v>33.0771942138672</v>
       </c>
       <c r="H806" t="n">
         <v>141822</v>
@@ -23772,7 +23772,7 @@
         <v>35.1500015258789</v>
       </c>
       <c r="G807" t="n">
-        <v>33.1715660095215</v>
+        <v>33.1715698242188</v>
       </c>
       <c r="H807" t="n">
         <v>199845</v>
@@ -23830,7 +23830,7 @@
         <v>34.9000015258789</v>
       </c>
       <c r="G809" t="n">
-        <v>32.9356346130371</v>
+        <v>32.9356422424316</v>
       </c>
       <c r="H809" t="n">
         <v>65476</v>
@@ -23859,7 +23859,7 @@
         <v>34.7999992370605</v>
       </c>
       <c r="G810" t="n">
-        <v>32.8412704467773</v>
+        <v>32.8412628173828</v>
       </c>
       <c r="H810" t="n">
         <v>59955</v>
@@ -23917,7 +23917,7 @@
         <v>34.7999992370605</v>
       </c>
       <c r="G812" t="n">
-        <v>32.8412704467773</v>
+        <v>32.8412628173828</v>
       </c>
       <c r="H812" t="n">
         <v>74517</v>
@@ -23946,7 +23946,7 @@
         <v>34.7000007629395</v>
       </c>
       <c r="G813" t="n">
-        <v>32.746898651123</v>
+        <v>32.7468948364258</v>
       </c>
       <c r="H813" t="n">
         <v>53683</v>
@@ -24004,7 +24004,7 @@
         <v>35.1500015258789</v>
       </c>
       <c r="G815" t="n">
-        <v>33.1715660095215</v>
+        <v>33.1715698242188</v>
       </c>
       <c r="H815" t="n">
         <v>143904</v>
@@ -24033,7 +24033,7 @@
         <v>31.5</v>
       </c>
       <c r="G816" t="n">
-        <v>29.7270088195801</v>
+        <v>29.7270107269287</v>
       </c>
       <c r="H816" t="n">
         <v>794021</v>
@@ -24178,7 +24178,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G821" t="n">
-        <v>29.6326389312744</v>
+        <v>29.6326370239258</v>
       </c>
       <c r="H821" t="n">
         <v>132091</v>
@@ -24207,7 +24207,7 @@
         <v>31.25</v>
       </c>
       <c r="G822" t="n">
-        <v>29.491081237793</v>
+        <v>29.4910793304443</v>
       </c>
       <c r="H822" t="n">
         <v>144245</v>
@@ -24265,7 +24265,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G824" t="n">
-        <v>28.5001811981201</v>
+        <v>28.5001792907715</v>
       </c>
       <c r="H824" t="n">
         <v>173549</v>
@@ -24526,7 +24526,7 @@
         <v>31.5</v>
       </c>
       <c r="G833" t="n">
-        <v>29.7270088195801</v>
+        <v>29.7270107269287</v>
       </c>
       <c r="H833" t="n">
         <v>86351</v>
@@ -24555,7 +24555,7 @@
         <v>31.4599990844727</v>
       </c>
       <c r="G834" t="n">
-        <v>29.6892604827881</v>
+        <v>29.6892585754395</v>
       </c>
       <c r="H834" t="n">
         <v>34864</v>
@@ -24642,7 +24642,7 @@
         <v>31.4599990844727</v>
       </c>
       <c r="G837" t="n">
-        <v>29.6892604827881</v>
+        <v>29.6892585754395</v>
       </c>
       <c r="H837" t="n">
         <v>67872</v>
@@ -24671,7 +24671,7 @@
         <v>31.6200008392334</v>
       </c>
       <c r="G838" t="n">
-        <v>29.8402557373047</v>
+        <v>29.8402538299561</v>
       </c>
       <c r="H838" t="n">
         <v>76856</v>
@@ -24758,7 +24758,7 @@
         <v>31.5</v>
       </c>
       <c r="G841" t="n">
-        <v>29.7270088195801</v>
+        <v>29.7270107269287</v>
       </c>
       <c r="H841" t="n">
         <v>39273</v>
@@ -24845,7 +24845,7 @@
         <v>31.8400001525879</v>
       </c>
       <c r="G844" t="n">
-        <v>30.0478687286377</v>
+        <v>30.0478706359863</v>
       </c>
       <c r="H844" t="n">
         <v>43380</v>
@@ -24932,7 +24932,7 @@
         <v>31.1200008392334</v>
       </c>
       <c r="G847" t="n">
-        <v>29.3683986663818</v>
+        <v>29.3683967590332</v>
       </c>
       <c r="H847" t="n">
         <v>112025</v>
@@ -24990,7 +24990,7 @@
         <v>31.8400001525879</v>
       </c>
       <c r="G849" t="n">
-        <v>30.0478687286377</v>
+        <v>30.0478706359863</v>
       </c>
       <c r="H849" t="n">
         <v>51025</v>
@@ -25048,7 +25048,7 @@
         <v>31.0799999237061</v>
       </c>
       <c r="G851" t="n">
-        <v>29.3306484222412</v>
+        <v>29.3306503295898</v>
       </c>
       <c r="H851" t="n">
         <v>79835</v>
@@ -25135,7 +25135,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G854" t="n">
-        <v>28.1226921081543</v>
+        <v>28.1226940155029</v>
       </c>
       <c r="H854" t="n">
         <v>69348</v>
@@ -25164,7 +25164,7 @@
         <v>30.0400009155273</v>
       </c>
       <c r="G855" t="n">
-        <v>28.3491859436035</v>
+        <v>28.3491878509521</v>
       </c>
       <c r="H855" t="n">
         <v>67058</v>
@@ -25251,7 +25251,7 @@
         <v>30.6800003051758</v>
       </c>
       <c r="G858" t="n">
-        <v>28.9531650543213</v>
+        <v>28.9531631469727</v>
       </c>
       <c r="H858" t="n">
         <v>45457</v>
@@ -25280,7 +25280,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G859" t="n">
-        <v>28.2097969055176</v>
+        <v>28.2097988128662</v>
       </c>
       <c r="H859" t="n">
         <v>37746</v>
@@ -25309,7 +25309,7 @@
         <v>29.9599990844727</v>
       </c>
       <c r="G860" t="n">
-        <v>28.5528888702393</v>
+        <v>28.5528907775879</v>
       </c>
       <c r="H860" t="n">
         <v>78047</v>
@@ -25338,7 +25338,7 @@
         <v>29.6800003051758</v>
       </c>
       <c r="G861" t="n">
-        <v>28.2860412597656</v>
+        <v>28.286039352417</v>
       </c>
       <c r="H861" t="n">
         <v>73612</v>
@@ -25367,7 +25367,7 @@
         <v>29.3199996948242</v>
       </c>
       <c r="G862" t="n">
-        <v>27.9429473876953</v>
+        <v>27.9429492950439</v>
       </c>
       <c r="H862" t="n">
         <v>156992</v>
@@ -25396,7 +25396,7 @@
         <v>29.3799991607666</v>
       </c>
       <c r="G863" t="n">
-        <v>28.000129699707</v>
+        <v>28.0001316070557</v>
       </c>
       <c r="H863" t="n">
         <v>73817</v>
@@ -25483,7 +25483,7 @@
         <v>29.0799999237061</v>
       </c>
       <c r="G866" t="n">
-        <v>27.7142219543457</v>
+        <v>27.7142200469971</v>
       </c>
       <c r="H866" t="n">
         <v>171179</v>
@@ -25599,7 +25599,7 @@
         <v>28.1800003051758</v>
       </c>
       <c r="G870" t="n">
-        <v>26.8564891815186</v>
+        <v>26.8564910888672</v>
       </c>
       <c r="H870" t="n">
         <v>141181</v>
@@ -25628,7 +25628,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G871" t="n">
-        <v>26.9708518981934</v>
+        <v>26.970853805542</v>
       </c>
       <c r="H871" t="n">
         <v>91299</v>
@@ -25686,7 +25686,7 @@
         <v>28.6399993896484</v>
       </c>
       <c r="G873" t="n">
-        <v>27.2948818206787</v>
+        <v>27.2948837280273</v>
       </c>
       <c r="H873" t="n">
         <v>67494</v>
@@ -25715,7 +25715,7 @@
         <v>28.6399993896484</v>
       </c>
       <c r="G874" t="n">
-        <v>27.2948818206787</v>
+        <v>27.2948837280273</v>
       </c>
       <c r="H874" t="n">
         <v>22991</v>
@@ -25831,7 +25831,7 @@
         <v>28.7800006866455</v>
       </c>
       <c r="G878" t="n">
-        <v>27.4283103942871</v>
+        <v>27.4283123016357</v>
       </c>
       <c r="H878" t="n">
         <v>34633</v>
@@ -25918,7 +25918,7 @@
         <v>29</v>
       </c>
       <c r="G881" t="n">
-        <v>27.6379776000977</v>
+        <v>27.637975692749</v>
       </c>
       <c r="H881" t="n">
         <v>57892</v>
@@ -25947,7 +25947,7 @@
         <v>29.5200004577637</v>
       </c>
       <c r="G882" t="n">
-        <v>28.1335544586182</v>
+        <v>28.1335563659668</v>
       </c>
       <c r="H882" t="n">
         <v>41094</v>
@@ -25976,7 +25976,7 @@
         <v>29.2600002288818</v>
       </c>
       <c r="G883" t="n">
-        <v>27.8857669830322</v>
+        <v>27.8857650756836</v>
       </c>
       <c r="H883" t="n">
         <v>88623</v>
@@ -26005,7 +26005,7 @@
         <v>29.3400001525879</v>
       </c>
       <c r="G884" t="n">
-        <v>27.9620094299316</v>
+        <v>27.9620113372803</v>
       </c>
       <c r="H884" t="n">
         <v>24966</v>
@@ -26034,7 +26034,7 @@
         <v>28.8400001525879</v>
       </c>
       <c r="G885" t="n">
-        <v>27.4854907989502</v>
+        <v>27.4854927062988</v>
       </c>
       <c r="H885" t="n">
         <v>35197</v>
@@ -26092,7 +26092,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G887" t="n">
-        <v>27.7332801818848</v>
+        <v>27.7332820892334</v>
       </c>
       <c r="H887" t="n">
         <v>42887</v>
@@ -26121,7 +26121,7 @@
         <v>29.6599998474121</v>
       </c>
       <c r="G888" t="n">
-        <v>28.2669773101807</v>
+        <v>28.2669792175293</v>
       </c>
       <c r="H888" t="n">
         <v>35623</v>
@@ -26208,7 +26208,7 @@
         <v>30.3199996948242</v>
       </c>
       <c r="G891" t="n">
-        <v>28.8959827423096</v>
+        <v>28.8959808349609</v>
       </c>
       <c r="H891" t="n">
         <v>61917</v>
@@ -26266,7 +26266,7 @@
         <v>30.9799995422363</v>
       </c>
       <c r="G893" t="n">
-        <v>29.5249843597412</v>
+        <v>29.5249824523926</v>
       </c>
       <c r="H893" t="n">
         <v>80724</v>
@@ -26295,7 +26295,7 @@
         <v>30.9200000762939</v>
       </c>
       <c r="G894" t="n">
-        <v>29.4678001403809</v>
+        <v>29.4678020477295</v>
       </c>
       <c r="H894" t="n">
         <v>45483</v>
@@ -26527,7 +26527,7 @@
         <v>30.4799995422363</v>
       </c>
       <c r="G902" t="n">
-        <v>29.0484676361084</v>
+        <v>29.0484657287598</v>
       </c>
       <c r="H902" t="n">
         <v>70874</v>
@@ -26556,7 +26556,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G903" t="n">
-        <v>28.8769207000732</v>
+        <v>28.8769226074219</v>
       </c>
       <c r="H903" t="n">
         <v>54877</v>
@@ -26643,7 +26643,7 @@
         <v>29.9400005340576</v>
       </c>
       <c r="G906" t="n">
-        <v>28.5338287353516</v>
+        <v>28.5338325500488</v>
       </c>
       <c r="H906" t="n">
         <v>54692</v>
@@ -26672,7 +26672,7 @@
         <v>29.9599990844727</v>
       </c>
       <c r="G907" t="n">
-        <v>28.5528888702393</v>
+        <v>28.5528907775879</v>
       </c>
       <c r="H907" t="n">
         <v>58552</v>
@@ -26701,7 +26701,7 @@
         <v>29.7199993133545</v>
       </c>
       <c r="G908" t="n">
-        <v>28.3241634368896</v>
+        <v>28.324161529541</v>
       </c>
       <c r="H908" t="n">
         <v>39355</v>
@@ -26759,7 +26759,7 @@
         <v>28.7800006866455</v>
       </c>
       <c r="G910" t="n">
-        <v>27.4283103942871</v>
+        <v>27.4283123016357</v>
       </c>
       <c r="H910" t="n">
         <v>52028</v>
@@ -26788,7 +26788,7 @@
         <v>28.6399993896484</v>
       </c>
       <c r="G911" t="n">
-        <v>27.2948818206787</v>
+        <v>27.2948837280273</v>
       </c>
       <c r="H911" t="n">
         <v>41123</v>
@@ -26817,7 +26817,7 @@
         <v>28.7600002288818</v>
       </c>
       <c r="G912" t="n">
-        <v>27.4092483520508</v>
+        <v>27.4092502593994</v>
       </c>
       <c r="H912" t="n">
         <v>65212</v>
@@ -26846,7 +26846,7 @@
         <v>28.1399993896484</v>
       </c>
       <c r="G913" t="n">
-        <v>26.8183670043945</v>
+        <v>26.8183689117432</v>
       </c>
       <c r="H913" t="n">
         <v>65952</v>
@@ -26875,7 +26875,7 @@
         <v>27.9200000762939</v>
       </c>
       <c r="G914" t="n">
-        <v>26.6087017059326</v>
+        <v>26.608699798584</v>
       </c>
       <c r="H914" t="n">
         <v>91862</v>
@@ -26962,7 +26962,7 @@
         <v>28.5400009155273</v>
       </c>
       <c r="G917" t="n">
-        <v>27.1995830535889</v>
+        <v>27.1995811462402</v>
       </c>
       <c r="H917" t="n">
         <v>35252</v>
@@ -26991,7 +26991,7 @@
         <v>28.1800003051758</v>
       </c>
       <c r="G918" t="n">
-        <v>26.8564891815186</v>
+        <v>26.8564910888672</v>
       </c>
       <c r="H918" t="n">
         <v>39931</v>
@@ -27020,7 +27020,7 @@
         <v>27.9200000762939</v>
       </c>
       <c r="G919" t="n">
-        <v>26.6087017059326</v>
+        <v>26.608699798584</v>
       </c>
       <c r="H919" t="n">
         <v>28115</v>
@@ -27049,7 +27049,7 @@
         <v>28.1800003051758</v>
       </c>
       <c r="G920" t="n">
-        <v>26.8564891815186</v>
+        <v>26.8564910888672</v>
       </c>
       <c r="H920" t="n">
         <v>52458</v>
@@ -27107,7 +27107,7 @@
         <v>27.4599990844727</v>
       </c>
       <c r="G922" t="n">
-        <v>26.1703071594238</v>
+        <v>26.1703052520752</v>
       </c>
       <c r="H922" t="n">
         <v>43546</v>
@@ -27165,7 +27165,7 @@
         <v>28.8799991607666</v>
       </c>
       <c r="G924" t="n">
-        <v>27.5236148834229</v>
+        <v>27.5236129760742</v>
       </c>
       <c r="H924" t="n">
         <v>63306</v>
@@ -27194,7 +27194,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G925" t="n">
-        <v>28.2097969055176</v>
+        <v>28.2097988128662</v>
       </c>
       <c r="H925" t="n">
         <v>50335</v>
@@ -27223,7 +27223,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G926" t="n">
-        <v>28.2097969055176</v>
+        <v>28.2097988128662</v>
       </c>
       <c r="H926" t="n">
         <v>62035</v>
@@ -27252,7 +27252,7 @@
         <v>29.2600002288818</v>
       </c>
       <c r="G927" t="n">
-        <v>27.8857669830322</v>
+        <v>27.8857650756836</v>
       </c>
       <c r="H927" t="n">
         <v>40065</v>
@@ -27397,7 +27397,7 @@
         <v>28.2399997711182</v>
       </c>
       <c r="G932" t="n">
-        <v>26.9136714935303</v>
+        <v>26.9136695861816</v>
       </c>
       <c r="H932" t="n">
         <v>115149</v>
@@ -27484,7 +27484,7 @@
         <v>28.1399993896484</v>
       </c>
       <c r="G935" t="n">
-        <v>26.8183670043945</v>
+        <v>26.8183689117432</v>
       </c>
       <c r="H935" t="n">
         <v>80482</v>
@@ -27542,7 +27542,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G937" t="n">
-        <v>27.0661544799805</v>
+        <v>27.0661563873291</v>
       </c>
       <c r="H937" t="n">
         <v>96364</v>
@@ -27571,7 +27571,7 @@
         <v>28.8400001525879</v>
       </c>
       <c r="G938" t="n">
-        <v>27.4854907989502</v>
+        <v>27.4854927062988</v>
       </c>
       <c r="H938" t="n">
         <v>148644</v>
@@ -27629,7 +27629,7 @@
         <v>29.3199996948242</v>
       </c>
       <c r="G940" t="n">
-        <v>27.9429473876953</v>
+        <v>27.9429492950439</v>
       </c>
       <c r="H940" t="n">
         <v>83855</v>
@@ -27658,7 +27658,7 @@
         <v>29</v>
       </c>
       <c r="G941" t="n">
-        <v>27.6379776000977</v>
+        <v>27.637975692749</v>
       </c>
       <c r="H941" t="n">
         <v>55503</v>
@@ -27687,7 +27687,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G942" t="n">
-        <v>27.7332801818848</v>
+        <v>27.7332820892334</v>
       </c>
       <c r="H942" t="n">
         <v>38249</v>
@@ -27745,7 +27745,7 @@
         <v>28.0599994659424</v>
       </c>
       <c r="G944" t="n">
-        <v>26.7421245574951</v>
+        <v>26.7421264648438</v>
       </c>
       <c r="H944" t="n">
         <v>51408</v>
@@ -27803,7 +27803,7 @@
         <v>27.9200000762939</v>
       </c>
       <c r="G946" t="n">
-        <v>26.6087017059326</v>
+        <v>26.608699798584</v>
       </c>
       <c r="H946" t="n">
         <v>57557</v>
@@ -27832,7 +27832,7 @@
         <v>27.9599990844727</v>
       </c>
       <c r="G947" t="n">
-        <v>26.646821975708</v>
+        <v>26.6468181610107</v>
       </c>
       <c r="H947" t="n">
         <v>65133</v>
@@ -27861,7 +27861,7 @@
         <v>27.9599990844727</v>
       </c>
       <c r="G948" t="n">
-        <v>26.646821975708</v>
+        <v>26.6468181610107</v>
       </c>
       <c r="H948" t="n">
         <v>50142</v>
@@ -28006,7 +28006,7 @@
         <v>28.5799999237061</v>
       </c>
       <c r="G953" t="n">
-        <v>27.2377033233643</v>
+        <v>27.2377014160156</v>
       </c>
       <c r="H953" t="n">
         <v>57862</v>
@@ -28035,7 +28035,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G954" t="n">
-        <v>27.2567653656006</v>
+        <v>27.256763458252</v>
       </c>
       <c r="H954" t="n">
         <v>101950</v>
@@ -28064,7 +28064,7 @@
         <v>28.1399993896484</v>
       </c>
       <c r="G955" t="n">
-        <v>26.8183670043945</v>
+        <v>26.8183689117432</v>
       </c>
       <c r="H955" t="n">
         <v>130394</v>
@@ -28093,7 +28093,7 @@
         <v>28.6800003051758</v>
       </c>
       <c r="G956" t="n">
-        <v>27.3330078125</v>
+        <v>27.3330097198486</v>
       </c>
       <c r="H956" t="n">
         <v>123467</v>
@@ -28267,7 +28267,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G962" t="n">
-        <v>25.5413017272949</v>
+        <v>25.5412998199463</v>
       </c>
       <c r="H962" t="n">
         <v>161606</v>
@@ -28325,7 +28325,7 @@
         <v>28.2800006866455</v>
       </c>
       <c r="G964" t="n">
-        <v>26.9517955780029</v>
+        <v>26.9517936706543</v>
       </c>
       <c r="H964" t="n">
         <v>840056</v>
@@ -28383,7 +28383,7 @@
         <v>28.4400005340576</v>
       </c>
       <c r="G966" t="n">
-        <v>27.1042804718018</v>
+        <v>27.1042785644531</v>
       </c>
       <c r="H966" t="n">
         <v>138480</v>
@@ -28499,7 +28499,7 @@
         <v>26.7199993133545</v>
       </c>
       <c r="G970" t="n">
-        <v>25.4650573730469</v>
+        <v>25.4650611877441</v>
       </c>
       <c r="H970" t="n">
         <v>187321</v>
@@ -28586,7 +28586,7 @@
         <v>28.7399997711182</v>
       </c>
       <c r="G973" t="n">
-        <v>27.3901901245117</v>
+        <v>27.3901882171631</v>
       </c>
       <c r="H973" t="n">
         <v>196336</v>
@@ -28644,7 +28644,7 @@
         <v>27.9599990844727</v>
       </c>
       <c r="G975" t="n">
-        <v>26.646821975708</v>
+        <v>26.6468181610107</v>
       </c>
       <c r="H975" t="n">
         <v>111654</v>
@@ -28702,7 +28702,7 @@
         <v>28.8400001525879</v>
       </c>
       <c r="G977" t="n">
-        <v>27.4854907989502</v>
+        <v>27.4854927062988</v>
       </c>
       <c r="H977" t="n">
         <v>93603</v>
@@ -28760,7 +28760,7 @@
         <v>28.7399997711182</v>
       </c>
       <c r="G979" t="n">
-        <v>27.3901901245117</v>
+        <v>27.3901882171631</v>
       </c>
       <c r="H979" t="n">
         <v>130955</v>
@@ -28876,7 +28876,7 @@
         <v>29.9799995422363</v>
       </c>
       <c r="G983" t="n">
-        <v>28.571949005127</v>
+        <v>28.5719509124756</v>
       </c>
       <c r="H983" t="n">
         <v>217359</v>
@@ -29050,7 +29050,7 @@
         <v>29.8600006103516</v>
       </c>
       <c r="G989" t="n">
-        <v>28.4575862884521</v>
+        <v>28.4575843811035</v>
       </c>
       <c r="H989" t="n">
         <v>70096</v>
@@ -29108,7 +29108,7 @@
         <v>29.6200008392334</v>
       </c>
       <c r="G991" t="n">
-        <v>28.2288589477539</v>
+        <v>28.2288570404053</v>
       </c>
       <c r="H991" t="n">
         <v>48636</v>
@@ -29224,7 +29224,7 @@
         <v>33.0800018310547</v>
       </c>
       <c r="G995" t="n">
-        <v>31.5263595581055</v>
+        <v>31.5263576507568</v>
       </c>
       <c r="H995" t="n">
         <v>331354</v>
@@ -29282,7 +29282,7 @@
         <v>33.6199989318848</v>
       </c>
       <c r="G997" t="n">
-        <v>32.0409889221191</v>
+        <v>32.0409851074219</v>
       </c>
       <c r="H997" t="n">
         <v>132474</v>
@@ -29369,7 +29369,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G1000" t="n">
-        <v>30.7829895019531</v>
+        <v>30.7829875946045</v>
       </c>
       <c r="H1000" t="n">
         <v>52091</v>
@@ -29398,7 +29398,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G1001" t="n">
-        <v>31.2595062255859</v>
+        <v>31.2595024108887</v>
       </c>
       <c r="H1001" t="n">
         <v>92461</v>
@@ -29514,7 +29514,7 @@
         <v>32.1599998474121</v>
       </c>
       <c r="G1005" t="n">
-        <v>30.649564743042</v>
+        <v>30.6495666503906</v>
       </c>
       <c r="H1005" t="n">
         <v>38088</v>
@@ -29601,7 +29601,7 @@
         <v>32.2400016784668</v>
       </c>
       <c r="G1008" t="n">
-        <v>30.72580909729</v>
+        <v>30.7258071899414</v>
       </c>
       <c r="H1008" t="n">
         <v>48986</v>
@@ -29717,7 +29717,7 @@
         <v>31.9200000762939</v>
       </c>
       <c r="G1012" t="n">
-        <v>30.4208335876465</v>
+        <v>30.4208374023438</v>
       </c>
       <c r="H1012" t="n">
         <v>79954</v>
@@ -29804,7 +29804,7 @@
         <v>31.5599994659424</v>
       </c>
       <c r="G1015" t="n">
-        <v>30.0777416229248</v>
+        <v>30.0777435302734</v>
       </c>
       <c r="H1015" t="n">
         <v>38656</v>
@@ -29949,7 +29949,7 @@
         <v>34.560001373291</v>
       </c>
       <c r="G1020" t="n">
-        <v>32.9368438720703</v>
+        <v>32.9368476867676</v>
       </c>
       <c r="H1020" t="n">
         <v>233304</v>
@@ -29978,7 +29978,7 @@
         <v>35.1199989318848</v>
       </c>
       <c r="G1021" t="n">
-        <v>33.4705429077148</v>
+        <v>33.4705390930176</v>
       </c>
       <c r="H1021" t="n">
         <v>121933</v>
@@ -30007,7 +30007,7 @@
         <v>35.0999984741211</v>
       </c>
       <c r="G1022" t="n">
-        <v>33.4514808654785</v>
+        <v>33.4514770507812</v>
       </c>
       <c r="H1022" t="n">
         <v>95929</v>
@@ -30065,7 +30065,7 @@
         <v>36.2799987792969</v>
       </c>
       <c r="G1024" t="n">
-        <v>34.5760650634766</v>
+        <v>34.5760612487793</v>
       </c>
       <c r="H1024" t="n">
         <v>135765</v>
@@ -30210,7 +30210,7 @@
         <v>36.9799995422363</v>
       </c>
       <c r="G1029" t="n">
-        <v>35.2431907653809</v>
+        <v>35.2431869506836</v>
       </c>
       <c r="H1029" t="n">
         <v>232388</v>
@@ -30268,7 +30268,7 @@
         <v>36.2400016784668</v>
       </c>
       <c r="G1031" t="n">
-        <v>34.5379447937012</v>
+        <v>34.5379409790039</v>
       </c>
       <c r="H1031" t="n">
         <v>163954</v>
@@ -30297,7 +30297,7 @@
         <v>36.2799987792969</v>
       </c>
       <c r="G1032" t="n">
-        <v>34.5760650634766</v>
+        <v>34.5760612487793</v>
       </c>
       <c r="H1032" t="n">
         <v>79914</v>
@@ -30355,7 +30355,7 @@
         <v>34.2200012207031</v>
       </c>
       <c r="G1034" t="n">
-        <v>32.6128158569336</v>
+        <v>32.6128196716309</v>
       </c>
       <c r="H1034" t="n">
         <v>96283</v>
@@ -30442,7 +30442,7 @@
         <v>32.8199996948242</v>
       </c>
       <c r="G1037" t="n">
-        <v>31.2785663604736</v>
+        <v>31.2785625457764</v>
       </c>
       <c r="H1037" t="n">
         <v>113273</v>
@@ -30471,7 +30471,7 @@
         <v>33.0200004577637</v>
       </c>
       <c r="G1038" t="n">
-        <v>31.4691734313965</v>
+        <v>31.4691753387451</v>
       </c>
       <c r="H1038" t="n">
         <v>48314</v>
@@ -30500,7 +30500,7 @@
         <v>33.5200004577637</v>
       </c>
       <c r="G1039" t="n">
-        <v>31.9456901550293</v>
+        <v>31.9456939697266</v>
       </c>
       <c r="H1039" t="n">
         <v>154526</v>
@@ -30529,7 +30529,7 @@
         <v>34.5800018310547</v>
       </c>
       <c r="G1040" t="n">
-        <v>32.9559059143066</v>
+        <v>32.9559097290039</v>
       </c>
       <c r="H1040" t="n">
         <v>159760</v>
@@ -30558,7 +30558,7 @@
         <v>34.0200004577637</v>
       </c>
       <c r="G1041" t="n">
-        <v>32.4222068786621</v>
+        <v>32.4222030639648</v>
       </c>
       <c r="H1041" t="n">
         <v>196653</v>
@@ -30587,7 +30587,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G1042" t="n">
-        <v>31.2595062255859</v>
+        <v>31.2595024108887</v>
       </c>
       <c r="H1042" t="n">
         <v>106030</v>
@@ -30674,7 +30674,7 @@
         <v>34</v>
       </c>
       <c r="G1045" t="n">
-        <v>32.4031448364258</v>
+        <v>32.4031410217285</v>
       </c>
       <c r="H1045" t="n">
         <v>76602</v>
@@ -30848,7 +30848,7 @@
         <v>33.8800010681152</v>
       </c>
       <c r="G1051" t="n">
-        <v>32.2887802124023</v>
+        <v>32.2887840270996</v>
       </c>
       <c r="H1051" t="n">
         <v>112720</v>
@@ -30877,7 +30877,7 @@
         <v>33.0800018310547</v>
       </c>
       <c r="G1052" t="n">
-        <v>31.5263595581055</v>
+        <v>31.5263576507568</v>
       </c>
       <c r="H1052" t="n">
         <v>46250</v>
@@ -30906,7 +30906,7 @@
         <v>32.1599998474121</v>
       </c>
       <c r="G1053" t="n">
-        <v>30.649564743042</v>
+        <v>30.6495666503906</v>
       </c>
       <c r="H1053" t="n">
         <v>301162</v>
@@ -30935,7 +30935,7 @@
         <v>30.4400005340576</v>
       </c>
       <c r="G1054" t="n">
-        <v>29.0103435516357</v>
+        <v>29.0103454589844</v>
       </c>
       <c r="H1054" t="n">
         <v>211581</v>
@@ -31022,7 +31022,7 @@
         <v>30</v>
       </c>
       <c r="G1057" t="n">
-        <v>28.5910110473633</v>
+        <v>28.5910129547119</v>
       </c>
       <c r="H1057" t="n">
         <v>228697</v>
@@ -31080,7 +31080,7 @@
         <v>30.8400001525879</v>
       </c>
       <c r="G1059" t="n">
-        <v>29.3915615081787</v>
+        <v>29.3915596008301</v>
       </c>
       <c r="H1059" t="n">
         <v>169966</v>
@@ -31109,7 +31109,7 @@
         <v>31.0799999237061</v>
       </c>
       <c r="G1060" t="n">
-        <v>29.6202850341797</v>
+        <v>29.6202869415283</v>
       </c>
       <c r="H1060" t="n">
         <v>158118</v>
@@ -31138,7 +31138,7 @@
         <v>29.6800003051758</v>
       </c>
       <c r="G1061" t="n">
-        <v>28.2860412597656</v>
+        <v>28.286039352417</v>
       </c>
       <c r="H1061" t="n">
         <v>107813</v>
@@ -31196,7 +31196,7 @@
         <v>26.9599990844727</v>
       </c>
       <c r="G1063" t="n">
-        <v>25.6937885284424</v>
+        <v>25.6937866210938</v>
       </c>
       <c r="H1063" t="n">
         <v>251128</v>
@@ -31312,7 +31312,7 @@
         <v>26.9599990844727</v>
       </c>
       <c r="G1067" t="n">
-        <v>25.6937885284424</v>
+        <v>25.6937866210938</v>
       </c>
       <c r="H1067" t="n">
         <v>374254</v>
@@ -31341,7 +31341,7 @@
         <v>26.9599990844727</v>
       </c>
       <c r="G1068" t="n">
-        <v>25.6937885284424</v>
+        <v>25.6937866210938</v>
       </c>
       <c r="H1068" t="n">
         <v>294084</v>
@@ -31399,7 +31399,7 @@
         <v>27.0599994659424</v>
       </c>
       <c r="G1070" t="n">
-        <v>25.7890911102295</v>
+        <v>25.7890930175781</v>
       </c>
       <c r="H1070" t="n">
         <v>78053</v>
@@ -31428,7 +31428,7 @@
         <v>25.4200000762939</v>
       </c>
       <c r="G1071" t="n">
-        <v>24.2261180877686</v>
+        <v>24.2261161804199</v>
       </c>
       <c r="H1071" t="n">
         <v>166693</v>
@@ -31515,7 +31515,7 @@
         <v>26.1800003051758</v>
       </c>
       <c r="G1074" t="n">
-        <v>24.9504222869873</v>
+        <v>24.9504241943359</v>
       </c>
       <c r="H1074" t="n">
         <v>191065</v>
@@ -31631,7 +31631,7 @@
         <v>26</v>
       </c>
       <c r="G1078" t="n">
-        <v>24.7788772583008</v>
+        <v>24.7788753509521</v>
       </c>
       <c r="H1078" t="n">
         <v>70176</v>
@@ -31689,7 +31689,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1080" t="n">
-        <v>26.4943351745605</v>
+        <v>26.4943370819092</v>
       </c>
       <c r="H1080" t="n">
         <v>75696</v>
@@ -31747,7 +31747,7 @@
         <v>25.6800003051758</v>
       </c>
       <c r="G1082" t="n">
-        <v>24.4739036560059</v>
+        <v>24.4739055633545</v>
       </c>
       <c r="H1082" t="n">
         <v>122811</v>
@@ -31776,7 +31776,7 @@
         <v>24.6800003051758</v>
       </c>
       <c r="G1083" t="n">
-        <v>23.5208721160889</v>
+        <v>23.5208702087402</v>
       </c>
       <c r="H1083" t="n">
         <v>173158</v>
@@ -31834,7 +31834,7 @@
         <v>24.8199996948242</v>
       </c>
       <c r="G1085" t="n">
-        <v>23.6542987823486</v>
+        <v>23.654296875</v>
       </c>
       <c r="H1085" t="n">
         <v>67794</v>
@@ -31892,7 +31892,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G1087" t="n">
-        <v>24.5882682800293</v>
+        <v>24.5882663726807</v>
       </c>
       <c r="H1087" t="n">
         <v>125440</v>
@@ -31921,7 +31921,7 @@
         <v>25.9400005340576</v>
       </c>
       <c r="G1088" t="n">
-        <v>24.7216968536377</v>
+        <v>24.7216949462891</v>
       </c>
       <c r="H1088" t="n">
         <v>117443</v>
@@ -31979,7 +31979,7 @@
         <v>27.3400001525879</v>
       </c>
       <c r="G1090" t="n">
-        <v>26.0559425354004</v>
+        <v>26.0559406280518</v>
       </c>
       <c r="H1090" t="n">
         <v>64848</v>
@@ -32008,7 +32008,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G1091" t="n">
-        <v>27.0661544799805</v>
+        <v>27.0661563873291</v>
       </c>
       <c r="H1091" t="n">
         <v>63854</v>
@@ -32095,7 +32095,7 @@
         <v>28.7399997711182</v>
       </c>
       <c r="G1094" t="n">
-        <v>27.3901901245117</v>
+        <v>27.3901882171631</v>
       </c>
       <c r="H1094" t="n">
         <v>66015</v>
@@ -32124,7 +32124,7 @@
         <v>28.8199996948242</v>
       </c>
       <c r="G1095" t="n">
-        <v>27.4664287567139</v>
+        <v>27.4664306640625</v>
       </c>
       <c r="H1095" t="n">
         <v>34130</v>
@@ -32153,7 +32153,7 @@
         <v>29.1000003814697</v>
       </c>
       <c r="G1096" t="n">
-        <v>27.7332801818848</v>
+        <v>27.7332820892334</v>
       </c>
       <c r="H1096" t="n">
         <v>63490</v>
@@ -32211,7 +32211,7 @@
         <v>28.7800006866455</v>
       </c>
       <c r="G1098" t="n">
-        <v>27.4283103942871</v>
+        <v>27.4283123016357</v>
       </c>
       <c r="H1098" t="n">
         <v>40542</v>
@@ -32240,7 +32240,7 @@
         <v>29.3799991607666</v>
       </c>
       <c r="G1099" t="n">
-        <v>28.000129699707</v>
+        <v>28.0001316070557</v>
       </c>
       <c r="H1099" t="n">
         <v>64098</v>
@@ -32298,7 +32298,7 @@
         <v>27.4599990844727</v>
       </c>
       <c r="G1101" t="n">
-        <v>26.1703071594238</v>
+        <v>26.1703052520752</v>
       </c>
       <c r="H1101" t="n">
         <v>65475</v>
@@ -32414,7 +32414,7 @@
         <v>26.6399993896484</v>
       </c>
       <c r="G1105" t="n">
-        <v>25.3888206481934</v>
+        <v>25.3888187408447</v>
       </c>
       <c r="H1105" t="n">
         <v>62416</v>
@@ -32443,7 +32443,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1106" t="n">
-        <v>25.5413017272949</v>
+        <v>25.5412998199463</v>
       </c>
       <c r="H1106" t="n">
         <v>38576</v>
@@ -32501,7 +32501,7 @@
         <v>26.5</v>
       </c>
       <c r="G1108" t="n">
-        <v>25.2553939819336</v>
+        <v>25.255392074585</v>
       </c>
       <c r="H1108" t="n">
         <v>58650</v>
@@ -32530,7 +32530,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1109" t="n">
-        <v>25.5413017272949</v>
+        <v>25.5412998199463</v>
       </c>
       <c r="H1109" t="n">
         <v>60542</v>
@@ -32588,7 +32588,7 @@
         <v>27.5</v>
       </c>
       <c r="G1111" t="n">
-        <v>26.2084255218506</v>
+        <v>26.2084274291992</v>
       </c>
       <c r="H1111" t="n">
         <v>148283</v>
@@ -32617,7 +32617,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1112" t="n">
-        <v>26.5896415710449</v>
+        <v>26.5896396636963</v>
       </c>
       <c r="H1112" t="n">
         <v>91229</v>
@@ -32675,7 +32675,7 @@
         <v>26.8199996948242</v>
       </c>
       <c r="G1114" t="n">
-        <v>25.5603618621826</v>
+        <v>25.5603637695312</v>
       </c>
       <c r="H1114" t="n">
         <v>244809</v>
@@ -32762,7 +32762,7 @@
         <v>27.3199996948242</v>
       </c>
       <c r="G1117" t="n">
-        <v>26.0368804931641</v>
+        <v>26.0368785858154</v>
       </c>
       <c r="H1117" t="n">
         <v>71913</v>
@@ -32791,7 +32791,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G1118" t="n">
-        <v>28.2097969055176</v>
+        <v>28.2097988128662</v>
       </c>
       <c r="H1118" t="n">
         <v>213940</v>
@@ -32820,7 +32820,7 @@
         <v>29.2600002288818</v>
       </c>
       <c r="G1119" t="n">
-        <v>27.8857669830322</v>
+        <v>27.8857650756836</v>
       </c>
       <c r="H1119" t="n">
         <v>133951</v>
@@ -32849,7 +32849,7 @@
         <v>29.0200004577637</v>
       </c>
       <c r="G1120" t="n">
-        <v>27.657039642334</v>
+        <v>27.6570377349854</v>
       </c>
       <c r="H1120" t="n">
         <v>102691</v>
@@ -32878,7 +32878,7 @@
         <v>29.9799995422363</v>
       </c>
       <c r="G1121" t="n">
-        <v>28.571949005127</v>
+        <v>28.5719509124756</v>
       </c>
       <c r="H1121" t="n">
         <v>127065</v>
@@ -32936,7 +32936,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1123" t="n">
-        <v>29.639347076416</v>
+        <v>29.6393451690674</v>
       </c>
       <c r="H1123" t="n">
         <v>428781</v>
@@ -32965,7 +32965,7 @@
         <v>33.439998626709</v>
       </c>
       <c r="G1124" t="n">
-        <v>31.869441986084</v>
+        <v>31.8694458007812</v>
       </c>
       <c r="H1124" t="n">
         <v>328700</v>
@@ -33023,7 +33023,7 @@
         <v>31.0799999237061</v>
       </c>
       <c r="G1126" t="n">
-        <v>29.6202850341797</v>
+        <v>29.6202869415283</v>
       </c>
       <c r="H1126" t="n">
         <v>158897</v>
@@ -33081,7 +33081,7 @@
         <v>29.3199996948242</v>
       </c>
       <c r="G1128" t="n">
-        <v>27.9429473876953</v>
+        <v>27.9429492950439</v>
       </c>
       <c r="H1128" t="n">
         <v>132062</v>
@@ -33110,7 +33110,7 @@
         <v>29.0799999237061</v>
       </c>
       <c r="G1129" t="n">
-        <v>27.7142219543457</v>
+        <v>27.7142200469971</v>
       </c>
       <c r="H1129" t="n">
         <v>182805</v>
@@ -33139,7 +33139,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G1130" t="n">
-        <v>26.9708518981934</v>
+        <v>26.970853805542</v>
       </c>
       <c r="H1130" t="n">
         <v>236210</v>
@@ -33168,7 +33168,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1131" t="n">
-        <v>27.2567653656006</v>
+        <v>27.256763458252</v>
       </c>
       <c r="H1131" t="n">
         <v>140499</v>
@@ -33226,7 +33226,7 @@
         <v>28.5599994659424</v>
       </c>
       <c r="G1133" t="n">
-        <v>27.2186431884766</v>
+        <v>27.2186412811279</v>
       </c>
       <c r="H1133" t="n">
         <v>75733</v>
@@ -33429,7 +33429,7 @@
         <v>26.2999992370605</v>
       </c>
       <c r="G1140" t="n">
-        <v>25.0647869110107</v>
+        <v>25.0647850036621</v>
       </c>
       <c r="H1140" t="n">
         <v>91766</v>
@@ -33487,7 +33487,7 @@
         <v>25.2800006866455</v>
       </c>
       <c r="G1142" t="n">
-        <v>24.0926933288574</v>
+        <v>24.0926914215088</v>
       </c>
       <c r="H1142" t="n">
         <v>247776</v>
@@ -33516,7 +33516,7 @@
         <v>25.3600006103516</v>
       </c>
       <c r="G1143" t="n">
-        <v>24.1689338684082</v>
+        <v>24.1689357757568</v>
       </c>
       <c r="H1143" t="n">
         <v>168864</v>
@@ -33545,7 +33545,7 @@
         <v>25.5400009155273</v>
       </c>
       <c r="G1144" t="n">
-        <v>24.3404808044434</v>
+        <v>24.340482711792</v>
       </c>
       <c r="H1144" t="n">
         <v>69506</v>
@@ -33574,7 +33574,7 @@
         <v>25.1200008392334</v>
       </c>
       <c r="G1145" t="n">
-        <v>23.94020652771</v>
+        <v>23.9402084350586</v>
       </c>
       <c r="H1145" t="n">
         <v>151299</v>
@@ -33603,7 +33603,7 @@
         <v>25.1599998474121</v>
       </c>
       <c r="G1146" t="n">
-        <v>23.978328704834</v>
+        <v>23.9783267974854</v>
       </c>
       <c r="H1146" t="n">
         <v>161680</v>
@@ -33690,7 +33690,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G1149" t="n">
-        <v>24.0164489746094</v>
+        <v>24.016450881958</v>
       </c>
       <c r="H1149" t="n">
         <v>302963</v>
@@ -33748,7 +33748,7 @@
         <v>25.1599998474121</v>
       </c>
       <c r="G1151" t="n">
-        <v>23.978328704834</v>
+        <v>23.9783267974854</v>
       </c>
       <c r="H1151" t="n">
         <v>113319</v>
@@ -33864,7 +33864,7 @@
         <v>25</v>
       </c>
       <c r="G1155" t="n">
-        <v>23.8258438110352</v>
+        <v>23.8258419036865</v>
       </c>
       <c r="H1155" t="n">
         <v>74398</v>
@@ -33922,7 +33922,7 @@
         <v>24.8999996185303</v>
       </c>
       <c r="G1157" t="n">
-        <v>23.7305374145508</v>
+        <v>23.730541229248</v>
       </c>
       <c r="H1157" t="n">
         <v>64924</v>
@@ -34009,7 +34009,7 @@
         <v>24.2199993133545</v>
       </c>
       <c r="G1160" t="n">
-        <v>23.0824737548828</v>
+        <v>23.0824756622314</v>
       </c>
       <c r="H1160" t="n">
         <v>91810</v>
@@ -34067,7 +34067,7 @@
         <v>24.6200008392334</v>
       </c>
       <c r="G1162" t="n">
-        <v>23.4636898040771</v>
+        <v>23.4636917114258</v>
       </c>
       <c r="H1162" t="n">
         <v>75630</v>
@@ -34096,7 +34096,7 @@
         <v>24.4400005340576</v>
       </c>
       <c r="G1163" t="n">
-        <v>23.292142868042</v>
+        <v>23.2921447753906</v>
       </c>
       <c r="H1163" t="n">
         <v>69021</v>
@@ -34125,7 +34125,7 @@
         <v>24.6399993896484</v>
       </c>
       <c r="G1164" t="n">
-        <v>23.4827499389648</v>
+        <v>23.4827480316162</v>
       </c>
       <c r="H1164" t="n">
         <v>148705</v>
@@ -34212,7 +34212,7 @@
         <v>25.9799995422363</v>
       </c>
       <c r="G1167" t="n">
-        <v>24.7598152160645</v>
+        <v>24.7598133087158</v>
       </c>
       <c r="H1167" t="n">
         <v>277635</v>
@@ -34241,7 +34241,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G1168" t="n">
-        <v>24.5882682800293</v>
+        <v>24.5882663726807</v>
       </c>
       <c r="H1168" t="n">
         <v>237909</v>
@@ -34270,7 +34270,7 @@
         <v>25</v>
       </c>
       <c r="G1169" t="n">
-        <v>23.8258438110352</v>
+        <v>23.8258419036865</v>
       </c>
       <c r="H1169" t="n">
         <v>140861</v>
@@ -34444,7 +34444,7 @@
         <v>27.0200004577637</v>
       </c>
       <c r="G1175" t="n">
-        <v>25.7509689331055</v>
+        <v>25.7509708404541</v>
       </c>
       <c r="H1175" t="n">
         <v>92845</v>
@@ -34502,7 +34502,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G1177" t="n">
-        <v>24.5882682800293</v>
+        <v>24.5882663726807</v>
       </c>
       <c r="H1177" t="n">
         <v>119570</v>
@@ -34560,7 +34560,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G1179" t="n">
-        <v>24.0164489746094</v>
+        <v>24.016450881958</v>
       </c>
       <c r="H1179" t="n">
         <v>42190</v>
@@ -34647,7 +34647,7 @@
         <v>26</v>
       </c>
       <c r="G1182" t="n">
-        <v>24.7788772583008</v>
+        <v>24.7788753509521</v>
       </c>
       <c r="H1182" t="n">
         <v>110610</v>
@@ -34676,7 +34676,7 @@
         <v>26.0200004577637</v>
       </c>
       <c r="G1183" t="n">
-        <v>24.7979354858398</v>
+        <v>24.7979373931885</v>
       </c>
       <c r="H1183" t="n">
         <v>67893</v>
@@ -34705,7 +34705,7 @@
         <v>25.8400001525879</v>
       </c>
       <c r="G1184" t="n">
-        <v>24.626392364502</v>
+        <v>24.6263904571533</v>
       </c>
       <c r="H1184" t="n">
         <v>372331</v>
@@ -34792,7 +34792,7 @@
         <v>25.7000007629395</v>
       </c>
       <c r="G1187" t="n">
-        <v>24.4929656982422</v>
+        <v>24.4929676055908</v>
       </c>
       <c r="H1187" t="n">
         <v>99029</v>
@@ -34879,7 +34879,7 @@
         <v>25.9799995422363</v>
       </c>
       <c r="G1190" t="n">
-        <v>24.7598152160645</v>
+        <v>24.7598133087158</v>
       </c>
       <c r="H1190" t="n">
         <v>35557</v>
@@ -34966,7 +34966,7 @@
         <v>25.2800006866455</v>
       </c>
       <c r="G1193" t="n">
-        <v>24.0926933288574</v>
+        <v>24.0926914215088</v>
       </c>
       <c r="H1193" t="n">
         <v>88485</v>
@@ -35053,7 +35053,7 @@
         <v>26.9599990844727</v>
       </c>
       <c r="G1196" t="n">
-        <v>25.6937885284424</v>
+        <v>25.6937866210938</v>
       </c>
       <c r="H1196" t="n">
         <v>207237</v>
@@ -35111,7 +35111,7 @@
         <v>27.7199993133545</v>
       </c>
       <c r="G1198" t="n">
-        <v>26.4180927276611</v>
+        <v>26.4180946350098</v>
       </c>
       <c r="H1198" t="n">
         <v>95199</v>
@@ -35140,7 +35140,7 @@
         <v>27.1599998474121</v>
       </c>
       <c r="G1199" t="n">
-        <v>25.8843936920166</v>
+        <v>25.8843955993652</v>
       </c>
       <c r="H1199" t="n">
         <v>129339</v>
@@ -35169,7 +35169,7 @@
         <v>26.0200004577637</v>
       </c>
       <c r="G1200" t="n">
-        <v>24.7979354858398</v>
+        <v>24.7979373931885</v>
       </c>
       <c r="H1200" t="n">
         <v>91247</v>
@@ -35285,7 +35285,7 @@
         <v>25.3400001525879</v>
       </c>
       <c r="G1204" t="n">
-        <v>24.1498737335205</v>
+        <v>24.1498718261719</v>
       </c>
       <c r="H1204" t="n">
         <v>150658</v>
@@ -35314,7 +35314,7 @@
         <v>26.1399993896484</v>
       </c>
       <c r="G1205" t="n">
-        <v>24.9123001098633</v>
+        <v>24.9123020172119</v>
       </c>
       <c r="H1205" t="n">
         <v>93518</v>
@@ -35517,7 +35517,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1212" t="n">
-        <v>26.5896415710449</v>
+        <v>26.5896396636963</v>
       </c>
       <c r="H1212" t="n">
         <v>79212</v>
@@ -35604,7 +35604,7 @@
         <v>27.5599994659424</v>
       </c>
       <c r="G1215" t="n">
-        <v>26.2656078338623</v>
+        <v>26.2656097412109</v>
       </c>
       <c r="H1215" t="n">
         <v>81019</v>
@@ -35633,7 +35633,7 @@
         <v>27.4599990844727</v>
       </c>
       <c r="G1216" t="n">
-        <v>26.1703071594238</v>
+        <v>26.1703052520752</v>
       </c>
       <c r="H1216" t="n">
         <v>72518</v>
@@ -35662,7 +35662,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1217" t="n">
-        <v>26.4943351745605</v>
+        <v>26.4943370819092</v>
       </c>
       <c r="H1217" t="n">
         <v>76117</v>
@@ -35720,7 +35720,7 @@
         <v>27.4599990844727</v>
       </c>
       <c r="G1219" t="n">
-        <v>26.1703071594238</v>
+        <v>26.1703052520752</v>
       </c>
       <c r="H1219" t="n">
         <v>156120</v>
@@ -35749,7 +35749,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1220" t="n">
-        <v>25.9225177764893</v>
+        <v>25.9225158691406</v>
       </c>
       <c r="H1220" t="n">
         <v>54546</v>
@@ -35778,7 +35778,7 @@
         <v>27.3400001525879</v>
       </c>
       <c r="G1221" t="n">
-        <v>26.0559425354004</v>
+        <v>26.0559406280518</v>
       </c>
       <c r="H1221" t="n">
         <v>42997</v>
@@ -35836,7 +35836,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1223" t="n">
-        <v>25.9225177764893</v>
+        <v>25.9225158691406</v>
       </c>
       <c r="H1223" t="n">
         <v>45131</v>
@@ -35865,7 +35865,7 @@
         <v>27.3600006103516</v>
       </c>
       <c r="G1224" t="n">
-        <v>26.0750007629395</v>
+        <v>26.0750026702881</v>
       </c>
       <c r="H1224" t="n">
         <v>35799</v>
@@ -35952,7 +35952,7 @@
         <v>26.3799991607666</v>
       </c>
       <c r="G1227" t="n">
-        <v>25.1410255432129</v>
+        <v>25.1410274505615</v>
       </c>
       <c r="H1227" t="n">
         <v>112146</v>
@@ -35981,7 +35981,7 @@
         <v>25.4400005340576</v>
       </c>
       <c r="G1228" t="n">
-        <v>24.2451782226562</v>
+        <v>24.2451801300049</v>
       </c>
       <c r="H1228" t="n">
         <v>62206</v>
@@ -36039,7 +36039,7 @@
         <v>25.6599998474121</v>
       </c>
       <c r="G1230" t="n">
-        <v>24.4548473358154</v>
+        <v>24.4548454284668</v>
       </c>
       <c r="H1230" t="n">
         <v>86901</v>
@@ -36213,7 +36213,7 @@
         <v>28.2999992370605</v>
       </c>
       <c r="G1236" t="n">
-        <v>26.9708518981934</v>
+        <v>26.970853805542</v>
       </c>
       <c r="H1236" t="n">
         <v>113799</v>
@@ -36271,7 +36271,7 @@
         <v>27.9599990844727</v>
       </c>
       <c r="G1238" t="n">
-        <v>26.646821975708</v>
+        <v>26.6468181610107</v>
       </c>
       <c r="H1238" t="n">
         <v>120983</v>
@@ -36300,7 +36300,7 @@
         <v>28.2800006866455</v>
       </c>
       <c r="G1239" t="n">
-        <v>26.9517955780029</v>
+        <v>26.9517936706543</v>
       </c>
       <c r="H1239" t="n">
         <v>166847</v>
@@ -36329,7 +36329,7 @@
         <v>29.9799995422363</v>
       </c>
       <c r="G1240" t="n">
-        <v>28.571949005127</v>
+        <v>28.5719509124756</v>
       </c>
       <c r="H1240" t="n">
         <v>191239</v>
@@ -36387,7 +36387,7 @@
         <v>31.0799999237061</v>
       </c>
       <c r="G1242" t="n">
-        <v>29.6202850341797</v>
+        <v>29.6202869415283</v>
       </c>
       <c r="H1242" t="n">
         <v>122780</v>
@@ -36416,7 +36416,7 @@
         <v>31.2199993133545</v>
       </c>
       <c r="G1243" t="n">
-        <v>29.7537117004395</v>
+        <v>29.7537136077881</v>
       </c>
       <c r="H1243" t="n">
         <v>166317</v>
@@ -36445,7 +36445,7 @@
         <v>32.9000015258789</v>
       </c>
       <c r="G1244" t="n">
-        <v>31.3548107147217</v>
+        <v>31.354808807373</v>
       </c>
       <c r="H1244" t="n">
         <v>392879</v>
@@ -36474,7 +36474,7 @@
         <v>33.2999992370605</v>
       </c>
       <c r="G1245" t="n">
-        <v>31.7360210418701</v>
+        <v>31.7360248565674</v>
       </c>
       <c r="H1245" t="n">
         <v>220738</v>
@@ -36503,7 +36503,7 @@
         <v>33.3600006103516</v>
       </c>
       <c r="G1246" t="n">
-        <v>31.7932071685791</v>
+        <v>31.7932033538818</v>
       </c>
       <c r="H1246" t="n">
         <v>179044</v>
@@ -36561,7 +36561,7 @@
         <v>33.1199989318848</v>
       </c>
       <c r="G1248" t="n">
-        <v>31.564474105835</v>
+        <v>31.5644760131836</v>
       </c>
       <c r="H1248" t="n">
         <v>79399</v>
@@ -36590,7 +36590,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G1249" t="n">
-        <v>31.5454120635986</v>
+        <v>31.5454139709473</v>
       </c>
       <c r="H1249" t="n">
         <v>74582</v>
@@ -36648,7 +36648,7 @@
         <v>33.5400009155273</v>
       </c>
       <c r="G1251" t="n">
-        <v>31.9647521972656</v>
+        <v>31.9647483825684</v>
       </c>
       <c r="H1251" t="n">
         <v>103648</v>
@@ -36735,7 +36735,7 @@
         <v>35.3800010681152</v>
       </c>
       <c r="G1254" t="n">
-        <v>33.7183303833008</v>
+        <v>33.718334197998</v>
       </c>
       <c r="H1254" t="n">
         <v>106108</v>
@@ -36764,7 +36764,7 @@
         <v>35.1399993896484</v>
       </c>
       <c r="G1255" t="n">
-        <v>33.4896011352539</v>
+        <v>33.4896049499512</v>
       </c>
       <c r="H1255" t="n">
         <v>97549</v>
@@ -36793,7 +36793,7 @@
         <v>36.2400016784668</v>
       </c>
       <c r="G1256" t="n">
-        <v>34.5379447937012</v>
+        <v>34.5379409790039</v>
       </c>
       <c r="H1256" t="n">
         <v>113207</v>
@@ -36851,7 +36851,7 @@
         <v>36.6399993896484</v>
       </c>
       <c r="G1258" t="n">
-        <v>34.9191551208496</v>
+        <v>34.9191513061523</v>
       </c>
       <c r="H1258" t="n">
         <v>156163</v>
@@ -36938,7 +36938,7 @@
         <v>36.5400009155273</v>
       </c>
       <c r="G1261" t="n">
-        <v>34.8238525390625</v>
+        <v>34.8238563537598</v>
       </c>
       <c r="H1261" t="n">
         <v>187205</v>
@@ -36967,7 +36967,7 @@
         <v>36.3800010681152</v>
       </c>
       <c r="G1262" t="n">
-        <v>34.6713638305664</v>
+        <v>34.6713676452637</v>
       </c>
       <c r="H1262" t="n">
         <v>99555</v>
@@ -36996,7 +36996,7 @@
         <v>36.2400016784668</v>
       </c>
       <c r="G1263" t="n">
-        <v>34.5379447937012</v>
+        <v>34.5379409790039</v>
       </c>
       <c r="H1263" t="n">
         <v>103103</v>
@@ -37083,7 +37083,7 @@
         <v>36.9199981689453</v>
       </c>
       <c r="G1266" t="n">
-        <v>35.1860008239746</v>
+        <v>35.1860046386719</v>
       </c>
       <c r="H1266" t="n">
         <v>77361</v>
@@ -37112,7 +37112,7 @@
         <v>36.2999992370605</v>
       </c>
       <c r="G1267" t="n">
-        <v>34.5951232910156</v>
+        <v>34.5951271057129</v>
       </c>
       <c r="H1267" t="n">
         <v>47270</v>
@@ -37141,7 +37141,7 @@
         <v>36.4799995422363</v>
       </c>
       <c r="G1268" t="n">
-        <v>34.7666702270508</v>
+        <v>34.7666664123535</v>
       </c>
       <c r="H1268" t="n">
         <v>50727</v>
@@ -37170,7 +37170,7 @@
         <v>36.2999992370605</v>
       </c>
       <c r="G1269" t="n">
-        <v>34.5951232910156</v>
+        <v>34.5951271057129</v>
       </c>
       <c r="H1269" t="n">
         <v>129323</v>
@@ -37199,7 +37199,7 @@
         <v>35.7000007629395</v>
       </c>
       <c r="G1270" t="n">
-        <v>34.0233039855957</v>
+        <v>34.0233001708984</v>
       </c>
       <c r="H1270" t="n">
         <v>91616</v>
@@ -37228,7 +37228,7 @@
         <v>35.8400001525879</v>
       </c>
       <c r="G1271" t="n">
-        <v>34.1567268371582</v>
+        <v>34.1567306518555</v>
       </c>
       <c r="H1271" t="n">
         <v>126398</v>
@@ -37257,7 +37257,7 @@
         <v>34.5800018310547</v>
       </c>
       <c r="G1272" t="n">
-        <v>32.9559059143066</v>
+        <v>32.9559097290039</v>
       </c>
       <c r="H1272" t="n">
         <v>139911</v>
@@ -37286,7 +37286,7 @@
         <v>33.4199981689453</v>
       </c>
       <c r="G1273" t="n">
-        <v>31.8503837585449</v>
+        <v>31.8503875732422</v>
       </c>
       <c r="H1273" t="n">
         <v>171180</v>
@@ -37373,7 +37373,7 @@
         <v>35.2799987792969</v>
       </c>
       <c r="G1276" t="n">
-        <v>33.6230239868164</v>
+        <v>33.6230278015137</v>
       </c>
       <c r="H1276" t="n">
         <v>318056</v>
@@ -37431,7 +37431,7 @@
         <v>35.5200004577637</v>
       </c>
       <c r="G1278" t="n">
-        <v>33.8517570495605</v>
+        <v>33.8517608642578</v>
       </c>
       <c r="H1278" t="n">
         <v>82467</v>
@@ -37460,7 +37460,7 @@
         <v>34.8600006103516</v>
       </c>
       <c r="G1279" t="n">
-        <v>33.2227554321289</v>
+        <v>33.2227516174316</v>
       </c>
       <c r="H1279" t="n">
         <v>37394</v>
@@ -37489,7 +37489,7 @@
         <v>34.1800003051758</v>
       </c>
       <c r="G1280" t="n">
-        <v>32.5746955871582</v>
+        <v>32.5746917724609</v>
       </c>
       <c r="H1280" t="n">
         <v>44618</v>
@@ -37518,7 +37518,7 @@
         <v>34.939998626709</v>
       </c>
       <c r="G1281" t="n">
-        <v>33.298999786377</v>
+        <v>33.2989959716797</v>
       </c>
       <c r="H1281" t="n">
         <v>27276</v>
@@ -37663,7 +37663,7 @@
         <v>33.5400009155273</v>
       </c>
       <c r="G1286" t="n">
-        <v>31.9647521972656</v>
+        <v>31.9647483825684</v>
       </c>
       <c r="H1286" t="n">
         <v>94928</v>
@@ -37692,7 +37692,7 @@
         <v>34.1399993896484</v>
       </c>
       <c r="G1287" t="n">
-        <v>32.5365676879883</v>
+        <v>32.5365753173828</v>
       </c>
       <c r="H1287" t="n">
         <v>36839</v>
@@ -37750,7 +37750,7 @@
         <v>34</v>
       </c>
       <c r="G1289" t="n">
-        <v>32.4031448364258</v>
+        <v>32.4031410217285</v>
       </c>
       <c r="H1289" t="n">
         <v>67031</v>
@@ -37808,7 +37808,7 @@
         <v>33.2200012207031</v>
       </c>
       <c r="G1291" t="n">
-        <v>31.6597805023193</v>
+        <v>31.659782409668</v>
       </c>
       <c r="H1291" t="n">
         <v>46416</v>
@@ -37837,7 +37837,7 @@
         <v>33.6199989318848</v>
       </c>
       <c r="G1292" t="n">
-        <v>32.0409889221191</v>
+        <v>32.0409851074219</v>
       </c>
       <c r="H1292" t="n">
         <v>96187</v>
@@ -37866,7 +37866,7 @@
         <v>33.5200004577637</v>
       </c>
       <c r="G1293" t="n">
-        <v>31.9456901550293</v>
+        <v>31.9456939697266</v>
       </c>
       <c r="H1293" t="n">
         <v>80484</v>
@@ -37982,7 +37982,7 @@
         <v>35</v>
       </c>
       <c r="G1297" t="n">
-        <v>33.3561820983887</v>
+        <v>33.3561782836914</v>
       </c>
       <c r="H1297" t="n">
         <v>66747</v>
@@ -38040,7 +38040,7 @@
         <v>35.2000007629395</v>
       </c>
       <c r="G1299" t="n">
-        <v>33.5467872619629</v>
+        <v>33.5467834472656</v>
       </c>
       <c r="H1299" t="n">
         <v>38838</v>
@@ -38127,7 +38127,7 @@
         <v>35.3199996948242</v>
       </c>
       <c r="G1302" t="n">
-        <v>33.6611557006836</v>
+        <v>33.6611480712891</v>
       </c>
       <c r="H1302" t="n">
         <v>31836</v>
@@ -38185,7 +38185,7 @@
         <v>34.1399993896484</v>
       </c>
       <c r="G1304" t="n">
-        <v>32.5365676879883</v>
+        <v>32.5365753173828</v>
       </c>
       <c r="H1304" t="n">
         <v>43294</v>
@@ -38214,7 +38214,7 @@
         <v>34.7999992370605</v>
       </c>
       <c r="G1305" t="n">
-        <v>33.1655693054199</v>
+        <v>33.1655731201172</v>
       </c>
       <c r="H1305" t="n">
         <v>42170</v>
@@ -38272,7 +38272,7 @@
         <v>34.2599983215332</v>
       </c>
       <c r="G1307" t="n">
-        <v>32.6509323120117</v>
+        <v>32.650936126709</v>
       </c>
       <c r="H1307" t="n">
         <v>30425</v>
@@ -38359,7 +38359,7 @@
         <v>34.1199989318848</v>
       </c>
       <c r="G1310" t="n">
-        <v>32.517505645752</v>
+        <v>32.5175132751465</v>
       </c>
       <c r="H1310" t="n">
         <v>53924</v>
@@ -38388,7 +38388,7 @@
         <v>34.6399993896484</v>
       </c>
       <c r="G1311" t="n">
-        <v>33.0130920410156</v>
+        <v>33.0130844116211</v>
       </c>
       <c r="H1311" t="n">
         <v>52414</v>
@@ -38417,7 +38417,7 @@
         <v>34.8600006103516</v>
       </c>
       <c r="G1312" t="n">
-        <v>33.2227554321289</v>
+        <v>33.2227516174316</v>
       </c>
       <c r="H1312" t="n">
         <v>51841</v>
@@ -38446,7 +38446,7 @@
         <v>35.1399993896484</v>
       </c>
       <c r="G1313" t="n">
-        <v>33.4896011352539</v>
+        <v>33.4896049499512</v>
       </c>
       <c r="H1313" t="n">
         <v>75221</v>
@@ -38475,7 +38475,7 @@
         <v>34.060001373291</v>
       </c>
       <c r="G1314" t="n">
-        <v>32.4603309631348</v>
+        <v>32.4603271484375</v>
       </c>
       <c r="H1314" t="n">
         <v>48600</v>
@@ -38504,7 +38504,7 @@
         <v>33.3600006103516</v>
       </c>
       <c r="G1315" t="n">
-        <v>31.7932071685791</v>
+        <v>31.7932033538818</v>
       </c>
       <c r="H1315" t="n">
         <v>74431</v>
@@ -38562,7 +38562,7 @@
         <v>34.2599983215332</v>
       </c>
       <c r="G1317" t="n">
-        <v>32.6509323120117</v>
+        <v>32.650936126709</v>
       </c>
       <c r="H1317" t="n">
         <v>35342</v>
@@ -38649,7 +38649,7 @@
         <v>38.8800010681152</v>
       </c>
       <c r="G1320" t="n">
-        <v>37.0539474487305</v>
+        <v>37.0539512634277</v>
       </c>
       <c r="H1320" t="n">
         <v>596087</v>
@@ -38678,7 +38678,7 @@
         <v>37.1199989318848</v>
       </c>
       <c r="G1321" t="n">
-        <v>35.3766098022461</v>
+        <v>35.3766136169434</v>
       </c>
       <c r="H1321" t="n">
         <v>116645</v>
@@ -38707,7 +38707,7 @@
         <v>38.7400016784668</v>
       </c>
       <c r="G1322" t="n">
-        <v>36.920524597168</v>
+        <v>36.9205284118652</v>
       </c>
       <c r="H1322" t="n">
         <v>79712</v>
@@ -38736,7 +38736,7 @@
         <v>37.7999992370605</v>
       </c>
       <c r="G1323" t="n">
-        <v>36.0246772766113</v>
+        <v>36.0246696472168</v>
       </c>
       <c r="H1323" t="n">
         <v>55424</v>
@@ -38765,7 +38765,7 @@
         <v>38.4799995422363</v>
       </c>
       <c r="G1324" t="n">
-        <v>36.672737121582</v>
+        <v>36.6727333068848</v>
       </c>
       <c r="H1324" t="n">
         <v>41671</v>
@@ -38794,7 +38794,7 @@
         <v>37.7999992370605</v>
       </c>
       <c r="G1325" t="n">
-        <v>36.0246772766113</v>
+        <v>36.0246696472168</v>
       </c>
       <c r="H1325" t="n">
         <v>63026</v>
@@ -38823,7 +38823,7 @@
         <v>37.5999984741211</v>
       </c>
       <c r="G1326" t="n">
-        <v>35.8340682983398</v>
+        <v>35.8340644836426</v>
       </c>
       <c r="H1326" t="n">
         <v>73998</v>
@@ -38881,7 +38881,7 @@
         <v>37</v>
       </c>
       <c r="G1328" t="n">
-        <v>35.2622489929199</v>
+        <v>35.2622528076172</v>
       </c>
       <c r="H1328" t="n">
         <v>35636</v>
@@ -38910,7 +38910,7 @@
         <v>37</v>
       </c>
       <c r="G1329" t="n">
-        <v>35.2622489929199</v>
+        <v>35.2622528076172</v>
       </c>
       <c r="H1329" t="n">
         <v>34302</v>
@@ -38968,7 +38968,7 @@
         <v>36.8800010681152</v>
       </c>
       <c r="G1331" t="n">
-        <v>35.1478805541992</v>
+        <v>35.1478843688965</v>
       </c>
       <c r="H1331" t="n">
         <v>24527</v>
@@ -38997,7 +38997,7 @@
         <v>36.8400001525879</v>
       </c>
       <c r="G1332" t="n">
-        <v>35.1097602844238</v>
+        <v>35.1097640991211</v>
       </c>
       <c r="H1332" t="n">
         <v>49832</v>
@@ -39142,7 +39142,7 @@
         <v>38.7200012207031</v>
       </c>
       <c r="G1337" t="n">
-        <v>36.9014701843262</v>
+        <v>36.9014625549316</v>
       </c>
       <c r="H1337" t="n">
         <v>48656</v>
@@ -39229,7 +39229,7 @@
         <v>40.2400016784668</v>
       </c>
       <c r="G1340" t="n">
-        <v>38.3500823974609</v>
+        <v>38.3500785827637</v>
       </c>
       <c r="H1340" t="n">
         <v>90654</v>
@@ -39258,7 +39258,7 @@
         <v>40.9799995422363</v>
       </c>
       <c r="G1341" t="n">
-        <v>39.0553169250488</v>
+        <v>39.0553207397461</v>
       </c>
       <c r="H1341" t="n">
         <v>89917</v>
@@ -39287,7 +39287,7 @@
         <v>41</v>
       </c>
       <c r="G1342" t="n">
-        <v>39.0743789672852</v>
+        <v>39.0743827819824</v>
       </c>
       <c r="H1342" t="n">
         <v>45226</v>
@@ -39374,7 +39374,7 @@
         <v>40.6199989318848</v>
       </c>
       <c r="G1345" t="n">
-        <v>38.7122268676758</v>
+        <v>38.7122344970703</v>
       </c>
       <c r="H1345" t="n">
         <v>59157</v>
@@ -39403,7 +39403,7 @@
         <v>42.4199981689453</v>
       </c>
       <c r="G1346" t="n">
-        <v>40.4276885986328</v>
+        <v>40.4276847839355</v>
       </c>
       <c r="H1346" t="n">
         <v>70945</v>
@@ -39490,7 +39490,7 @@
         <v>43.9799995422363</v>
       </c>
       <c r="G1349" t="n">
-        <v>41.9144248962402</v>
+        <v>41.914421081543</v>
       </c>
       <c r="H1349" t="n">
         <v>93011</v>
@@ -39548,7 +39548,7 @@
         <v>43.0200004577637</v>
       </c>
       <c r="G1351" t="n">
-        <v>40.99951171875</v>
+        <v>40.9995079040527</v>
       </c>
       <c r="H1351" t="n">
         <v>35735</v>
@@ -39722,7 +39722,7 @@
         <v>42.0200004577637</v>
       </c>
       <c r="G1357" t="n">
-        <v>40.0464744567871</v>
+        <v>40.0464820861816</v>
       </c>
       <c r="H1357" t="n">
         <v>51474</v>
@@ -39751,7 +39751,7 @@
         <v>43.8600006103516</v>
       </c>
       <c r="G1358" t="n">
-        <v>41.8000564575195</v>
+        <v>41.8000602722168</v>
       </c>
       <c r="H1358" t="n">
         <v>80674</v>
@@ -39896,7 +39896,7 @@
         <v>43.8400001525879</v>
       </c>
       <c r="G1363" t="n">
-        <v>41.7809982299805</v>
+        <v>41.7809944152832</v>
       </c>
       <c r="H1363" t="n">
         <v>60946</v>
@@ -40012,7 +40012,7 @@
         <v>45.4599990844727</v>
       </c>
       <c r="G1367" t="n">
-        <v>43.3249092102051</v>
+        <v>43.3249053955078</v>
       </c>
       <c r="H1367" t="n">
         <v>126510</v>
@@ -40041,7 +40041,7 @@
         <v>45.1399993896484</v>
       </c>
       <c r="G1368" t="n">
-        <v>43.019947052002</v>
+        <v>43.0199432373047</v>
       </c>
       <c r="H1368" t="n">
         <v>50649</v>
@@ -40070,7 +40070,7 @@
         <v>45.560001373291</v>
       </c>
       <c r="G1369" t="n">
-        <v>43.4202194213867</v>
+        <v>43.4202156066895</v>
       </c>
       <c r="H1369" t="n">
         <v>37886</v>
@@ -40099,7 +40099,7 @@
         <v>45.1800003051758</v>
       </c>
       <c r="G1370" t="n">
-        <v>43.0580596923828</v>
+        <v>43.0580635070801</v>
       </c>
       <c r="H1370" t="n">
         <v>58533</v>
@@ -40128,7 +40128,7 @@
         <v>45.4199981689453</v>
       </c>
       <c r="G1371" t="n">
-        <v>43.2867889404297</v>
+        <v>43.2867851257324</v>
       </c>
       <c r="H1371" t="n">
         <v>58394</v>
@@ -40157,7 +40157,7 @@
         <v>47</v>
       </c>
       <c r="G1372" t="n">
-        <v>44.7925834655762</v>
+        <v>44.7925872802734</v>
       </c>
       <c r="H1372" t="n">
         <v>175264</v>
@@ -40244,7 +40244,7 @@
         <v>51.75</v>
       </c>
       <c r="G1375" t="n">
-        <v>49.3194923400879</v>
+        <v>49.3194961547852</v>
       </c>
       <c r="H1375" t="n">
         <v>164541</v>
@@ -40273,7 +40273,7 @@
         <v>50.2999992370605</v>
       </c>
       <c r="G1376" t="n">
-        <v>47.9375953674316</v>
+        <v>47.9375915527344</v>
       </c>
       <c r="H1376" t="n">
         <v>55160</v>
@@ -40331,7 +40331,7 @@
         <v>48.9599990844727</v>
       </c>
       <c r="G1378" t="n">
-        <v>46.660530090332</v>
+        <v>46.6605339050293</v>
       </c>
       <c r="H1378" t="n">
         <v>114494</v>
@@ -40418,7 +40418,7 @@
         <v>49.2000007629395</v>
       </c>
       <c r="G1381" t="n">
-        <v>46.8892631530762</v>
+        <v>46.8892593383789</v>
       </c>
       <c r="H1381" t="n">
         <v>59594</v>
@@ -40447,7 +40447,7 @@
         <v>48.1399993896484</v>
       </c>
       <c r="G1382" t="n">
-        <v>45.8790397644043</v>
+        <v>45.879035949707</v>
       </c>
       <c r="H1382" t="n">
         <v>85939</v>
@@ -40476,7 +40476,7 @@
         <v>47.4599990844727</v>
       </c>
       <c r="G1383" t="n">
-        <v>45.2309761047363</v>
+        <v>45.2309799194336</v>
       </c>
       <c r="H1383" t="n">
         <v>83195</v>
@@ -40505,7 +40505,7 @@
         <v>47.7200012207031</v>
       </c>
       <c r="G1384" t="n">
-        <v>45.4787673950195</v>
+        <v>45.4787712097168</v>
       </c>
       <c r="H1384" t="n">
         <v>55250</v>
@@ -40592,7 +40592,7 @@
         <v>49.0999984741211</v>
       </c>
       <c r="G1387" t="n">
-        <v>46.7939491271973</v>
+        <v>46.7939529418945</v>
       </c>
       <c r="H1387" t="n">
         <v>34542</v>
@@ -40650,7 +40650,7 @@
         <v>50.0499992370605</v>
       </c>
       <c r="G1389" t="n">
-        <v>47.6993408203125</v>
+        <v>47.699333190918</v>
       </c>
       <c r="H1389" t="n">
         <v>45472</v>
@@ -40679,7 +40679,7 @@
         <v>50.9500007629395</v>
       </c>
       <c r="G1390" t="n">
-        <v>48.5570678710938</v>
+        <v>48.557071685791</v>
       </c>
       <c r="H1390" t="n">
         <v>44321</v>
@@ -40708,7 +40708,7 @@
         <v>49.6399993896484</v>
       </c>
       <c r="G1391" t="n">
-        <v>47.3085975646973</v>
+        <v>47.30859375</v>
       </c>
       <c r="H1391" t="n">
         <v>64212</v>
@@ -40882,7 +40882,7 @@
         <v>50</v>
       </c>
       <c r="G1397" t="n">
-        <v>47.6516876220703</v>
+        <v>47.651683807373</v>
       </c>
       <c r="H1397" t="n">
         <v>72320</v>
@@ -40911,7 +40911,7 @@
         <v>50.9500007629395</v>
       </c>
       <c r="G1398" t="n">
-        <v>48.5570678710938</v>
+        <v>48.557071685791</v>
       </c>
       <c r="H1398" t="n">
         <v>39436</v>
@@ -40969,7 +40969,7 @@
         <v>50.9500007629395</v>
       </c>
       <c r="G1400" t="n">
-        <v>48.5570678710938</v>
+        <v>48.557071685791</v>
       </c>
       <c r="H1400" t="n">
         <v>35366</v>
@@ -40998,7 +40998,7 @@
         <v>52.3499984741211</v>
       </c>
       <c r="G1401" t="n">
-        <v>49.8913078308105</v>
+        <v>49.8913116455078</v>
       </c>
       <c r="H1401" t="n">
         <v>63232</v>
@@ -41056,7 +41056,7 @@
         <v>51.0499992370605</v>
       </c>
       <c r="G1403" t="n">
-        <v>48.6523628234863</v>
+        <v>48.6523742675781</v>
       </c>
       <c r="H1403" t="n">
         <v>51071</v>
@@ -41085,7 +41085,7 @@
         <v>51.4000015258789</v>
       </c>
       <c r="G1404" t="n">
-        <v>48.9859313964844</v>
+        <v>48.9859352111816</v>
       </c>
       <c r="H1404" t="n">
         <v>29544</v>
@@ -41114,7 +41114,7 @@
         <v>51.4500007629395</v>
       </c>
       <c r="G1405" t="n">
-        <v>49.0335845947266</v>
+        <v>49.0335807800293</v>
       </c>
       <c r="H1405" t="n">
         <v>49409</v>
@@ -41143,7 +41143,7 @@
         <v>51.2999992370605</v>
       </c>
       <c r="G1406" t="n">
-        <v>48.8906326293945</v>
+        <v>48.8906288146973</v>
       </c>
       <c r="H1406" t="n">
         <v>64517</v>
@@ -41172,7 +41172,7 @@
         <v>49.1199989318848</v>
       </c>
       <c r="G1407" t="n">
-        <v>46.8130073547363</v>
+        <v>46.8130149841309</v>
       </c>
       <c r="H1407" t="n">
         <v>886633</v>
@@ -41201,7 +41201,7 @@
         <v>49.6599998474121</v>
       </c>
       <c r="G1408" t="n">
-        <v>47.3276557922363</v>
+        <v>47.3276596069336</v>
       </c>
       <c r="H1408" t="n">
         <v>104813</v>
@@ -41230,7 +41230,7 @@
         <v>48.7599983215332</v>
       </c>
       <c r="G1409" t="n">
-        <v>46.4699172973633</v>
+        <v>46.4699211120605</v>
       </c>
       <c r="H1409" t="n">
         <v>107450</v>
@@ -41259,7 +41259,7 @@
         <v>48.1399993896484</v>
       </c>
       <c r="G1410" t="n">
-        <v>45.8790397644043</v>
+        <v>45.879035949707</v>
       </c>
       <c r="H1410" t="n">
         <v>61909</v>
@@ -41288,7 +41288,7 @@
         <v>49.7000007629395</v>
       </c>
       <c r="G1411" t="n">
-        <v>47.3657760620117</v>
+        <v>47.365779876709</v>
       </c>
       <c r="H1411" t="n">
         <v>90751</v>
@@ -41317,7 +41317,7 @@
         <v>51.1500015258789</v>
       </c>
       <c r="G1412" t="n">
-        <v>48.747673034668</v>
+        <v>48.7476692199707</v>
       </c>
       <c r="H1412" t="n">
         <v>67201</v>
@@ -41375,7 +41375,7 @@
         <v>51.75</v>
       </c>
       <c r="G1414" t="n">
-        <v>49.3194923400879</v>
+        <v>49.3194961547852</v>
       </c>
       <c r="H1414" t="n">
         <v>31401</v>
@@ -41404,7 +41404,7 @@
         <v>51.4500007629395</v>
       </c>
       <c r="G1415" t="n">
-        <v>49.0335845947266</v>
+        <v>49.0335807800293</v>
       </c>
       <c r="H1415" t="n">
         <v>44816</v>
@@ -41433,7 +41433,7 @@
         <v>51.7999992370605</v>
       </c>
       <c r="G1416" t="n">
-        <v>49.3671417236328</v>
+        <v>49.3671455383301</v>
       </c>
       <c r="H1416" t="n">
         <v>53456</v>
@@ -41549,7 +41549,7 @@
         <v>55.7999992370605</v>
       </c>
       <c r="G1420" t="n">
-        <v>53.1792831420898</v>
+        <v>53.1792793273926</v>
       </c>
       <c r="H1420" t="n">
         <v>103774</v>
@@ -41607,7 +41607,7 @@
         <v>54.8499984741211</v>
       </c>
       <c r="G1422" t="n">
-        <v>52.2738952636719</v>
+        <v>52.2738914489746</v>
       </c>
       <c r="H1422" t="n">
         <v>59851</v>
@@ -41636,7 +41636,7 @@
         <v>54.8499984741211</v>
       </c>
       <c r="G1423" t="n">
-        <v>52.2738952636719</v>
+        <v>52.2738914489746</v>
       </c>
       <c r="H1423" t="n">
         <v>29890</v>
@@ -41694,7 +41694,7 @@
         <v>55.5999984741211</v>
       </c>
       <c r="G1425" t="n">
-        <v>52.9886703491211</v>
+        <v>52.9886741638184</v>
       </c>
       <c r="H1425" t="n">
         <v>41803</v>
@@ -41723,7 +41723,7 @@
         <v>55</v>
       </c>
       <c r="G1426" t="n">
-        <v>52.4168510437012</v>
+        <v>52.4168548583984</v>
       </c>
       <c r="H1426" t="n">
         <v>87017</v>
@@ -41810,7 +41810,7 @@
         <v>53.9000015258789</v>
       </c>
       <c r="G1429" t="n">
-        <v>51.3685150146484</v>
+        <v>51.3685188293457</v>
       </c>
       <c r="H1429" t="n">
         <v>62752</v>
@@ -41868,7 +41868,7 @@
         <v>52.3499984741211</v>
       </c>
       <c r="G1431" t="n">
-        <v>49.8913078308105</v>
+        <v>49.8913116455078</v>
       </c>
       <c r="H1431" t="n">
         <v>54572</v>
@@ -41897,7 +41897,7 @@
         <v>49.0999984741211</v>
       </c>
       <c r="G1432" t="n">
-        <v>46.7939491271973</v>
+        <v>46.7939529418945</v>
       </c>
       <c r="H1432" t="n">
         <v>199274</v>
@@ -42013,7 +42013,7 @@
         <v>50</v>
       </c>
       <c r="G1436" t="n">
-        <v>47.6516876220703</v>
+        <v>47.651683807373</v>
       </c>
       <c r="H1436" t="n">
         <v>49781</v>
@@ -42071,7 +42071,7 @@
         <v>50.4000015258789</v>
       </c>
       <c r="G1438" t="n">
-        <v>48.0328979492188</v>
+        <v>48.032901763916</v>
       </c>
       <c r="H1438" t="n">
         <v>174273</v>
@@ -42100,7 +42100,7 @@
         <v>49.7999992370605</v>
       </c>
       <c r="G1439" t="n">
-        <v>47.4610748291016</v>
+        <v>47.4610824584961</v>
       </c>
       <c r="H1439" t="n">
         <v>117871</v>
@@ -42129,7 +42129,7 @@
         <v>49.9000015258789</v>
       </c>
       <c r="G1440" t="n">
-        <v>47.5563850402832</v>
+        <v>47.5563812255859</v>
       </c>
       <c r="H1440" t="n">
         <v>54618</v>
@@ -42158,7 +42158,7 @@
         <v>50.0499992370605</v>
       </c>
       <c r="G1441" t="n">
-        <v>47.6993408203125</v>
+        <v>47.699333190918</v>
       </c>
       <c r="H1441" t="n">
         <v>77596</v>
@@ -42187,7 +42187,7 @@
         <v>50.0499992370605</v>
       </c>
       <c r="G1442" t="n">
-        <v>47.6993408203125</v>
+        <v>47.699333190918</v>
       </c>
       <c r="H1442" t="n">
         <v>30067</v>
@@ -42274,7 +42274,7 @@
         <v>49.6199989318848</v>
       </c>
       <c r="G1445" t="n">
-        <v>47.2895355224609</v>
+        <v>47.2895317077637</v>
       </c>
       <c r="H1445" t="n">
         <v>41941</v>
@@ -42332,7 +42332,7 @@
         <v>49.7000007629395</v>
       </c>
       <c r="G1447" t="n">
-        <v>47.3657760620117</v>
+        <v>47.365779876709</v>
       </c>
       <c r="H1447" t="n">
         <v>34314</v>
@@ -42390,7 +42390,7 @@
         <v>48.5800018310547</v>
       </c>
       <c r="G1449" t="n">
-        <v>46.2983779907227</v>
+        <v>46.2983818054199</v>
       </c>
       <c r="H1449" t="n">
         <v>55271</v>
@@ -42419,7 +42419,7 @@
         <v>48.0200004577637</v>
       </c>
       <c r="G1450" t="n">
-        <v>45.7646827697754</v>
+        <v>45.7646789550781</v>
       </c>
       <c r="H1450" t="n">
         <v>91232</v>
@@ -42448,7 +42448,7 @@
         <v>46.7599983215332</v>
       </c>
       <c r="G1451" t="n">
-        <v>44.5638580322266</v>
+        <v>44.5638542175293</v>
       </c>
       <c r="H1451" t="n">
         <v>77843</v>
@@ -42477,7 +42477,7 @@
         <v>47.1599998474121</v>
       </c>
       <c r="G1452" t="n">
-        <v>44.945068359375</v>
+        <v>44.9450721740723</v>
       </c>
       <c r="H1452" t="n">
         <v>49608</v>
@@ -42535,7 +42535,7 @@
         <v>48.2599983215332</v>
       </c>
       <c r="G1454" t="n">
-        <v>45.9934043884277</v>
+        <v>45.9934005737305</v>
       </c>
       <c r="H1454" t="n">
         <v>68637</v>
@@ -42593,7 +42593,7 @@
         <v>49.2000007629395</v>
       </c>
       <c r="G1456" t="n">
-        <v>46.8892631530762</v>
+        <v>46.8892593383789</v>
       </c>
       <c r="H1456" t="n">
         <v>58743</v>
@@ -42622,7 +42622,7 @@
         <v>49.7999992370605</v>
       </c>
       <c r="G1457" t="n">
-        <v>47.4610748291016</v>
+        <v>47.4610824584961</v>
       </c>
       <c r="H1457" t="n">
         <v>75775</v>
@@ -42680,7 +42680,7 @@
         <v>48.5800018310547</v>
       </c>
       <c r="G1459" t="n">
-        <v>46.2983779907227</v>
+        <v>46.2983818054199</v>
       </c>
       <c r="H1459" t="n">
         <v>60782</v>
@@ -42709,7 +42709,7 @@
         <v>47.2799987792969</v>
       </c>
       <c r="G1460" t="n">
-        <v>45.0594291687012</v>
+        <v>45.0594329833984</v>
       </c>
       <c r="H1460" t="n">
         <v>55766</v>
@@ -42796,7 +42796,7 @@
         <v>47.8199996948242</v>
       </c>
       <c r="G1463" t="n">
-        <v>45.5740737915039</v>
+        <v>45.5740699768066</v>
       </c>
       <c r="H1463" t="n">
         <v>58436</v>
@@ -42825,7 +42825,7 @@
         <v>47.2999992370605</v>
       </c>
       <c r="G1464" t="n">
-        <v>45.0784912109375</v>
+        <v>45.0784950256348</v>
       </c>
       <c r="H1464" t="n">
         <v>39681</v>
@@ -42883,7 +42883,7 @@
         <v>46.939998626709</v>
       </c>
       <c r="G1466" t="n">
-        <v>44.7354011535645</v>
+        <v>44.7353973388672</v>
       </c>
       <c r="H1466" t="n">
         <v>92727</v>
@@ -42912,7 +42912,7 @@
         <v>47.7200012207031</v>
       </c>
       <c r="G1467" t="n">
-        <v>45.4787673950195</v>
+        <v>45.4787712097168</v>
       </c>
       <c r="H1467" t="n">
         <v>52731</v>
@@ -43144,7 +43144,7 @@
         <v>48.8600006103516</v>
       </c>
       <c r="G1475" t="n">
-        <v>46.5652275085449</v>
+        <v>46.5652313232422</v>
       </c>
       <c r="H1475" t="n">
         <v>35271</v>
@@ -43231,7 +43231,7 @@
         <v>51.2999992370605</v>
       </c>
       <c r="G1478" t="n">
-        <v>48.8906326293945</v>
+        <v>48.8906288146973</v>
       </c>
       <c r="H1478" t="n">
         <v>114497</v>
@@ -43289,7 +43289,7 @@
         <v>51.4000015258789</v>
       </c>
       <c r="G1480" t="n">
-        <v>48.9859313964844</v>
+        <v>48.9859352111816</v>
       </c>
       <c r="H1480" t="n">
         <v>55344</v>
@@ -43318,7 +43318,7 @@
         <v>51.1500015258789</v>
       </c>
       <c r="G1481" t="n">
-        <v>48.747673034668</v>
+        <v>48.7476692199707</v>
       </c>
       <c r="H1481" t="n">
         <v>76754</v>
@@ -43347,7 +43347,7 @@
         <v>51.7999992370605</v>
       </c>
       <c r="G1482" t="n">
-        <v>49.3671417236328</v>
+        <v>49.3671455383301</v>
       </c>
       <c r="H1482" t="n">
         <v>41860</v>
@@ -43434,7 +43434,7 @@
         <v>53.5499992370605</v>
       </c>
       <c r="G1485" t="n">
-        <v>51.0349540710449</v>
+        <v>51.0349502563477</v>
       </c>
       <c r="H1485" t="n">
         <v>57424</v>
@@ -43492,7 +43492,7 @@
         <v>58.2000007629395</v>
       </c>
       <c r="G1487" t="n">
-        <v>55.4665603637695</v>
+        <v>55.4665641784668</v>
       </c>
       <c r="H1487" t="n">
         <v>179532</v>
@@ -43550,7 +43550,7 @@
         <v>62.2999992370605</v>
       </c>
       <c r="G1489" t="n">
-        <v>59.3740005493164</v>
+        <v>59.3739967346191</v>
       </c>
       <c r="H1489" t="n">
         <v>175947</v>
@@ -43579,7 +43579,7 @@
         <v>63.0999984741211</v>
       </c>
       <c r="G1490" t="n">
-        <v>60.1364212036133</v>
+        <v>60.1364250183105</v>
       </c>
       <c r="H1490" t="n">
         <v>141613</v>
@@ -43608,7 +43608,7 @@
         <v>61.8499984741211</v>
       </c>
       <c r="G1491" t="n">
-        <v>58.9451332092285</v>
+        <v>58.9451370239258</v>
       </c>
       <c r="H1491" t="n">
         <v>147656</v>
@@ -43695,7 +43695,7 @@
         <v>62.7000007629395</v>
       </c>
       <c r="G1494" t="n">
-        <v>59.7552146911621</v>
+        <v>59.7552185058594</v>
       </c>
       <c r="H1494" t="n">
         <v>87240</v>
@@ -43724,7 +43724,7 @@
         <v>62.4500007629395</v>
       </c>
       <c r="G1495" t="n">
-        <v>59.5169525146484</v>
+        <v>59.5169563293457</v>
       </c>
       <c r="H1495" t="n">
         <v>94805</v>
@@ -43782,7 +43782,7 @@
         <v>61.8499984741211</v>
       </c>
       <c r="G1497" t="n">
-        <v>58.9451332092285</v>
+        <v>58.9451370239258</v>
       </c>
       <c r="H1497" t="n">
         <v>54303</v>
@@ -43811,7 +43811,7 @@
         <v>60.0999984741211</v>
       </c>
       <c r="G1498" t="n">
-        <v>57.2773246765137</v>
+        <v>57.2773208618164</v>
       </c>
       <c r="H1498" t="n">
         <v>75473</v>
@@ -43898,7 +43898,7 @@
         <v>57.8499984741211</v>
       </c>
       <c r="G1501" t="n">
-        <v>55.132999420166</v>
+        <v>55.1329956054688</v>
       </c>
       <c r="H1501" t="n">
         <v>77453</v>
@@ -43956,7 +43956,7 @@
         <v>55.3499984741211</v>
       </c>
       <c r="G1503" t="n">
-        <v>52.7504119873047</v>
+        <v>52.750415802002</v>
       </c>
       <c r="H1503" t="n">
         <v>96543</v>
@@ -44043,7 +44043,7 @@
         <v>56.75</v>
       </c>
       <c r="G1506" t="n">
-        <v>54.0846633911133</v>
+        <v>54.0846672058105</v>
       </c>
       <c r="H1506" t="n">
         <v>82763</v>
@@ -44072,7 +44072,7 @@
         <v>55.5</v>
       </c>
       <c r="G1507" t="n">
-        <v>52.8933753967285</v>
+        <v>52.8933715820312</v>
       </c>
       <c r="H1507" t="n">
         <v>49119</v>
@@ -44101,7 +44101,7 @@
         <v>55.9500007629395</v>
       </c>
       <c r="G1508" t="n">
-        <v>53.3222312927246</v>
+        <v>53.3222389221191</v>
       </c>
       <c r="H1508" t="n">
         <v>38688</v>
@@ -44246,7 +44246,7 @@
         <v>56.1500015258789</v>
       </c>
       <c r="G1513" t="n">
-        <v>53.5128479003906</v>
+        <v>53.5128402709961</v>
       </c>
       <c r="H1513" t="n">
         <v>37098</v>
@@ -44391,7 +44391,7 @@
         <v>55.5999984741211</v>
       </c>
       <c r="G1518" t="n">
-        <v>52.9886703491211</v>
+        <v>52.9886741638184</v>
       </c>
       <c r="H1518" t="n">
         <v>69798</v>
@@ -44449,7 +44449,7 @@
         <v>55.9500007629395</v>
       </c>
       <c r="G1520" t="n">
-        <v>53.3222312927246</v>
+        <v>53.3222389221191</v>
       </c>
       <c r="H1520" t="n">
         <v>32997</v>
@@ -44507,7 +44507,7 @@
         <v>56.9500007629395</v>
       </c>
       <c r="G1522" t="n">
-        <v>54.2752685546875</v>
+        <v>54.2752723693848</v>
       </c>
       <c r="H1522" t="n">
         <v>28796</v>
@@ -44565,7 +44565,7 @@
         <v>59.4000015258789</v>
       </c>
       <c r="G1524" t="n">
-        <v>56.6102066040039</v>
+        <v>56.6102027893066</v>
       </c>
       <c r="H1524" t="n">
         <v>40601</v>
@@ -44594,7 +44594,7 @@
         <v>60.5999984741211</v>
       </c>
       <c r="G1525" t="n">
-        <v>57.7538414001465</v>
+        <v>57.7538452148438</v>
       </c>
       <c r="H1525" t="n">
         <v>85559</v>
@@ -44652,7 +44652,7 @@
         <v>63.1500015258789</v>
       </c>
       <c r="G1527" t="n">
-        <v>60.1840782165527</v>
+        <v>60.1840858459473</v>
       </c>
       <c r="H1527" t="n">
         <v>112767</v>
@@ -44710,7 +44710,7 @@
         <v>63.5</v>
       </c>
       <c r="G1529" t="n">
-        <v>60.5176429748535</v>
+        <v>60.5176391601562</v>
       </c>
       <c r="H1529" t="n">
         <v>69556</v>
@@ -44739,7 +44739,7 @@
         <v>62.5499992370605</v>
       </c>
       <c r="G1530" t="n">
-        <v>59.6122550964355</v>
+        <v>59.6122589111328</v>
       </c>
       <c r="H1530" t="n">
         <v>110929</v>
@@ -44768,7 +44768,7 @@
         <v>60.7999992370605</v>
       </c>
       <c r="G1531" t="n">
-        <v>57.944450378418</v>
+        <v>57.9444465637207</v>
       </c>
       <c r="H1531" t="n">
         <v>50759</v>
@@ -44797,7 +44797,7 @@
         <v>58.0499992370605</v>
       </c>
       <c r="G1532" t="n">
-        <v>55.3236045837402</v>
+        <v>55.3236083984375</v>
       </c>
       <c r="H1532" t="n">
         <v>99233</v>
@@ -44855,7 +44855,7 @@
         <v>57.2000007629395</v>
       </c>
       <c r="G1534" t="n">
-        <v>54.5135307312012</v>
+        <v>54.5135269165039</v>
       </c>
       <c r="H1534" t="n">
         <v>160505</v>
@@ -44942,7 +44942,7 @@
         <v>55.5999984741211</v>
       </c>
       <c r="G1537" t="n">
-        <v>52.9886703491211</v>
+        <v>52.9886741638184</v>
       </c>
       <c r="H1537" t="n">
         <v>55636</v>
@@ -44971,7 +44971,7 @@
         <v>53.9500007629395</v>
       </c>
       <c r="G1538" t="n">
-        <v>51.4161682128906</v>
+        <v>51.4161643981934</v>
       </c>
       <c r="H1538" t="n">
         <v>105480</v>
@@ -45116,7 +45116,7 @@
         <v>52.6500015258789</v>
       </c>
       <c r="G1543" t="n">
-        <v>50.1772270202637</v>
+        <v>50.1772232055664</v>
       </c>
       <c r="H1543" t="n">
         <v>70062</v>
@@ -45145,7 +45145,7 @@
         <v>53.75</v>
       </c>
       <c r="G1544" t="n">
-        <v>51.2255592346191</v>
+        <v>51.2255630493164</v>
       </c>
       <c r="H1544" t="n">
         <v>70856</v>
@@ -45232,7 +45232,7 @@
         <v>51.1500015258789</v>
       </c>
       <c r="G1547" t="n">
-        <v>48.747673034668</v>
+        <v>48.7476692199707</v>
       </c>
       <c r="H1547" t="n">
         <v>91006</v>
@@ -45290,7 +45290,7 @@
         <v>53.7000007629395</v>
       </c>
       <c r="G1549" t="n">
-        <v>51.1779136657715</v>
+        <v>51.1779098510742</v>
       </c>
       <c r="H1549" t="n">
         <v>78328</v>
@@ -45348,7 +45348,7 @@
         <v>52.5</v>
       </c>
       <c r="G1551" t="n">
-        <v>50.0342674255371</v>
+        <v>50.0342712402344</v>
       </c>
       <c r="H1551" t="n">
         <v>37463</v>
@@ -45377,7 +45377,7 @@
         <v>52.6500015258789</v>
       </c>
       <c r="G1552" t="n">
-        <v>50.1772270202637</v>
+        <v>50.1772232055664</v>
       </c>
       <c r="H1552" t="n">
         <v>29135</v>
@@ -45435,7 +45435,7 @@
         <v>54.25</v>
       </c>
       <c r="G1554" t="n">
-        <v>51.7020835876465</v>
+        <v>51.7020797729492</v>
       </c>
       <c r="H1554" t="n">
         <v>52478</v>
@@ -45464,7 +45464,7 @@
         <v>54.0499992370605</v>
       </c>
       <c r="G1555" t="n">
-        <v>51.5114707946777</v>
+        <v>51.5114669799805</v>
       </c>
       <c r="H1555" t="n">
         <v>67457</v>
@@ -45551,7 +45551,7 @@
         <v>53.2999992370605</v>
       </c>
       <c r="G1558" t="n">
-        <v>50.7966995239258</v>
+        <v>50.7966957092285</v>
       </c>
       <c r="H1558" t="n">
         <v>40581</v>
@@ -45580,7 +45580,7 @@
         <v>52.6500015258789</v>
       </c>
       <c r="G1559" t="n">
-        <v>50.1772270202637</v>
+        <v>50.1772232055664</v>
       </c>
       <c r="H1559" t="n">
         <v>27733</v>
@@ -45609,7 +45609,7 @@
         <v>52.75</v>
       </c>
       <c r="G1560" t="n">
-        <v>50.2725257873535</v>
+        <v>50.2725219726562</v>
       </c>
       <c r="H1560" t="n">
         <v>33964</v>
@@ -45638,7 +45638,7 @@
         <v>52.5999984741211</v>
       </c>
       <c r="G1561" t="n">
-        <v>50.1295738220215</v>
+        <v>50.1295700073242</v>
       </c>
       <c r="H1561" t="n">
         <v>41794</v>
@@ -45696,7 +45696,7 @@
         <v>51.4500007629395</v>
       </c>
       <c r="G1563" t="n">
-        <v>49.0335845947266</v>
+        <v>49.0335807800293</v>
       </c>
       <c r="H1563" t="n">
         <v>48482</v>
@@ -45783,7 +45783,7 @@
         <v>51.75</v>
       </c>
       <c r="G1566" t="n">
-        <v>49.3194923400879</v>
+        <v>49.3194961547852</v>
       </c>
       <c r="H1566" t="n">
         <v>79209</v>
@@ -45812,7 +45812,7 @@
         <v>50.2999992370605</v>
       </c>
       <c r="G1567" t="n">
-        <v>47.9375953674316</v>
+        <v>47.9375915527344</v>
       </c>
       <c r="H1567" t="n">
         <v>185743</v>
@@ -45870,7 +45870,7 @@
         <v>48.060001373291</v>
       </c>
       <c r="G1569" t="n">
-        <v>45.8028030395508</v>
+        <v>45.8027992248535</v>
       </c>
       <c r="H1569" t="n">
         <v>232213</v>
@@ -45986,7 +45986,7 @@
         <v>41.939998626709</v>
       </c>
       <c r="G1573" t="n">
-        <v>39.9702339172363</v>
+        <v>39.9702377319336</v>
       </c>
       <c r="H1573" t="n">
         <v>122667</v>
@@ -46015,7 +46015,7 @@
         <v>44.0800018310547</v>
       </c>
       <c r="G1574" t="n">
-        <v>42.0097274780273</v>
+        <v>42.0097236633301</v>
       </c>
       <c r="H1574" t="n">
         <v>105267</v>
@@ -46044,7 +46044,7 @@
         <v>43.6599998474121</v>
       </c>
       <c r="G1575" t="n">
-        <v>41.609447479248</v>
+        <v>41.6094512939453</v>
       </c>
       <c r="H1575" t="n">
         <v>89737</v>
@@ -46073,7 +46073,7 @@
         <v>46.939998626709</v>
       </c>
       <c r="G1576" t="n">
-        <v>44.7354011535645</v>
+        <v>44.7353973388672</v>
       </c>
       <c r="H1576" t="n">
         <v>196936</v>
@@ -46102,7 +46102,7 @@
         <v>47.1800003051758</v>
       </c>
       <c r="G1577" t="n">
-        <v>44.9641304016113</v>
+        <v>44.9641342163086</v>
       </c>
       <c r="H1577" t="n">
         <v>103762</v>
@@ -46131,7 +46131,7 @@
         <v>48.5</v>
       </c>
       <c r="G1578" t="n">
-        <v>46.2221374511719</v>
+        <v>46.2221412658691</v>
       </c>
       <c r="H1578" t="n">
         <v>104526</v>
@@ -46247,7 +46247,7 @@
         <v>53.7000007629395</v>
       </c>
       <c r="G1582" t="n">
-        <v>51.1779136657715</v>
+        <v>51.1779098510742</v>
       </c>
       <c r="H1582" t="n">
         <v>74602</v>
@@ -46276,7 +46276,7 @@
         <v>51.75</v>
       </c>
       <c r="G1583" t="n">
-        <v>49.3194923400879</v>
+        <v>49.3194961547852</v>
       </c>
       <c r="H1583" t="n">
         <v>89656</v>
@@ -46334,7 +46334,7 @@
         <v>51.0499992370605</v>
       </c>
       <c r="G1585" t="n">
-        <v>48.6523628234863</v>
+        <v>48.6523742675781</v>
       </c>
       <c r="H1585" t="n">
         <v>40274</v>
@@ -46392,7 +46392,7 @@
         <v>51.75</v>
       </c>
       <c r="G1587" t="n">
-        <v>49.3194923400879</v>
+        <v>49.3194961547852</v>
       </c>
       <c r="H1587" t="n">
         <v>43271</v>
@@ -46421,7 +46421,7 @@
         <v>54.0499992370605</v>
       </c>
       <c r="G1588" t="n">
-        <v>51.5114707946777</v>
+        <v>51.5114669799805</v>
       </c>
       <c r="H1588" t="n">
         <v>60554</v>
@@ -46508,7 +46508,7 @@
         <v>52.6500015258789</v>
       </c>
       <c r="G1591" t="n">
-        <v>50.1772270202637</v>
+        <v>50.1772232055664</v>
       </c>
       <c r="H1591" t="n">
         <v>44149</v>
@@ -46566,7 +46566,7 @@
         <v>53.7000007629395</v>
       </c>
       <c r="G1593" t="n">
-        <v>51.1779136657715</v>
+        <v>51.1779098510742</v>
       </c>
       <c r="H1593" t="n">
         <v>48342</v>
@@ -46595,7 +46595,7 @@
         <v>51.3499984741211</v>
       </c>
       <c r="G1594" t="n">
-        <v>48.9382820129395</v>
+        <v>48.9382781982422</v>
       </c>
       <c r="H1594" t="n">
         <v>63727</v>
@@ -46653,7 +46653,7 @@
         <v>52.5999984741211</v>
       </c>
       <c r="G1596" t="n">
-        <v>50.1295738220215</v>
+        <v>50.1295700073242</v>
       </c>
       <c r="H1596" t="n">
         <v>58823</v>
@@ -46769,7 +46769,7 @@
         <v>52.3499984741211</v>
       </c>
       <c r="G1600" t="n">
-        <v>49.8913078308105</v>
+        <v>49.8913116455078</v>
       </c>
       <c r="H1600" t="n">
         <v>83132</v>
@@ -46914,7 +46914,7 @@
         <v>48.3199996948242</v>
       </c>
       <c r="G1605" t="n">
-        <v>46.0505867004395</v>
+        <v>46.0505905151367</v>
       </c>
       <c r="H1605" t="n">
         <v>55941</v>
@@ -46972,7 +46972,7 @@
         <v>47.1599998474121</v>
       </c>
       <c r="G1607" t="n">
-        <v>44.945068359375</v>
+        <v>44.9450721740723</v>
       </c>
       <c r="H1607" t="n">
         <v>69822</v>
@@ -47088,7 +47088,7 @@
         <v>48.6800003051758</v>
       </c>
       <c r="G1611" t="n">
-        <v>46.3936767578125</v>
+        <v>46.3936805725098</v>
       </c>
       <c r="H1611" t="n">
         <v>55936</v>
@@ -47117,7 +47117,7 @@
         <v>48.0800018310547</v>
       </c>
       <c r="G1612" t="n">
-        <v>45.8218650817871</v>
+        <v>45.8218612670898</v>
       </c>
       <c r="H1612" t="n">
         <v>48947</v>
@@ -47146,7 +47146,7 @@
         <v>46.560001373291</v>
       </c>
       <c r="G1613" t="n">
-        <v>44.3732490539551</v>
+        <v>44.3732528686523</v>
       </c>
       <c r="H1613" t="n">
         <v>98439</v>
@@ -47233,7 +47233,7 @@
         <v>44.3400001525879</v>
       </c>
       <c r="G1616" t="n">
-        <v>42.257511138916</v>
+        <v>42.2575149536133</v>
       </c>
       <c r="H1616" t="n">
         <v>73971</v>
@@ -47262,7 +47262,7 @@
         <v>46.7599983215332</v>
       </c>
       <c r="G1617" t="n">
-        <v>44.5638580322266</v>
+        <v>44.5638542175293</v>
       </c>
       <c r="H1617" t="n">
         <v>59010</v>
@@ -47291,7 +47291,7 @@
         <v>45.7000007629395</v>
       </c>
       <c r="G1618" t="n">
-        <v>43.5536422729492</v>
+        <v>43.553638458252</v>
       </c>
       <c r="H1618" t="n">
         <v>72080</v>
@@ -47320,7 +47320,7 @@
         <v>47.2599983215332</v>
       </c>
       <c r="G1619" t="n">
-        <v>45.0403709411621</v>
+        <v>45.0403747558594</v>
       </c>
       <c r="H1619" t="n">
         <v>34098</v>
@@ -47378,7 +47378,7 @@
         <v>48.7200012207031</v>
       </c>
       <c r="G1621" t="n">
-        <v>46.4318046569824</v>
+        <v>46.4318008422852</v>
       </c>
       <c r="H1621" t="n">
         <v>50025</v>
@@ -47407,7 +47407,7 @@
         <v>47.4799995422363</v>
       </c>
       <c r="G1622" t="n">
-        <v>45.2500343322754</v>
+        <v>45.2500419616699</v>
       </c>
       <c r="H1622" t="n">
         <v>25974</v>
@@ -47494,7 +47494,7 @@
         <v>45.2799987792969</v>
       </c>
       <c r="G1625" t="n">
-        <v>43.5597457885742</v>
+        <v>43.559741973877</v>
       </c>
       <c r="H1625" t="n">
         <v>27475</v>
@@ -47523,7 +47523,7 @@
         <v>43.5</v>
       </c>
       <c r="G1626" t="n">
-        <v>41.8473663330078</v>
+        <v>41.8473701477051</v>
       </c>
       <c r="H1626" t="n">
         <v>34400</v>
@@ -47552,7 +47552,7 @@
         <v>43.1399993896484</v>
       </c>
       <c r="G1627" t="n">
-        <v>41.5010452270508</v>
+        <v>41.501049041748</v>
       </c>
       <c r="H1627" t="n">
         <v>63512</v>
@@ -47581,7 +47581,7 @@
         <v>44.5400009155273</v>
       </c>
       <c r="G1628" t="n">
-        <v>42.8478546142578</v>
+        <v>42.8478584289551</v>
       </c>
       <c r="H1628" t="n">
         <v>51931</v>
@@ -47610,7 +47610,7 @@
         <v>46</v>
       </c>
       <c r="G1629" t="n">
-        <v>44.2523880004883</v>
+        <v>44.2523918151855</v>
       </c>
       <c r="H1629" t="n">
         <v>51227</v>
@@ -47639,7 +47639,7 @@
         <v>47.6599998474121</v>
       </c>
       <c r="G1630" t="n">
-        <v>45.8493194580078</v>
+        <v>45.8493232727051</v>
       </c>
       <c r="H1630" t="n">
         <v>36632</v>
@@ -47697,7 +47697,7 @@
         <v>46.7200012207031</v>
       </c>
       <c r="G1632" t="n">
-        <v>44.9450340270996</v>
+        <v>44.9450378417969</v>
       </c>
       <c r="H1632" t="n">
         <v>32722</v>
@@ -47813,7 +47813,7 @@
         <v>46.5800018310547</v>
       </c>
       <c r="G1636" t="n">
-        <v>44.8103561401367</v>
+        <v>44.8103523254395</v>
       </c>
       <c r="H1636" t="n">
         <v>41005</v>
@@ -47871,7 +47871,7 @@
         <v>45.560001373291</v>
       </c>
       <c r="G1638" t="n">
-        <v>43.8291091918945</v>
+        <v>43.8291053771973</v>
       </c>
       <c r="H1638" t="n">
         <v>66639</v>
@@ -47900,7 +47900,7 @@
         <v>44.0800018310547</v>
       </c>
       <c r="G1639" t="n">
-        <v>42.4053344726562</v>
+        <v>42.405330657959</v>
       </c>
       <c r="H1639" t="n">
         <v>33548</v>
@@ -48016,7 +48016,7 @@
         <v>40.1599998474121</v>
       </c>
       <c r="G1643" t="n">
-        <v>38.6342620849609</v>
+        <v>38.6342582702637</v>
       </c>
       <c r="H1643" t="n">
         <v>42538</v>
@@ -48045,7 +48045,7 @@
         <v>40.7400016784668</v>
       </c>
       <c r="G1644" t="n">
-        <v>39.1922302246094</v>
+        <v>39.1922264099121</v>
       </c>
       <c r="H1644" t="n">
         <v>44561</v>
@@ -48103,7 +48103,7 @@
         <v>41.0800018310547</v>
       </c>
       <c r="G1646" t="n">
-        <v>39.5193061828613</v>
+        <v>39.5193099975586</v>
       </c>
       <c r="H1646" t="n">
         <v>24950</v>
@@ -48132,7 +48132,7 @@
         <v>41.3800010681152</v>
       </c>
       <c r="G1647" t="n">
-        <v>39.8079147338867</v>
+        <v>39.8079109191895</v>
       </c>
       <c r="H1647" t="n">
         <v>48890</v>
@@ -48161,7 +48161,7 @@
         <v>41.939998626709</v>
       </c>
       <c r="G1648" t="n">
-        <v>40.3466339111328</v>
+        <v>40.3466377258301</v>
       </c>
       <c r="H1648" t="n">
         <v>90741</v>
@@ -48306,7 +48306,7 @@
         <v>42.9799995422363</v>
       </c>
       <c r="G1653" t="n">
-        <v>41.3471221923828</v>
+        <v>41.3471183776855</v>
       </c>
       <c r="H1653" t="n">
         <v>29894</v>
@@ -48364,7 +48364,7 @@
         <v>43.060001373291</v>
       </c>
       <c r="G1655" t="n">
-        <v>41.4240875244141</v>
+        <v>41.4240837097168</v>
       </c>
       <c r="H1655" t="n">
         <v>32134</v>
@@ -48422,7 +48422,7 @@
         <v>43.9799995422363</v>
       </c>
       <c r="G1657" t="n">
-        <v>42.3091316223145</v>
+        <v>42.3091278076172</v>
       </c>
       <c r="H1657" t="n">
         <v>42640</v>
@@ -48451,7 +48451,7 @@
         <v>45.560001373291</v>
       </c>
       <c r="G1658" t="n">
-        <v>43.8291091918945</v>
+        <v>43.8291053771973</v>
       </c>
       <c r="H1658" t="n">
         <v>61996</v>
@@ -48480,7 +48480,7 @@
         <v>46.1800003051758</v>
       </c>
       <c r="G1659" t="n">
-        <v>44.4255485534668</v>
+        <v>44.4255523681641</v>
       </c>
       <c r="H1659" t="n">
         <v>52251</v>
@@ -48538,7 +48538,7 @@
         <v>46.7200012207031</v>
       </c>
       <c r="G1661" t="n">
-        <v>44.9450340270996</v>
+        <v>44.9450378417969</v>
       </c>
       <c r="H1661" t="n">
         <v>81265</v>
@@ -48683,7 +48683,7 @@
         <v>50.4500007629395</v>
       </c>
       <c r="G1666" t="n">
-        <v>48.5333251953125</v>
+        <v>48.5333290100098</v>
       </c>
       <c r="H1666" t="n">
         <v>56005</v>
@@ -48712,7 +48712,7 @@
         <v>51.4500007629395</v>
       </c>
       <c r="G1667" t="n">
-        <v>49.4953384399414</v>
+        <v>49.4953346252441</v>
       </c>
       <c r="H1667" t="n">
         <v>100100</v>
@@ -48741,7 +48741,7 @@
         <v>52.1500015258789</v>
       </c>
       <c r="G1668" t="n">
-        <v>50.1687431335449</v>
+        <v>50.1687469482422</v>
       </c>
       <c r="H1668" t="n">
         <v>85351</v>
@@ -48770,7 +48770,7 @@
         <v>52.5499992370605</v>
       </c>
       <c r="G1669" t="n">
-        <v>50.5535469055176</v>
+        <v>50.5535430908203</v>
       </c>
       <c r="H1669" t="n">
         <v>41705</v>
@@ -48828,7 +48828,7 @@
         <v>52.25</v>
       </c>
       <c r="G1671" t="n">
-        <v>50.2649421691895</v>
+        <v>50.2649459838867</v>
       </c>
       <c r="H1671" t="n">
         <v>37292</v>
@@ -48857,7 +48857,7 @@
         <v>52.9000015258789</v>
       </c>
       <c r="G1672" t="n">
-        <v>50.8902473449707</v>
+        <v>50.890251159668</v>
       </c>
       <c r="H1672" t="n">
         <v>32669</v>
@@ -48886,7 +48886,7 @@
         <v>54.9500007629395</v>
       </c>
       <c r="G1673" t="n">
-        <v>52.8623657226562</v>
+        <v>52.862361907959</v>
       </c>
       <c r="H1673" t="n">
         <v>63626</v>
@@ -48915,7 +48915,7 @@
         <v>56.4500007629395</v>
       </c>
       <c r="G1674" t="n">
-        <v>54.3053779602051</v>
+        <v>54.3053741455078</v>
       </c>
       <c r="H1674" t="n">
         <v>83013</v>
@@ -49089,7 +49089,7 @@
         <v>56.3499984741211</v>
       </c>
       <c r="G1680" t="n">
-        <v>54.209171295166</v>
+        <v>54.2091751098633</v>
       </c>
       <c r="H1680" t="n">
         <v>47219</v>
@@ -49176,7 +49176,7 @@
         <v>56.5499992370605</v>
       </c>
       <c r="G1683" t="n">
-        <v>54.4015808105469</v>
+        <v>54.4015769958496</v>
       </c>
       <c r="H1683" t="n">
         <v>45752</v>
@@ -49263,7 +49263,7 @@
         <v>56.8499984741211</v>
       </c>
       <c r="G1686" t="n">
-        <v>54.6901741027832</v>
+        <v>54.6901817321777</v>
       </c>
       <c r="H1686" t="n">
         <v>43195</v>
@@ -49379,7 +49379,7 @@
         <v>55.9000015258789</v>
       </c>
       <c r="G1690" t="n">
-        <v>53.7762794494629</v>
+        <v>53.7762756347656</v>
       </c>
       <c r="H1690" t="n">
         <v>33994</v>
@@ -49408,7 +49408,7 @@
         <v>56.5499992370605</v>
       </c>
       <c r="G1691" t="n">
-        <v>54.4015808105469</v>
+        <v>54.4015769958496</v>
       </c>
       <c r="H1691" t="n">
         <v>18311</v>
@@ -49437,7 +49437,7 @@
         <v>56.3499984741211</v>
       </c>
       <c r="G1692" t="n">
-        <v>54.209171295166</v>
+        <v>54.2091751098633</v>
       </c>
       <c r="H1692" t="n">
         <v>14778</v>
@@ -49495,7 +49495,7 @@
         <v>53.9500007629395</v>
       </c>
       <c r="G1694" t="n">
-        <v>51.9003601074219</v>
+        <v>51.9003562927246</v>
       </c>
       <c r="H1694" t="n">
         <v>31104</v>
@@ -49524,7 +49524,7 @@
         <v>53.9000015258789</v>
       </c>
       <c r="G1695" t="n">
-        <v>51.8522529602051</v>
+        <v>51.8522567749023</v>
       </c>
       <c r="H1695" t="n">
         <v>35420</v>
@@ -49582,7 +49582,7 @@
         <v>51.0999984741211</v>
       </c>
       <c r="G1697" t="n">
-        <v>49.158634185791</v>
+        <v>49.1586303710938</v>
       </c>
       <c r="H1697" t="n">
         <v>67863</v>
@@ -49640,7 +49640,7 @@
         <v>52.2000007629395</v>
       </c>
       <c r="G1699" t="n">
-        <v>50.2168426513672</v>
+        <v>50.2168464660645</v>
       </c>
       <c r="H1699" t="n">
         <v>26177</v>
@@ -49669,7 +49669,7 @@
         <v>52.0999984741211</v>
       </c>
       <c r="G1700" t="n">
-        <v>50.1206436157227</v>
+        <v>50.1206398010254</v>
       </c>
       <c r="H1700" t="n">
         <v>24111</v>
@@ -49727,7 +49727,7 @@
         <v>52.3499984741211</v>
       </c>
       <c r="G1702" t="n">
-        <v>50.361141204834</v>
+        <v>50.3611373901367</v>
       </c>
       <c r="H1702" t="n">
         <v>26690</v>
@@ -49785,7 +49785,7 @@
         <v>53.4000015258789</v>
       </c>
       <c r="G1704" t="n">
-        <v>51.3712501525879</v>
+        <v>51.3712539672852</v>
       </c>
       <c r="H1704" t="n">
         <v>26485</v>
@@ -49843,7 +49843,7 @@
         <v>52.9500007629395</v>
       </c>
       <c r="G1706" t="n">
-        <v>50.9383544921875</v>
+        <v>50.9383506774902</v>
       </c>
       <c r="H1706" t="n">
         <v>22445</v>
@@ -49872,7 +49872,7 @@
         <v>52.2000007629395</v>
       </c>
       <c r="G1707" t="n">
-        <v>50.2168426513672</v>
+        <v>50.2168464660645</v>
       </c>
       <c r="H1707" t="n">
         <v>27415</v>
@@ -49930,7 +49930,7 @@
         <v>51.4500007629395</v>
       </c>
       <c r="G1709" t="n">
-        <v>49.4953384399414</v>
+        <v>49.4953346252441</v>
       </c>
       <c r="H1709" t="n">
         <v>29004</v>
@@ -49988,7 +49988,7 @@
         <v>52.1500015258789</v>
       </c>
       <c r="G1711" t="n">
-        <v>50.1687431335449</v>
+        <v>50.1687469482422</v>
       </c>
       <c r="H1711" t="n">
         <v>33658</v>
@@ -50046,7 +50046,7 @@
         <v>47</v>
       </c>
       <c r="G1713" t="n">
-        <v>45.2143974304199</v>
+        <v>45.2144012451172</v>
       </c>
       <c r="H1713" t="n">
         <v>73831</v>
@@ -50104,7 +50104,7 @@
         <v>48.060001373291</v>
       </c>
       <c r="G1715" t="n">
-        <v>46.2341270446777</v>
+        <v>46.2341232299805</v>
       </c>
       <c r="H1715" t="n">
         <v>52770</v>
@@ -50191,7 +50191,7 @@
         <v>50.0499992370605</v>
       </c>
       <c r="G1718" t="n">
-        <v>48.1485252380371</v>
+        <v>48.1485214233398</v>
       </c>
       <c r="H1718" t="n">
         <v>48850</v>
@@ -50423,7 +50423,7 @@
         <v>50.0499992370605</v>
       </c>
       <c r="G1726" t="n">
-        <v>48.1485252380371</v>
+        <v>48.1485214233398</v>
       </c>
       <c r="H1726" t="n">
         <v>94149</v>
@@ -50452,7 +50452,7 @@
         <v>50.5999984741211</v>
       </c>
       <c r="G1727" t="n">
-        <v>48.6776313781738</v>
+        <v>48.6776275634766</v>
       </c>
       <c r="H1727" t="n">
         <v>73185</v>
@@ -50481,7 +50481,7 @@
         <v>50.6500015258789</v>
       </c>
       <c r="G1728" t="n">
-        <v>48.7257308959961</v>
+        <v>48.7257347106934</v>
       </c>
       <c r="H1728" t="n">
         <v>43869</v>
@@ -50539,7 +50539,7 @@
         <v>51.4500007629395</v>
       </c>
       <c r="G1730" t="n">
-        <v>49.4953384399414</v>
+        <v>49.4953346252441</v>
       </c>
       <c r="H1730" t="n">
         <v>51828</v>
@@ -50568,7 +50568,7 @@
         <v>52.2000007629395</v>
       </c>
       <c r="G1731" t="n">
-        <v>50.2168426513672</v>
+        <v>50.2168464660645</v>
       </c>
       <c r="H1731" t="n">
         <v>28508</v>
@@ -50626,7 +50626,7 @@
         <v>56.75</v>
       </c>
       <c r="G1733" t="n">
-        <v>54.5939788818359</v>
+        <v>54.5939826965332</v>
       </c>
       <c r="H1733" t="n">
         <v>93693</v>
@@ -50684,7 +50684,7 @@
         <v>61</v>
       </c>
       <c r="G1735" t="n">
-        <v>58.6825218200684</v>
+        <v>58.6825141906738</v>
       </c>
       <c r="H1735" t="n">
         <v>102517</v>
@@ -50771,7 +50771,7 @@
         <v>58.9500007629395</v>
       </c>
       <c r="G1738" t="n">
-        <v>56.7104034423828</v>
+        <v>56.7103996276855</v>
       </c>
       <c r="H1738" t="n">
         <v>44198</v>
@@ -50800,7 +50800,7 @@
         <v>58.6500015258789</v>
       </c>
       <c r="G1739" t="n">
-        <v>56.4217987060547</v>
+        <v>56.4217948913574</v>
       </c>
       <c r="H1739" t="n">
         <v>25892</v>
@@ -50829,7 +50829,7 @@
         <v>58.8499984741211</v>
       </c>
       <c r="G1740" t="n">
-        <v>56.614200592041</v>
+        <v>56.6141967773438</v>
       </c>
       <c r="H1740" t="n">
         <v>33672</v>
@@ -50974,7 +50974,7 @@
         <v>57.1500015258789</v>
       </c>
       <c r="G1745" t="n">
-        <v>54.9787826538086</v>
+        <v>54.9787864685059</v>
       </c>
       <c r="H1745" t="n">
         <v>30108</v>
@@ -51148,7 +51148,7 @@
         <v>60.3499984741211</v>
       </c>
       <c r="G1751" t="n">
-        <v>58.0572128295898</v>
+        <v>58.0572090148926</v>
       </c>
       <c r="H1751" t="n">
         <v>39131</v>
@@ -51177,7 +51177,7 @@
         <v>60.3499984741211</v>
       </c>
       <c r="G1752" t="n">
-        <v>58.0572128295898</v>
+        <v>58.0572090148926</v>
       </c>
       <c r="H1752" t="n">
         <v>30310</v>
@@ -51235,7 +51235,7 @@
         <v>60.4000015258789</v>
       </c>
       <c r="G1754" t="n">
-        <v>58.1053161621094</v>
+        <v>58.1053123474121</v>
       </c>
       <c r="H1754" t="n">
         <v>24567</v>
@@ -51380,7 +51380,7 @@
         <v>60.4000015258789</v>
       </c>
       <c r="G1759" t="n">
-        <v>58.1053161621094</v>
+        <v>58.1053123474121</v>
       </c>
       <c r="H1759" t="n">
         <v>22870</v>
@@ -51467,7 +51467,7 @@
         <v>65.9499969482422</v>
       </c>
       <c r="G1762" t="n">
-        <v>63.4444580078125</v>
+        <v>63.4444541931152</v>
       </c>
       <c r="H1762" t="n">
         <v>96039</v>
@@ -51496,7 +51496,7 @@
         <v>63.9500007629395</v>
       </c>
       <c r="G1763" t="n">
-        <v>61.5204467773438</v>
+        <v>61.5204429626465</v>
       </c>
       <c r="H1763" t="n">
         <v>72911</v>
@@ -51525,7 +51525,7 @@
         <v>64.6999969482422</v>
       </c>
       <c r="G1764" t="n">
-        <v>62.2419471740723</v>
+        <v>62.241943359375</v>
       </c>
       <c r="H1764" t="n">
         <v>84406</v>
@@ -51641,7 +51641,7 @@
         <v>69.25</v>
       </c>
       <c r="G1768" t="n">
-        <v>66.6190795898438</v>
+        <v>66.6190872192383</v>
       </c>
       <c r="H1768" t="n">
         <v>56450</v>
@@ -51670,7 +51670,7 @@
         <v>69.9000015258789</v>
       </c>
       <c r="G1769" t="n">
-        <v>67.2443923950195</v>
+        <v>67.2444000244141</v>
       </c>
       <c r="H1769" t="n">
         <v>64095</v>
@@ -51699,7 +51699,7 @@
         <v>71.6500015258789</v>
       </c>
       <c r="G1770" t="n">
-        <v>68.9279098510742</v>
+        <v>68.9279174804688</v>
       </c>
       <c r="H1770" t="n">
         <v>115053</v>
@@ -51728,7 +51728,7 @@
         <v>72.1999969482422</v>
       </c>
       <c r="G1771" t="n">
-        <v>69.4570007324219</v>
+        <v>69.4570083618164</v>
       </c>
       <c r="H1771" t="n">
         <v>74098</v>
@@ -51786,7 +51786,7 @@
         <v>69.9000015258789</v>
       </c>
       <c r="G1773" t="n">
-        <v>67.2443923950195</v>
+        <v>67.2444000244141</v>
       </c>
       <c r="H1773" t="n">
         <v>47405</v>
@@ -51815,7 +51815,7 @@
         <v>70.75</v>
       </c>
       <c r="G1774" t="n">
-        <v>68.0621032714844</v>
+        <v>68.0620956420898</v>
       </c>
       <c r="H1774" t="n">
         <v>31239</v>
@@ -51873,7 +51873,7 @@
         <v>69.9000015258789</v>
       </c>
       <c r="G1776" t="n">
-        <v>67.2443923950195</v>
+        <v>67.2444000244141</v>
       </c>
       <c r="H1776" t="n">
         <v>53563</v>
@@ -51902,7 +51902,7 @@
         <v>70.1999969482422</v>
       </c>
       <c r="G1777" t="n">
-        <v>67.5329971313477</v>
+        <v>67.5329895019531</v>
       </c>
       <c r="H1777" t="n">
         <v>43441</v>
@@ -51931,7 +51931,7 @@
         <v>69.6500015258789</v>
       </c>
       <c r="G1778" t="n">
-        <v>67.0038909912109</v>
+        <v>67.0038986206055</v>
       </c>
       <c r="H1778" t="n">
         <v>18248</v>
@@ -51960,7 +51960,7 @@
         <v>70.0999984741211</v>
       </c>
       <c r="G1779" t="n">
-        <v>67.4367904663086</v>
+        <v>67.4367980957031</v>
       </c>
       <c r="H1779" t="n">
         <v>56671</v>
@@ -51989,7 +51989,7 @@
         <v>68.9499969482422</v>
       </c>
       <c r="G1780" t="n">
-        <v>66.3304748535156</v>
+        <v>66.3304824829102</v>
       </c>
       <c r="H1780" t="n">
         <v>74120</v>
@@ -52076,7 +52076,7 @@
         <v>67.1999969482422</v>
       </c>
       <c r="G1783" t="n">
-        <v>64.6469650268555</v>
+        <v>64.64697265625</v>
       </c>
       <c r="H1783" t="n">
         <v>108338</v>
@@ -52134,7 +52134,7 @@
         <v>69.9000015258789</v>
       </c>
       <c r="G1785" t="n">
-        <v>67.2443923950195</v>
+        <v>67.2444000244141</v>
       </c>
       <c r="H1785" t="n">
         <v>48692</v>
@@ -52308,7 +52308,7 @@
         <v>67.8499984741211</v>
       </c>
       <c r="G1791" t="n">
-        <v>65.2722778320312</v>
+        <v>65.2722702026367</v>
       </c>
       <c r="H1791" t="n">
         <v>96268</v>
@@ -52337,7 +52337,7 @@
         <v>68.6500015258789</v>
       </c>
       <c r="G1792" t="n">
-        <v>66.0418930053711</v>
+        <v>66.0418853759766</v>
       </c>
       <c r="H1792" t="n">
         <v>77221</v>
@@ -52366,7 +52366,7 @@
         <v>68.8499984741211</v>
       </c>
       <c r="G1793" t="n">
-        <v>66.2342834472656</v>
+        <v>66.2342758178711</v>
       </c>
       <c r="H1793" t="n">
         <v>66212</v>
@@ -52424,7 +52424,7 @@
         <v>70.4499969482422</v>
       </c>
       <c r="G1795" t="n">
-        <v>67.7734985351562</v>
+        <v>67.7734909057617</v>
       </c>
       <c r="H1795" t="n">
         <v>190956</v>
@@ -52453,7 +52453,7 @@
         <v>70.8499984741211</v>
       </c>
       <c r="G1796" t="n">
-        <v>68.1583023071289</v>
+        <v>68.1582946777344</v>
       </c>
       <c r="H1796" t="n">
         <v>76885</v>
@@ -52482,7 +52482,7 @@
         <v>72.5</v>
       </c>
       <c r="G1797" t="n">
-        <v>69.7456130981445</v>
+        <v>69.7456207275391</v>
       </c>
       <c r="H1797" t="n">
         <v>71075</v>
@@ -52511,7 +52511,7 @@
         <v>73.5999984741211</v>
       </c>
       <c r="G1798" t="n">
-        <v>70.8038177490234</v>
+        <v>70.803825378418</v>
       </c>
       <c r="H1798" t="n">
         <v>73939</v>
@@ -52540,7 +52540,7 @@
         <v>73.3000030517578</v>
       </c>
       <c r="G1799" t="n">
-        <v>70.5152282714844</v>
+        <v>70.5152206420898</v>
       </c>
       <c r="H1799" t="n">
         <v>62093</v>
@@ -52598,7 +52598,7 @@
         <v>74.5999984741211</v>
       </c>
       <c r="G1801" t="n">
-        <v>71.7658309936523</v>
+        <v>71.7658386230469</v>
       </c>
       <c r="H1801" t="n">
         <v>65862</v>
@@ -52627,7 +52627,7 @@
         <v>77.6500015258789</v>
       </c>
       <c r="G1802" t="n">
-        <v>74.6999664306641</v>
+        <v>74.6999588012695</v>
       </c>
       <c r="H1802" t="n">
         <v>133734</v>
@@ -52656,7 +52656,7 @@
         <v>77</v>
       </c>
       <c r="G1803" t="n">
-        <v>74.0746459960938</v>
+        <v>74.0746536254883</v>
       </c>
       <c r="H1803" t="n">
         <v>109714</v>
@@ -52685,7 +52685,7 @@
         <v>76.25</v>
       </c>
       <c r="G1804" t="n">
-        <v>73.3531494140625</v>
+        <v>73.353141784668</v>
       </c>
       <c r="H1804" t="n">
         <v>57557</v>
@@ -52975,7 +52975,7 @@
         <v>79.9000015258789</v>
       </c>
       <c r="G1814" t="n">
-        <v>76.8644790649414</v>
+        <v>76.8644866943359</v>
       </c>
       <c r="H1814" t="n">
         <v>50449</v>
@@ -53120,7 +53120,7 @@
         <v>80.1999969482422</v>
       </c>
       <c r="G1819" t="n">
-        <v>77.153076171875</v>
+        <v>77.1530685424805</v>
       </c>
       <c r="H1819" t="n">
         <v>61655</v>
@@ -53352,7 +53352,7 @@
         <v>80.3499984741211</v>
       </c>
       <c r="G1827" t="n">
-        <v>77.2973785400391</v>
+        <v>77.2973709106445</v>
       </c>
       <c r="H1827" t="n">
         <v>45595</v>
@@ -53381,7 +53381,7 @@
         <v>81.0999984741211</v>
       </c>
       <c r="G1828" t="n">
-        <v>78.0188751220703</v>
+        <v>78.0188827514648</v>
       </c>
       <c r="H1828" t="n">
         <v>47304</v>
@@ -53410,7 +53410,7 @@
         <v>80.5</v>
       </c>
       <c r="G1829" t="n">
-        <v>77.4416885375977</v>
+        <v>77.4416809082031</v>
       </c>
       <c r="H1829" t="n">
         <v>51876</v>
@@ -53439,7 +53439,7 @@
         <v>79.8499984741211</v>
       </c>
       <c r="G1830" t="n">
-        <v>76.8163757324219</v>
+        <v>76.8163833618164</v>
       </c>
       <c r="H1830" t="n">
         <v>51056</v>
@@ -53497,7 +53497,7 @@
         <v>79.5</v>
       </c>
       <c r="G1832" t="n">
-        <v>76.4796752929688</v>
+        <v>76.4796676635742</v>
       </c>
       <c r="H1832" t="n">
         <v>71202</v>
@@ -53584,7 +53584,7 @@
         <v>73.6999969482422</v>
       </c>
       <c r="G1835" t="n">
-        <v>70.9000244140625</v>
+        <v>70.900016784668</v>
       </c>
       <c r="H1835" t="n">
         <v>118446</v>
@@ -53700,7 +53700,7 @@
         <v>82.5</v>
       </c>
       <c r="G1839" t="n">
-        <v>79.3656921386719</v>
+        <v>79.3656997680664</v>
       </c>
       <c r="H1839" t="n">
         <v>112852</v>
@@ -53787,7 +53787,7 @@
         <v>83.5999984741211</v>
       </c>
       <c r="G1842" t="n">
-        <v>80.4239120483398</v>
+        <v>80.4239044189453</v>
       </c>
       <c r="H1842" t="n">
         <v>73814</v>
@@ -53816,7 +53816,7 @@
         <v>84</v>
       </c>
       <c r="G1843" t="n">
-        <v>80.808708190918</v>
+        <v>80.8087158203125</v>
       </c>
       <c r="H1843" t="n">
         <v>57466</v>
@@ -53874,7 +53874,7 @@
         <v>87.5</v>
       </c>
       <c r="G1845" t="n">
-        <v>84.1757431030273</v>
+        <v>84.1757354736328</v>
       </c>
       <c r="H1845" t="n">
         <v>77492</v>
@@ -53990,7 +53990,7 @@
         <v>88.9499969482422</v>
       </c>
       <c r="G1849" t="n">
-        <v>85.5706481933594</v>
+        <v>85.5706558227539</v>
       </c>
       <c r="H1849" t="n">
         <v>73851</v>
@@ -54048,7 +54048,7 @@
         <v>90.1999969482422</v>
       </c>
       <c r="G1851" t="n">
-        <v>86.7731704711914</v>
+        <v>86.7731628417969</v>
       </c>
       <c r="H1851" t="n">
         <v>62234</v>
@@ -54164,7 +54164,7 @@
         <v>92.6500015258789</v>
       </c>
       <c r="G1855" t="n">
-        <v>89.1300811767578</v>
+        <v>89.1300888061523</v>
       </c>
       <c r="H1855" t="n">
         <v>85972</v>
@@ -54193,7 +54193,7 @@
         <v>90.1500015258789</v>
       </c>
       <c r="G1856" t="n">
-        <v>86.7250671386719</v>
+        <v>86.7250595092773</v>
       </c>
       <c r="H1856" t="n">
         <v>74823</v>
@@ -54222,7 +54222,7 @@
         <v>91.6999969482422</v>
       </c>
       <c r="G1857" t="n">
-        <v>88.2161712646484</v>
+        <v>88.216178894043</v>
       </c>
       <c r="H1857" t="n">
         <v>109671</v>
@@ -54541,7 +54541,7 @@
         <v>85.3000030517578</v>
       </c>
       <c r="G1868" t="n">
-        <v>82.0593338012695</v>
+        <v>82.059326171875</v>
       </c>
       <c r="H1868" t="n">
         <v>37393</v>
@@ -54628,7 +54628,7 @@
         <v>86.0500030517578</v>
       </c>
       <c r="G1871" t="n">
-        <v>82.7808227539062</v>
+        <v>82.7808303833008</v>
       </c>
       <c r="H1871" t="n">
         <v>39954</v>
@@ -54715,7 +54715,7 @@
         <v>84</v>
       </c>
       <c r="G1874" t="n">
-        <v>80.808708190918</v>
+        <v>80.8087158203125</v>
       </c>
       <c r="H1874" t="n">
         <v>52005</v>
@@ -54860,7 +54860,7 @@
         <v>82</v>
       </c>
       <c r="G1879" t="n">
-        <v>78.8846969604492</v>
+        <v>78.8847045898438</v>
       </c>
       <c r="H1879" t="n">
         <v>79720</v>
@@ -80125,6 +80125,35 @@
         <v>184281</v>
       </c>
       <c r="I2750" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2751">
+      <c r="A2751" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2751" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C2751" t="n">
+        <v>85.5599975585938</v>
+      </c>
+      <c r="D2751" t="n">
+        <v>85.6399993896484</v>
+      </c>
+      <c r="E2751" t="n">
+        <v>84.5</v>
+      </c>
+      <c r="F2751" t="n">
+        <v>85.379997253418</v>
+      </c>
+      <c r="G2751" t="n">
+        <v>85.379997253418</v>
+      </c>
+      <c r="H2751" t="n">
+        <v>108702</v>
+      </c>
+      <c r="I2751" t="s">
         <v>9</v>
       </c>
     </row>
